--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>991544.5600000001</v>
+        <v>1215526.8</v>
       </c>
       <c r="D2" t="n">
-        <v>5324</v>
+        <v>6721</v>
       </c>
       <c r="E2" t="n">
-        <v>882370.5600000001</v>
+        <v>1076088.8</v>
       </c>
       <c r="F2" t="n">
-        <v>109174</v>
+        <v>139438</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>852428</v>
+        <v>1031938</v>
       </c>
       <c r="D3" t="n">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="E3" t="n">
-        <v>751703</v>
+        <v>906354</v>
       </c>
       <c r="F3" t="n">
-        <v>100725</v>
+        <v>125584</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>139116.56</v>
+        <v>183588.8</v>
       </c>
       <c r="D4" t="n">
-        <v>5054</v>
+        <v>6418</v>
       </c>
       <c r="E4" t="n">
-        <v>130667.56</v>
+        <v>169734.8</v>
       </c>
       <c r="F4" t="n">
-        <v>8449</v>
+        <v>13854</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1722320</v>
+        <v>2285822</v>
       </c>
       <c r="D5" t="n">
-        <v>311</v>
+        <v>421</v>
       </c>
       <c r="E5" t="n">
-        <v>377474</v>
+        <v>471926</v>
       </c>
       <c r="F5" t="n">
-        <v>1344846</v>
+        <v>1813896</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1099440</v>
+        <v>1507918</v>
       </c>
       <c r="D6" t="n">
-        <v>185</v>
+        <v>256</v>
       </c>
       <c r="E6" t="n">
         <v>14820</v>
       </c>
       <c r="F6" t="n">
-        <v>1084620</v>
+        <v>1493098</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>612880</v>
+        <v>777904</v>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="E7" t="n">
-        <v>362654</v>
+        <v>457106</v>
       </c>
       <c r="F7" t="n">
-        <v>250226</v>
+        <v>320798</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>560585.09</v>
+        <v>889900.38</v>
       </c>
       <c r="D8" t="n">
-        <v>828</v>
+        <v>1023</v>
       </c>
       <c r="E8" t="n">
-        <v>11206.74</v>
+        <v>14807.22</v>
       </c>
       <c r="F8" t="n">
-        <v>549378.35</v>
+        <v>875093.16</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>325152.72</v>
+        <v>547015.98</v>
       </c>
       <c r="D9" t="n">
-        <v>394</v>
+        <v>453</v>
       </c>
       <c r="E9" t="n">
-        <v>2661.37</v>
+        <v>2993.86</v>
       </c>
       <c r="F9" t="n">
-        <v>322491.35</v>
+        <v>544022.12</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>235432.37</v>
+        <v>342884.4</v>
       </c>
       <c r="D10" t="n">
-        <v>434</v>
+        <v>570</v>
       </c>
       <c r="E10" t="n">
-        <v>8545.370000000001</v>
+        <v>11813.36</v>
       </c>
       <c r="F10" t="n">
-        <v>226887</v>
+        <v>331071.04</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>167600</v>
+        <v>305400</v>
       </c>
       <c r="D11" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>122000</v>
+        <v>123000</v>
       </c>
       <c r="F11" t="n">
-        <v>45600</v>
+        <v>182400</v>
       </c>
     </row>
     <row r="12">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>182391.9</v>
+        <v>291765.9</v>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E12" t="n">
-        <v>101495.9</v>
+        <v>107293.9</v>
       </c>
       <c r="F12" t="n">
-        <v>80896</v>
+        <v>184472</v>
       </c>
     </row>
     <row r="13">
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>263380</v>
+        <v>267340</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>235580</v>
+        <v>237560</v>
       </c>
       <c r="F13" t="n">
-        <v>27800</v>
+        <v>29780</v>
       </c>
     </row>
     <row r="14">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>95040</v>
+        <v>99000</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E14" t="n">
         <v>13860</v>
       </c>
       <c r="F14" t="n">
-        <v>81180</v>
+        <v>85140</v>
       </c>
     </row>
     <row r="15">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25871.6</v>
+        <v>69774</v>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="E15" t="n">
         <v>6536.36</v>
       </c>
       <c r="F15" t="n">
-        <v>19335.24</v>
+        <v>63237.64</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>517170.6</v>
+        <v>852317.24</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>95.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 496129.6；咨询线 10398.0；工作坊 9900.0；课程线 673.0；其他 70.0；菌群线 0.0</t>
+          <t>医疗线 830432.24；咨询线 11194.0；工作坊 9900.0；课程线 721.0；其他 70.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>270770.9</v>
+        <v>304201.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 226586.0；课程线 37405.0；工作坊 3960.0；医疗线 2819.9</t>
+          <t>咨询线 254174.0；课程线 41239.0；工作坊 3960.0；医疗线 2848.9；营地 1980.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>143231.35</v>
+        <v>143638.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 67580.0；考证 39588.0；营地 27800.0；课程线 5053.0；医疗线 2710.35；其他 500.0</t>
+          <t>咨询线 67978.0；考证 39588.0；营地 27800.0；课程线 5062.0；医疗线 2500.0；其他 710.35</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>285737.9</v>
+        <v>632424.9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>37.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 137192.0；工作坊 57420.0；菌群线 45600.0；课程线 42351.0；医疗线 3174.9；其他 0.0</t>
+          <t>咨询线 238400.0；菌群线 182400.0；考证 99776.0；工作坊 57420.0；课程线 50335.0；医疗线 3243.9；其他 850.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>211257.18</v>
+        <v>309747.18</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>92</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 194378.0；医疗线 8079.94；课程线 8034.0；其他 765.24；菌群线 0.0</t>
+          <t>咨询线 275474.0；医疗线 19029.12；课程线 8428.0；其他 6816.06；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>201094</v>
+        <v>281083</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 196198.0；课程线 2916.0；工作坊 1980.0</t>
+          <t>咨询线 261212.0；课程线 17891.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>192525.4</v>
+        <v>229924.41</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>94.90000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 182676.0；医疗线 8971.4；课程线 878.0；其他 0.0</t>
+          <t>咨询线 208860.0；其他 19928.41；课程线 897.0；医疗线 239.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113893.06</v>
+        <v>161943.52</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>82.2</v>
+        <v>85</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 93586.0；医疗线 20216.06；课程线 91.0</t>
+          <t>咨询线 137676.0；医疗线 16800.0；其他 7020.52；课程线 447.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123464.2</v>
+        <v>147271.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>85.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 106078.0；工作坊 7920.0；医疗线 7276.2；课程线 2190.0；菌群线 0.0</t>
+          <t>咨询线 127272.0；其他 9842.3；工作坊 7920.0；课程线 2237.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77070</v>
+        <v>98100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>64.3</v>
+        <v>62.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 49592.0；其他 18000.0；课程线 9478.0</t>
+          <t>咨询线 61582.0；其他 18000.0；课程线 10758.0；工作坊 3960.0；考证 3800.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>107075</v>
+        <v>197885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>62.9</v>
+        <v>79.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 67382.0；考证 39588.0；课程线 105.0</t>
+          <t>咨询线 156874.0；考证 39588.0；课程线 1423.0</t>
         </is>
       </c>
     </row>
@@ -1146,11 +1146,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>49800</v>
+        <v>54780</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47800</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44820</v>
+        <v>49680</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44700</v>
+        <v>47800</v>
       </c>
     </row>
     <row r="7">
@@ -1218,11 +1218,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>84414</v>
+        <v>126196</v>
       </c>
     </row>
     <row r="8">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>79196</v>
+        <v>116628</v>
       </c>
     </row>
     <row r="9">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>74584</v>
+        <v>84982</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>69208</v>
+        <v>84414</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65592</v>
+        <v>77486</v>
       </c>
     </row>
     <row r="12">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>95807</v>
+        <v>196419</v>
       </c>
     </row>
     <row r="13">
@@ -1326,11 +1326,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>91504</v>
+        <v>137560</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>88298</v>
+        <v>134512.5</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>64497</v>
+        <v>112964</v>
       </c>
     </row>
     <row r="16">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>35106.1</v>
+        <v>57792.1</v>
       </c>
     </row>
     <row r="17">
@@ -1398,11 +1398,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>70400</v>
+        <v>182400</v>
       </c>
     </row>
     <row r="18">
@@ -1416,11 +1416,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>45600</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="19">
@@ -1488,11 +1488,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>梁志超</t>
+          <t>王秋</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>67788</v>
+        <v>99776</v>
       </c>
     </row>
     <row r="23">
@@ -1506,11 +1506,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>梁志超</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>39588</v>
+        <v>71588</v>
       </c>
     </row>
     <row r="24">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1542,11 +1542,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5700</v>
+        <v>39588</v>
       </c>
     </row>
     <row r="26">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3800</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="27">
@@ -1776,11 +1776,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>765.24</v>
+        <v>16889.64</v>
       </c>
     </row>
     <row r="39">
@@ -1794,11 +1794,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>马雅丽</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>6267.9</v>
       </c>
     </row>
     <row r="40">
@@ -1812,11 +1812,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>3172.2</v>
       </c>
     </row>
     <row r="41">
@@ -1830,11 +1830,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>吴群</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>2735.36</v>
       </c>
     </row>
   </sheetData>
@@ -1900,26 +1900,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>991544.5600000001</v>
+        <v>1215526.8</v>
       </c>
       <c r="C2" t="n">
-        <v>241446.06</v>
+        <v>21388</v>
       </c>
       <c r="D2" t="n">
-        <v>16871</v>
+        <v>21388</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="F2" t="n">
-        <v>224575.06</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>22.65</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 92400.0；青少年同行者计划领航营 51740.0；青少年同行者计划护航营（6月） 16846.0</t>
+          <t>青少年同行者计划周训营网课，家长学习应对孩子青春期问题 2565.0；青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 1794.0；少年说7天线上训练营网课-帮家长应对孩子不愿沟通问题 1680.0</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1722320</v>
+        <v>2285822</v>
       </c>
       <c r="C3" t="n">
-        <v>228418.98</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1942,16 +1942,12 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>228418.98</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>13.26</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>儿童青少年 110499.98；精神心理 52398.0；家庭守护计划2.0一阶（4980补差价产品） 10621.0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1960,10 +1956,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>560585.09</v>
+        <v>889900.38</v>
       </c>
       <c r="C4" t="n">
-        <v>2849</v>
+        <v>49</v>
       </c>
       <c r="D4" t="n">
         <v>49</v>
@@ -1972,14 +1968,14 @@
         <v>0.01</v>
       </c>
       <c r="F4" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50分钟问诊（诸秉根） -线下 1800.0；医师50分钟问诊-线上 1000.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
+          <t>AI测评V9.0-多维父母教养行为测评 49.0</t>
         </is>
       </c>
     </row>
@@ -1990,10 +1986,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>167600</v>
+        <v>305400</v>
       </c>
       <c r="C5" t="n">
-        <v>45600</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -2002,16 +1998,12 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>45600</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>27.21</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>肠道菌群移植（双疗程） 45600.0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2020,26 +2012,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>182391.9</v>
+        <v>291765.9</v>
       </c>
       <c r="C6" t="n">
-        <v>95125.89999999999</v>
+        <v>2017.9</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>1.11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>93108</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>51.05</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派-高阶培训课程 79200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 13908.0；完形心理基训课 1998.0</t>
+          <t>完形心理基训课 1998.0；心理咨询师通关取证班体验课 19.9</t>
         </is>
       </c>
     </row>
@@ -2050,26 +2042,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>263380</v>
+        <v>267340</v>
       </c>
       <c r="C7" t="n">
-        <v>149666.67</v>
+        <v>29800</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>29800</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>11.15</v>
       </c>
       <c r="F7" t="n">
-        <v>149666.67</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>56.83</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 128666.67；青少年【未来之翼】身心节律复能7日营 16800.0；青少年营地食宿费补差价 4200.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 29800.0</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>95040</v>
+        <v>99000</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2106,7 +2098,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25871.6</v>
+        <v>69774</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -1903,7 +1903,7 @@
         <v>1215526.8</v>
       </c>
       <c r="C2" t="n">
-        <v>21388</v>
+        <v>260999.06</v>
       </c>
       <c r="D2" t="n">
         <v>21388</v>
@@ -1912,14 +1912,14 @@
         <v>1.76</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>239611.06</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>19.71</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划周训营网课，家长学习应对孩子青春期问题 2565.0；青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 1794.0；少年说7天线上训练营网课-帮家长应对孩子不愿沟通问题 1680.0</t>
+          <t>少年说陪伴计划 92400.0；青少年同行者计划领航营 55720.0；青少年同行者计划-护航营 17039.16</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v>2285822</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>247918.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1942,12 +1942,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>247918.98</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>10.85</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>儿童青少年 121999.98；精神心理 52398.0；暑假礼遇咨询套餐 14800.0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1959,7 +1963,7 @@
         <v>889900.38</v>
       </c>
       <c r="C4" t="n">
-        <v>49</v>
+        <v>2849</v>
       </c>
       <c r="D4" t="n">
         <v>49</v>
@@ -1968,14 +1972,14 @@
         <v>0.01</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AI测评V9.0-多维父母教养行为测评 49.0</t>
+          <t>50分钟问诊（诸秉根） -线下 1800.0；医师50分钟问诊-线上 1000.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1993,7 @@
         <v>305400</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>70400</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1998,12 +2002,16 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>70400</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>23.05</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>肠道菌群移植（双疗程） 45600.0；肠道菌群移植（活动专享） 24800.0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2015,7 +2023,7 @@
         <v>291765.9</v>
       </c>
       <c r="C6" t="n">
-        <v>2017.9</v>
+        <v>98913.89999999999</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -2024,14 +2032,14 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>96896</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>33.21</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>完形心理基训课 1998.0；心理咨询师通关取证班体验课 19.9</t>
+          <t>心灯计划-实战派-高阶培训课程 79200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 13908.0；心理咨询师职业能力水平评价考试培训 3788.0</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2053,7 @@
         <v>267340</v>
       </c>
       <c r="C7" t="n">
-        <v>29800</v>
+        <v>206066.67</v>
       </c>
       <c r="D7" t="n">
         <v>29800</v>
@@ -2054,14 +2062,14 @@
         <v>11.15</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>176266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 29800.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 168266.67；青少年【未来之翼】身心节律复能7日营 33600.0；青少年营地食宿费补差价 4200.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1215526.8</v>
+        <v>1407282.8</v>
       </c>
       <c r="D2" t="n">
-        <v>6721</v>
+        <v>7245</v>
       </c>
       <c r="E2" t="n">
-        <v>1076088.8</v>
+        <v>1252909.8</v>
       </c>
       <c r="F2" t="n">
-        <v>139438</v>
+        <v>154373</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1031938</v>
+        <v>1208750</v>
       </c>
       <c r="D3" t="n">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="E3" t="n">
-        <v>906354</v>
+        <v>1068207</v>
       </c>
       <c r="F3" t="n">
-        <v>125584</v>
+        <v>140543</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>183588.8</v>
+        <v>198532.8</v>
       </c>
       <c r="D4" t="n">
-        <v>6418</v>
+        <v>6903</v>
       </c>
       <c r="E4" t="n">
-        <v>169734.8</v>
+        <v>184702.8</v>
       </c>
       <c r="F4" t="n">
-        <v>13854</v>
+        <v>13830</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2285822</v>
+        <v>2528510</v>
       </c>
       <c r="D5" t="n">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="E5" t="n">
-        <v>471926</v>
+        <v>555940</v>
       </c>
       <c r="F5" t="n">
-        <v>1813896</v>
+        <v>1972570</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1507918</v>
+        <v>1639996</v>
       </c>
       <c r="D6" t="n">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="E6" t="n">
-        <v>14820</v>
+        <v>15218</v>
       </c>
       <c r="F6" t="n">
-        <v>1493098</v>
+        <v>1624778</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>777904</v>
+        <v>878514</v>
       </c>
       <c r="D7" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="E7" t="n">
-        <v>457106</v>
+        <v>540722</v>
       </c>
       <c r="F7" t="n">
-        <v>320798</v>
+        <v>337792</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>889900.38</v>
+        <v>963712.97</v>
       </c>
       <c r="D8" t="n">
-        <v>1023</v>
+        <v>1288</v>
       </c>
       <c r="E8" t="n">
-        <v>14807.22</v>
+        <v>15890.21</v>
       </c>
       <c r="F8" t="n">
-        <v>875093.16</v>
+        <v>947822.76</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>547015.98</v>
+        <v>578574.4</v>
       </c>
       <c r="D9" t="n">
-        <v>453</v>
+        <v>571</v>
       </c>
       <c r="E9" t="n">
-        <v>2993.86</v>
+        <v>3042.86</v>
       </c>
       <c r="F9" t="n">
-        <v>544022.12</v>
+        <v>575531.54</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>342884.4</v>
+        <v>385138.57</v>
       </c>
       <c r="D10" t="n">
-        <v>570</v>
+        <v>717</v>
       </c>
       <c r="E10" t="n">
-        <v>11813.36</v>
+        <v>12847.35</v>
       </c>
       <c r="F10" t="n">
-        <v>331071.04</v>
+        <v>372291.22</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>305400</v>
+        <v>306400</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E11" t="n">
         <v>123000</v>
       </c>
       <c r="F11" t="n">
-        <v>182400</v>
+        <v>183400</v>
       </c>
     </row>
     <row r="12">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>99000</v>
+        <v>102960</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E14" t="n">
-        <v>13860</v>
+        <v>15840</v>
       </c>
       <c r="F14" t="n">
-        <v>85140</v>
+        <v>87120</v>
       </c>
     </row>
     <row r="15">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69774</v>
+        <v>27001.61</v>
       </c>
       <c r="D15" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="E15" t="n">
         <v>6536.36</v>
       </c>
       <c r="F15" t="n">
-        <v>63237.64</v>
+        <v>20465.25</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>852317.24</v>
+        <v>865730.24</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 830432.24；咨询线 11194.0；工作坊 9900.0；课程线 721.0；其他 70.0；菌群线 0.0</t>
+          <t>医疗线 843428.24；咨询线 11592.0；工作坊 9900.0；课程线 740.0；其他 70.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>304201.9</v>
+        <v>315158.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>83.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 254174.0；课程线 41239.0；工作坊 3960.0；医疗线 2848.9；营地 1980.0</t>
+          <t>咨询线 264970.0；课程线 41400.0；工作坊 3960.0；医疗线 2848.9；营地 1980.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>143638.35</v>
+        <v>157851.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47.3</v>
+        <v>50.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 67978.0；考证 39588.0；营地 27800.0；课程线 5062.0；医疗线 2500.0；其他 710.35</t>
+          <t>咨询线 79372.0；考证 39588.0；营地 27800.0；医疗线 5510.35；课程线 5081.0；其他 500.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>632424.9</v>
+        <v>677602.9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.7</v>
+        <v>40.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 238400.0；菌群线 182400.0；考证 99776.0；工作坊 57420.0；课程线 50335.0；医疗线 3243.9；其他 850.0</t>
+          <t>咨询线 274998.0；菌群线 182400.0；考证 99776.0；工作坊 59400.0；课程线 56935.0；医疗线 3243.9；其他 850.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>309747.18</v>
+        <v>326952.78</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 275474.0；医疗线 19029.12；课程线 8428.0；其他 6816.06；菌群线 0.0</t>
+          <t>咨询线 290274.0；医疗线 25786.54；课程线 10127.0；其他 765.24；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>281083</v>
+        <v>288179</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>92.90000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 261212.0；课程线 17891.0；工作坊 1980.0</t>
+          <t>咨询线 261610.0；课程线 24589.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>229924.41</v>
+        <v>288920.41</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>90.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 208860.0；其他 19928.41；课程线 897.0；医疗线 239.0</t>
+          <t>咨询线 253856.0；医疗线 32887.4；菌群线 1000.0；课程线 897.0；其他 280.01</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161943.52</v>
+        <v>193126.13</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>85</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 137676.0；医疗线 16800.0；其他 7020.52；课程线 447.0</t>
+          <t>咨询线 168776.0；医疗线 24183.13；课程线 167.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>147271.3</v>
+        <v>137761.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>86.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 127272.0；其他 9842.3；工作坊 7920.0；课程线 2237.0；菌群线 0.0</t>
+          <t>咨询线 117670.0；医疗线 9934.3；工作坊 7920.0；课程线 2237.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>98100</v>
+        <v>98498</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 61582.0；其他 18000.0；课程线 10758.0；工作坊 3960.0；考证 3800.0</t>
+          <t>咨询线 61980.0；其他 18000.0；课程线 10758.0；工作坊 3960.0；考证 3800.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>197885</v>
+        <v>215302</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79.3</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 156874.0；考证 39588.0；课程线 1423.0</t>
+          <t>咨询线 174272.0；考证 39588.0；课程线 1442.0</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>59380</v>
+        <v>84280</v>
       </c>
     </row>
     <row r="3">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54780</v>
+        <v>62740</v>
       </c>
     </row>
     <row r="4">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>49800</v>
+        <v>59760</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>49680</v>
+        <v>56400</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>47800</v>
+        <v>54780</v>
       </c>
     </row>
     <row r="7">
@@ -1218,11 +1218,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>126196</v>
+        <v>153226</v>
       </c>
     </row>
     <row r="8">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>116628</v>
+        <v>140196</v>
       </c>
     </row>
     <row r="9">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>84982</v>
+        <v>87486</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>84414</v>
+        <v>84982</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>77486</v>
+        <v>84414</v>
       </c>
     </row>
     <row r="12">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>196419</v>
+        <v>198311</v>
       </c>
     </row>
     <row r="13">
@@ -1326,11 +1326,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>137560</v>
+        <v>134512.5</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>134512.5</v>
+        <v>124166</v>
       </c>
     </row>
     <row r="15">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>51480</v>
+        <v>53460</v>
       </c>
     </row>
     <row r="33">
@@ -1704,11 +1704,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>王凯</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5940</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="35">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>王凯</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1776,11 +1776,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16889.64</v>
+        <v>850</v>
       </c>
     </row>
     <row r="39">
@@ -1794,11 +1794,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>马雅丽</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6267.9</v>
+        <v>765.24</v>
       </c>
     </row>
     <row r="40">
@@ -1812,11 +1812,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>陈舒羽</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3172.2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41">
@@ -1830,11 +1830,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2735.36</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1900,26 +1900,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1215526.8</v>
+        <v>1407282.8</v>
       </c>
       <c r="C2" t="n">
-        <v>260999.06</v>
+        <v>292000.06</v>
       </c>
       <c r="D2" t="n">
-        <v>21388</v>
+        <v>28577</v>
       </c>
       <c r="E2" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="F2" t="n">
-        <v>239611.06</v>
+        <v>263423.06</v>
       </c>
       <c r="G2" t="n">
-        <v>19.71</v>
+        <v>18.72</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 92400.0；青少年同行者计划领航营 55720.0；青少年同行者计划-护航营 17039.16</t>
+          <t>少年说陪伴计划 99000.0；青少年同行者计划领航营 64680.0；青少年同行者计划-护航营 22019.16</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2285822</v>
+        <v>2528510</v>
       </c>
       <c r="C3" t="n">
-        <v>247918.98</v>
+        <v>278718.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>247918.98</v>
+        <v>278718.98</v>
       </c>
       <c r="G3" t="n">
-        <v>10.85</v>
+        <v>11.02</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 121999.98；精神心理 52398.0；暑假礼遇咨询套餐 14800.0</t>
+          <t>儿童青少年 152799.98；精神心理 52398.0；暑假礼遇咨询套餐 14800.0</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>889900.38</v>
+        <v>963712.97</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -1975,7 +1975,7 @@
         <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>305400</v>
+        <v>306400</v>
       </c>
       <c r="C5" t="n">
         <v>70400</v>
@@ -2005,7 +2005,7 @@
         <v>70400</v>
       </c>
       <c r="G5" t="n">
-        <v>23.05</v>
+        <v>22.98</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>291765.9</v>
       </c>
       <c r="C6" t="n">
-        <v>98913.89999999999</v>
+        <v>138913.9</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -2032,14 +2032,14 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>96896</v>
+        <v>136896</v>
       </c>
       <c r="G6" t="n">
-        <v>33.21</v>
+        <v>46.92</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派-高阶培训课程 79200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 13908.0；心理咨询师职业能力水平评价考试培训 3788.0</t>
+          <t>心灯计划-实战派-高阶培训课程 119200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 13908.0；心理咨询师职业能力水平评价考试培训 3788.0</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>99000</v>
+        <v>102960</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69774</v>
+        <v>27001.61</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1407282.8</v>
+        <v>1513756.8</v>
       </c>
       <c r="D2" t="n">
-        <v>7245</v>
+        <v>7674</v>
       </c>
       <c r="E2" t="n">
-        <v>1252909.8</v>
+        <v>1363283.8</v>
       </c>
       <c r="F2" t="n">
-        <v>154373</v>
+        <v>150473</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1208750</v>
+        <v>1306490</v>
       </c>
       <c r="D3" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="E3" t="n">
-        <v>1068207</v>
+        <v>1170927</v>
       </c>
       <c r="F3" t="n">
-        <v>140543</v>
+        <v>135563</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>198532.8</v>
+        <v>207266.8</v>
       </c>
       <c r="D4" t="n">
-        <v>6903</v>
+        <v>7313</v>
       </c>
       <c r="E4" t="n">
-        <v>184702.8</v>
+        <v>192356.8</v>
       </c>
       <c r="F4" t="n">
-        <v>13830</v>
+        <v>14910</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2528510</v>
+        <v>2652364</v>
       </c>
       <c r="D5" t="n">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="E5" t="n">
-        <v>555940</v>
+        <v>602138</v>
       </c>
       <c r="F5" t="n">
-        <v>1972570</v>
+        <v>2050226</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1639996</v>
+        <v>1730266</v>
       </c>
       <c r="D6" t="n">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="E6" t="n">
-        <v>15218</v>
+        <v>35218</v>
       </c>
       <c r="F6" t="n">
-        <v>1624778</v>
+        <v>1695048</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>878514</v>
+        <v>912098</v>
       </c>
       <c r="D7" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E7" t="n">
-        <v>540722</v>
+        <v>566920</v>
       </c>
       <c r="F7" t="n">
-        <v>337792</v>
+        <v>345178</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>963712.97</v>
+        <v>977116.0600000001</v>
       </c>
       <c r="D8" t="n">
-        <v>1288</v>
+        <v>1313</v>
       </c>
       <c r="E8" t="n">
-        <v>15890.21</v>
+        <v>16888.2</v>
       </c>
       <c r="F8" t="n">
-        <v>947822.76</v>
+        <v>960227.86</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>578574.4</v>
+        <v>580508.8</v>
       </c>
       <c r="D9" t="n">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="E9" t="n">
         <v>3042.86</v>
       </c>
       <c r="F9" t="n">
-        <v>575531.54</v>
+        <v>577465.9399999999</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>385138.57</v>
+        <v>396607.26</v>
       </c>
       <c r="D10" t="n">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="E10" t="n">
-        <v>12847.35</v>
+        <v>13845.34</v>
       </c>
       <c r="F10" t="n">
-        <v>372291.22</v>
+        <v>382761.92</v>
       </c>
     </row>
     <row r="11">
@@ -682,7 +682,7 @@
         <v>306400</v>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11" t="n">
         <v>123000</v>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>267340</v>
+        <v>285160</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E13" t="n">
-        <v>237560</v>
+        <v>255380</v>
       </c>
       <c r="F13" t="n">
         <v>29780</v>
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>102960</v>
+        <v>106920</v>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>15840</v>
+        <v>17820</v>
       </c>
       <c r="F14" t="n">
-        <v>87120</v>
+        <v>89100</v>
       </c>
     </row>
     <row r="15">
@@ -778,7 +778,7 @@
         <v>27001.61</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E15" t="n">
         <v>6536.36</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>865730.24</v>
+        <v>876837.24</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 843428.24；咨询线 11592.0；工作坊 9900.0；课程线 740.0；其他 70.0；菌群线 0.0</t>
+          <t>医疗线 854535.24；咨询线 11592.0；工作坊 9900.0；课程线 740.0；其他 70.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>315158.9</v>
+        <v>317884.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 264970.0；课程线 41400.0；工作坊 3960.0；医疗线 2848.9；营地 1980.0</t>
+          <t>咨询线 267462.0；课程线 41634.0；工作坊 3960.0；医疗线 2848.9；营地 1980.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>157851.35</v>
+        <v>170748.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50.3</v>
+        <v>53.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 79372.0；考证 39588.0；营地 27800.0；医疗线 5510.35；课程线 5081.0；其他 500.0</t>
+          <t>咨询线 91970.0；考证 39588.0；营地 27800.0；医疗线 5510.35；课程线 5380.0；其他 500.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>677602.9</v>
+        <v>693057.9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.6</v>
+        <v>41.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 274998.0；菌群线 182400.0；考证 99776.0；工作坊 59400.0；课程线 56935.0；医疗线 3243.9；其他 850.0</t>
+          <t>咨询线 290396.0；菌群线 182400.0；考证 99776.0；工作坊 59400.0；课程线 56992.0；医疗线 3243.9；其他 850.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>326952.78</v>
+        <v>331040.18</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.8</v>
+        <v>88</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 290274.0；医疗线 25786.54；课程线 10127.0；其他 765.24；菌群线 0.0</t>
+          <t>咨询线 291468.0；医疗线 26651.94；课程线 10175.0；工作坊 1980.0；其他 765.24；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>288179</v>
+        <v>323995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>90.8</v>
+        <v>93.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 261610.0；课程线 24589.0；工作坊 1980.0</t>
+          <t>咨询线 302406.0；课程线 19609.0；工作坊 1980.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>288920.41</v>
+        <v>290874.41</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>87.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 253856.0；医疗线 32887.4；菌群线 1000.0；课程线 897.0；其他 280.01</t>
+          <t>咨询线 255450.0；医疗线 33247.4；菌群线 1000.0；课程线 897.0；其他 280.01</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>193126.13</v>
+        <v>183516.83</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>87.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 168776.0；医疗线 24183.13；课程线 167.0</t>
+          <t>咨询线 158776.0；医疗线 24255.83；课程线 485.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>137761.3</v>
+        <v>139203.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 117670.0；医疗线 9934.3；工作坊 7920.0；课程线 2237.0；菌群线 0.0</t>
+          <t>咨询线 119064.0；医疗线 9934.3；工作坊 7920.0；课程线 2285.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>98498</v>
+        <v>98915</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62.9</v>
+        <v>63.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 61980.0；其他 18000.0；课程线 10758.0；工作坊 3960.0；考证 3800.0</t>
+          <t>咨询线 62378.0；其他 18000.0；课程线 10777.0；工作坊 3960.0；考证 3800.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>215302</v>
+        <v>227151</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>80.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 174272.0；考证 39588.0；课程线 1442.0</t>
+          <t>咨询线 186064.0；考证 39588.0；课程线 1499.0</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>84280</v>
+        <v>94240</v>
       </c>
     </row>
     <row r="3">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>62740</v>
+        <v>67720</v>
       </c>
     </row>
     <row r="4">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>59760</v>
+        <v>64740</v>
       </c>
     </row>
     <row r="5">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>153226</v>
+        <v>168624</v>
       </c>
     </row>
     <row r="8">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>140196</v>
+        <v>141390</v>
       </c>
     </row>
     <row r="9">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>87486</v>
+        <v>99606</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>84982</v>
+        <v>92214</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>84414</v>
+        <v>87884</v>
       </c>
     </row>
     <row r="12">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>198311</v>
+        <v>198850</v>
       </c>
     </row>
     <row r="13">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>57792.1</v>
+        <v>57962.1</v>
       </c>
     </row>
     <row r="17">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>89400</v>
+        <v>95340</v>
       </c>
     </row>
     <row r="28">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>袁登玉</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>袁登玉</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1900,26 +1900,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1407282.8</v>
+        <v>1513756.8</v>
       </c>
       <c r="C2" t="n">
-        <v>292000.06</v>
+        <v>316406.06</v>
       </c>
       <c r="D2" t="n">
-        <v>28577</v>
+        <v>32444</v>
       </c>
       <c r="E2" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="F2" t="n">
-        <v>263423.06</v>
+        <v>283962.06</v>
       </c>
       <c r="G2" t="n">
-        <v>18.72</v>
+        <v>18.76</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 99000.0；青少年同行者计划领航营 64680.0；青少年同行者计划-护航营 22019.16</t>
+          <t>少年说陪伴计划 99000.0；青少年同行者计划领航营 68659.0；青少年同行者计划-护航营 26999.16</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2528510</v>
+        <v>2652364</v>
       </c>
       <c r="C3" t="n">
-        <v>278718.98</v>
+        <v>325218.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>278718.98</v>
+        <v>325218.98</v>
       </c>
       <c r="G3" t="n">
-        <v>11.02</v>
+        <v>12.26</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 152799.98；精神心理 52398.0；暑假礼遇咨询套餐 14800.0</t>
+          <t>儿童青少年 191299.98；精神心理 59398.0；暑假礼遇咨询套餐 14800.0</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>963712.97</v>
+        <v>977116.0600000001</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -2050,26 +2050,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>267340</v>
+        <v>285160</v>
       </c>
       <c r="C7" t="n">
-        <v>206066.67</v>
+        <v>260466.67</v>
       </c>
       <c r="D7" t="n">
-        <v>29800</v>
+        <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>11.15</v>
+        <v>18.59</v>
       </c>
       <c r="F7" t="n">
-        <v>176266.67</v>
+        <v>207466.67</v>
       </c>
       <c r="G7" t="n">
-        <v>65.93000000000001</v>
+        <v>72.75</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 168266.67；青少年【未来之翼】身心节律复能7日营 33600.0；青少年营地食宿费补差价 4200.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 191466.67；青少年【未来之翼】身心节律复能7日营 33600.0；青少年成长基地3月营（金盏基地） 31200.0</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>102960</v>
+        <v>106920</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1513756.8</v>
+        <v>1603908.8</v>
       </c>
       <c r="D2" t="n">
-        <v>7674</v>
+        <v>8132</v>
       </c>
       <c r="E2" t="n">
-        <v>1363283.8</v>
+        <v>1398507.8</v>
       </c>
       <c r="F2" t="n">
-        <v>150473</v>
+        <v>205401</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1306490</v>
+        <v>1382230</v>
       </c>
       <c r="D3" t="n">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="E3" t="n">
-        <v>1170927</v>
+        <v>1192187</v>
       </c>
       <c r="F3" t="n">
-        <v>135563</v>
+        <v>190043</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>207266.8</v>
+        <v>221678.8</v>
       </c>
       <c r="D4" t="n">
-        <v>7313</v>
+        <v>7761</v>
       </c>
       <c r="E4" t="n">
-        <v>192356.8</v>
+        <v>206320.8</v>
       </c>
       <c r="F4" t="n">
-        <v>14910</v>
+        <v>15358</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2652364</v>
+        <v>2866890</v>
       </c>
       <c r="D5" t="n">
-        <v>498</v>
+        <v>539</v>
       </c>
       <c r="E5" t="n">
-        <v>602138</v>
+        <v>742696</v>
       </c>
       <c r="F5" t="n">
-        <v>2050226</v>
+        <v>2124194</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1730266</v>
+        <v>1823248</v>
       </c>
       <c r="D6" t="n">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="E6" t="n">
-        <v>35218</v>
+        <v>57218</v>
       </c>
       <c r="F6" t="n">
-        <v>1695048</v>
+        <v>1766030</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>912098</v>
+        <v>1033642</v>
       </c>
       <c r="D7" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="E7" t="n">
-        <v>566920</v>
+        <v>685478</v>
       </c>
       <c r="F7" t="n">
-        <v>345178</v>
+        <v>348164</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>977116.0600000001</v>
+        <v>1047216.27</v>
       </c>
       <c r="D8" t="n">
-        <v>1313</v>
+        <v>1412</v>
       </c>
       <c r="E8" t="n">
-        <v>16888.2</v>
+        <v>18167.41</v>
       </c>
       <c r="F8" t="n">
-        <v>960227.86</v>
+        <v>1029048.86</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>580508.8</v>
+        <v>641433.8</v>
       </c>
       <c r="D9" t="n">
-        <v>589</v>
+        <v>656</v>
       </c>
       <c r="E9" t="n">
         <v>3042.86</v>
       </c>
       <c r="F9" t="n">
-        <v>577465.9399999999</v>
+        <v>638390.9399999999</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>396607.26</v>
+        <v>405782.47</v>
       </c>
       <c r="D10" t="n">
-        <v>724</v>
+        <v>756</v>
       </c>
       <c r="E10" t="n">
-        <v>13845.34</v>
+        <v>15124.55</v>
       </c>
       <c r="F10" t="n">
-        <v>382761.92</v>
+        <v>390657.92</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>306400</v>
+        <v>397600</v>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E11" t="n">
         <v>123000</v>
       </c>
       <c r="F11" t="n">
-        <v>183400</v>
+        <v>274600</v>
       </c>
     </row>
     <row r="12">
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>291765.9</v>
+        <v>297465.9</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E12" t="n">
-        <v>107293.9</v>
+        <v>112993.9</v>
       </c>
       <c r="F12" t="n">
         <v>184472</v>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>285160</v>
+        <v>291100</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>255380</v>
+        <v>261320</v>
       </c>
       <c r="F13" t="n">
         <v>29780</v>
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27001.61</v>
+        <v>29297.61</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E15" t="n">
-        <v>6536.36</v>
+        <v>8434.360000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>20465.25</v>
+        <v>20863.25</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>876837.24</v>
+        <v>943411.24</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 854535.24；咨询线 11592.0；工作坊 9900.0；课程线 740.0；其他 70.0；菌群线 0.0</t>
+          <t>医疗线 921096.24；咨询线 11592.0；工作坊 9900.0；课程线 753.0；其他 70.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>317884.9</v>
+        <v>348482.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>84.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 267462.0；课程线 41634.0；工作坊 3960.0；医疗线 2848.9；营地 1980.0</t>
+          <t>咨询线 297452.0；课程线 41742.0；工作坊 3960.0；医疗线 3348.9；营地 1980.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170748.35</v>
+        <v>171155.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 91970.0；考证 39588.0；营地 27800.0；医疗线 5510.35；课程线 5380.0；其他 500.0</t>
+          <t>咨询线 92368.0；考证 39588.0；营地 27800.0；医疗线 5510.35；课程线 5389.0；其他 500.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>693057.9</v>
+        <v>735249.9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>41.9</v>
+        <v>39.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 290396.0；菌群线 182400.0；考证 99776.0；工作坊 59400.0；课程线 56992.0；医疗线 3243.9；其他 850.0</t>
+          <t>咨询线 292988.0；菌群线 182400.0；考证 99776.0；课程线 96592.0；工作坊 59400.0；医疗线 3243.9；其他 850.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>331040.18</v>
+        <v>390798.18</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88</v>
+        <v>77.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 291468.0；医疗线 26651.94；课程线 10175.0；工作坊 1980.0；其他 765.24；菌群线 0.0</t>
+          <t>咨询线 303866.0；菌群线 45600.0；医疗线 28411.94；课程线 10175.0；工作坊 1980.0；其他 765.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>323995</v>
+        <v>330614</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>93.3</v>
+        <v>91.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 302406.0；课程线 19609.0；工作坊 1980.0；菌群线 0.0</t>
+          <t>咨询线 302406.0；课程线 26228.0；工作坊 1980.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>290874.41</v>
+        <v>296969.41</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 255450.0；医疗线 33247.4；菌群线 1000.0；课程线 897.0；其他 280.01</t>
+          <t>咨询线 260848.0；医疗线 33247.4；课程线 1196.0；菌群线 1000.0；其他 678.01</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>183516.83</v>
+        <v>231996.83</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>86.5</v>
+        <v>69</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 158776.0；医疗线 24255.83；课程线 485.0</t>
+          <t>咨询线 159976.0；菌群线 45600.0；医疗线 24255.83；课程线 2165.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>139203.3</v>
+        <v>166999.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>85.5</v>
+        <v>84</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 119064.0；医疗线 9934.3；工作坊 7920.0；课程线 2285.0；菌群线 0.0</t>
+          <t>咨询线 140260.0；医疗线 9934.3；课程线 8885.0；工作坊 7920.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>98915</v>
+        <v>99313</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 62378.0；其他 18000.0；课程线 10777.0；工作坊 3960.0；考证 3800.0</t>
+          <t>咨询线 62776.0；其他 18000.0；课程线 10777.0；工作坊 3960.0；考证 3800.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>227151</v>
+        <v>227549</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 186064.0；考证 39588.0；课程线 1499.0</t>
+          <t>咨询线 186462.0；考证 39588.0；课程线 1499.0</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>94240</v>
+        <v>99220</v>
       </c>
     </row>
     <row r="3">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>56400</v>
+        <v>61380</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>54780</v>
+        <v>56400</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>168624</v>
+        <v>169420</v>
       </c>
     </row>
     <row r="8">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>141390</v>
+        <v>153390</v>
       </c>
     </row>
     <row r="9">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>99606</v>
+        <v>120160</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>92214</v>
+        <v>99606</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>87884</v>
+        <v>92214</v>
       </c>
     </row>
     <row r="12">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>198850</v>
+        <v>216049</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>134512.5</v>
+        <v>142401.5</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>124166</v>
+        <v>136095</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>112964</v>
+        <v>128222</v>
       </c>
     </row>
     <row r="16">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>57962.1</v>
+        <v>61756.1</v>
       </c>
     </row>
     <row r="17">
@@ -1434,11 +1434,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>何媛媛</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>24800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="20">
@@ -1452,11 +1452,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>24800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="21">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>何媛媛</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2000</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="22">
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>71588</v>
+        <v>77288</v>
       </c>
     </row>
     <row r="24">
@@ -1812,11 +1812,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>陈舒羽</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>280</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41">
@@ -1830,11 +1830,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>陈舒羽</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>30</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -1900,26 +1900,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1513756.8</v>
+        <v>1603908.8</v>
       </c>
       <c r="C2" t="n">
-        <v>316406.06</v>
+        <v>365562.06</v>
       </c>
       <c r="D2" t="n">
-        <v>32444</v>
+        <v>35641</v>
       </c>
       <c r="E2" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="F2" t="n">
-        <v>283962.06</v>
+        <v>329921.06</v>
       </c>
       <c r="G2" t="n">
-        <v>18.76</v>
+        <v>20.57</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 99000.0；青少年同行者计划领航营 68659.0；青少年同行者计划-护航营 26999.16</t>
+          <t>少年说陪伴计划 132000.0；青少年同行者计划领航营 76619.0；青少年同行者计划-护航营 26999.16</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2652364</v>
+        <v>2866890</v>
       </c>
       <c r="C3" t="n">
-        <v>325218.98</v>
+        <v>383467.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>325218.98</v>
+        <v>383467.98</v>
       </c>
       <c r="G3" t="n">
-        <v>12.26</v>
+        <v>13.38</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 191299.98；精神心理 59398.0；暑假礼遇咨询套餐 14800.0</t>
+          <t>儿童青少年 234699.98；精神心理 59398.0；家庭守护计划2.0（一阶） 14820.0</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>977116.0600000001</v>
+        <v>1047216.27</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -1969,13 +1969,13 @@
         <v>49</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>306400</v>
+        <v>397600</v>
       </c>
       <c r="C5" t="n">
-        <v>70400</v>
+        <v>91200</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -2002,14 +2002,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>70400</v>
+        <v>91200</v>
       </c>
       <c r="G5" t="n">
-        <v>22.98</v>
+        <v>22.94</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程） 45600.0；肠道菌群移植（活动专享） 24800.0</t>
+          <t>肠道菌群移植（双疗程） 45600.0；肠道菌群移植（活动专享） 24800.0；肠道菌群移植（双疗程优惠） 20800.0</t>
         </is>
       </c>
     </row>
@@ -2020,26 +2020,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>291765.9</v>
+        <v>297465.9</v>
       </c>
       <c r="C6" t="n">
-        <v>138913.9</v>
+        <v>152021.9</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="F6" t="n">
-        <v>136896</v>
+        <v>150004</v>
       </c>
       <c r="G6" t="n">
-        <v>46.92</v>
+        <v>50.43</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派-高阶培训课程 119200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 13908.0；心理咨询师职业能力水平评价考试培训 3788.0</t>
+          <t>心灯计划-实战派-高阶培训课程 119200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 27016.0；心理咨询师职业能力水平评价考试培训 3788.0</t>
         </is>
       </c>
     </row>
@@ -2050,26 +2050,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>285160</v>
+        <v>291100</v>
       </c>
       <c r="C7" t="n">
-        <v>260466.67</v>
+        <v>290266.67</v>
       </c>
       <c r="D7" t="n">
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>18.59</v>
+        <v>18.21</v>
       </c>
       <c r="F7" t="n">
-        <v>207466.67</v>
+        <v>237266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>72.75</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 191466.67；青少年【未来之翼】身心节律复能7日营 33600.0；青少年成长基地3月营（金盏基地） 31200.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 221266.67；青少年【未来之翼】身心节律复能7日营 33600.0；青少年成长基地3月营（金盏基地） 31200.0</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27001.61</v>
+        <v>29297.61</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1047216.27</v>
+        <v>1119548.25</v>
       </c>
       <c r="D8" t="n">
-        <v>1412</v>
+        <v>1575</v>
       </c>
       <c r="E8" t="n">
         <v>18167.41</v>
       </c>
       <c r="F8" t="n">
-        <v>1029048.86</v>
+        <v>1101380.84</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>641433.8</v>
+        <v>658712.39</v>
       </c>
       <c r="D9" t="n">
-        <v>656</v>
+        <v>688</v>
       </c>
       <c r="E9" t="n">
         <v>3042.86</v>
       </c>
       <c r="F9" t="n">
-        <v>638390.9399999999</v>
+        <v>655669.53</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>405782.47</v>
+        <v>460835.86</v>
       </c>
       <c r="D10" t="n">
-        <v>756</v>
+        <v>887</v>
       </c>
       <c r="E10" t="n">
         <v>15124.55</v>
       </c>
       <c r="F10" t="n">
-        <v>390657.92</v>
+        <v>445711.31</v>
       </c>
     </row>
     <row r="11">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>297465.9</v>
+        <v>307465.9</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
         <v>112993.9</v>
       </c>
       <c r="F12" t="n">
-        <v>184472</v>
+        <v>194472</v>
       </c>
     </row>
     <row r="13">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>29297.61</v>
+        <v>31217.61</v>
       </c>
       <c r="D15" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E15" t="n">
         <v>8434.360000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>20863.25</v>
+        <v>22783.25</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>943411.24</v>
+        <v>1008670.42</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 921096.24；咨询线 11592.0；工作坊 9900.0；课程线 753.0；其他 70.0；菌群线 0.0</t>
+          <t>医疗线 985635.42；咨询线 11592.0；工作坊 9900.0；其他 790.0；课程线 753.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>390798.18</v>
+        <v>408275.58</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>77.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 303866.0；菌群线 45600.0；医疗线 28411.94；课程线 10175.0；工作坊 1980.0；其他 765.24</t>
+          <t>咨询线 303866.0；菌群线 45600.0；医疗线 35889.34；课程线 10175.0；考证 10000.0；工作坊 1980.0；其他 765.24</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>296969.41</v>
+        <v>297284.81</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 260848.0；医疗线 33247.4；课程线 1196.0；菌群线 1000.0；其他 678.01</t>
+          <t>咨询线 260848.0；医疗线 33562.8；课程线 1196.0；菌群线 1000.0；其他 678.01</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>231996.83</v>
+        <v>233196.83</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>69</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 159976.0；菌群线 45600.0；医疗线 24255.83；课程线 2165.0</t>
+          <t>咨询线 159976.0；菌群线 45600.0；医疗线 24255.83；课程线 2165.0；其他 1200.0</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>216049</v>
+        <v>229204.64</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>142401.5</v>
+        <v>148555.04</v>
       </c>
     </row>
     <row r="14">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>136095</v>
+        <v>137495</v>
       </c>
     </row>
     <row r="15">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>61756.1</v>
+        <v>75486.64</v>
       </c>
     </row>
     <row r="17">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>李明</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5700</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="27">
@@ -1776,11 +1776,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈茜</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>850</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="39">
@@ -1794,11 +1794,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>765.24</v>
+        <v>850</v>
       </c>
     </row>
     <row r="40">
@@ -1812,11 +1812,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>沈悦</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>398</v>
+        <v>765.24</v>
       </c>
     </row>
     <row r="41">
@@ -1830,11 +1830,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>陈舒羽</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>280</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1047216.27</v>
+        <v>1119548.25</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -1975,7 +1975,7 @@
         <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>297465.9</v>
+        <v>307465.9</v>
       </c>
       <c r="C6" t="n">
         <v>152021.9</v>
@@ -2029,13 +2029,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="F6" t="n">
         <v>150004</v>
       </c>
       <c r="G6" t="n">
-        <v>50.43</v>
+        <v>48.79</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29297.61</v>
+        <v>31217.61</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1603908.8</v>
+        <v>1819191.8</v>
       </c>
       <c r="D2" t="n">
-        <v>8132</v>
+        <v>8542</v>
       </c>
       <c r="E2" t="n">
-        <v>1398507.8</v>
+        <v>1590121.8</v>
       </c>
       <c r="F2" t="n">
-        <v>205401</v>
+        <v>229070</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1382230</v>
+        <v>1583350</v>
       </c>
       <c r="D3" t="n">
-        <v>371</v>
+        <v>410</v>
       </c>
       <c r="E3" t="n">
-        <v>1192187</v>
+        <v>1369667</v>
       </c>
       <c r="F3" t="n">
-        <v>190043</v>
+        <v>213683</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>221678.8</v>
+        <v>235841.8</v>
       </c>
       <c r="D4" t="n">
-        <v>7761</v>
+        <v>8132</v>
       </c>
       <c r="E4" t="n">
-        <v>206320.8</v>
+        <v>220454.8</v>
       </c>
       <c r="F4" t="n">
-        <v>15358</v>
+        <v>15387</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2866890</v>
+        <v>3048762</v>
       </c>
       <c r="D5" t="n">
-        <v>539</v>
+        <v>577</v>
       </c>
       <c r="E5" t="n">
-        <v>742696</v>
+        <v>757270</v>
       </c>
       <c r="F5" t="n">
-        <v>2124194</v>
+        <v>2291492</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1823248</v>
+        <v>1988954</v>
       </c>
       <c r="D6" t="n">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="E6" t="n">
-        <v>57218</v>
+        <v>57816</v>
       </c>
       <c r="F6" t="n">
-        <v>1766030</v>
+        <v>1931138</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1033642</v>
+        <v>1049808</v>
       </c>
       <c r="D7" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E7" t="n">
-        <v>685478</v>
+        <v>699454</v>
       </c>
       <c r="F7" t="n">
-        <v>348164</v>
+        <v>350354</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1119548.25</v>
+        <v>1123240.05</v>
       </c>
       <c r="D8" t="n">
-        <v>1575</v>
+        <v>1584</v>
       </c>
       <c r="E8" t="n">
-        <v>18167.41</v>
+        <v>20472.81</v>
       </c>
       <c r="F8" t="n">
-        <v>1101380.84</v>
+        <v>1102767.24</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>658712.39</v>
+        <v>659769.1899999999</v>
       </c>
       <c r="D9" t="n">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="E9" t="n">
-        <v>3042.86</v>
+        <v>3548.26</v>
       </c>
       <c r="F9" t="n">
-        <v>655669.53</v>
+        <v>656220.9300000001</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>460835.86</v>
+        <v>463470.86</v>
       </c>
       <c r="D10" t="n">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="E10" t="n">
-        <v>15124.55</v>
+        <v>16924.55</v>
       </c>
       <c r="F10" t="n">
-        <v>445711.31</v>
+        <v>446546.31</v>
       </c>
     </row>
     <row r="11">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>397600</v>
+        <v>492800</v>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E11" t="n">
-        <v>123000</v>
+        <v>218200</v>
       </c>
       <c r="F11" t="n">
         <v>274600</v>
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>31217.61</v>
+        <v>35306.61</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E15" t="n">
-        <v>8434.360000000001</v>
+        <v>10632.36</v>
       </c>
       <c r="F15" t="n">
-        <v>22783.25</v>
+        <v>24674.25</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1008670.42</v>
+        <v>1008689.42</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 985635.42；咨询线 11592.0；工作坊 9900.0；其他 790.0；课程线 753.0；菌群线 0.0</t>
+          <t>医疗线 985635.42；咨询线 11592.0；工作坊 9900.0；其他 790.0；课程线 772.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>348482.9</v>
+        <v>372425.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>85.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 297452.0；课程线 41742.0；工作坊 3960.0；医疗线 3348.9；营地 1980.0</t>
+          <t>咨询线 321452.0；课程线 41685.0；工作坊 3960.0；医疗线 3348.9；营地 1980.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>171155.35</v>
+        <v>172549.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>54.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 92368.0；考证 39588.0；营地 27800.0；医疗线 5510.35；课程线 5389.0；其他 500.0</t>
+          <t>咨询线 93762.0；考证 39588.0；营地 27800.0；医疗线 5510.35；课程线 5389.0；其他 500.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>735249.9</v>
+        <v>789443.9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>39.8</v>
+        <v>43.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 292988.0；菌群线 182400.0；考证 99776.0；课程线 96592.0；工作坊 59400.0；医疗线 3243.9；其他 850.0</t>
+          <t>咨询线 342202.0；菌群线 182400.0；课程线 101572.0；考证 99776.0；工作坊 59400.0；医疗线 3243.9；其他 850.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>408275.58</v>
+        <v>416207.98</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>74.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 303866.0；菌群线 45600.0；医疗线 35889.34；课程线 10175.0；考证 10000.0；工作坊 1980.0；其他 765.24</t>
+          <t>咨询线 304264.0；菌群线 45600.0；医疗线 36775.74；课程线 16823.0；考证 10000.0；工作坊 1980.0；其他 765.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>330614</v>
+        <v>347513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>91.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 302406.0；课程线 26228.0；工作坊 1980.0；菌群线 0.0</t>
+          <t>咨询线 312406.0；课程线 32828.0；工作坊 1980.0；其他 299.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>297284.81</v>
+        <v>327376.81</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>87.7</v>
+        <v>88.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 260848.0；医疗线 33562.8；课程线 1196.0；菌群线 1000.0；其他 678.01</t>
+          <t>咨询线 288848.0；医疗线 34062.8；其他 2270.01；课程线 1196.0；菌群线 1000.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233196.83</v>
+        <v>254472.83</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>68.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 159976.0；菌群线 45600.0；医疗线 24255.83；课程线 2165.0；其他 1200.0</t>
+          <t>咨询线 176272.0；菌群线 45600.0；医疗线 24255.83；课程线 7145.0；其他 1200.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166999.3</v>
+        <v>192199.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>84</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 140260.0；医疗线 9934.3；课程线 8885.0；工作坊 7920.0；菌群线 0.0</t>
+          <t>咨询线 165460.0；医疗线 9934.3；课程线 8885.0；工作坊 7920.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99313</v>
+        <v>100210</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>63.2</v>
+        <v>63</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 62776.0；其他 18000.0；课程线 10777.0；工作坊 3960.0；考证 3800.0</t>
+          <t>咨询线 63174.0；其他 18000.0；课程线 11276.0；工作坊 3960.0；考证 3800.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>227549</v>
+        <v>239947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>81.90000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 186462.0；考证 39588.0；课程线 1499.0</t>
+          <t>咨询线 198860.0；考证 39588.0；课程线 1499.0</t>
         </is>
       </c>
     </row>
@@ -1146,11 +1146,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>67720</v>
+        <v>85020</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>64740</v>
+        <v>72700</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61380</v>
+        <v>69720</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>56400</v>
+        <v>68850</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>169420</v>
+        <v>191018</v>
       </c>
     </row>
     <row r="8">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>99606</v>
+        <v>115884</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>92214</v>
+        <v>114778</v>
       </c>
     </row>
     <row r="12">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>何媛媛</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="22">
@@ -1812,11 +1812,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>张回</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>765.24</v>
+        <v>796</v>
       </c>
     </row>
     <row r="41">
@@ -1830,11 +1830,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>沈悦</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -1900,26 +1900,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1603908.8</v>
+        <v>1819191.8</v>
       </c>
       <c r="C2" t="n">
-        <v>365562.06</v>
+        <v>379236.86</v>
       </c>
       <c r="D2" t="n">
-        <v>35641</v>
+        <v>45346</v>
       </c>
       <c r="E2" t="n">
-        <v>2.22</v>
+        <v>2.49</v>
       </c>
       <c r="F2" t="n">
-        <v>329921.06</v>
+        <v>333890.86</v>
       </c>
       <c r="G2" t="n">
-        <v>20.57</v>
+        <v>18.35</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 132000.0；青少年同行者计划领航营 76619.0；青少年同行者计划-护航营 26999.16</t>
+          <t>少年说陪伴计划 132000.0；青少年同行者计划领航营 85579.0；青少年同行者计划-护航营 26999.16</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2866890</v>
+        <v>3048762</v>
       </c>
       <c r="C3" t="n">
-        <v>383467.98</v>
+        <v>442301.38</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>383467.98</v>
+        <v>442301.38</v>
       </c>
       <c r="G3" t="n">
-        <v>13.38</v>
+        <v>14.51</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 234699.98；精神心理 59398.0；家庭守护计划2.0（一阶） 14820.0</t>
+          <t>儿童青少年 273533.38；精神心理 72398.0；电商咨询 18000.0</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1119548.25</v>
+        <v>1123240.05</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>397600</v>
+        <v>492800</v>
       </c>
       <c r="C5" t="n">
         <v>91200</v>
@@ -2005,7 +2005,7 @@
         <v>91200</v>
       </c>
       <c r="G5" t="n">
-        <v>22.94</v>
+        <v>18.51</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>307465.9</v>
       </c>
       <c r="C6" t="n">
-        <v>152021.9</v>
+        <v>154862.9</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -2032,10 +2032,10 @@
         <v>0.66</v>
       </c>
       <c r="F6" t="n">
-        <v>150004</v>
+        <v>152845</v>
       </c>
       <c r="G6" t="n">
-        <v>48.79</v>
+        <v>49.71</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31217.61</v>
+        <v>35306.61</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -2123,7 +2123,11 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[自我成长/疗愈] 完形心理认知课，增加智慧。 999.0</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1819191.8</v>
+        <v>1973367.8</v>
       </c>
       <c r="D2" t="n">
-        <v>8542</v>
+        <v>8973</v>
       </c>
       <c r="E2" t="n">
-        <v>1590121.8</v>
+        <v>1722850.8</v>
       </c>
       <c r="F2" t="n">
-        <v>229070</v>
+        <v>250517</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1583350</v>
+        <v>1729700</v>
       </c>
       <c r="D3" t="n">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="E3" t="n">
-        <v>1369667</v>
+        <v>1494038</v>
       </c>
       <c r="F3" t="n">
-        <v>213683</v>
+        <v>235662</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>235841.8</v>
+        <v>243667.8</v>
       </c>
       <c r="D4" t="n">
-        <v>8132</v>
+        <v>8536</v>
       </c>
       <c r="E4" t="n">
-        <v>220454.8</v>
+        <v>228812.8</v>
       </c>
       <c r="F4" t="n">
-        <v>15387</v>
+        <v>14855</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3048762</v>
+        <v>3316840</v>
       </c>
       <c r="D5" t="n">
-        <v>577</v>
+        <v>641</v>
       </c>
       <c r="E5" t="n">
-        <v>757270</v>
+        <v>782106</v>
       </c>
       <c r="F5" t="n">
-        <v>2291492</v>
+        <v>2534734</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1988954</v>
+        <v>2203122</v>
       </c>
       <c r="D6" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="E6" t="n">
         <v>57816</v>
       </c>
       <c r="F6" t="n">
-        <v>1931138</v>
+        <v>2145306</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1049808</v>
+        <v>1103718</v>
       </c>
       <c r="D7" t="n">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="E7" t="n">
-        <v>699454</v>
+        <v>724290</v>
       </c>
       <c r="F7" t="n">
-        <v>350354</v>
+        <v>379428</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1123240.05</v>
+        <v>1421855.15</v>
       </c>
       <c r="D8" t="n">
-        <v>1584</v>
+        <v>1950</v>
       </c>
       <c r="E8" t="n">
-        <v>20472.81</v>
+        <v>24790.61</v>
       </c>
       <c r="F8" t="n">
-        <v>1102767.24</v>
+        <v>1397064.54</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>659769.1899999999</v>
+        <v>887675.0699999999</v>
       </c>
       <c r="D9" t="n">
-        <v>693</v>
+        <v>832</v>
       </c>
       <c r="E9" t="n">
-        <v>3548.26</v>
+        <v>5628.16</v>
       </c>
       <c r="F9" t="n">
-        <v>656220.9300000001</v>
+        <v>882046.91</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>463470.86</v>
+        <v>534180.08</v>
       </c>
       <c r="D10" t="n">
-        <v>891</v>
+        <v>1118</v>
       </c>
       <c r="E10" t="n">
-        <v>16924.55</v>
+        <v>19162.45</v>
       </c>
       <c r="F10" t="n">
-        <v>446546.31</v>
+        <v>515017.63</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>492800</v>
+        <v>589000</v>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E11" t="n">
         <v>218200</v>
       </c>
       <c r="F11" t="n">
-        <v>274600</v>
+        <v>370800</v>
       </c>
     </row>
     <row r="12">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>307465.9</v>
+        <v>317465.9</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
         <v>112993.9</v>
       </c>
       <c r="F12" t="n">
-        <v>194472</v>
+        <v>204472</v>
       </c>
     </row>
     <row r="13">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>291100</v>
+        <v>324700</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>261320</v>
+        <v>294920</v>
       </c>
       <c r="F13" t="n">
         <v>29780</v>
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>106920</v>
+        <v>110880</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
         <v>17820</v>
       </c>
       <c r="F14" t="n">
-        <v>89100</v>
+        <v>93060</v>
       </c>
     </row>
     <row r="15">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>35306.61</v>
+        <v>79325.61</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E15" t="n">
-        <v>10632.36</v>
+        <v>11631.36</v>
       </c>
       <c r="F15" t="n">
-        <v>24674.25</v>
+        <v>67694.25</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1008689.42</v>
+        <v>1255462.42</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>97.7</v>
+        <v>98.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 985635.42；咨询线 11592.0；工作坊 9900.0；其他 790.0；课程线 772.0；菌群线 0.0</t>
+          <t>医疗线 1232406.42；咨询线 11592.0；工作坊 9900.0；其他 820.0；课程线 744.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>372425.9</v>
+        <v>434136.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>86.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 321452.0；课程线 41685.0；工作坊 3960.0；医疗线 3348.9；营地 1980.0</t>
+          <t>咨询线 371650.0；课程线 53198.0；工作坊 3960.0；医疗线 3348.9；营地 1980.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>172549.35</v>
+        <v>206143.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>54.3</v>
+        <v>61.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 93762.0；考证 39588.0；营地 27800.0；医疗线 5510.35；课程线 5389.0；其他 500.0</t>
+          <t>咨询线 127156.0；考证 39588.0；营地 27800.0；医疗线 5710.35；课程线 5389.0；其他 500.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>789443.9</v>
+        <v>895353.9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>43.3</v>
+        <v>40.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 342202.0；菌群线 182400.0；课程线 101572.0；考证 99776.0；工作坊 59400.0；医疗线 3243.9；其他 850.0</t>
+          <t>咨询线 362998.0；菌群线 252800.0；课程线 103206.0；考证 99776.0；工作坊 61380.0；医疗线 14343.9；其他 850.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>416207.98</v>
+        <v>469457.47</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 304264.0；菌群线 45600.0；医疗线 36775.74；课程线 16823.0；考证 10000.0；工作坊 1980.0；其他 765.24</t>
+          <t>咨询线 352060.0；菌群线 46600.0；医疗线 41614.23；课程线 16438.0；考证 10000.0；工作坊 1980.0；其他 765.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>347513</v>
+        <v>365307</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>89.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 312406.0；课程线 32828.0；工作坊 1980.0；其他 299.0；菌群线 0.0</t>
+          <t>咨询线 323600.0；课程线 39428.0；工作坊 1980.0；其他 299.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>327376.81</v>
+        <v>431788.69</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>88.2</v>
+        <v>69.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 288848.0；医疗线 34062.8；其他 2270.01；课程线 1196.0；菌群线 1000.0</t>
+          <t>咨询线 301438.0；医疗线 59288.68；其他 44066.01；菌群线 25800.0；课程线 1196.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254472.83</v>
+        <v>301622.56</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>69.3</v>
+        <v>69.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 176272.0；菌群线 45600.0；医疗线 24255.83；课程线 7145.0；其他 1200.0</t>
+          <t>咨询线 209566.0；菌群线 45600.0；医疗线 26506.56；考证 10000.0；课程线 8750.0；其他 1200.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>192199.3</v>
+        <v>197921.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>86.09999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 165460.0；医疗线 9934.3；课程线 8885.0；工作坊 7920.0；菌群线 0.0</t>
+          <t>咨询线 167252.0；医疗线 13845.5；课程线 8904.0；工作坊 7920.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>100210</v>
+        <v>110728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 63174.0；其他 18000.0；课程线 11276.0；工作坊 3960.0；考证 3800.0</t>
+          <t>咨询线 73174.0；其他 18000.0；课程线 11794.0；工作坊 3960.0；考证 3800.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>239947</v>
+        <v>265280</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>82.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 198860.0；考证 39588.0；课程线 1499.0</t>
+          <t>咨询线 221048.0；考证 39588.0；工作坊 1980.0；课程线 1470.0；其他 1194.0</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>99220</v>
+        <v>95240</v>
       </c>
     </row>
     <row r="3">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>85020</v>
+        <v>94980</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>72700</v>
+        <v>81180</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>69720</v>
+        <v>74700</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>68850</v>
+        <v>74700</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>191018</v>
+        <v>191814</v>
       </c>
     </row>
     <row r="8">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>153390</v>
+        <v>163390</v>
       </c>
     </row>
     <row r="9">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>120160</v>
+        <v>158578</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>115884</v>
+        <v>120160</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>114778</v>
+        <v>115884</v>
       </c>
     </row>
     <row r="12">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>229204.64</v>
+        <v>298696.64</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>148555.04</v>
+        <v>219861.04</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>137495</v>
+        <v>154930</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>128222</v>
+        <v>141485.1</v>
       </c>
     </row>
     <row r="16">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75486.64</v>
+        <v>137495</v>
       </c>
     </row>
     <row r="17">
@@ -1434,11 +1434,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>45600</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="20">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>95340</v>
+        <v>110160</v>
       </c>
     </row>
     <row r="28">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>53460</v>
+        <v>55440</v>
       </c>
     </row>
     <row r="33">
@@ -1758,11 +1758,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>田婉丽</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>18000</v>
+        <v>36796</v>
       </c>
     </row>
     <row r="38">
@@ -1776,11 +1776,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>陈茜</t>
+          <t>田婉丽</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1200</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="39">
@@ -1794,11 +1794,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>850</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="40">
@@ -1812,11 +1812,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>张回</t>
+          <t>陈茜</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>796</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="41">
@@ -1830,11 +1830,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>796</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -1900,26 +1900,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1819191.8</v>
+        <v>1973367.8</v>
       </c>
       <c r="C2" t="n">
-        <v>379236.86</v>
+        <v>390988.86</v>
       </c>
       <c r="D2" t="n">
-        <v>45346</v>
+        <v>48763</v>
       </c>
       <c r="E2" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="F2" t="n">
-        <v>333890.86</v>
+        <v>342225.86</v>
       </c>
       <c r="G2" t="n">
-        <v>18.35</v>
+        <v>17.34</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 132000.0；青少年同行者计划领航营 85579.0；青少年同行者计划-护航营 26999.16</t>
+          <t>少年说陪伴计划 132000.0；青少年同行者计划领航营 88896.0；青少年同行者计划-护航营 26999.16</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3048762</v>
+        <v>3316840</v>
       </c>
       <c r="C3" t="n">
-        <v>442301.38</v>
+        <v>472001.38</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1942,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>442301.38</v>
+        <v>472001.38</v>
       </c>
       <c r="G3" t="n">
-        <v>14.51</v>
+        <v>14.23</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 273533.38；精神心理 72398.0；电商咨询 18000.0</t>
+          <t>儿童青少年 289033.38；精神心理 84598.0；电商咨询 20000.0</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1123240.05</v>
+        <v>1421855.15</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -1975,7 +1975,7 @@
         <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>492800</v>
+        <v>589000</v>
       </c>
       <c r="C5" t="n">
-        <v>91200</v>
+        <v>116000</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -2002,14 +2002,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>91200</v>
+        <v>116000</v>
       </c>
       <c r="G5" t="n">
-        <v>18.51</v>
+        <v>19.69</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程） 45600.0；肠道菌群移植（活动专享） 24800.0；肠道菌群移植（双疗程优惠） 20800.0</t>
+          <t>肠道菌群移植（双疗程） 45600.0；肠道菌群移植 24800.0；肠道菌群移植（活动专享） 24800.0</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>307465.9</v>
+        <v>317465.9</v>
       </c>
       <c r="C6" t="n">
         <v>154862.9</v>
@@ -2029,13 +2029,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="F6" t="n">
         <v>152845</v>
       </c>
       <c r="G6" t="n">
-        <v>49.71</v>
+        <v>48.15</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>291100</v>
+        <v>324700</v>
       </c>
       <c r="C7" t="n">
         <v>290266.67</v>
@@ -2059,13 +2059,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>18.21</v>
+        <v>16.32</v>
       </c>
       <c r="F7" t="n">
         <v>237266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>81.51000000000001</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106920</v>
+        <v>110880</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35306.61</v>
+        <v>79325.61</v>
       </c>
       <c r="C9" t="n">
         <v>999</v>
@@ -2115,7 +2115,7 @@
         <v>999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.83</v>
+        <v>1.26</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1973367.8</v>
+        <v>2005960.8</v>
       </c>
       <c r="D2" t="n">
-        <v>8973</v>
+        <v>8969</v>
       </c>
       <c r="E2" t="n">
-        <v>1722850.8</v>
+        <v>1748632.8</v>
       </c>
       <c r="F2" t="n">
-        <v>250517</v>
+        <v>257328</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1729700</v>
+        <v>1760384</v>
       </c>
       <c r="D3" t="n">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E3" t="n">
-        <v>1494038</v>
+        <v>1515981</v>
       </c>
       <c r="F3" t="n">
-        <v>235662</v>
+        <v>244403</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>243667.8</v>
+        <v>245576.8</v>
       </c>
       <c r="D4" t="n">
         <v>8536</v>
       </c>
       <c r="E4" t="n">
-        <v>228812.8</v>
+        <v>232651.8</v>
       </c>
       <c r="F4" t="n">
-        <v>14855</v>
+        <v>12925</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3316840</v>
+        <v>3338036</v>
       </c>
       <c r="D5" t="n">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="E5" t="n">
-        <v>782106</v>
+        <v>770504</v>
       </c>
       <c r="F5" t="n">
-        <v>2534734</v>
+        <v>2567532</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2203122</v>
+        <v>2303734</v>
       </c>
       <c r="D6" t="n">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="E6" t="n">
         <v>57816</v>
       </c>
       <c r="F6" t="n">
-        <v>2145306</v>
+        <v>2245918</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1103718</v>
+        <v>1024302</v>
       </c>
       <c r="D7" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E7" t="n">
-        <v>724290</v>
+        <v>712688</v>
       </c>
       <c r="F7" t="n">
-        <v>379428</v>
+        <v>311614</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1421855.15</v>
+        <v>1519353.76</v>
       </c>
       <c r="D8" t="n">
-        <v>1950</v>
+        <v>2048</v>
       </c>
       <c r="E8" t="n">
-        <v>24790.61</v>
+        <v>23214.61</v>
       </c>
       <c r="F8" t="n">
-        <v>1397064.54</v>
+        <v>1496139.15</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>887675.0699999999</v>
+        <v>944562.33</v>
       </c>
       <c r="D9" t="n">
-        <v>832</v>
+        <v>861</v>
       </c>
       <c r="E9" t="n">
-        <v>5628.16</v>
+        <v>5428.16</v>
       </c>
       <c r="F9" t="n">
-        <v>882046.91</v>
+        <v>939134.17</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>534180.08</v>
+        <v>574791.4300000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1118</v>
+        <v>1187</v>
       </c>
       <c r="E10" t="n">
-        <v>19162.45</v>
+        <v>17786.45</v>
       </c>
       <c r="F10" t="n">
-        <v>515017.63</v>
+        <v>557004.98</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>589000</v>
+        <v>544400</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
         <v>218200</v>
       </c>
       <c r="F11" t="n">
-        <v>370800</v>
+        <v>326200</v>
       </c>
     </row>
     <row r="12">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>317465.9</v>
+        <v>355153.9</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12" t="n">
-        <v>112993.9</v>
+        <v>111093.9</v>
       </c>
       <c r="F12" t="n">
-        <v>204472</v>
+        <v>244060</v>
       </c>
     </row>
     <row r="13">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>324700</v>
+        <v>298880</v>
       </c>
       <c r="D13" t="n">
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>294920</v>
+        <v>269100</v>
       </c>
       <c r="F13" t="n">
         <v>29780</v>
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>110880</v>
+        <v>87120</v>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E14" t="n">
-        <v>17820</v>
+        <v>11880</v>
       </c>
       <c r="F14" t="n">
-        <v>93060</v>
+        <v>75240</v>
       </c>
     </row>
     <row r="15">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>79325.61</v>
+        <v>79525.61</v>
       </c>
       <c r="D15" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E15" t="n">
         <v>11631.36</v>
       </c>
       <c r="F15" t="n">
-        <v>67694.25</v>
+        <v>67894.25</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1255462.42</v>
+        <v>1353399.43</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>98.2</v>
+        <v>98.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1232406.42；咨询线 11592.0；工作坊 9900.0；其他 820.0；课程线 744.0；菌群线 0.0</t>
+          <t>医疗线 1330340.43；咨询线 11194.0；工作坊 7920.0；课程线 2125.0；菌群线 1000.0；其他 820.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>434136.9</v>
+        <v>409500.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 371650.0；课程线 53198.0；工作坊 3960.0；医疗线 3348.9；营地 1980.0</t>
+          <t>咨询线 350654.0；课程线 53518.0；医疗线 3348.9；营地 1980.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>206143.35</v>
+        <v>204306.34</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61.7</v>
+        <v>62.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 127156.0；考证 39588.0；营地 27800.0；医疗线 5710.35；课程线 5389.0；其他 500.0</t>
+          <t>咨询线 127156.0；考证 39588.0；营地 27800.0；课程线 5351.0；医疗线 3911.34；其他 500.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>895353.9</v>
+        <v>878621.9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.5</v>
+        <v>44.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 362998.0；菌群线 252800.0；课程线 103206.0；考证 99776.0；工作坊 61380.0；医疗线 14343.9；其他 850.0</t>
+          <t>咨询线 389198.0；菌群线 207200.0；课程线 109834.0；考证 99776.0；工作坊 57420.0；医疗线 14343.9；其他 850.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>469457.47</v>
+        <v>473605.47</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>75.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 352060.0；菌群线 46600.0；医疗线 41614.23；课程线 16438.0；考证 10000.0；工作坊 1980.0；其他 765.24</t>
+          <t>咨询线 356554.0；菌群线 46600.0；医疗线 41614.23；课程线 16092.0；考证 10000.0；工作坊 1980.0；其他 765.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>365307</v>
+        <v>344701</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>88.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 323600.0；课程线 39428.0；工作坊 1980.0；其他 299.0；菌群线 0.0</t>
+          <t>咨询线 302804.0；课程线 39418.0；工作坊 1980.0；其他 499.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>431788.69</v>
+        <v>454157.69</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>69.8</v>
+        <v>71.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 301438.0；医疗线 59288.68；其他 44066.01；菌群线 25800.0；课程线 1196.0</t>
+          <t>咨询线 324036.0；医疗线 59288.68；其他 44066.01；菌群线 25800.0；课程线 967.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>301622.56</v>
+        <v>313911.37</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>69.5</v>
+        <v>70.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 209566.0；菌群线 45600.0；医疗线 26506.56；考证 10000.0；课程线 8750.0；其他 1200.0</t>
+          <t>咨询线 221462.0；菌群线 45600.0；医疗线 26937.37；考证 10000.0；课程线 8712.0；其他 1200.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>197921.5</v>
+        <v>241898.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>84.5</v>
+        <v>73.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 167252.0；医疗线 13845.5；课程线 8904.0；工作坊 7920.0；菌群线 0.0</t>
+          <t>咨询线 177052.0；考证 39588.0；医疗线 16354.3；课程线 8904.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>110728</v>
+        <v>109890</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>66.09999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 73174.0；其他 18000.0；课程线 11794.0；工作坊 3960.0；考证 3800.0</t>
+          <t>咨询线 73174.0；其他 18000.0；课程线 10956.0；工作坊 3960.0；考证 3800.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>265280</v>
+        <v>265261</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 221048.0；考证 39588.0；工作坊 1980.0；课程线 1470.0；其他 1194.0</t>
+          <t>咨询线 221048.0；考证 39588.0；工作坊 1980.0；课程线 1451.0；其他 1194.0</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>95240</v>
+        <v>98600</v>
       </c>
     </row>
     <row r="3">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>94980</v>
+        <v>96260</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>81180</v>
+        <v>81690</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74700</v>
+        <v>81180</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>74700</v>
+        <v>79680</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>191814</v>
+        <v>208014</v>
       </c>
     </row>
     <row r="8">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>158578</v>
+        <v>147184</v>
       </c>
     </row>
     <row r="10">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>115884</v>
+        <v>116084</v>
       </c>
     </row>
     <row r="12">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>298696.64</v>
+        <v>319549.65</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>219861.04</v>
+        <v>231661.04</v>
       </c>
     </row>
     <row r="14">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>154930</v>
+        <v>172389</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>141485.1</v>
+        <v>162293</v>
       </c>
     </row>
     <row r="16">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>137495</v>
+        <v>144388.1</v>
       </c>
     </row>
     <row r="17">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>182400</v>
+        <v>136800</v>
       </c>
     </row>
     <row r="18">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>77288</v>
+        <v>79188</v>
       </c>
     </row>
     <row r="24">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>马雅丽</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10000</v>
+        <v>39588</v>
       </c>
     </row>
     <row r="27">
@@ -1614,11 +1614,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>冯岚</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>34100</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="30">
@@ -1632,11 +1632,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>29800</v>
+        <v>27800</v>
       </c>
     </row>
     <row r="31">
@@ -1650,11 +1650,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="32">
@@ -1704,11 +1704,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>袁登玉</t>
+          <t>王凯</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7920</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="35">
@@ -1722,11 +1722,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>王凯</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5940</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="36">
@@ -1740,11 +1740,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>梁志超</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3960</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="37">
@@ -1900,26 +1900,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1973367.8</v>
+        <v>2005960.8</v>
       </c>
       <c r="C2" t="n">
-        <v>390988.86</v>
+        <v>411574.86</v>
       </c>
       <c r="D2" t="n">
-        <v>48763</v>
+        <v>50157</v>
       </c>
       <c r="E2" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="F2" t="n">
-        <v>342225.86</v>
+        <v>361417.86</v>
       </c>
       <c r="G2" t="n">
-        <v>17.34</v>
+        <v>18.02</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 132000.0；青少年同行者计划领航营 88896.0；青少年同行者计划-护航营 26999.16</t>
+          <t>少年说陪伴计划 138600.0；青少年同行者计划领航营 88896.0；青少年同行者计划-护航营 31182.16</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3316840</v>
+        <v>3338036</v>
       </c>
       <c r="C3" t="n">
         <v>472001.38</v>
@@ -1945,7 +1945,7 @@
         <v>472001.38</v>
       </c>
       <c r="G3" t="n">
-        <v>14.23</v>
+        <v>14.14</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1421855.15</v>
+        <v>1519353.76</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -1975,7 +1975,7 @@
         <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>589000</v>
+        <v>544400</v>
       </c>
       <c r="C5" t="n">
         <v>116000</v>
@@ -2005,7 +2005,7 @@
         <v>116000</v>
       </c>
       <c r="G5" t="n">
-        <v>19.69</v>
+        <v>21.31</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>317465.9</v>
+        <v>355153.9</v>
       </c>
       <c r="C6" t="n">
         <v>154862.9</v>
@@ -2029,13 +2029,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="F6" t="n">
         <v>152845</v>
       </c>
       <c r="G6" t="n">
-        <v>48.15</v>
+        <v>43.04</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>324700</v>
+        <v>298880</v>
       </c>
       <c r="C7" t="n">
         <v>290266.67</v>
@@ -2059,13 +2059,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>16.32</v>
+        <v>17.73</v>
       </c>
       <c r="F7" t="n">
         <v>237266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>73.06999999999999</v>
+        <v>79.39</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110880</v>
+        <v>87120</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79325.61</v>
+        <v>79525.61</v>
       </c>
       <c r="C9" t="n">
         <v>999</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2005960.8</v>
+        <v>2064246.8</v>
       </c>
       <c r="D2" t="n">
-        <v>8969</v>
+        <v>9481</v>
       </c>
       <c r="E2" t="n">
-        <v>1748632.8</v>
+        <v>1804310.8</v>
       </c>
       <c r="F2" t="n">
-        <v>257328</v>
+        <v>259936</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1760384</v>
+        <v>1805279</v>
       </c>
       <c r="D3" t="n">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="E3" t="n">
-        <v>1515981</v>
+        <v>1560857</v>
       </c>
       <c r="F3" t="n">
-        <v>244403</v>
+        <v>244422</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>245576.8</v>
+        <v>258967.8</v>
       </c>
       <c r="D4" t="n">
-        <v>8536</v>
+        <v>9032</v>
       </c>
       <c r="E4" t="n">
-        <v>232651.8</v>
+        <v>243453.8</v>
       </c>
       <c r="F4" t="n">
-        <v>12925</v>
+        <v>15514</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3338036</v>
+        <v>3440314</v>
       </c>
       <c r="D5" t="n">
-        <v>652</v>
+        <v>673</v>
       </c>
       <c r="E5" t="n">
-        <v>770504</v>
+        <v>792902</v>
       </c>
       <c r="F5" t="n">
-        <v>2567532</v>
+        <v>2647412</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2303734</v>
+        <v>2351424</v>
       </c>
       <c r="D6" t="n">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="E6" t="n">
         <v>57816</v>
       </c>
       <c r="F6" t="n">
-        <v>2245918</v>
+        <v>2293608</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1024302</v>
+        <v>1078890</v>
       </c>
       <c r="D7" t="n">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="E7" t="n">
-        <v>712688</v>
+        <v>735086</v>
       </c>
       <c r="F7" t="n">
-        <v>311614</v>
+        <v>343804</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1519353.76</v>
+        <v>1524429.76</v>
       </c>
       <c r="D8" t="n">
-        <v>2048</v>
+        <v>2057</v>
       </c>
       <c r="E8" t="n">
-        <v>23214.61</v>
+        <v>26290.61</v>
       </c>
       <c r="F8" t="n">
-        <v>1496139.15</v>
+        <v>1498139.15</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>944562.33</v>
+        <v>946762.33</v>
       </c>
       <c r="D9" t="n">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="E9" t="n">
-        <v>5428.16</v>
+        <v>5628.16</v>
       </c>
       <c r="F9" t="n">
-        <v>939134.17</v>
+        <v>941134.17</v>
       </c>
     </row>
     <row r="10">
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>574791.4300000001</v>
+        <v>577667.4300000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="E10" t="n">
-        <v>17786.45</v>
+        <v>20662.45</v>
       </c>
       <c r="F10" t="n">
         <v>557004.98</v>
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>544400</v>
+        <v>590000</v>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
         <v>218200</v>
       </c>
       <c r="F11" t="n">
-        <v>326200</v>
+        <v>371800</v>
       </c>
     </row>
     <row r="12">
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>355153.9</v>
+        <v>358953.9</v>
       </c>
       <c r="D12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12" t="n">
-        <v>111093.9</v>
+        <v>114893.9</v>
       </c>
       <c r="F12" t="n">
         <v>244060</v>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>298880</v>
+        <v>326680</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>269100</v>
+        <v>296900</v>
       </c>
       <c r="F13" t="n">
         <v>29780</v>
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>87120</v>
+        <v>110880</v>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
-        <v>11880</v>
+        <v>17820</v>
       </c>
       <c r="F14" t="n">
-        <v>75240</v>
+        <v>93060</v>
       </c>
     </row>
     <row r="15">
@@ -778,7 +778,7 @@
         <v>79525.61</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E15" t="n">
         <v>11631.36</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1353399.43</v>
+        <v>1356095.43</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>98.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1330340.43；咨询线 11194.0；工作坊 7920.0；课程线 2125.0；菌群线 1000.0；其他 820.0</t>
+          <t>医疗线 1330340.43；咨询线 11592.0；工作坊 9900.0；课程线 2443.0；菌群线 1000.0；其他 820.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>409500.9</v>
+        <v>445175.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>85.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 350654.0；课程线 53518.0；医疗线 3348.9；营地 1980.0</t>
+          <t>咨询线 382048.0；课程线 53839.0；工作坊 3960.0；医疗线 3348.9；营地 1980.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>204306.34</v>
+        <v>206523.34</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62.2</v>
+        <v>61.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 127156.0；考证 39588.0；营地 27800.0；课程线 5351.0；医疗线 3911.34；其他 500.0</t>
+          <t>咨询线 127554.0；考证 39588.0；营地 27800.0；医疗线 5711.34；课程线 5370.0；其他 500.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>878621.9</v>
+        <v>928588.9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44.3</v>
+        <v>42</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 389198.0；菌群线 207200.0；课程线 109834.0；考证 99776.0；工作坊 57420.0；医疗线 14343.9；其他 850.0</t>
+          <t>咨询线 389596.0；菌群线 252800.0；课程线 109843.0；考证 99776.0；工作坊 61380.0；医疗线 14343.9；其他 850.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>473605.47</v>
+        <v>481680.47</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>75.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 356554.0；菌群线 46600.0；医疗线 41614.23；课程线 16092.0；考证 10000.0；工作坊 1980.0；其他 765.24</t>
+          <t>咨询线 364054.0；菌群线 46600.0；医疗线 41814.23；课程线 16467.0；考证 10000.0；工作坊 1980.0；其他 765.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>344701</v>
+        <v>375497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>87.8</v>
+        <v>88.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 302804.0；课程线 39418.0；工作坊 1980.0；其他 499.0；菌群线 0.0</t>
+          <t>咨询线 333600.0；课程线 39418.0；工作坊 1980.0；其他 499.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>454157.69</v>
+        <v>454755.69</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 324036.0；医疗线 59288.68；其他 44066.01；菌群线 25800.0；课程线 967.0</t>
+          <t>咨询线 324434.0；医疗线 59288.68；其他 44066.01；菌群线 25800.0；课程线 1167.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>313911.37</v>
+        <v>321930.37</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70.5</v>
+        <v>71.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 221462.0；菌群线 45600.0；医疗线 26937.37；考证 10000.0；课程线 8712.0；其他 1200.0</t>
+          <t>咨询线 229462.0；菌群线 45600.0；医疗线 26937.37；考证 10000.0；课程线 8731.0；其他 1200.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>241898.3</v>
+        <v>250416.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>73.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 177052.0；考证 39588.0；医疗线 16354.3；课程线 8904.0；菌群线 0.0</t>
+          <t>咨询线 177650.0；考证 39588.0；医疗线 16354.3；课程线 8904.0；工作坊 7920.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>109890</v>
+        <v>111208</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>66.59999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 73174.0；其他 18000.0；课程线 10956.0；工作坊 3960.0；考证 3800.0</t>
+          <t>咨询线 73174.0；其他 18000.0；课程线 12274.0；工作坊 3960.0；考证 3800.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>265261</v>
+        <v>265290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 221048.0；考证 39588.0；工作坊 1980.0；课程线 1451.0；其他 1194.0</t>
+          <t>咨询线 221048.0；考证 39588.0；工作坊 1980.0；课程线 1480.0；其他 1194.0</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>98600</v>
+        <v>102580</v>
       </c>
     </row>
     <row r="3">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>208014</v>
+        <v>208412</v>
       </c>
     </row>
     <row r="8">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>163390</v>
+        <v>168578</v>
       </c>
     </row>
     <row r="9">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>147184</v>
+        <v>163390</v>
       </c>
     </row>
     <row r="10">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>116084</v>
+        <v>116482</v>
       </c>
     </row>
     <row r="12">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>136800</v>
+        <v>182400</v>
       </c>
     </row>
     <row r="18">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>马雅丽</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>马雅丽</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1614,11 +1614,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>冯岚</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29800</v>
+        <v>34100</v>
       </c>
     </row>
     <row r="30">
@@ -1632,11 +1632,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27800</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="31">
@@ -1650,11 +1650,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>23200</v>
+        <v>27800</v>
       </c>
     </row>
     <row r="32">
@@ -1704,11 +1704,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>王凯</t>
+          <t>袁登玉</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5940</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="35">
@@ -1722,11 +1722,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>王凯</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3960</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="36">
@@ -1740,11 +1740,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>梁志超</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="37">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2005960.8</v>
+        <v>2064246.8</v>
       </c>
       <c r="C2" t="n">
         <v>411574.86</v>
@@ -1909,13 +1909,13 @@
         <v>50157</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="F2" t="n">
         <v>361417.86</v>
       </c>
       <c r="G2" t="n">
-        <v>18.02</v>
+        <v>17.51</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3338036</v>
+        <v>3440314</v>
       </c>
       <c r="C3" t="n">
         <v>472001.38</v>
@@ -1945,7 +1945,7 @@
         <v>472001.38</v>
       </c>
       <c r="G3" t="n">
-        <v>14.14</v>
+        <v>13.72</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1519353.76</v>
+        <v>1524429.76</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>544400</v>
+        <v>590000</v>
       </c>
       <c r="C5" t="n">
         <v>116000</v>
@@ -2005,7 +2005,7 @@
         <v>116000</v>
       </c>
       <c r="G5" t="n">
-        <v>21.31</v>
+        <v>19.66</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>355153.9</v>
+        <v>358953.9</v>
       </c>
       <c r="C6" t="n">
         <v>154862.9</v>
@@ -2029,13 +2029,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>152845</v>
       </c>
       <c r="G6" t="n">
-        <v>43.04</v>
+        <v>42.58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>298880</v>
+        <v>326680</v>
       </c>
       <c r="C7" t="n">
         <v>290266.67</v>
@@ -2059,13 +2059,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>17.73</v>
+        <v>16.22</v>
       </c>
       <c r="F7" t="n">
         <v>237266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>79.39</v>
+        <v>72.63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>87120</v>
+        <v>110880</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2064246.8</v>
+        <v>892008</v>
       </c>
       <c r="D2" t="n">
-        <v>9481</v>
+        <v>2690</v>
       </c>
       <c r="E2" t="n">
-        <v>1804310.8</v>
+        <v>765825</v>
       </c>
       <c r="F2" t="n">
-        <v>259936</v>
+        <v>126183</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1805279</v>
+        <v>819147</v>
       </c>
       <c r="D3" t="n">
-        <v>449</v>
+        <v>154</v>
       </c>
       <c r="E3" t="n">
-        <v>1560857</v>
+        <v>695370</v>
       </c>
       <c r="F3" t="n">
-        <v>244422</v>
+        <v>123777</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>258967.8</v>
+        <v>72861</v>
       </c>
       <c r="D4" t="n">
-        <v>9032</v>
+        <v>2536</v>
       </c>
       <c r="E4" t="n">
-        <v>243453.8</v>
+        <v>70455</v>
       </c>
       <c r="F4" t="n">
-        <v>15514</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3440314</v>
+        <v>1041076</v>
       </c>
       <c r="D5" t="n">
-        <v>673</v>
+        <v>240</v>
       </c>
       <c r="E5" t="n">
-        <v>792902</v>
+        <v>242360</v>
       </c>
       <c r="F5" t="n">
-        <v>2647412</v>
+        <v>798716</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2351424</v>
+        <v>726900</v>
       </c>
       <c r="D6" t="n">
-        <v>429</v>
+        <v>150</v>
       </c>
       <c r="E6" t="n">
-        <v>57816</v>
+        <v>42598</v>
       </c>
       <c r="F6" t="n">
-        <v>2293608</v>
+        <v>684302</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1078890</v>
+        <v>301176</v>
       </c>
       <c r="D7" t="n">
-        <v>243</v>
+        <v>88</v>
       </c>
       <c r="E7" t="n">
-        <v>735086</v>
+        <v>199762</v>
       </c>
       <c r="F7" t="n">
-        <v>343804</v>
+        <v>101414</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1524429.76</v>
+        <v>1526886.8</v>
       </c>
       <c r="D8" t="n">
-        <v>2057</v>
+        <v>2044</v>
       </c>
       <c r="E8" t="n">
-        <v>26290.61</v>
+        <v>11310.73</v>
       </c>
       <c r="F8" t="n">
-        <v>1498139.15</v>
+        <v>1515576.07</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>946762.33</v>
+        <v>942636.61</v>
       </c>
       <c r="D9" t="n">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E9" t="n">
-        <v>5628.16</v>
+        <v>2945.64</v>
       </c>
       <c r="F9" t="n">
-        <v>941134.17</v>
+        <v>939690.97</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>577667.4300000001</v>
+        <v>584250.1899999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="E10" t="n">
-        <v>20662.45</v>
+        <v>8365.09</v>
       </c>
       <c r="F10" t="n">
-        <v>557004.98</v>
+        <v>575885.1</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>590000</v>
+        <v>382800</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>218200</v>
+        <v>194400</v>
       </c>
       <c r="F11" t="n">
-        <v>371800</v>
+        <v>188400</v>
       </c>
     </row>
     <row r="12">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>358953.9</v>
+        <v>74788</v>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>114893.9</v>
+        <v>15200</v>
       </c>
       <c r="F12" t="n">
-        <v>244060</v>
+        <v>59588</v>
       </c>
     </row>
     <row r="13">
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>326680</v>
+        <v>59340</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>296900</v>
+        <v>59340</v>
       </c>
       <c r="F13" t="n">
-        <v>29780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>110880</v>
+        <v>7920</v>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>17820</v>
+        <v>1980</v>
       </c>
       <c r="F14" t="n">
-        <v>93060</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="15">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>79525.61</v>
+        <v>57187.24</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="E15" t="n">
-        <v>11631.36</v>
+        <v>8092</v>
       </c>
       <c r="F15" t="n">
-        <v>67894.25</v>
+        <v>49095.24</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1356095.43</v>
+        <v>1407992.43</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>98.09999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1330340.43；咨询线 11592.0；工作坊 9900.0；课程线 2443.0；菌群线 1000.0；其他 820.0</t>
+          <t>医疗线 1404441.43；课程线 1731.0；菌群线 1000.0；其他 820.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>445175.9</v>
+        <v>130665</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>85.8</v>
+        <v>90</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 382048.0；课程线 53839.0；工作坊 3960.0；医疗线 3348.9；营地 1980.0</t>
+          <t>咨询线 117574.0；课程线 12591.0；医疗线 500.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>206523.34</v>
+        <v>71697.34</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61.8</v>
+        <v>99</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 127554.0；考证 39588.0；营地 27800.0；医疗线 5711.34；课程线 5370.0；其他 500.0</t>
+          <t>咨询线 70978.0；医疗线 411.34；课程线 308.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>928588.9</v>
+        <v>250375.78</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>42</v>
+        <v>46.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 389596.0；菌群线 252800.0；课程线 109843.0；考证 99776.0；工作坊 61380.0；医疗线 14343.9；其他 850.0</t>
+          <t>咨询线 115394.0；菌群线 70400.0；课程线 61263.0；工作坊 1980.0；其他 850.0；医疗线 488.78</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>481680.47</v>
+        <v>170943.25</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>75.59999999999999</v>
+        <v>43.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 364054.0；菌群线 46600.0；医疗线 41814.23；课程线 16467.0；考证 10000.0；工作坊 1980.0；其他 765.24</t>
+          <t>咨询线 74576.0；菌群线 46600.0；医疗线 23726.01；课程线 13296.0；考证 10000.0；工作坊 1980.0；其他 765.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>375497</v>
+        <v>92047</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>88.8</v>
+        <v>78.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 333600.0；课程线 39418.0；工作坊 1980.0；其他 499.0；菌群线 0.0</t>
+          <t>咨询线 71990.0；课程线 19857.0；其他 200.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>454755.69</v>
+        <v>255590.68</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>71.3</v>
+        <v>49.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 324434.0；医疗线 59288.68；其他 44066.01；菌群线 25800.0；课程线 1167.0</t>
+          <t>咨询线 126976.0；医疗线 59449.68；其他 44066.0；菌群线 24800.0；课程线 299.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>321930.37</v>
+        <v>149705.53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>71.3</v>
+        <v>49.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 229462.0；菌群线 45600.0；医疗线 26937.37；考证 10000.0；课程线 8731.0；其他 1200.0</t>
+          <t>咨询线 74084.0；菌群线 45600.0；医疗线 10204.53；考证 10000.0；课程线 8617.0；其他 1200.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250416.3</v>
+        <v>142968.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>70.90000000000001</v>
+        <v>56.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 177650.0；考证 39588.0；医疗线 16354.3；课程线 8904.0；工作坊 7920.0；菌群线 0.0</t>
+          <t>咨询线 80378.0；考证 39588.0；医疗线 16354.3；课程线 6648.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>111208</v>
+        <v>23127</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 73174.0；其他 18000.0；课程线 12274.0；工作坊 3960.0；考证 3800.0</t>
+          <t>咨询线 21592.0；课程线 1535.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>265290</v>
+        <v>48386</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>83.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 221048.0；考证 39588.0；工作坊 1980.0；课程线 1480.0；其他 1194.0</t>
+          <t>咨询线 45174.0；工作坊 1980.0；其他 1194.0；课程线 38.0</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,11 +1128,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>102580</v>
+        <v>59400</v>
       </c>
     </row>
     <row r="3">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>96260</v>
+        <v>52240</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>81690</v>
+        <v>49680</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>81180</v>
+        <v>44820</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79680</v>
+        <v>43080</v>
       </c>
     </row>
     <row r="7">
@@ -1218,11 +1218,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>208412</v>
+        <v>83596</v>
       </c>
     </row>
     <row r="8">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>168578</v>
+        <v>55584</v>
       </c>
     </row>
     <row r="9">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>163390</v>
+        <v>42520</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>120160</v>
+        <v>40398</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>马雅丽</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>116482</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="12">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>319549.65</v>
+        <v>320413.65</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>231661.04</v>
+        <v>241661.04</v>
       </c>
     </row>
     <row r="14">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>172389</v>
+        <v>185531</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>162293</v>
+        <v>163372</v>
       </c>
     </row>
     <row r="16">
@@ -1398,11 +1398,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>182400</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70400</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="19">
@@ -1434,11 +1434,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70400</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="20">
@@ -1488,11 +1488,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>王秋</t>
+          <t>马雅丽</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>99776</v>
+        <v>39588</v>
       </c>
     </row>
     <row r="23">
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79188</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="24">
@@ -1524,11 +1524,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>39588</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="25">
@@ -1542,11 +1542,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>李明</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>39588</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="26">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>马雅丽</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>39588</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="27">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>110160</v>
+        <v>20760</v>
       </c>
     </row>
     <row r="28">
@@ -1596,11 +1596,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>55600</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="29">
@@ -1614,11 +1614,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>冯岚</t>
+          <t>何媛媛</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>34100</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="30">
@@ -1632,11 +1632,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>闫丽东</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>29800</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="31">
@@ -1650,11 +1650,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27800</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="32">
@@ -1668,11 +1668,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>55440</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="33">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7920</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="34">
@@ -1704,11 +1704,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>袁登玉</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7920</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="35">
@@ -1722,29 +1722,29 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>王凯</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5940</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>梁志超</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3960</v>
+        <v>36796</v>
       </c>
     </row>
     <row r="37">
@@ -1754,15 +1754,15 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>36796</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="38">
@@ -1772,15 +1772,15 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>田婉丽</t>
+          <t>陈茜</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>18000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="39">
@@ -1790,15 +1790,15 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>沈悦</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5398</v>
+        <v>850</v>
       </c>
     </row>
     <row r="40">
@@ -1808,33 +1808,15 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>陈茜</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>5</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>岳伟伟</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>850</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -1900,26 +1882,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2064246.8</v>
+        <v>892008</v>
       </c>
       <c r="C2" t="n">
-        <v>411574.86</v>
+        <v>434481.86</v>
       </c>
       <c r="D2" t="n">
-        <v>50157</v>
+        <v>60716</v>
       </c>
       <c r="E2" t="n">
-        <v>2.43</v>
+        <v>6.81</v>
       </c>
       <c r="F2" t="n">
-        <v>361417.86</v>
+        <v>373765.86</v>
       </c>
       <c r="G2" t="n">
-        <v>17.51</v>
+        <v>41.9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 138600.0；青少年同行者计划领航营 88896.0；青少年同行者计划-护航营 31182.16</t>
+          <t>少年说陪伴计划 138600.0；青少年同行者计划领航营 93876.0；青少年同行者计划-护航营 31182.16</t>
         </is>
       </c>
     </row>
@@ -1930,26 +1912,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3440314</v>
+        <v>1041076</v>
       </c>
       <c r="C3" t="n">
-        <v>472001.38</v>
+        <v>494001.38</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>472001.38</v>
+        <v>493001.38</v>
       </c>
       <c r="G3" t="n">
-        <v>13.72</v>
+        <v>47.35</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 289033.38；精神心理 84598.0；电商咨询 20000.0</t>
+          <t>儿童青少年 301033.38；精神心理 93598.0；电商咨询 20000.0</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1942,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1524429.76</v>
+        <v>1526886.8</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -1990,7 +1972,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>590000</v>
+        <v>382800</v>
       </c>
       <c r="C5" t="n">
         <v>116000</v>
@@ -2005,7 +1987,7 @@
         <v>116000</v>
       </c>
       <c r="G5" t="n">
-        <v>19.66</v>
+        <v>30.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2020,26 +2002,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>358953.9</v>
+        <v>74788</v>
       </c>
       <c r="C6" t="n">
-        <v>154862.9</v>
+        <v>196919.9</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="F6" t="n">
-        <v>152845</v>
+        <v>194902</v>
       </c>
       <c r="G6" t="n">
-        <v>42.58</v>
+        <v>260.61</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派-高阶培训课程 119200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 27016.0；心理咨询师职业能力水平评价考试培训 3788.0</t>
+          <t>心灯计划-实战派-高阶培训课程 119200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 64193.0；心理咨询基本功实战营 4880.0</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2032,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>326680</v>
+        <v>59340</v>
       </c>
       <c r="C7" t="n">
         <v>290266.67</v>
@@ -2059,13 +2041,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>16.22</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="F7" t="n">
         <v>237266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>72.63</v>
+        <v>399.84</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2080,7 +2062,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110880</v>
+        <v>7920</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2106,16 +2088,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79525.61</v>
+        <v>57187.24</v>
       </c>
       <c r="C9" t="n">
-        <v>999</v>
+        <v>1199</v>
       </c>
       <c r="D9" t="n">
-        <v>999</v>
+        <v>1199</v>
       </c>
       <c r="E9" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -2125,7 +2107,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[自我成长/疗愈] 完形心理认知课，增加智慧。 999.0</t>
+          <t>[自我成长/疗愈] 完形心理认知课，增加智慧。 999.0；100天疗愈  第1周基础课 心理成长课 200.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>892008</v>
+        <v>858325</v>
       </c>
       <c r="D2" t="n">
-        <v>2690</v>
+        <v>2572</v>
       </c>
       <c r="E2" t="n">
-        <v>765825</v>
+        <v>726343</v>
       </c>
       <c r="F2" t="n">
-        <v>126183</v>
+        <v>131982</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>819147</v>
+        <v>786587</v>
       </c>
       <c r="D3" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E3" t="n">
-        <v>695370</v>
+        <v>656210</v>
       </c>
       <c r="F3" t="n">
-        <v>123777</v>
+        <v>130377</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>72861</v>
+        <v>71738</v>
       </c>
       <c r="D4" t="n">
-        <v>2536</v>
+        <v>2426</v>
       </c>
       <c r="E4" t="n">
-        <v>70455</v>
+        <v>70133</v>
       </c>
       <c r="F4" t="n">
-        <v>2406</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1041076</v>
+        <v>997436</v>
       </c>
       <c r="D5" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E5" t="n">
-        <v>242360</v>
+        <v>133900</v>
       </c>
       <c r="F5" t="n">
-        <v>798716</v>
+        <v>863536</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>726900</v>
+        <v>761820</v>
       </c>
       <c r="D6" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E6" t="n">
-        <v>42598</v>
+        <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>684302</v>
+        <v>739222</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>301176</v>
+        <v>215616</v>
       </c>
       <c r="D7" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E7" t="n">
-        <v>199762</v>
+        <v>111302</v>
       </c>
       <c r="F7" t="n">
-        <v>101414</v>
+        <v>104314</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1526886.8</v>
+        <v>1533282.74</v>
       </c>
       <c r="D8" t="n">
-        <v>2044</v>
+        <v>2071</v>
       </c>
       <c r="E8" t="n">
-        <v>11310.73</v>
+        <v>12251.53</v>
       </c>
       <c r="F8" t="n">
-        <v>1515576.07</v>
+        <v>1521031.21</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>942636.61</v>
+        <v>946289.28</v>
       </c>
       <c r="D9" t="n">
-        <v>863</v>
+        <v>877</v>
       </c>
       <c r="E9" t="n">
         <v>2945.64</v>
       </c>
       <c r="F9" t="n">
-        <v>939690.97</v>
+        <v>943343.64</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>584250.1899999999</v>
+        <v>586993.46</v>
       </c>
       <c r="D10" t="n">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="E10" t="n">
-        <v>8365.09</v>
+        <v>9305.889999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>575885.1</v>
+        <v>577687.5699999999</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>382800</v>
+        <v>474000</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>194400</v>
+        <v>240000</v>
       </c>
       <c r="F11" t="n">
-        <v>188400</v>
+        <v>234000</v>
       </c>
     </row>
     <row r="12">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>74788</v>
+        <v>100788</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>15200</v>
       </c>
       <c r="F12" t="n">
-        <v>59588</v>
+        <v>85588</v>
       </c>
     </row>
     <row r="13">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>59340</v>
+        <v>45480</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>59340</v>
+        <v>45480</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -751,13 +751,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7920</v>
+        <v>5940</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>5940</v>
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57187.24</v>
+        <v>57887.24</v>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E15" t="n">
-        <v>8092</v>
+        <v>8792</v>
       </c>
       <c r="F15" t="n">
         <v>49095.24</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1407992.43</v>
+        <v>1408205.43</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1404441.43；课程线 1731.0；菌群线 1000.0；其他 820.0</t>
+          <t>医疗线 1404635.43；课程线 1750.0；菌群线 1000.0；其他 820.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>130665</v>
+        <v>151423</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>90</v>
+        <v>90.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 117574.0；课程线 12591.0；医疗线 500.0</t>
+          <t>咨询线 136782.0；课程线 14141.0；医疗线 500.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71697.34</v>
+        <v>68612.10000000001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>99</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 70978.0；医疗线 411.34；课程线 308.0</t>
+          <t>咨询线 59778.0；课程线 6609.0；医疗线 2225.1</t>
         </is>
       </c>
     </row>
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>250375.78</v>
+        <v>289392.09</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>咨询线</t>
+          <t>菌群线</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>46.1</v>
+        <v>40.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 115394.0；菌群线 70400.0；课程线 61263.0；工作坊 1980.0；其他 850.0；医疗线 488.78</t>
+          <t>菌群线 116000.0；咨询线 110394.0；课程线 59564.0；工作坊 1980.0；其他 850.0；医疗线 604.09</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>170943.25</v>
+        <v>204881.25</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43.6</v>
+        <v>53.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 74576.0；菌群线 46600.0；医疗线 23726.01；课程线 13296.0；考证 10000.0；工作坊 1980.0；其他 765.24</t>
+          <t>咨询线 110474.0；菌群线 46600.0；医疗线 23775.01；课程线 13267.0；考证 10000.0；其他 765.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>92047</v>
+        <v>51688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78.2</v>
+        <v>61.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 71990.0；课程线 19857.0；其他 200.0；菌群线 0.0</t>
+          <t>咨询线 31592.0；课程线 19857.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>255590.68</v>
+        <v>284821.68</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>49.7</v>
+        <v>54.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 126976.0；医疗线 59449.68；其他 44066.0；菌群线 24800.0；课程线 299.0</t>
+          <t>咨询线 156178.0；医疗线 59449.68；其他 44066.0；菌群线 24800.0；课程线 328.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>149705.53</v>
+        <v>210408</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49.5</v>
+        <v>51.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 74084.0；菌群线 45600.0；医疗线 10204.53；考证 10000.0；课程线 8617.0；其他 1200.0</t>
+          <t>咨询线 108584.0；菌群线 45600.0；考证 36000.0；医疗线 10725.0；课程线 8299.0；其他 1200.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142968.3</v>
+        <v>134268.9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>56.2</v>
+        <v>51.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 80378.0；考证 39588.0；医疗线 16354.3；课程线 6648.0</t>
+          <t>咨询线 68984.0；考证 39588.0；医疗线 19077.9；课程线 6619.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23127</v>
+        <v>23140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>93.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 21592.0；课程线 1535.0；其他 0.0</t>
+          <t>咨询线 21592.0；课程线 1548.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48386</v>
+        <v>64332</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>93.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 45174.0；工作坊 1980.0；其他 1194.0；课程线 38.0</t>
+          <t>咨询线 59178.0；工作坊 3960.0；其他 1194.0</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>52240</v>
+        <v>56280</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>49680</v>
+        <v>53520</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44820</v>
+        <v>39840</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43080</v>
+        <v>39720</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>83596</v>
+        <v>83198</v>
       </c>
     </row>
     <row r="8">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55584</v>
+        <v>50592</v>
       </c>
     </row>
     <row r="9">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>40398</v>
+        <v>40186</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>马雅丽</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>40000</v>
+        <v>39194</v>
       </c>
     </row>
     <row r="12">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>185531</v>
+        <v>184929</v>
       </c>
     </row>
     <row r="15">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1506,11 +1506,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>梁志超</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11400</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="24">
@@ -1524,11 +1524,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>林非凡</t>
+          <t>梁志超</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10000</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="25">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>陈紫灵</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3800</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="27">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>20760</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="28">
@@ -1614,11 +1614,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>何媛媛</t>
+          <t>关万辉</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5940</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="30">
@@ -1632,11 +1632,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>闫丽东</t>
+          <t>何媛媛</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3960</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="31">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>朱碧丹</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1714,19 +1714,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1980</v>
+        <v>36796</v>
       </c>
     </row>
     <row r="36">
@@ -1736,15 +1736,15 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>36796</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="37">
@@ -1754,15 +1754,15 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>沈悦</t>
+          <t>陈茜</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5398</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="38">
@@ -1772,15 +1772,15 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>陈茜</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1200</v>
+        <v>850</v>
       </c>
     </row>
     <row r="39">
@@ -1790,32 +1790,14 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>5</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>郑巨光</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
         <v>796</v>
       </c>
     </row>
@@ -1882,26 +1864,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>892008</v>
+        <v>858325</v>
       </c>
       <c r="C2" t="n">
-        <v>434481.86</v>
+        <v>481656.86</v>
       </c>
       <c r="D2" t="n">
-        <v>60716</v>
+        <v>77320</v>
       </c>
       <c r="E2" t="n">
-        <v>6.81</v>
+        <v>9.01</v>
       </c>
       <c r="F2" t="n">
-        <v>373765.86</v>
+        <v>404336.86</v>
       </c>
       <c r="G2" t="n">
-        <v>41.9</v>
+        <v>47.11</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 138600.0；青少年同行者计划领航营 93876.0；青少年同行者计划-护航营 31182.16</t>
+          <t>少年说陪伴计划 158400.0；青少年同行者计划领航营 112796.0；青少年同行者计划-护航营 32974.16</t>
         </is>
       </c>
     </row>
@@ -1912,10 +1894,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1041076</v>
+        <v>997436</v>
       </c>
       <c r="C3" t="n">
-        <v>494001.38</v>
+        <v>504001.38</v>
       </c>
       <c r="D3" t="n">
         <v>1000</v>
@@ -1924,14 +1906,14 @@
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>493001.38</v>
+        <v>503001.38</v>
       </c>
       <c r="G3" t="n">
-        <v>47.35</v>
+        <v>50.43</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 301033.38；精神心理 93598.0；电商咨询 20000.0</t>
+          <t>儿童青少年 309033.38；精神心理 93598.0；电商咨询 20000.0</t>
         </is>
       </c>
     </row>
@@ -1942,10 +1924,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1526886.8</v>
+        <v>1533282.74</v>
       </c>
       <c r="C4" t="n">
-        <v>2849</v>
+        <v>4649</v>
       </c>
       <c r="D4" t="n">
         <v>49</v>
@@ -1954,14 +1936,14 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2800</v>
+        <v>4600</v>
       </c>
       <c r="G4" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50分钟问诊（诸秉根） -线下 1800.0；医师50分钟问诊-线上 1000.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
+          <t>50分钟问诊（诸秉根） -线下 3600.0；医师50分钟问诊-线上 1000.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1954,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382800</v>
+        <v>474000</v>
       </c>
       <c r="C5" t="n">
         <v>116000</v>
@@ -1987,7 +1969,7 @@
         <v>116000</v>
       </c>
       <c r="G5" t="n">
-        <v>30.3</v>
+        <v>24.47</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2002,7 +1984,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74788</v>
+        <v>100788</v>
       </c>
       <c r="C6" t="n">
         <v>196919.9</v>
@@ -2011,13 +1993,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>194902</v>
       </c>
       <c r="G6" t="n">
-        <v>260.61</v>
+        <v>193.38</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2032,7 +2014,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59340</v>
+        <v>45480</v>
       </c>
       <c r="C7" t="n">
         <v>290266.67</v>
@@ -2041,13 +2023,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>89.31999999999999</v>
+        <v>116.53</v>
       </c>
       <c r="F7" t="n">
         <v>237266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>399.84</v>
+        <v>521.6900000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2062,7 +2044,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7920</v>
+        <v>5940</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2088,7 +2070,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57187.24</v>
+        <v>57887.24</v>
       </c>
       <c r="C9" t="n">
         <v>1199</v>
@@ -2097,7 +2079,7 @@
         <v>1199</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>858325</v>
+        <v>945493.9399999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2572</v>
+        <v>2918</v>
       </c>
       <c r="E2" t="n">
-        <v>726343</v>
+        <v>92429</v>
       </c>
       <c r="F2" t="n">
-        <v>131982</v>
+        <v>853064.9399999999</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>786587</v>
+        <v>859547</v>
       </c>
       <c r="D3" t="n">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E3" t="n">
-        <v>656210</v>
+        <v>92400</v>
       </c>
       <c r="F3" t="n">
-        <v>130377</v>
+        <v>767147</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>71738</v>
+        <v>85946.94</v>
       </c>
       <c r="D4" t="n">
-        <v>2426</v>
+        <v>2756</v>
       </c>
       <c r="E4" t="n">
-        <v>70133</v>
+        <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>1605</v>
+        <v>85917.94</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>997436</v>
+        <v>1229826</v>
       </c>
       <c r="D5" t="n">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="E5" t="n">
-        <v>133900</v>
+        <v>85812</v>
       </c>
       <c r="F5" t="n">
-        <v>863536</v>
+        <v>1144014</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>761820</v>
+        <v>907204</v>
       </c>
       <c r="D6" t="n">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="E6" t="n">
         <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>739222</v>
+        <v>884606</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>215616</v>
+        <v>302622</v>
       </c>
       <c r="D7" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E7" t="n">
-        <v>111302</v>
+        <v>63214</v>
       </c>
       <c r="F7" t="n">
-        <v>104314</v>
+        <v>239408</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1533282.74</v>
+        <v>1574530.64</v>
       </c>
       <c r="D8" t="n">
-        <v>2071</v>
+        <v>2160</v>
       </c>
       <c r="E8" t="n">
-        <v>12251.53</v>
+        <v>8284.469999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1521031.21</v>
+        <v>1566246.17</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>946289.28</v>
+        <v>979701.9399999999</v>
       </c>
       <c r="D9" t="n">
-        <v>877</v>
+        <v>947</v>
       </c>
       <c r="E9" t="n">
-        <v>2945.64</v>
+        <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>943343.64</v>
+        <v>977901.9399999999</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>586993.46</v>
+        <v>594828.7</v>
       </c>
       <c r="D10" t="n">
-        <v>1194</v>
+        <v>1213</v>
       </c>
       <c r="E10" t="n">
-        <v>9305.889999999999</v>
+        <v>6484.47</v>
       </c>
       <c r="F10" t="n">
-        <v>577687.5699999999</v>
+        <v>588344.23</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>474000</v>
+        <v>523600</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E11" t="n">
-        <v>240000</v>
+        <v>120000</v>
       </c>
       <c r="F11" t="n">
-        <v>234000</v>
+        <v>403600</v>
       </c>
     </row>
     <row r="12">
@@ -709,10 +709,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>15200</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>85588</v>
+        <v>100788</v>
       </c>
     </row>
     <row r="13">
@@ -733,10 +733,10 @@
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>45480</v>
+        <v>33600</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>11880</v>
       </c>
     </row>
     <row r="14">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57887.24</v>
+        <v>59885.24</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E15" t="n">
-        <v>8792</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>49095.24</v>
+        <v>59885.24</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1408205.43</v>
+        <v>1445048.13</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1404635.43；课程线 1750.0；菌群线 1000.0；其他 820.0</t>
+          <t>医疗线 1441478.13；课程线 1750.0；菌群线 1000.0；其他 820.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>151423</v>
+        <v>163557</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>90.3</v>
+        <v>90</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 136782.0；课程线 14141.0；医疗线 500.0</t>
+          <t>咨询线 147180.0；课程线 15877.0；医疗线 500.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68612.10000000001</v>
+        <v>68631.10000000001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 59778.0；课程线 6609.0；医疗线 2225.1</t>
+          <t>咨询线 59778.0；课程线 6628.0；医疗线 2225.1</t>
         </is>
       </c>
     </row>
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>289392.09</v>
+        <v>307545.09</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>菌群线</t>
+          <t>咨询线</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.1</v>
+        <v>41.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>菌群线 116000.0；咨询线 110394.0；课程线 59564.0；工作坊 1980.0；其他 850.0；医疗线 604.09</t>
+          <t>咨询线 127190.0；菌群线 116000.0；课程线 59863.0；工作坊 1980.0；其他 1849.0；医疗线 663.09</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>204881.25</v>
+        <v>236403.15</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>53.9</v>
+        <v>59.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 110474.0；菌群线 46600.0；医疗线 23775.01；课程线 13267.0；考证 10000.0；其他 765.24</t>
+          <t>咨询线 141270.0；菌群线 46600.0；医疗线 24452.91；课程线 13315.0；考证 10000.0；其他 765.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51688</v>
+        <v>62385</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61.1</v>
+        <v>67.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 31592.0；课程线 19857.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
+          <t>咨询线 41990.0；课程线 20156.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>284821.68</v>
+        <v>286587.04</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>54.8</v>
+        <v>54.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 156178.0；医疗线 59449.68；其他 44066.0；菌群线 24800.0；课程线 328.0</t>
+          <t>咨询线 157374.0；医疗线 60019.04；其他 44066.0；菌群线 24800.0；课程线 328.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>210408</v>
+        <v>235223</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>51.6</v>
+        <v>56.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 108584.0；菌群线 45600.0；考证 36000.0；医疗线 10725.0；课程线 8299.0；其他 1200.0</t>
+          <t>咨询线 133380.0；菌群线 45600.0；考证 36000.0；医疗线 10725.0；课程线 8318.0；其他 1200.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134268.9</v>
+        <v>136593.95</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 68984.0；考证 39588.0；医疗线 19077.9；课程线 6619.0</t>
+          <t>咨询线 69980.0；考证 39588.0；医疗线 20406.95；课程线 6619.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64332</v>
+        <v>84332</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 59178.0；工作坊 3960.0；其他 1194.0</t>
+          <t>咨询线 79178.0；工作坊 3960.0；其他 1194.0</t>
         </is>
       </c>
     </row>
@@ -1128,11 +1128,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>59400</v>
+        <v>60120</v>
       </c>
     </row>
     <row r="3">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>56280</v>
+        <v>59400</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53520</v>
+        <v>56280</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>39840</v>
+        <v>44700</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>39720</v>
+        <v>43080</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>83198</v>
+        <v>83596</v>
       </c>
     </row>
     <row r="8">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50592</v>
+        <v>63194</v>
       </c>
     </row>
     <row r="9">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>42520</v>
+        <v>62592</v>
       </c>
     </row>
     <row r="10">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>40186</v>
+        <v>56982</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>林非凡</t>
+          <t>姜人荷</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>39194</v>
+        <v>52816</v>
       </c>
     </row>
     <row r="12">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>320413.65</v>
+        <v>337432.15</v>
       </c>
     </row>
     <row r="13">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>184929</v>
+        <v>186166</v>
       </c>
     </row>
     <row r="15">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>144388.1</v>
+        <v>149570.3</v>
       </c>
     </row>
     <row r="17">
@@ -1434,11 +1434,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>49600</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="20">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1864,26 +1864,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>858325</v>
+        <v>945493.9399999999</v>
       </c>
       <c r="C2" t="n">
-        <v>481656.86</v>
+        <v>486680.76</v>
       </c>
       <c r="D2" t="n">
-        <v>77320</v>
+        <v>83539</v>
       </c>
       <c r="E2" t="n">
-        <v>9.01</v>
+        <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>404336.86</v>
+        <v>403141.76</v>
       </c>
       <c r="G2" t="n">
-        <v>47.11</v>
+        <v>42.64</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 158400.0；青少年同行者计划领航营 112796.0；青少年同行者计划-护航营 32974.16</t>
+          <t>少年说陪伴计划 158400.0；青少年同行者计划领航营 112796.0；青少年同行者计划-护航营 34966.16</t>
         </is>
       </c>
     </row>
@@ -1894,26 +1894,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>997436</v>
+        <v>1229826</v>
       </c>
       <c r="C3" t="n">
-        <v>504001.38</v>
+        <v>579999.38</v>
       </c>
       <c r="D3" t="n">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="F3" t="n">
-        <v>503001.38</v>
+        <v>572399.38</v>
       </c>
       <c r="G3" t="n">
-        <v>50.43</v>
+        <v>46.54</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 309033.38；精神心理 93598.0；电商咨询 20000.0</t>
+          <t>儿童青少年 358033.38；精神心理 93996.0；青少年-资深咨询 30000.0</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1533282.74</v>
+        <v>1574530.64</v>
       </c>
       <c r="C4" t="n">
-        <v>4649</v>
+        <v>28799</v>
       </c>
       <c r="D4" t="n">
         <v>49</v>
@@ -1936,14 +1936,14 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4600</v>
+        <v>28750</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3</v>
+        <v>1.83</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50分钟问诊（诸秉根） -线下 3600.0；医师50分钟问诊-线上 1000.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
+          <t>儿童多动精灵专注站 PEERS 专项（16 节课） 16800.0；多动精灵专注站（PEERS） 7350.0；50分钟问诊（诸秉根） -线下 3600.0</t>
         </is>
       </c>
     </row>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>474000</v>
+        <v>523600</v>
       </c>
       <c r="C5" t="n">
-        <v>116000</v>
+        <v>140800</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1966,14 +1966,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>116000</v>
+        <v>140800</v>
       </c>
       <c r="G5" t="n">
-        <v>24.47</v>
+        <v>26.89</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程） 45600.0；肠道菌群移植 24800.0；肠道菌群移植（活动专享） 24800.0</t>
+          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群移植 24800.0；肠道菌群移植（活动专享） 24800.0</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
         <v>100788</v>
       </c>
       <c r="C6" t="n">
-        <v>196919.9</v>
+        <v>156919.9</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -1996,14 +1996,14 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>194902</v>
+        <v>154902</v>
       </c>
       <c r="G6" t="n">
-        <v>193.38</v>
+        <v>153.69</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派-高阶培训课程 119200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 64193.0；心理咨询基本功实战营 4880.0</t>
+          <t>心灯计划-实战派-高阶培训课程 79200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 64193.0；心理咨询基本功实战营 4880.0</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
         <v>45480</v>
       </c>
       <c r="C7" t="n">
-        <v>290266.67</v>
+        <v>291066.67</v>
       </c>
       <c r="D7" t="n">
         <v>53000</v>
@@ -2026,10 +2026,10 @@
         <v>116.53</v>
       </c>
       <c r="F7" t="n">
-        <v>237266.67</v>
+        <v>238066.67</v>
       </c>
       <c r="G7" t="n">
-        <v>521.6900000000001</v>
+        <v>523.45</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2070,26 +2070,26 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57887.24</v>
+        <v>59885.24</v>
       </c>
       <c r="C9" t="n">
-        <v>1199</v>
+        <v>17999</v>
       </c>
       <c r="D9" t="n">
         <v>1199</v>
       </c>
       <c r="E9" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>16800</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>28.05</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[自我成长/疗愈] 完形心理认知课，增加智慧。 999.0；100天疗愈  第1周基础课 心理成长课 200.0</t>
+          <t>未来商战（社交力营） 16800.0；[自我成长/疗愈] 完形心理认知课，增加智慧。 999.0；100天疗愈  第1周基础课 心理成长课 200.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>945493.9399999999</v>
+        <v>1152601.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2918</v>
+        <v>3508</v>
       </c>
       <c r="E2" t="n">
-        <v>92429</v>
+        <v>99369</v>
       </c>
       <c r="F2" t="n">
-        <v>853064.9399999999</v>
+        <v>1053232.5</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>859547</v>
+        <v>1046047</v>
       </c>
       <c r="D3" t="n">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="E3" t="n">
-        <v>92400</v>
+        <v>99340</v>
       </c>
       <c r="F3" t="n">
-        <v>767147</v>
+        <v>946707</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85946.94</v>
+        <v>106554.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2756</v>
+        <v>3308</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>85917.94</v>
+        <v>106525.5</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1229826</v>
+        <v>1499560</v>
       </c>
       <c r="D5" t="n">
-        <v>272</v>
+        <v>338</v>
       </c>
       <c r="E5" t="n">
-        <v>85812</v>
+        <v>86210</v>
       </c>
       <c r="F5" t="n">
-        <v>1144014</v>
+        <v>1413350</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>907204</v>
+        <v>1099480</v>
       </c>
       <c r="D6" t="n">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="E6" t="n">
         <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>884606</v>
+        <v>1076882</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>302622</v>
+        <v>380080</v>
       </c>
       <c r="D7" t="n">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="E7" t="n">
-        <v>63214</v>
+        <v>63612</v>
       </c>
       <c r="F7" t="n">
-        <v>239408</v>
+        <v>316468</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1574530.64</v>
+        <v>1841363.51</v>
       </c>
       <c r="D8" t="n">
-        <v>2160</v>
+        <v>2367</v>
       </c>
       <c r="E8" t="n">
-        <v>8284.469999999999</v>
+        <v>8784.469999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1566246.17</v>
+        <v>1832579.04</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>979701.9399999999</v>
+        <v>1083856.96</v>
       </c>
       <c r="D9" t="n">
-        <v>947</v>
+        <v>1022</v>
       </c>
       <c r="E9" t="n">
         <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>977901.9399999999</v>
+        <v>1082056.96</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>594828.7</v>
+        <v>757506.55</v>
       </c>
       <c r="D10" t="n">
-        <v>1213</v>
+        <v>1345</v>
       </c>
       <c r="E10" t="n">
-        <v>6484.47</v>
+        <v>6984.47</v>
       </c>
       <c r="F10" t="n">
-        <v>588344.23</v>
+        <v>750522.08</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>523600</v>
+        <v>529608.4</v>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
-        <v>120000</v>
+        <v>129202</v>
       </c>
       <c r="F11" t="n">
-        <v>403600</v>
+        <v>400406.4</v>
       </c>
     </row>
     <row r="12">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5940</v>
+        <v>8318</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>5940</v>
+        <v>8318</v>
       </c>
     </row>
     <row r="15">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>59885.24</v>
+        <v>64354.24</v>
       </c>
       <c r="D15" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>59885.24</v>
+        <v>64354.24</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1445048.13</v>
+        <v>1670580.35</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>99.8</v>
+        <v>100.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1441478.13；课程线 1750.0；菌群线 1000.0；其他 820.0</t>
+          <t>医疗线 1685951.95；其他 2672.0；课程线 1750.0；菌群线 -19793.6</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>163557</v>
+        <v>180298</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>90</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 147180.0；课程线 15877.0；医疗线 500.0</t>
+          <t>咨询线 158772.0；课程线 21026.0；医疗线 500.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68631.10000000001</v>
+        <v>85848.10000000001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>87.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 59778.0；课程线 6628.0；医疗线 2225.1</t>
+          <t>咨询线 60176.0；医疗线 19025.1；课程线 6647.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>307545.09</v>
+        <v>354168.07</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>41.4</v>
+        <v>46.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 127190.0；菌群线 116000.0；课程线 59863.0；工作坊 1980.0；其他 1849.0；医疗线 663.09</t>
+          <t>咨询线 163986.0；菌群线 116000.0；课程线 66482.0；工作坊 4358.0；其他 1849.0；医疗线 1493.07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>236403.15</v>
+        <v>243472.03</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59.8</v>
+        <v>60.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 141270.0；菌群线 46600.0；医疗线 24452.91；课程线 13315.0；考证 10000.0；其他 765.24</t>
+          <t>咨询线 148266.0；菌群线 46600.0；医疗线 24487.79；课程线 13353.0；考证 10000.0；其他 765.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62385</v>
+        <v>86403</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>67.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 41990.0；课程线 20156.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
+          <t>咨询线 65970.0；课程线 20194.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>286587.04</v>
+        <v>332981.04</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>54.9</v>
+        <v>55.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 157374.0；医疗线 60019.04；其他 44066.0；菌群线 24800.0；课程线 328.0</t>
+          <t>咨询线 186168.0；医疗线 60019.04；其他 44066.0；菌群线 42400.0；课程线 328.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>235223</v>
+        <v>317336.3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56.7</v>
+        <v>65.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 133380.0；菌群线 45600.0；考证 36000.0；医疗线 10725.0；课程线 8318.0；其他 1200.0</t>
+          <t>咨询线 208678.0；菌群线 45600.0；考证 36000.0；课程线 13257.0；医疗线 12001.3；其他 1800.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>136593.95</v>
+        <v>167249.55</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.2</v>
+        <v>60</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 69980.0；考证 39588.0；医疗线 20406.95；课程线 6619.0</t>
+          <t>咨询线 100378.0；考证 39588.0；医疗线 20645.55；课程线 6638.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23140</v>
+        <v>42997</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>93.3</v>
+        <v>96.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 21592.0；课程线 1548.0；其他 0.0</t>
+          <t>咨询线 41392.0；课程线 1605.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>84332</v>
+        <v>93528</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>93.90000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 79178.0；工作坊 3960.0；其他 1194.0</t>
+          <t>咨询线 88374.0；工作坊 3960.0；其他 1194.0</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>60120</v>
+        <v>80040</v>
       </c>
     </row>
     <row r="3">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>59400</v>
+        <v>67720</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>56280</v>
+        <v>59760</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44700</v>
+        <v>59400</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43080</v>
+        <v>56280</v>
       </c>
     </row>
     <row r="7">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>63194</v>
+        <v>79194</v>
       </c>
     </row>
     <row r="9">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62592</v>
+        <v>73380</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>56982</v>
+        <v>66594</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>姜人荷</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>52816</v>
+        <v>62592</v>
       </c>
     </row>
     <row r="12">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>337432.15</v>
+        <v>363270.97</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>241661.04</v>
+        <v>274837.04</v>
       </c>
     </row>
     <row r="14">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>186166</v>
+        <v>220015</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>163372</v>
+        <v>208871.3</v>
       </c>
     </row>
     <row r="16">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>149570.3</v>
+        <v>196777.64</v>
       </c>
     </row>
     <row r="17">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1980</v>
+        <v>4358</v>
       </c>
     </row>
     <row r="33">
@@ -1758,11 +1758,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>陈茜</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1200</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="38">
@@ -1776,11 +1776,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈茜</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>850</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="39">
@@ -1794,11 +1794,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>796</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -1864,22 +1864,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>945493.9399999999</v>
+        <v>1152601.5</v>
       </c>
       <c r="C2" t="n">
-        <v>486680.76</v>
+        <v>495823.76</v>
       </c>
       <c r="D2" t="n">
-        <v>83539</v>
+        <v>86522</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>7.51</v>
       </c>
       <c r="F2" t="n">
-        <v>403141.76</v>
+        <v>409301.76</v>
       </c>
       <c r="G2" t="n">
-        <v>42.64</v>
+        <v>35.51</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1894,26 +1894,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1229826</v>
+        <v>1499560</v>
       </c>
       <c r="C3" t="n">
-        <v>579999.38</v>
+        <v>677032.75</v>
       </c>
       <c r="D3" t="n">
         <v>7600</v>
       </c>
       <c r="E3" t="n">
-        <v>0.62</v>
+        <v>0.51</v>
       </c>
       <c r="F3" t="n">
-        <v>572399.38</v>
+        <v>669432.75</v>
       </c>
       <c r="G3" t="n">
-        <v>46.54</v>
+        <v>44.64</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 358033.38；精神心理 93996.0；青少年-资深咨询 30000.0</t>
+          <t>儿童青少年 388866.75；精神心理 115496.0；电商咨询 55700.0</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1574530.64</v>
+        <v>1841363.51</v>
       </c>
       <c r="C4" t="n">
         <v>28799</v>
@@ -1939,7 +1939,7 @@
         <v>28750</v>
       </c>
       <c r="G4" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>523600</v>
+        <v>529608.4</v>
       </c>
       <c r="C5" t="n">
         <v>140800</v>
@@ -1969,7 +1969,7 @@
         <v>140800</v>
       </c>
       <c r="G5" t="n">
-        <v>26.89</v>
+        <v>26.59</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45480</v>
       </c>
       <c r="C7" t="n">
-        <v>291066.67</v>
+        <v>299246.67</v>
       </c>
       <c r="D7" t="n">
         <v>53000</v>
@@ -2026,14 +2026,14 @@
         <v>116.53</v>
       </c>
       <c r="F7" t="n">
-        <v>238066.67</v>
+        <v>246246.67</v>
       </c>
       <c r="G7" t="n">
-        <v>523.45</v>
+        <v>541.4400000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 221266.67；青少年【未来之翼】身心节律复能7日营 33600.0；青少年成长基地3月营（金盏基地） 31200.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 221266.67；青少年成长基地3月营（金盏基地） 39380.0；青少年【未来之翼】身心节律复能7日营 33600.0</t>
         </is>
       </c>
     </row>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5940</v>
+        <v>8318</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -2056,12 +2056,16 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>23.8</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>【廖文婷】萨提亚家庭系统工作坊 1980.0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2070,7 +2074,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59885.24</v>
+        <v>64354.24</v>
       </c>
       <c r="C9" t="n">
         <v>17999</v>
@@ -2079,13 +2083,13 @@
         <v>1199</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="F9" t="n">
         <v>16800</v>
       </c>
       <c r="G9" t="n">
-        <v>28.05</v>
+        <v>26.11</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1152601.5</v>
+        <v>1189368.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3508</v>
+        <v>3600</v>
       </c>
       <c r="E2" t="n">
-        <v>99369</v>
+        <v>105969</v>
       </c>
       <c r="F2" t="n">
-        <v>1053232.5</v>
+        <v>1083399.5</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1046047</v>
+        <v>1079167</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E3" t="n">
-        <v>99340</v>
+        <v>105940</v>
       </c>
       <c r="F3" t="n">
-        <v>946707</v>
+        <v>973227</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>106554.5</v>
+        <v>110201.5</v>
       </c>
       <c r="D4" t="n">
-        <v>3308</v>
+        <v>3393</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>106525.5</v>
+        <v>110172.5</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1499560</v>
+        <v>1620340</v>
       </c>
       <c r="D5" t="n">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="E5" t="n">
         <v>86210</v>
       </c>
       <c r="F5" t="n">
-        <v>1413350</v>
+        <v>1534130</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1099480</v>
+        <v>1219168</v>
       </c>
       <c r="D6" t="n">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="E6" t="n">
         <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>1076882</v>
+        <v>1196570</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>380080</v>
+        <v>381172</v>
       </c>
       <c r="D7" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E7" t="n">
         <v>63612</v>
       </c>
       <c r="F7" t="n">
-        <v>316468</v>
+        <v>317560</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1841363.51</v>
+        <v>1970376.27</v>
       </c>
       <c r="D8" t="n">
-        <v>2367</v>
+        <v>2531</v>
       </c>
       <c r="E8" t="n">
         <v>8784.469999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1832579.04</v>
+        <v>1961591.8</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1083856.96</v>
+        <v>1145798.69</v>
       </c>
       <c r="D9" t="n">
-        <v>1022</v>
+        <v>1111</v>
       </c>
       <c r="E9" t="n">
         <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>1082056.96</v>
+        <v>1143998.69</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>757506.55</v>
+        <v>824577.58</v>
       </c>
       <c r="D10" t="n">
-        <v>1345</v>
+        <v>1420</v>
       </c>
       <c r="E10" t="n">
         <v>6984.47</v>
       </c>
       <c r="F10" t="n">
-        <v>750522.08</v>
+        <v>817593.11</v>
       </c>
     </row>
     <row r="11">
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>45480</v>
+        <v>47460</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>33600</v>
       </c>
       <c r="F13" t="n">
-        <v>11880</v>
+        <v>13860</v>
       </c>
     </row>
     <row r="14">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8318</v>
+        <v>11880</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>8318</v>
+        <v>11880</v>
       </c>
     </row>
     <row r="15">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>64354.24</v>
+        <v>68932.24000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>64354.24</v>
+        <v>68932.24000000001</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1670580.35</v>
+        <v>1789749.67</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1685951.95；其他 2672.0；课程线 1750.0；菌群线 -19793.6</t>
+          <t>医疗线 1805121.27；其他 2672.0；课程线 1750.0；菌群线 -19793.6</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>180298</v>
+        <v>217324</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>88.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 158772.0；课程线 21026.0；医疗线 500.0</t>
+          <t>咨询线 189170.0；课程线 27654.0；医疗线 500.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85848.10000000001</v>
+        <v>86067.10000000001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>70.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 60176.0；医疗线 19025.1；课程线 6647.0</t>
+          <t>咨询线 60176.0；医疗线 19225.1；课程线 6666.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>354168.07</v>
+        <v>375329.07</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>46.3</v>
+        <v>46.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 163986.0；菌群线 116000.0；课程线 66482.0；工作坊 4358.0；其他 1849.0；医疗线 1493.07</t>
+          <t>咨询线 174986.0；菌群线 116000.0；课程线 66501.0；工作坊 7920.0；其他 5849.0；医疗线 4073.07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>243472.03</v>
+        <v>274087.03</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>60.9</v>
+        <v>65.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 148266.0；菌群线 46600.0；医疗线 24487.79；课程线 13353.0；考证 10000.0；其他 765.24</t>
+          <t>咨询线 178862.0；菌群线 46600.0；医疗线 24487.79；课程线 13372.0；考证 10000.0；其他 765.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>86403</v>
+        <v>107597</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>76.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 65970.0；课程线 20194.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
+          <t>咨询线 87164.0；课程线 20194.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>317336.3</v>
+        <v>334386.64</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 208678.0；菌群线 45600.0；考证 36000.0；课程线 13257.0；医疗线 12001.3；其他 1800.0</t>
+          <t>咨询线 224478.0；菌群线 45600.0；考证 36000.0；课程线 13257.0；医疗线 13251.64；其他 1800.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>167249.55</v>
+        <v>183571.65</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 100378.0；考证 39588.0；医疗线 20645.55；课程线 6638.0</t>
+          <t>咨询线 110378.0；考证 39588.0；医疗线 26389.65；课程线 6638.0；其他 578.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42997</v>
+        <v>43395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 41392.0；课程线 1605.0；其他 0.0</t>
+          <t>咨询线 41790.0；课程线 1605.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>93528</v>
+        <v>96204</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>94.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 88374.0；工作坊 3960.0；其他 1194.0</t>
+          <t>咨询线 89370.0；工作坊 3960.0；课程线 1680.0；其他 1194.0</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>56280</v>
+        <v>58020</v>
       </c>
     </row>
     <row r="7">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>林非凡</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>79194</v>
+        <v>83380</v>
       </c>
     </row>
     <row r="9">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>73380</v>
+        <v>79990</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>66594</v>
+        <v>79194</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62592</v>
+        <v>66594</v>
       </c>
     </row>
     <row r="12">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>363270.97</v>
+        <v>383884.97</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>274837.04</v>
+        <v>286122.04</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>220015</v>
+        <v>227203.8</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>208871.3</v>
+        <v>224576</v>
       </c>
     </row>
     <row r="16">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>196777.64</v>
+        <v>221318.46</v>
       </c>
     </row>
     <row r="17">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>关万辉</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>何媛媛</t>
+          <t>关万辉</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>何媛媛</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4358</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="33">
@@ -1714,19 +1714,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>36796</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="36">
@@ -1736,15 +1736,15 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>沈悦</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5398</v>
+        <v>36796</v>
       </c>
     </row>
     <row r="37">
@@ -1754,15 +1754,15 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2272</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="38">
@@ -1772,15 +1772,15 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>陈茜</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1200</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="39">
@@ -1790,15 +1790,33 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>陈洁</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
         <v>5</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>岳伟伟</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>850</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>陈茜</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
@@ -1864,22 +1882,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1152601.5</v>
+        <v>1189368.5</v>
       </c>
       <c r="C2" t="n">
-        <v>495823.76</v>
+        <v>499061.76</v>
       </c>
       <c r="D2" t="n">
-        <v>86522</v>
+        <v>89798</v>
       </c>
       <c r="E2" t="n">
-        <v>7.51</v>
+        <v>7.55</v>
       </c>
       <c r="F2" t="n">
-        <v>409301.76</v>
+        <v>409263.76</v>
       </c>
       <c r="G2" t="n">
-        <v>35.51</v>
+        <v>34.41</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1894,7 +1912,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1499560</v>
+        <v>1620340</v>
       </c>
       <c r="C3" t="n">
         <v>677032.75</v>
@@ -1903,13 +1921,13 @@
         <v>7600</v>
       </c>
       <c r="E3" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="F3" t="n">
         <v>669432.75</v>
       </c>
       <c r="G3" t="n">
-        <v>44.64</v>
+        <v>41.31</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1924,7 +1942,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1841363.51</v>
+        <v>1970376.27</v>
       </c>
       <c r="C4" t="n">
         <v>28799</v>
@@ -1939,7 +1957,7 @@
         <v>28750</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2014,7 +2032,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45480</v>
+        <v>47460</v>
       </c>
       <c r="C7" t="n">
         <v>299246.67</v>
@@ -2023,13 +2041,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>116.53</v>
+        <v>111.67</v>
       </c>
       <c r="F7" t="n">
         <v>246246.67</v>
       </c>
       <c r="G7" t="n">
-        <v>541.4400000000001</v>
+        <v>518.85</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2044,7 +2062,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8318</v>
+        <v>11880</v>
       </c>
       <c r="C8" t="n">
         <v>1980</v>
@@ -2059,7 +2077,7 @@
         <v>1980</v>
       </c>
       <c r="G8" t="n">
-        <v>23.8</v>
+        <v>16.67</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2074,7 +2092,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64354.24</v>
+        <v>68932.24000000001</v>
       </c>
       <c r="C9" t="n">
         <v>17999</v>
@@ -2083,13 +2101,13 @@
         <v>1199</v>
       </c>
       <c r="E9" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="F9" t="n">
         <v>16800</v>
       </c>
       <c r="G9" t="n">
-        <v>26.11</v>
+        <v>24.37</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1189368.5</v>
+        <v>1354650.52</v>
       </c>
       <c r="D2" t="n">
-        <v>3600</v>
+        <v>3808</v>
       </c>
       <c r="E2" t="n">
-        <v>105969</v>
+        <v>119169</v>
       </c>
       <c r="F2" t="n">
-        <v>1083399.5</v>
+        <v>1235481.52</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1079167</v>
+        <v>1238526</v>
       </c>
       <c r="D3" t="n">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="E3" t="n">
-        <v>105940</v>
+        <v>119140</v>
       </c>
       <c r="F3" t="n">
-        <v>973227</v>
+        <v>1119386</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>110201.5</v>
+        <v>116124.52</v>
       </c>
       <c r="D4" t="n">
-        <v>3393</v>
+        <v>3570</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>110172.5</v>
+        <v>116095.52</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1620340</v>
+        <v>1777488</v>
       </c>
       <c r="D5" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="E5" t="n">
         <v>86210</v>
       </c>
       <c r="F5" t="n">
-        <v>1534130</v>
+        <v>1691278</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1219168</v>
+        <v>1316136</v>
       </c>
       <c r="D6" t="n">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="E6" t="n">
         <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>1196570</v>
+        <v>1293538</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>381172</v>
+        <v>441352</v>
       </c>
       <c r="D7" t="n">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="E7" t="n">
         <v>63612</v>
       </c>
       <c r="F7" t="n">
-        <v>317560</v>
+        <v>377740</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1970376.27</v>
+        <v>2023212.69</v>
       </c>
       <c r="D8" t="n">
-        <v>2531</v>
+        <v>2558</v>
       </c>
       <c r="E8" t="n">
         <v>8784.469999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1961591.8</v>
+        <v>2014428.22</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1145798.69</v>
+        <v>1198345.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1111</v>
+        <v>1130</v>
       </c>
       <c r="E9" t="n">
         <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>1143998.69</v>
+        <v>1196545.9</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>824577.58</v>
+        <v>824866.79</v>
       </c>
       <c r="D10" t="n">
-        <v>1420</v>
+        <v>1428</v>
       </c>
       <c r="E10" t="n">
         <v>6984.47</v>
       </c>
       <c r="F10" t="n">
-        <v>817593.11</v>
+        <v>817882.3199999999</v>
       </c>
     </row>
     <row r="11">
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47460</v>
+        <v>140820</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>33600</v>
+        <v>93200</v>
       </c>
       <c r="F13" t="n">
-        <v>13860</v>
+        <v>47620</v>
       </c>
     </row>
     <row r="14">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11880</v>
+        <v>13860</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>11880</v>
+        <v>13860</v>
       </c>
     </row>
     <row r="15">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>68932.24000000001</v>
+        <v>128129.24</v>
       </c>
       <c r="D15" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>68932.24000000001</v>
+        <v>128129.24</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1789749.67</v>
+        <v>1824198.67</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100.9</v>
+        <v>100.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1805121.27；其他 2672.0；课程线 1750.0；菌群线 -19793.6</t>
+          <t>医疗线 1839570.27；其他 2672.0；课程线 1750.0；菌群线 -19793.6</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>217324</v>
+        <v>235819</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>87</v>
+        <v>80.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 189170.0；课程线 27654.0；医疗线 500.0</t>
+          <t>咨询线 189170.0；课程线 29349.0；医疗线 17300.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>86067.10000000001</v>
+        <v>86077.45</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 60176.0；医疗线 19225.1；课程线 6666.0</t>
+          <t>咨询线 60176.0；医疗线 19235.45；课程线 6666.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>375329.07</v>
+        <v>390447.69</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>46.6</v>
+        <v>48</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 174986.0；菌群线 116000.0；课程线 66501.0；工作坊 7920.0；其他 5849.0；医疗线 4073.07</t>
+          <t>咨询线 187578.0；菌群线 116000.0；课程线 66800.0；工作坊 9900.0；其他 5849.0；医疗线 4320.69</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>274087.03</v>
+        <v>294868.03</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>65.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 178862.0；菌群线 46600.0；医疗线 24487.79；课程线 13372.0；考证 10000.0；其他 765.24</t>
+          <t>咨询线 199462.0；菌群线 46600.0；医疗线 24487.79；课程线 13353.0；考证 10000.0；其他 965.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>107597</v>
+        <v>129587</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81</v>
+        <v>84.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 87164.0；课程线 20194.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
+          <t>咨询线 109154.0；课程线 20194.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>332981.04</v>
+        <v>371944.28</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55.9</v>
+        <v>50.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 186168.0；医疗线 60019.04；其他 44066.0；菌群线 42400.0；课程线 328.0</t>
+          <t>咨询线 189062.0；其他 80066.0；医疗线 60088.28；菌群线 42400.0；课程线 328.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>334386.64</v>
+        <v>365526.87</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>67.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 224478.0；菌群线 45600.0；考证 36000.0；课程线 13257.0；医疗线 13251.64；其他 1800.0</t>
+          <t>咨询线 255478.0；菌群线 45600.0；考证 36000.0；医疗线 13391.87；课程线 13257.0；其他 1800.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>183571.65</v>
+        <v>193969.65</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>60.1</v>
+        <v>62.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 110378.0；考证 39588.0；医疗线 26389.65；课程线 6638.0；其他 578.0</t>
+          <t>咨询线 120776.0；考证 39588.0；医疗线 26389.65；课程线 6638.0；其他 578.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43395</v>
+        <v>49413</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>96.3</v>
+        <v>94.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 41790.0；课程线 1605.0；其他 0.0</t>
+          <t>咨询线 46770.0；课程线 1643.0；医疗线 1000.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>96204</v>
+        <v>127000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>92.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 89370.0；工作坊 3960.0；课程线 1680.0；其他 1194.0</t>
+          <t>咨询线 120166.0；工作坊 3960.0；课程线 1680.0；其他 1194.0</t>
         </is>
       </c>
     </row>
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>59760</v>
+        <v>64620</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>59400</v>
+        <v>59760</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>58020</v>
+        <v>59400</v>
       </c>
     </row>
     <row r="7">
@@ -1218,11 +1218,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>83596</v>
+        <v>94972</v>
       </c>
     </row>
     <row r="8">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>83380</v>
+        <v>89990</v>
       </c>
     </row>
     <row r="9">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79990</v>
+        <v>83596</v>
       </c>
     </row>
     <row r="10">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>66594</v>
+        <v>66782</v>
       </c>
     </row>
     <row r="12">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>383884.97</v>
+        <v>386278.97</v>
       </c>
     </row>
     <row r="13">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>227203.8</v>
+        <v>237295.8</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>224576</v>
+        <v>231318.46</v>
       </c>
     </row>
     <row r="16">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>221318.46</v>
+        <v>226539</v>
       </c>
     </row>
     <row r="17">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16800</v>
+        <v>76400</v>
       </c>
     </row>
     <row r="28">
@@ -1596,11 +1596,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16800</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="29">
@@ -1614,11 +1614,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1980</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="30">
@@ -1632,11 +1632,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>关万辉</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="31">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="32">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5940</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="33">
@@ -1740,11 +1740,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>36796</v>
+        <v>41398</v>
       </c>
     </row>
     <row r="37">
@@ -1758,11 +1758,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>沈悦</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5398</v>
+        <v>36796</v>
       </c>
     </row>
     <row r="38">
@@ -1776,11 +1776,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4850</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="39">
@@ -1794,11 +1794,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2272</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="40">
@@ -1812,11 +1812,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>陈茜</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1200</v>
+        <v>2272</v>
       </c>
     </row>
   </sheetData>
@@ -1882,26 +1882,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1189368.5</v>
+        <v>1354650.52</v>
       </c>
       <c r="C2" t="n">
-        <v>499061.76</v>
+        <v>552232.1800000001</v>
       </c>
       <c r="D2" t="n">
-        <v>89798</v>
+        <v>100988.02</v>
       </c>
       <c r="E2" t="n">
-        <v>7.55</v>
+        <v>7.45</v>
       </c>
       <c r="F2" t="n">
-        <v>409263.76</v>
+        <v>451244.16</v>
       </c>
       <c r="G2" t="n">
-        <v>34.41</v>
+        <v>33.31</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 158400.0；青少年同行者计划领航营 112796.0；青少年同行者计划-护航营 34966.16</t>
+          <t>少年说陪伴计划 184800.0；青少年同行者计划领航营 135859.4；青少年同行者计划 35690.0</t>
         </is>
       </c>
     </row>
@@ -1912,26 +1912,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1620340</v>
+        <v>1777488</v>
       </c>
       <c r="C3" t="n">
-        <v>677032.75</v>
+        <v>783252.99</v>
       </c>
       <c r="D3" t="n">
-        <v>7600</v>
+        <v>45598</v>
       </c>
       <c r="E3" t="n">
-        <v>0.47</v>
+        <v>2.57</v>
       </c>
       <c r="F3" t="n">
-        <v>669432.75</v>
+        <v>737654.99</v>
       </c>
       <c r="G3" t="n">
-        <v>41.31</v>
+        <v>41.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 388866.75；精神心理 115496.0；电商咨询 55700.0</t>
+          <t>儿童青少年 434088.99；精神心理 126896.0；电商咨询 59700.0</t>
         </is>
       </c>
     </row>
@@ -1942,22 +1942,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1970376.27</v>
+        <v>2023212.69</v>
       </c>
       <c r="C4" t="n">
-        <v>28799</v>
+        <v>28999</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>249</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F4" t="n">
         <v>28750</v>
       </c>
       <c r="G4" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>529608.4</v>
       </c>
       <c r="C5" t="n">
-        <v>140800</v>
+        <v>190400</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1984,14 +1984,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>140800</v>
+        <v>190400</v>
       </c>
       <c r="G5" t="n">
-        <v>26.59</v>
+        <v>35.95</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群移植 24800.0；肠道菌群移植（活动专享） 24800.0</t>
+          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群移植 49600.0；肠道菌群移植（活动专享） 49600.0</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47460</v>
+        <v>140820</v>
       </c>
       <c r="C7" t="n">
         <v>299246.67</v>
@@ -2041,13 +2041,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>111.67</v>
+        <v>37.64</v>
       </c>
       <c r="F7" t="n">
         <v>246246.67</v>
       </c>
       <c r="G7" t="n">
-        <v>518.85</v>
+        <v>174.87</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11880</v>
+        <v>13860</v>
       </c>
       <c r="C8" t="n">
         <v>1980</v>
@@ -2077,7 +2077,7 @@
         <v>1980</v>
       </c>
       <c r="G8" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2092,26 +2092,26 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68932.24000000001</v>
+        <v>128129.24</v>
       </c>
       <c r="C9" t="n">
-        <v>17999</v>
+        <v>18998</v>
       </c>
       <c r="D9" t="n">
-        <v>1199</v>
+        <v>2198</v>
       </c>
       <c r="E9" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="F9" t="n">
         <v>16800</v>
       </c>
       <c r="G9" t="n">
-        <v>24.37</v>
+        <v>13.11</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>未来商战（社交力营） 16800.0；[自我成长/疗愈] 完形心理认知课，增加智慧。 999.0；100天疗愈  第1周基础课 心理成长课 200.0</t>
+          <t>未来商战（社交力营） 16800.0；[自我成长/疗愈] 完形心理认知课，增加智慧。 1998.0；100天疗愈  第1周基础课 心理成长课 200.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1354650.52</v>
+        <v>1418370.53</v>
       </c>
       <c r="D2" t="n">
-        <v>3808</v>
+        <v>4017</v>
       </c>
       <c r="E2" t="n">
-        <v>119169</v>
+        <v>129069</v>
       </c>
       <c r="F2" t="n">
-        <v>1235481.52</v>
+        <v>1289301.53</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1238526</v>
+        <v>1295676</v>
       </c>
       <c r="D3" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="E3" t="n">
-        <v>119140</v>
+        <v>129040</v>
       </c>
       <c r="F3" t="n">
-        <v>1119386</v>
+        <v>1166636</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116124.52</v>
+        <v>122694.53</v>
       </c>
       <c r="D4" t="n">
-        <v>3570</v>
+        <v>3769</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>116095.52</v>
+        <v>122665.53</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1777488</v>
+        <v>1988824</v>
       </c>
       <c r="D5" t="n">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="E5" t="n">
-        <v>86210</v>
+        <v>117432</v>
       </c>
       <c r="F5" t="n">
-        <v>1691278</v>
+        <v>1871392</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1316136</v>
+        <v>1442646</v>
       </c>
       <c r="D6" t="n">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E6" t="n">
         <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>1293538</v>
+        <v>1420048</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>441352</v>
+        <v>526178</v>
       </c>
       <c r="D7" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="E7" t="n">
-        <v>63612</v>
+        <v>94834</v>
       </c>
       <c r="F7" t="n">
-        <v>377740</v>
+        <v>431344</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023212.69</v>
+        <v>2068959.54</v>
       </c>
       <c r="D8" t="n">
-        <v>2558</v>
+        <v>2587</v>
       </c>
       <c r="E8" t="n">
         <v>8784.469999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2014428.22</v>
+        <v>2060175.07</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1198345.9</v>
+        <v>1218203.38</v>
       </c>
       <c r="D9" t="n">
-        <v>1130</v>
+        <v>1145</v>
       </c>
       <c r="E9" t="n">
         <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>1196545.9</v>
+        <v>1216403.38</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>824866.79</v>
+        <v>850756.16</v>
       </c>
       <c r="D10" t="n">
-        <v>1428</v>
+        <v>1442</v>
       </c>
       <c r="E10" t="n">
         <v>6984.47</v>
       </c>
       <c r="F10" t="n">
-        <v>817882.3199999999</v>
+        <v>843771.6899999999</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>529608.4</v>
+        <v>577206.4</v>
       </c>
       <c r="D11" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E11" t="n">
-        <v>129202</v>
+        <v>144800</v>
       </c>
       <c r="F11" t="n">
-        <v>400406.4</v>
+        <v>432406.4</v>
       </c>
     </row>
     <row r="12">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>100788</v>
+        <v>102688</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>100788</v>
+        <v>102688</v>
       </c>
     </row>
     <row r="13">
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>140820</v>
+        <v>113000</v>
       </c>
       <c r="D13" t="n">
         <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>93200</v>
+        <v>63400</v>
       </c>
       <c r="F13" t="n">
-        <v>47620</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="14">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>128129.24</v>
+        <v>144128.24</v>
       </c>
       <c r="D15" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>128129.24</v>
+        <v>144128.24</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1824198.67</v>
+        <v>1848001.67</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1839570.27；其他 2672.0；课程线 1750.0；菌群线 -19793.6</t>
+          <t>医疗线 1863373.27；其他 2672.0；课程线 1750.0；菌群线 -19793.6</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>235819</v>
+        <v>266013</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 189170.0；课程线 29349.0；医疗线 17300.0</t>
+          <t>咨询线 202564.0；医疗线 34100.0；课程线 29349.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>86077.45</v>
+        <v>102965.45</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>69.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 60176.0；医疗线 19235.45；课程线 6666.0</t>
+          <t>咨询线 72774.0；医疗线 21035.45；课程线 9156.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>390447.69</v>
+        <v>431444.69</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>52.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 187578.0；菌群线 116000.0；课程线 66800.0；工作坊 9900.0；其他 5849.0；医疗线 4320.69</t>
+          <t>咨询线 227976.0；菌群线 116000.0；课程线 67099.0；工作坊 9900.0；其他 5849.0；医疗线 4620.69</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>294868.03</v>
+        <v>346460.03</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 199462.0；菌群线 46600.0；医疗线 24487.79；课程线 13353.0；考证 10000.0；其他 965.24</t>
+          <t>咨询线 251054.0；菌群线 46600.0；医疗线 24487.79；课程线 13353.0；考证 10000.0；其他 965.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>129587</v>
+        <v>166983</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>84.2</v>
+        <v>83.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 109154.0；课程线 20194.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
+          <t>咨询线 139950.0；课程线 26794.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>371944.28</v>
+        <v>374144.28</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 189062.0；其他 80066.0；医疗线 60088.28；菌群线 42400.0；课程线 328.0</t>
+          <t>咨询线 189062.0；其他 75066.0；医疗线 60088.28；菌群线 49600.0；课程线 328.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>365526.87</v>
+        <v>373061.58</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 255478.0；菌群线 45600.0；考证 36000.0；医疗线 13391.87；课程线 13257.0；其他 1800.0</t>
+          <t>咨询线 262978.0；菌群线 45600.0；考证 36000.0；医疗线 13426.58；课程线 13257.0；其他 1800.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>193969.65</v>
+        <v>195740.45</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>62.3</v>
+        <v>62.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 120776.0；考证 39588.0；医疗线 26389.65；课程线 6638.0；其他 578.0</t>
+          <t>咨询线 121572.0；考证 39588.0；医疗线 27345.45；课程线 6657.0；其他 578.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49413</v>
+        <v>44452</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>94.7</v>
+        <v>94</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 46770.0；课程线 1643.0；医疗线 1000.0；其他 0.0</t>
+          <t>咨询线 41790.0；课程线 1662.0；医疗线 1000.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>127000</v>
+        <v>122020</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>94.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 120166.0；工作坊 3960.0；课程线 1680.0；其他 1194.0</t>
+          <t>咨询线 115186.0；工作坊 3960.0；课程线 1680.0；其他 1194.0</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>94972</v>
+        <v>122972</v>
       </c>
     </row>
     <row r="8">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>89990</v>
+        <v>106184</v>
       </c>
     </row>
     <row r="9">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>83596</v>
+        <v>96194</v>
       </c>
     </row>
     <row r="10">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>66782</v>
+        <v>68998</v>
       </c>
     </row>
     <row r="12">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>237295.8</v>
+        <v>236295.8</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>231318.46</v>
+        <v>235121.46</v>
       </c>
     </row>
     <row r="16">
@@ -1434,11 +1434,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>姜人荷</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>45600</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="20">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>76400</v>
+        <v>46600</v>
       </c>
     </row>
     <row r="28">
@@ -1740,11 +1740,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>沈悦</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>41398</v>
+        <v>36796</v>
       </c>
     </row>
     <row r="37">
@@ -1758,11 +1758,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>36796</v>
+        <v>36398</v>
       </c>
     </row>
     <row r="38">
@@ -1794,11 +1794,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4850</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="40">
@@ -1812,11 +1812,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2272</v>
+        <v>4850</v>
       </c>
     </row>
   </sheetData>
@@ -1882,26 +1882,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1354650.52</v>
+        <v>1418370.53</v>
       </c>
       <c r="C2" t="n">
-        <v>552232.1800000001</v>
+        <v>568156.74</v>
       </c>
       <c r="D2" t="n">
-        <v>100988.02</v>
+        <v>111932.58</v>
       </c>
       <c r="E2" t="n">
-        <v>7.45</v>
+        <v>7.89</v>
       </c>
       <c r="F2" t="n">
-        <v>451244.16</v>
+        <v>456224.16</v>
       </c>
       <c r="G2" t="n">
-        <v>33.31</v>
+        <v>32.17</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 184800.0；青少年同行者计划领航营 135859.4；青少年同行者计划 35690.0</t>
+          <t>少年说陪伴计划 184800.0；青少年同行者计划领航营 145819.4；青少年同行者计划 40670.0</t>
         </is>
       </c>
     </row>
@@ -1912,26 +1912,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1777488</v>
+        <v>1988824</v>
       </c>
       <c r="C3" t="n">
-        <v>783252.99</v>
+        <v>812252.99</v>
       </c>
       <c r="D3" t="n">
         <v>45598</v>
       </c>
       <c r="E3" t="n">
-        <v>2.57</v>
+        <v>2.29</v>
       </c>
       <c r="F3" t="n">
-        <v>737654.99</v>
+        <v>766654.99</v>
       </c>
       <c r="G3" t="n">
-        <v>41.5</v>
+        <v>38.55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 434088.99；精神心理 126896.0；电商咨询 59700.0</t>
+          <t>儿童青少年 448088.99；精神心理 131896.0；电商咨询 69700.0</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023212.69</v>
+        <v>2068959.54</v>
       </c>
       <c r="C4" t="n">
         <v>28999</v>
@@ -1957,7 +1957,7 @@
         <v>28750</v>
       </c>
       <c r="G4" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>529608.4</v>
+        <v>577206.4</v>
       </c>
       <c r="C5" t="n">
         <v>190400</v>
@@ -1987,7 +1987,7 @@
         <v>190400</v>
       </c>
       <c r="G5" t="n">
-        <v>35.95</v>
+        <v>32.99</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100788</v>
+        <v>102688</v>
       </c>
       <c r="C6" t="n">
         <v>156919.9</v>
@@ -2011,13 +2011,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="F6" t="n">
         <v>154902</v>
       </c>
       <c r="G6" t="n">
-        <v>153.69</v>
+        <v>150.85</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>140820</v>
+        <v>113000</v>
       </c>
       <c r="C7" t="n">
         <v>299246.67</v>
@@ -2041,13 +2041,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>37.64</v>
+        <v>46.9</v>
       </c>
       <c r="F7" t="n">
         <v>246246.67</v>
       </c>
       <c r="G7" t="n">
-        <v>174.87</v>
+        <v>217.92</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128129.24</v>
+        <v>144128.24</v>
       </c>
       <c r="C9" t="n">
         <v>18998</v>
@@ -2101,13 +2101,13 @@
         <v>2198</v>
       </c>
       <c r="E9" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="F9" t="n">
         <v>16800</v>
       </c>
       <c r="G9" t="n">
-        <v>13.11</v>
+        <v>11.66</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1418370.53</v>
+        <v>1540712.53</v>
       </c>
       <c r="D2" t="n">
-        <v>4017</v>
+        <v>4165</v>
       </c>
       <c r="E2" t="n">
         <v>129069</v>
       </c>
       <c r="F2" t="n">
-        <v>1289301.53</v>
+        <v>1411643.53</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1295676</v>
+        <v>1413097</v>
       </c>
       <c r="D3" t="n">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="E3" t="n">
         <v>129040</v>
       </c>
       <c r="F3" t="n">
-        <v>1166636</v>
+        <v>1284057</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>122694.53</v>
+        <v>127615.53</v>
       </c>
       <c r="D4" t="n">
-        <v>3769</v>
+        <v>3893</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>122665.53</v>
+        <v>127586.53</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1988824</v>
+        <v>2107422</v>
       </c>
       <c r="D5" t="n">
-        <v>450</v>
+        <v>501</v>
       </c>
       <c r="E5" t="n">
         <v>117432</v>
       </c>
       <c r="F5" t="n">
-        <v>1871392</v>
+        <v>1989990</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1442646</v>
+        <v>1512040</v>
       </c>
       <c r="D6" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="E6" t="n">
         <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>1420048</v>
+        <v>1489442</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>526178</v>
+        <v>575382</v>
       </c>
       <c r="D7" t="n">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="E7" t="n">
         <v>94834</v>
       </c>
       <c r="F7" t="n">
-        <v>431344</v>
+        <v>480548</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2068959.54</v>
+        <v>2136679.13</v>
       </c>
       <c r="D8" t="n">
-        <v>2587</v>
+        <v>2726</v>
       </c>
       <c r="E8" t="n">
         <v>8784.469999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2060175.07</v>
+        <v>2127894.66</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1218203.38</v>
+        <v>1276047.08</v>
       </c>
       <c r="D9" t="n">
-        <v>1145</v>
+        <v>1202</v>
       </c>
       <c r="E9" t="n">
         <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>1216403.38</v>
+        <v>1274247.08</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>850756.16</v>
+        <v>860632.05</v>
       </c>
       <c r="D10" t="n">
-        <v>1442</v>
+        <v>1524</v>
       </c>
       <c r="E10" t="n">
         <v>6984.47</v>
       </c>
       <c r="F10" t="n">
-        <v>843771.6899999999</v>
+        <v>853647.58</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>577206.4</v>
+        <v>843006.4</v>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>144800</v>
+        <v>336200</v>
       </c>
       <c r="F11" t="n">
-        <v>432406.4</v>
+        <v>506806.4</v>
       </c>
     </row>
     <row r="12">
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>113000</v>
+        <v>128000</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>63400</v>
+        <v>73400</v>
       </c>
       <c r="F13" t="n">
-        <v>49600</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="14">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>144128.24</v>
+        <v>145127.25</v>
       </c>
       <c r="D15" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>144128.24</v>
+        <v>145127.25</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1848001.67</v>
+        <v>1896904.67</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1863373.27；其他 2672.0；课程线 1750.0；菌群线 -19793.6</t>
+          <t>医疗线 1912257.27；其他 2672.0；课程线 1769.0；菌群线 -19793.6</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>266013</v>
+        <v>294362</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>76.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 202564.0；医疗线 34100.0；课程线 29349.0</t>
+          <t>咨询线 213758.0；医疗线 50900.0；课程线 29704.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>102965.45</v>
+        <v>102984.45</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 72774.0；医疗线 21035.45；课程线 9156.0</t>
+          <t>咨询线 72774.0；医疗线 21035.45；课程线 9175.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>431444.69</v>
+        <v>455042.7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.8</v>
+        <v>52.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 227976.0；菌群线 116000.0；课程线 67099.0；工作坊 9900.0；其他 5849.0；医疗线 4620.69</t>
+          <t>咨询线 238374.0；菌群线 116000.0；课程线 80299.0；工作坊 9900.0；其他 5849.01；医疗线 4620.69</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>346460.03</v>
+        <v>382024.43</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>72.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 251054.0；菌群线 46600.0；医疗线 24487.79；课程线 13353.0；考证 10000.0；其他 965.24</t>
+          <t>咨询线 286054.0；菌群线 46600.0；医疗线 25052.19；课程线 13353.0；考证 10000.0；其他 965.24</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>166983</v>
+        <v>187381</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>83.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 139950.0；课程线 26794.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
+          <t>咨询线 160348.0；课程线 26794.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>374144.28</v>
+        <v>378340.28</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.5</v>
+        <v>51.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 189062.0；其他 75066.0；医疗线 60088.28；菌群线 49600.0；课程线 328.0</t>
+          <t>咨询线 193258.0；其他 75066.0；医疗线 60088.28；菌群线 49600.0；课程线 328.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373061.58</v>
+        <v>373861.58</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 262978.0；菌群线 45600.0；考证 36000.0；医疗线 13426.58；课程线 13257.0；其他 1800.0</t>
+          <t>咨询线 263778.0；菌群线 45600.0；考证 36000.0；医疗线 13426.58；课程线 13257.0；其他 1800.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>195740.45</v>
+        <v>206788.75</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>62.1</v>
+        <v>63.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 121572.0；考证 39588.0；医疗线 27345.45；课程线 6657.0；其他 578.0</t>
+          <t>咨询线 132170.0；考证 39588.0；医疗线 27795.75；课程线 6657.0；其他 578.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44452</v>
+        <v>44869.9</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 41790.0；课程线 1662.0；医疗线 1000.0；其他 0.0</t>
+          <t>咨询线 42188.0；课程线 1662.0；医疗线 1019.9；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>122020</v>
+        <v>122816</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 115186.0；工作坊 3960.0；课程线 1680.0；其他 1194.0</t>
+          <t>咨询线 115982.0；工作坊 3960.0；课程线 1680.0；其他 1194.0</t>
         </is>
       </c>
     </row>
@@ -1146,11 +1146,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>67720</v>
+        <v>79560</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>64620</v>
+        <v>72700</v>
       </c>
     </row>
     <row r="5">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>59760</v>
+        <v>64740</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59400</v>
+        <v>61260</v>
       </c>
     </row>
     <row r="7">
@@ -1218,11 +1218,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>122972</v>
+        <v>141184</v>
       </c>
     </row>
     <row r="8">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>106184</v>
+        <v>132972</v>
       </c>
     </row>
     <row r="9">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>96194</v>
+        <v>96990</v>
       </c>
     </row>
     <row r="10">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68998</v>
+        <v>73980</v>
       </c>
     </row>
     <row r="12">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>386278.97</v>
+        <v>426329.97</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>286122.04</v>
+        <v>297151.04</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>236295.8</v>
+        <v>239414.46</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>235121.46</v>
+        <v>238253.8</v>
       </c>
     </row>
     <row r="16">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>226539</v>
+        <v>231185</v>
       </c>
     </row>
     <row r="17">
@@ -1398,11 +1398,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>70400</v>
+        <v>169600</v>
       </c>
     </row>
     <row r="18">
@@ -1416,11 +1416,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>49600</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="19">
@@ -1434,11 +1434,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>姜人荷</t>
+          <t>龙少海</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>49600</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="20">
@@ -1452,11 +1452,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>45600</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="21">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>姜人荷</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45600</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="22">
@@ -1632,11 +1632,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3960</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="31">
@@ -1650,11 +1650,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>何媛媛</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3960</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="32">
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4850</v>
+        <v>4850.01</v>
       </c>
     </row>
   </sheetData>
@@ -1882,26 +1882,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1418370.53</v>
+        <v>1540712.53</v>
       </c>
       <c r="C2" t="n">
-        <v>568156.74</v>
+        <v>604082.74</v>
       </c>
       <c r="D2" t="n">
-        <v>111932.58</v>
+        <v>118096.58</v>
       </c>
       <c r="E2" t="n">
-        <v>7.89</v>
+        <v>7.67</v>
       </c>
       <c r="F2" t="n">
-        <v>456224.16</v>
+        <v>485986.16</v>
       </c>
       <c r="G2" t="n">
-        <v>32.17</v>
+        <v>31.54</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 184800.0；青少年同行者计划领航营 145819.4；青少年同行者计划 40670.0</t>
+          <t>少年说陪伴计划 191400.0；青少年同行者计划领航营 145819.4；青少年同行者计划 45649.0</t>
         </is>
       </c>
     </row>
@@ -1912,26 +1912,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1988824</v>
+        <v>2107422</v>
       </c>
       <c r="C3" t="n">
-        <v>812252.99</v>
+        <v>883152.99</v>
       </c>
       <c r="D3" t="n">
-        <v>45598</v>
+        <v>54598</v>
       </c>
       <c r="E3" t="n">
-        <v>2.29</v>
+        <v>2.59</v>
       </c>
       <c r="F3" t="n">
-        <v>766654.99</v>
+        <v>828554.99</v>
       </c>
       <c r="G3" t="n">
-        <v>38.55</v>
+        <v>39.32</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 448088.99；精神心理 131896.0；电商咨询 69700.0</t>
+          <t>儿童青少年 490988.99；精神心理 149896.0；电商咨询 69700.0</t>
         </is>
       </c>
     </row>
@@ -1942,22 +1942,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2068959.54</v>
+        <v>2136679.13</v>
       </c>
       <c r="C4" t="n">
-        <v>28999</v>
+        <v>29799</v>
       </c>
       <c r="D4" t="n">
-        <v>249</v>
+        <v>1049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="F4" t="n">
         <v>28750</v>
       </c>
       <c r="G4" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>577206.4</v>
+        <v>843006.4</v>
       </c>
       <c r="C5" t="n">
         <v>190400</v>
@@ -1987,7 +1987,7 @@
         <v>190400</v>
       </c>
       <c r="G5" t="n">
-        <v>32.99</v>
+        <v>22.59</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2032,26 +2032,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113000</v>
+        <v>128000</v>
       </c>
       <c r="C7" t="n">
-        <v>299246.67</v>
+        <v>327046.67</v>
       </c>
       <c r="D7" t="n">
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>46.9</v>
+        <v>41.41</v>
       </c>
       <c r="F7" t="n">
-        <v>246246.67</v>
+        <v>274046.67</v>
       </c>
       <c r="G7" t="n">
-        <v>217.92</v>
+        <v>214.1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 221266.67；青少年成长基地3月营（金盏基地） 39380.0；青少年【未来之翼】身心节律复能7日营 33600.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 249066.67；青少年成长基地3月营（金盏基地） 39380.0；青少年【未来之翼】身心节律复能7日营 33600.0</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
         <v>13860</v>
       </c>
       <c r="C8" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -2074,14 +2074,14 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
       <c r="G8" t="n">
-        <v>14.29</v>
+        <v>28.57</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>【廖文婷】萨提亚家庭系统工作坊 1980.0</t>
+          <t>【廖文婷】萨提亚家庭系统工作坊 3960.0</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>144128.24</v>
+        <v>145127.25</v>
       </c>
       <c r="C9" t="n">
         <v>18998</v>
@@ -2101,13 +2101,13 @@
         <v>2198</v>
       </c>
       <c r="E9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="F9" t="n">
         <v>16800</v>
       </c>
       <c r="G9" t="n">
-        <v>11.66</v>
+        <v>11.58</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1540712.53</v>
+        <v>87221</v>
       </c>
       <c r="D2" t="n">
-        <v>4165</v>
+        <v>997</v>
       </c>
       <c r="E2" t="n">
-        <v>129069</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1411643.53</v>
+        <v>87221</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1413097</v>
+        <v>53040</v>
       </c>
       <c r="D3" t="n">
-        <v>272</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>129040</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1284057</v>
+        <v>53040</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>127615.53</v>
+        <v>34181</v>
       </c>
       <c r="D4" t="n">
-        <v>3893</v>
+        <v>986</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>127586.53</v>
+        <v>34181</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2107422</v>
+        <v>547748</v>
       </c>
       <c r="D5" t="n">
-        <v>501</v>
+        <v>106</v>
       </c>
       <c r="E5" t="n">
-        <v>117432</v>
+        <v>60820</v>
       </c>
       <c r="F5" t="n">
-        <v>1989990</v>
+        <v>486928</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1512040</v>
+        <v>349086</v>
       </c>
       <c r="D6" t="n">
-        <v>275</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>22598</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1489442</v>
+        <v>349086</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>575382</v>
+        <v>198264</v>
       </c>
       <c r="D7" t="n">
-        <v>223</v>
+        <v>44</v>
       </c>
       <c r="E7" t="n">
-        <v>94834</v>
+        <v>60820</v>
       </c>
       <c r="F7" t="n">
-        <v>480548</v>
+        <v>137444</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2136679.13</v>
+        <v>258666.54</v>
       </c>
       <c r="D8" t="n">
-        <v>2726</v>
+        <v>248</v>
       </c>
       <c r="E8" t="n">
-        <v>8784.469999999999</v>
+        <v>17440</v>
       </c>
       <c r="F8" t="n">
-        <v>2127894.66</v>
+        <v>241226.54</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1276047.08</v>
+        <v>157865.89</v>
       </c>
       <c r="D9" t="n">
-        <v>1202</v>
+        <v>150</v>
       </c>
       <c r="E9" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1274247.08</v>
+        <v>157865.89</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>860632.05</v>
+        <v>100800.65</v>
       </c>
       <c r="D10" t="n">
-        <v>1524</v>
+        <v>98</v>
       </c>
       <c r="E10" t="n">
-        <v>6984.47</v>
+        <v>17440</v>
       </c>
       <c r="F10" t="n">
-        <v>853647.58</v>
+        <v>83360.64999999999</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>843006.4</v>
+        <v>49600</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>336200</v>
+        <v>49600</v>
       </c>
       <c r="F11" t="n">
-        <v>506806.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>102688</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>102688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>128000</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>73400</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>54600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13860</v>
+        <v>1980</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>13860</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="15">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>145127.25</v>
+        <v>4275.36</v>
       </c>
       <c r="D15" t="n">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>2277.36</v>
       </c>
       <c r="F15" t="n">
-        <v>145127.25</v>
+        <v>1998</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1896904.67</v>
+        <v>185298</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100.8</v>
+        <v>100</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1912257.27；其他 2672.0；课程线 1769.0；菌群线 -19793.6</t>
+          <t>医疗线 185279.0；课程线 19.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>294362</v>
+        <v>48592</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>72.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 213758.0；医疗线 50900.0；课程线 29704.0</t>
+          <t>咨询线 48490.0；课程线 102.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>102984.45</v>
+        <v>24628</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>70.7</v>
+        <v>99.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 72774.0；医疗线 21035.45；课程线 9175.0</t>
+          <t>咨询线 24590.0；课程线 38.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>455042.7</v>
+        <v>101937</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.4</v>
+        <v>50.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 238374.0；菌群线 116000.0；课程线 80299.0；工作坊 9900.0；其他 5849.01；医疗线 4620.69</t>
+          <t>咨询线 51606.0；医疗线 37064.0；课程线 11287.0；工作坊 1980.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>382024.43</v>
+        <v>70287.87</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>74.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 286054.0；菌群线 46600.0；医疗线 25052.19；课程线 13353.0；考证 10000.0；其他 965.24</t>
+          <t>咨询线 58194.0；课程线 6600.0；医疗线 5493.87；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>187381</v>
+        <v>101194</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>85.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 160348.0；课程线 26794.0；其他 200.0；医疗线 39.0；菌群线 0.0</t>
+          <t>咨询线 101194.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>378340.28</v>
+        <v>19334.88</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>51.1</v>
+        <v>54.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 193258.0；其他 75066.0；医疗线 60088.28；菌群线 49600.0；课程线 328.0</t>
+          <t>咨询线 10490.0；课程线 6619.0；医疗线 2225.88</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373861.58</v>
+        <v>65824.82000000001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 263778.0；菌群线 45600.0；考证 36000.0；医疗线 13426.58；课程线 13257.0；其他 1800.0</t>
+          <t>咨询线 60388.0；医疗线 5436.82</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>206788.75</v>
+        <v>34101.1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>63.9</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 132170.0；考证 39588.0；医疗线 27795.75；课程线 6657.0；其他 578.0</t>
+          <t>咨询线 32598.0；医疗线 1494.1；课程线 9.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44869.9</v>
+        <v>6053</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 42188.0；课程线 1662.0；医疗线 1019.9；其他 0.0</t>
+          <t>咨询线 5996.0；课程线 57.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>122816</v>
+        <v>46811</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 115982.0；工作坊 3960.0；课程线 1680.0；其他 1194.0</t>
+          <t>咨询线 46792.0；课程线 19.0</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,11 +1128,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80040</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="3">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79560</v>
+        <v>7880</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>72700</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64740</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61260</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="7">
@@ -1218,11 +1218,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>141184</v>
+        <v>50398</v>
       </c>
     </row>
     <row r="8">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>132972</v>
+        <v>49616</v>
       </c>
     </row>
     <row r="9">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>96990</v>
+        <v>38820</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>林非凡</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79194</v>
+        <v>32796</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73980</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="12">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>426329.97</v>
+        <v>47668</v>
       </c>
     </row>
     <row r="13">
@@ -1326,11 +1326,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>297151.04</v>
+        <v>36695</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>239414.46</v>
+        <v>30887</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>238253.8</v>
+        <v>28196</v>
       </c>
     </row>
     <row r="16">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>231185</v>
+        <v>26469</v>
       </c>
     </row>
     <row r="17">
@@ -1398,11 +1398,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>169600</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="18">
@@ -1416,11 +1416,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1434,11 +1434,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>龙少海</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1452,35 +1452,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>49600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>菌群线</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>姜人荷</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>49600</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>考证</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1488,335 +1488,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>马雅丽</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>39588</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>考证</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>林非凡</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>考证</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>梁志超</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11400</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>考证</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>李明</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>考证</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>陈紫灵</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>营地</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>江敏</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>46600</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>营地</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>高曌</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>29800</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>营地</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>郑鲁</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>16800</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>营地</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>4</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>张孟蝶</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>营地</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>刘士明</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>工作坊</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>岳伟伟</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>7920</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>工作坊</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>张虹</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>工作坊</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>朱碧丹</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>工作坊</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>陶雯</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>黄雅晴</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>36796</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>沈悦</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>36398</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>陈斌斌</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>唐歌</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>5</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>岳伟伟</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>4850.01</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1882,26 +1558,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1540712.53</v>
+        <v>87221</v>
       </c>
       <c r="C2" t="n">
-        <v>604082.74</v>
+        <v>3426</v>
       </c>
       <c r="D2" t="n">
-        <v>118096.58</v>
+        <v>2056</v>
       </c>
       <c r="E2" t="n">
-        <v>7.67</v>
+        <v>2.36</v>
       </c>
       <c r="F2" t="n">
-        <v>485986.16</v>
+        <v>1370</v>
       </c>
       <c r="G2" t="n">
-        <v>31.54</v>
+        <v>1.57</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 191400.0；青少年同行者计划领航营 145819.4；青少年同行者计划 45649.0</t>
+          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 897.0；青少年同行者计划：试听课 304.0；青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题 266.0</t>
         </is>
       </c>
     </row>
@@ -1912,28 +1588,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2107422</v>
+        <v>547748</v>
       </c>
       <c r="C3" t="n">
-        <v>883152.99</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>54598</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>828554.99</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>39.32</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>儿童青少年 490988.99；精神心理 149896.0；电商咨询 69700.0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1942,28 +1614,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2136679.13</v>
+        <v>258666.54</v>
       </c>
       <c r="C4" t="n">
-        <v>29799</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1049</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>28750</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>儿童多动精灵专注站 PEERS 专项（16 节课） 16800.0；多动精灵专注站（PEERS） 7350.0；50分钟问诊（诸秉根） -线下 3600.0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1972,10 +1640,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>843006.4</v>
+        <v>49600</v>
       </c>
       <c r="C5" t="n">
-        <v>190400</v>
+        <v>45600</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1984,14 +1652,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>190400</v>
+        <v>45600</v>
       </c>
       <c r="G5" t="n">
-        <v>22.59</v>
+        <v>91.94</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群移植 49600.0；肠道菌群移植（活动专享） 49600.0</t>
+          <t>肠道菌群移植（双疗程） 45600.0</t>
         </is>
       </c>
     </row>
@@ -2002,28 +1670,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102688</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>156919.9</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2017.9</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>154902</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>150.85</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>心灯计划-实战派-高阶培训课程 79200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 64193.0；心理咨询基本功实战营 4880.0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2032,28 +1696,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>128000</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>327046.67</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>53000</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>41.41</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>274046.67</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>214.1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 249066.67；青少年成长基地3月营（金盏基地） 39380.0；青少年【未来之翼】身心节律复能7日营 33600.0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2062,10 +1722,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13860</v>
+        <v>1980</v>
       </c>
       <c r="C8" t="n">
-        <v>3960</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -2074,16 +1734,12 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>3960</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>【廖文婷】萨提亚家庭系统工作坊 3960.0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2092,28 +1748,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>145127.25</v>
+        <v>4275.36</v>
       </c>
       <c r="C9" t="n">
-        <v>18998</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2198</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>16800</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>11.58</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>未来商战（社交力营） 16800.0；[自我成长/疗愈] 完形心理认知课，增加智慧。 1998.0；100天疗愈  第1周基础课 心理成长课 200.0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>87221</v>
+        <v>270074</v>
       </c>
       <c r="D2" t="n">
-        <v>997</v>
+        <v>1308</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>87221</v>
+        <v>270074</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53040</v>
+        <v>224711</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>53040</v>
+        <v>224711</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34181</v>
+        <v>45363</v>
       </c>
       <c r="D4" t="n">
-        <v>986</v>
+        <v>1265</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>34181</v>
+        <v>45363</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>547748</v>
+        <v>676704</v>
       </c>
       <c r="D5" t="n">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="E5" t="n">
-        <v>60820</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>486928</v>
+        <v>676704</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>349086</v>
+        <v>461472</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>349086</v>
+        <v>461472</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>198264</v>
+        <v>214834</v>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E7" t="n">
-        <v>60820</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>137444</v>
+        <v>214834</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>258666.54</v>
+        <v>279909.35</v>
       </c>
       <c r="D8" t="n">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="E8" t="n">
-        <v>17440</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>241226.54</v>
+        <v>279909.35</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>157865.89</v>
+        <v>167911.71</v>
       </c>
       <c r="D9" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>157865.89</v>
+        <v>167911.71</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100800.65</v>
+        <v>111997.64</v>
       </c>
       <c r="D10" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E10" t="n">
-        <v>17440</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>83360.64999999999</v>
+        <v>111997.64</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49600</v>
+        <v>95200</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>49600</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>95200</v>
       </c>
     </row>
     <row r="12">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4275.36</v>
+        <v>7272.36</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>2277.36</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1998</v>
+        <v>7272.36</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>185298</v>
+        <v>204607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 185279.0；课程线 19.0</t>
+          <t>医疗线 204588.0；课程线 19.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48592</v>
+        <v>49388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 48490.0；课程线 102.0</t>
+          <t>咨询线 49286.0；课程线 102.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24628</v>
+        <v>26225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>99.8</v>
+        <v>95.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 24590.0；课程线 38.0</t>
+          <t>咨询线 24988.0；其他 999.0；医疗线 200.0；课程线 38.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>101937</v>
+        <v>113750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50.6</v>
+        <v>55.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 51606.0；医疗线 37064.0；课程线 11287.0；工作坊 1980.0；其他 0.0</t>
+          <t>咨询线 62800.0；医疗线 37664.0；课程线 11306.0；工作坊 1980.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70287.87</v>
+        <v>100163.37</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 58194.0；课程线 6600.0；医疗线 5493.87；菌群线 0.0</t>
+          <t>咨询线 86192.0；课程线 6638.0；医疗线 6334.37；其他 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101194</v>
+        <v>167988</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>100</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 101194.0</t>
+          <t>咨询线 122388.0；菌群线 45600.0；课程线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19334.88</v>
+        <v>33617.2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>54.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 10490.0；课程线 6619.0；医疗线 2225.88</t>
+          <t>咨询线 24680.0；课程线 6619.0；医疗线 2318.2</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65824.82000000001</v>
+        <v>85824.82000000001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>91.7</v>
+        <v>93.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 60388.0；医疗线 5436.82</t>
+          <t>咨询线 80388.0；医疗线 5436.82；课程线 0.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34101.1</v>
+        <v>34130.1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>95.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 32598.0；医疗线 1494.1；课程线 9.0</t>
+          <t>咨询线 32598.0；医疗线 1494.1；课程线 38.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6053</v>
+        <v>14053</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>99.09999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 5996.0；课程线 57.0；其他 0.0</t>
+          <t>咨询线 13996.0；课程线 57.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46811</v>
+        <v>54407</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>87.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 46792.0；课程线 19.0</t>
+          <t>咨询线 47788.0；课程线 6619.0</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9960</v>
+        <v>26520</v>
       </c>
     </row>
     <row r="3">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7880</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6600</v>
+        <v>19920</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6600</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50398</v>
+        <v>70796</v>
       </c>
     </row>
     <row r="8">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>49616</v>
+        <v>59616</v>
       </c>
     </row>
     <row r="9">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>32796</v>
+        <v>33394</v>
       </c>
     </row>
     <row r="11">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31500</v>
+        <v>32296</v>
       </c>
     </row>
     <row r="12">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47668</v>
+        <v>50606</v>
       </c>
     </row>
     <row r="13">
@@ -1326,11 +1326,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>36695</v>
+        <v>48066</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>30887</v>
+        <v>31469</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>28196</v>
+        <v>30887</v>
       </c>
     </row>
     <row r="16">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26469</v>
+        <v>28196</v>
       </c>
     </row>
     <row r="17">
@@ -1416,11 +1416,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>李颜君</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="19">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1462,25 +1462,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>菌群线</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1492,6 +1492,42 @@
         </is>
       </c>
       <c r="D22" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>刘俊彤</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>岳伟伟</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1558,26 +1594,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>87221</v>
+        <v>270074</v>
       </c>
       <c r="C2" t="n">
-        <v>3426</v>
+        <v>29489</v>
       </c>
       <c r="D2" t="n">
-        <v>2056</v>
+        <v>2483</v>
       </c>
       <c r="E2" t="n">
-        <v>2.36</v>
+        <v>0.92</v>
       </c>
       <c r="F2" t="n">
-        <v>1370</v>
+        <v>27006</v>
       </c>
       <c r="G2" t="n">
-        <v>1.57</v>
+        <v>10</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 897.0；青少年同行者计划：试听课 304.0；青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题 266.0</t>
+          <t>青少年同行者计划护航营（6月） 8365.0；青少年同行者计划-护航营 5643.0；青少年同行者计划护航营（10周） 4980.0</t>
         </is>
       </c>
     </row>
@@ -1588,10 +1624,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>547748</v>
+        <v>676704</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>60600</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1600,12 +1636,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60600</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>8.960000000000001</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>儿童青少年 36400.0；精神心理 9000.0；电商咨询 6000.0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1614,7 +1654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>258666.54</v>
+        <v>279909.35</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1640,10 +1680,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49600</v>
+        <v>95200</v>
       </c>
       <c r="C5" t="n">
-        <v>45600</v>
+        <v>91200</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1652,14 +1692,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>45600</v>
+        <v>91200</v>
       </c>
       <c r="G5" t="n">
-        <v>91.94</v>
+        <v>95.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程） 45600.0</t>
+          <t>肠道菌群移植（双疗程） 91200.0</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>87380</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1708,12 +1748,16 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>87380</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>青少年成长基地3月营（金盏基地） 46800.0；青少年【未来之翼】身心节律复能7日营 33600.0；蛋壳跳动身心复能营21天（一阶） 5000.0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1725,7 +1769,7 @@
         <v>1980</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1734,12 +1778,16 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>【廖文婷】萨提亚家庭系统工作坊 1980.0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1748,7 +1796,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4275.36</v>
+        <v>7272.36</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>270074</v>
+        <v>390289</v>
       </c>
       <c r="D2" t="n">
-        <v>1308</v>
+        <v>1550</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>270074</v>
+        <v>390289</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>224711</v>
+        <v>334891</v>
       </c>
       <c r="D3" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>224711</v>
+        <v>334891</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45363</v>
+        <v>55398</v>
       </c>
       <c r="D4" t="n">
-        <v>1265</v>
+        <v>1484</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>45363</v>
+        <v>55398</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>676704</v>
+        <v>881376</v>
       </c>
       <c r="D5" t="n">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>676704</v>
+        <v>881376</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>461472</v>
+        <v>538164</v>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>461472</v>
+        <v>538164</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>214834</v>
+        <v>332814</v>
       </c>
       <c r="D7" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>214834</v>
+        <v>332814</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>279909.35</v>
+        <v>378795.56</v>
       </c>
       <c r="D8" t="n">
-        <v>275</v>
+        <v>432</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>279909.35</v>
+        <v>378795.56</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>167911.71</v>
+        <v>198804.33</v>
       </c>
       <c r="D9" t="n">
-        <v>167</v>
+        <v>259</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>167911.71</v>
+        <v>198804.33</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>111997.64</v>
+        <v>179991.23</v>
       </c>
       <c r="D10" t="n">
-        <v>108</v>
+        <v>173</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>111997.64</v>
+        <v>179991.23</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>95200</v>
+        <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>95200</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="12">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="13">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7272.36</v>
+        <v>8771.360000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>7272.36</v>
+        <v>8771.360000000001</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>204607</v>
+        <v>279698.92</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 204588.0；课程线 19.0</t>
+          <t>医疗线 279679.92；课程线 19.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49388</v>
+        <v>49786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 49286.0；课程线 102.0</t>
+          <t>咨询线 49684.0；课程线 102.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26225</v>
+        <v>56438</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95.3</v>
+        <v>68</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 24988.0；其他 999.0；医疗线 200.0；课程线 38.0</t>
+          <t>咨询线 38382.0；医疗线 17000.0；其他 999.0；课程线 57.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>113750</v>
+        <v>120748</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55.2</v>
+        <v>52.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 62800.0；医疗线 37664.0；课程线 11306.0；工作坊 1980.0；其他 0.0</t>
+          <t>咨询线 63198.0；医疗线 37664.0；课程线 17906.0；工作坊 1980.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100163.37</v>
+        <v>130482.37</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>86.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 86192.0；课程线 6638.0；医疗线 6334.37；其他 999.0；菌群线 0.0</t>
+          <t>咨询线 116292.0；课程线 6657.0；医疗线 6534.37；其他 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>167988</v>
+        <v>178784</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>72.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 122388.0；菌群线 45600.0；课程线 0.0</t>
+          <t>咨询线 133184.0；菌群线 45600.0；课程线 0.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33617.2</v>
+        <v>64413.2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 24680.0；课程线 6619.0；医疗线 2318.2</t>
+          <t>咨询线 55476.0；课程线 6619.0；医疗线 2318.2</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85824.82000000001</v>
+        <v>107777.21</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>93.7</v>
+        <v>85</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 80388.0；医疗线 5436.82；课程线 0.0</t>
+          <t>咨询线 91586.0；考证 10000.0；医疗线 6182.21；课程线 9.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34130.1</v>
+        <v>45155.1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>95.5</v>
+        <v>96.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 32598.0；医疗线 1494.1；课程线 38.0</t>
+          <t>咨询线 43594.0；医疗线 1494.1；课程线 67.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14053</v>
+        <v>15733</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>99.59999999999999</v>
+        <v>89</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 13996.0；课程线 57.0；其他 0.0</t>
+          <t>咨询线 13996.0；课程线 1737.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,11 +1128,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26520</v>
+        <v>34860</v>
       </c>
     </row>
     <row r="3">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23500</v>
+        <v>32180</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19920</v>
+        <v>27800</v>
       </c>
     </row>
     <row r="5">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14940</v>
+        <v>23620</v>
       </c>
     </row>
     <row r="6">
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="7">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>张天昂</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>38820</v>
+        <v>49000</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>33394</v>
+        <v>43800</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>32296</v>
+        <v>33394</v>
       </c>
     </row>
     <row r="12">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>50606</v>
+        <v>85298.64</v>
       </c>
     </row>
     <row r="13">
@@ -1326,11 +1326,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48066</v>
+        <v>64963.61</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31469</v>
+        <v>50606</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>30887</v>
+        <v>49866</v>
       </c>
     </row>
     <row r="16">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>28196</v>
+        <v>29394</v>
       </c>
     </row>
     <row r="17">
@@ -1434,11 +1434,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="20">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1480,7 +1480,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>考证</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈紫灵</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1980</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1506,11 +1506,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="24">
@@ -1520,14 +1520,50 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>刘俊彤</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>2</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>岳伟伟</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>闫丽东</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1594,26 +1630,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>270074</v>
+        <v>390289</v>
       </c>
       <c r="C2" t="n">
-        <v>29489</v>
+        <v>67667.03999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2483</v>
+        <v>3611</v>
       </c>
       <c r="E2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="F2" t="n">
-        <v>27006</v>
+        <v>64056.04</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>16.41</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划护航营（6月） 8365.0；青少年同行者计划-护航营 5643.0；青少年同行者计划护航营（10周） 4980.0</t>
+          <t>青少年同行者计划领航营 17542.7；青少年同行者计划护航营（6月） 11685.0；青少年同行者计划-护航营 9826.0</t>
         </is>
       </c>
     </row>
@@ -1624,10 +1660,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>676704</v>
+        <v>881376</v>
       </c>
       <c r="C3" t="n">
-        <v>60600</v>
+        <v>98600</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1636,14 +1672,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>60600</v>
+        <v>98600</v>
       </c>
       <c r="G3" t="n">
-        <v>8.960000000000001</v>
+        <v>11.19</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 36400.0；精神心理 9000.0；电商咨询 6000.0</t>
+          <t>儿童青少年 65900.0；精神心理 9000.0；暑假礼遇咨询套餐 8500.0</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1690,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>279909.35</v>
+        <v>378795.56</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1680,7 +1716,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95200</v>
+        <v>120000</v>
       </c>
       <c r="C5" t="n">
         <v>91200</v>
@@ -1695,7 +1731,7 @@
         <v>91200</v>
       </c>
       <c r="G5" t="n">
-        <v>95.8</v>
+        <v>76</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1710,7 +1746,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1796,10 +1832,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7272.36</v>
+        <v>8771.360000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1808,12 +1844,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>44.46</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8周系统性心身综合干预+深度服务包（全国统一价） 3900.0</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>390289</v>
+        <v>488348.57</v>
       </c>
       <c r="D2" t="n">
-        <v>1550</v>
+        <v>1955</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>390289</v>
+        <v>488348.57</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>334891</v>
+        <v>421051</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>334891</v>
+        <v>421051</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>55398</v>
+        <v>67297.57000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1484</v>
+        <v>1873</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>55398</v>
+        <v>67297.57000000001</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>881376</v>
+        <v>1503890</v>
       </c>
       <c r="D5" t="n">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>881376</v>
+        <v>1503890</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>538164</v>
+        <v>974626</v>
       </c>
       <c r="D6" t="n">
-        <v>91</v>
+        <v>155</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>538164</v>
+        <v>974626</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>332814</v>
+        <v>498866</v>
       </c>
       <c r="D7" t="n">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>332814</v>
+        <v>498866</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>378795.56</v>
+        <v>675688.11</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>775</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>378795.56</v>
+        <v>675688.11</v>
       </c>
     </row>
     <row r="9">
@@ -627,20 +627,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>复诊</t>
+          <t>初诊</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>198804.33</v>
+        <v>71337.03</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>86</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>198804.33</v>
+        <v>71337.03</v>
       </c>
     </row>
     <row r="10">
@@ -651,20 +651,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>初诊</t>
+          <t>复诊</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>179991.23</v>
+        <v>55105.91</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>99</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>179991.23</v>
+        <v>55105.91</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>120000</v>
+        <v>144800</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>120000</v>
+        <v>144800</v>
       </c>
     </row>
     <row r="12">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="13">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1980</v>
+        <v>9900</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1980</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="15">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8771.360000000001</v>
+        <v>110467.86</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>8771.360000000001</v>
+        <v>110467.86</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>279698.92</v>
+        <v>570022.17</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 279679.92；课程线 19.0</t>
+          <t>医疗线 549245.17；咨询线 20398.0；其他 360.0；课程线 19.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49786</v>
+        <v>62113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>99.8</v>
+        <v>99.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 49684.0；课程线 102.0</t>
+          <t>咨询线 61674.0；课程线 439.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56438</v>
+        <v>57135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>68</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 38382.0；医疗线 17000.0；其他 999.0；课程线 57.0</t>
+          <t>咨询线 38780.0；医疗线 17000.0；其他 999.0；课程线 356.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120748</v>
+        <v>478417.99</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.3</v>
+        <v>72.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 63198.0；医疗线 37664.0；课程线 17906.0；工作坊 1980.0；其他 0.0</t>
+          <t>咨询线 347576.0；医疗线 56312.99；其他 40000.0；课程线 24629.0；工作坊 9900.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>130482.37</v>
+        <v>192656.97</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>89.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 116292.0；课程线 6657.0；医疗线 6534.37；其他 999.0；菌群线 0.0</t>
+          <t>咨询线 178086.0；医疗线 6914.97；课程线 6657.0；其他 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>178784</v>
+        <v>236801</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>74.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 133184.0；菌群线 45600.0；课程线 0.0</t>
+          <t>咨询线 184582.0；菌群线 45600.0；课程线 6619.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>64413.2</v>
+        <v>87201.2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>86.09999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 55476.0；课程线 6619.0；医疗线 2318.2</t>
+          <t>咨询线 78264.0；课程线 6619.0；医疗线 2318.2</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>107777.21</v>
+        <v>166831.25</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>85</v>
+        <v>77.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 91586.0；考证 10000.0；医疗线 6182.21；课程线 9.0</t>
+          <t>咨询线 128980.0；考证 30000.0；医疗线 7842.25；课程线 9.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45155.1</v>
+        <v>51228.9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>96.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 43594.0；医疗线 1494.1；课程线 67.0</t>
+          <t>咨询线 44788.0；医疗线 6021.4；其他 333.5；课程线 86.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15733</v>
+        <v>16952</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>89</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 13996.0；课程线 1737.0；其他 0.0</t>
+          <t>咨询线 15196.0；课程线 1756.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54407</v>
+        <v>150397</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>87.8</v>
+        <v>82.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 47788.0；课程线 6619.0</t>
+          <t>咨询线 123778.0；其他 20000.0；课程线 6619.0</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32180</v>
+        <v>32780</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27800</v>
+        <v>32180</v>
       </c>
     </row>
     <row r="5">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23620</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>刘士明</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14940</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="7">
@@ -1218,11 +1218,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>70796</v>
+        <v>231208</v>
       </c>
     </row>
     <row r="8">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>59616</v>
+        <v>70796</v>
       </c>
     </row>
     <row r="9">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49000</v>
+        <v>62388</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>张天昂</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>43800</v>
+        <v>59398</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>朱碧丹</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>33394</v>
+        <v>52398</v>
       </c>
     </row>
     <row r="12">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>仇晓艳</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>85298.64</v>
+        <v>60977.64</v>
       </c>
     </row>
     <row r="13">
@@ -1326,11 +1326,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>仇</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64963.61</v>
+        <v>39679</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>50606</v>
+        <v>39316</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>49866</v>
+        <v>32384</v>
       </c>
     </row>
     <row r="16">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>小程序</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>29394</v>
+        <v>31691.11</v>
       </c>
     </row>
     <row r="17">
@@ -1452,11 +1452,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="21">
@@ -1488,35 +1488,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>陈紫灵</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>考证</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈紫灵</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1980</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1542,11 +1542,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="26">
@@ -1556,15 +1556,87 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>陈翔宇</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>高曌</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>3</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>闫丽东</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>张虹</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>邓璐</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>333.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>汪贝妮</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -1630,22 +1702,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>390289</v>
+        <v>488348.57</v>
       </c>
       <c r="C2" t="n">
-        <v>67667.03999999999</v>
+        <v>74561.03999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>3611</v>
+        <v>6666</v>
       </c>
       <c r="E2" t="n">
-        <v>0.93</v>
+        <v>1.37</v>
       </c>
       <c r="F2" t="n">
-        <v>64056.04</v>
+        <v>67895.03999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>16.41</v>
+        <v>13.9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1660,10 +1732,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>881376</v>
+        <v>1503890</v>
       </c>
       <c r="C3" t="n">
-        <v>98600</v>
+        <v>228103.33</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1672,14 +1744,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>98600</v>
+        <v>228103.33</v>
       </c>
       <c r="G3" t="n">
-        <v>11.19</v>
+        <v>15.17</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 65900.0；精神心理 9000.0；暑假礼遇咨询套餐 8500.0</t>
+          <t>儿童青少年 127383.33；家庭守护计划2.0（二阶） 26820.0；电商咨询 26000.0</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1762,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>378795.56</v>
+        <v>675688.11</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1716,10 +1788,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120000</v>
+        <v>144800</v>
       </c>
       <c r="C5" t="n">
-        <v>91200</v>
+        <v>92200</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1728,14 +1800,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>91200</v>
+        <v>92200</v>
       </c>
       <c r="G5" t="n">
-        <v>76</v>
+        <v>63.67</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程） 91200.0</t>
+          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群检测（医生专用） 1000.0</t>
         </is>
       </c>
     </row>
@@ -1746,10 +1818,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>27354</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1758,12 +1830,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>27354</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>91.18000000000001</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 27354.0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1775,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>87380</v>
+        <v>97180</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1784,14 +1860,14 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>87380</v>
+        <v>97180</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>青少年成长基地3月营（金盏基地） 46800.0；青少年【未来之翼】身心节律复能7日营 33600.0；蛋壳跳动身心复能营21天（一阶） 5000.0</t>
+          <t>青少年成长基地3月营（金盏基地） 46800.0；青少年【未来之翼】身心节律复能7日营 33600.0；蛋壳跳动身心复能营21天（一阶） 14800.0</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1878,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1980</v>
+        <v>9900</v>
       </c>
       <c r="C8" t="n">
         <v>1980</v>
@@ -1817,7 +1893,7 @@
         <v>1980</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1832,10 +1908,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8771.360000000001</v>
+        <v>110467.86</v>
       </c>
       <c r="C9" t="n">
-        <v>3900</v>
+        <v>4696</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1844,14 +1920,14 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3900</v>
+        <v>4696</v>
       </c>
       <c r="G9" t="n">
-        <v>44.46</v>
+        <v>4.25</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8周系统性心身综合干预+深度服务包（全国统一价） 3900.0</t>
+          <t>8周系统性心身综合干预+深度服务包（全国统一价） 3900.0；门店《一日一生》 796.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>488348.57</v>
+        <v>670171.5699999999</v>
       </c>
       <c r="D2" t="n">
-        <v>1955</v>
+        <v>2264</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>488348.57</v>
+        <v>670171.5699999999</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>421051</v>
+        <v>595051</v>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>421051</v>
+        <v>595051</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>67297.57000000001</v>
+        <v>75120.57000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1873</v>
+        <v>2151</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>67297.57000000001</v>
+        <v>75120.57000000001</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1503890</v>
+        <v>1582374</v>
       </c>
       <c r="D5" t="n">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1503890</v>
+        <v>1582374</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>974626</v>
+        <v>1019916</v>
       </c>
       <c r="D6" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>974626</v>
+        <v>1019916</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>498866</v>
+        <v>532060</v>
       </c>
       <c r="D7" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>498866</v>
+        <v>532060</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>675688.11</v>
+        <v>684305.78</v>
       </c>
       <c r="D8" t="n">
-        <v>775</v>
+        <v>795</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>675688.11</v>
+        <v>684305.78</v>
       </c>
     </row>
     <row r="9">
@@ -627,20 +627,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>初诊</t>
+          <t>复诊</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>71337.03</v>
+        <v>433234.54</v>
       </c>
       <c r="D9" t="n">
-        <v>86</v>
+        <v>443</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>71337.03</v>
+        <v>433234.54</v>
       </c>
     </row>
     <row r="10">
@@ -651,20 +651,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>复诊</t>
+          <t>初诊</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>55105.91</v>
+        <v>251071.24</v>
       </c>
       <c r="D10" t="n">
-        <v>99</v>
+        <v>352</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>55105.91</v>
+        <v>251071.24</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>144800</v>
+        <v>170600</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>144800</v>
+        <v>170600</v>
       </c>
     </row>
     <row r="12">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>110467.86</v>
+        <v>190467.86</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>110467.86</v>
+        <v>190467.86</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>570022.17</v>
+        <v>575901.63</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 549245.17；咨询线 20398.0；其他 360.0；课程线 19.0</t>
+          <t>医疗线 555124.63；咨询线 20398.0；其他 360.0；课程线 19.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62113</v>
+        <v>69069</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>99.3</v>
+        <v>89.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 61674.0；课程线 439.0</t>
+          <t>咨询线 61674.0；课程线 7395.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>478417.99</v>
+        <v>529416.99</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72.7</v>
+        <v>63.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 347576.0；医疗线 56312.99；其他 40000.0；课程线 24629.0；工作坊 9900.0</t>
+          <t>咨询线 337176.0；其他 80000.0；医疗线 56612.99；课程线 44728.0；工作坊 9900.0；菌群线 1000.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>192656.97</v>
+        <v>203952.18</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>92.40000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 178086.0；医疗线 6914.97；课程线 6657.0；其他 999.0；菌群线 0.0</t>
+          <t>咨询线 188882.0；医疗线 7414.18；课程线 6657.0；其他 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>236801</v>
+        <v>257597</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 184582.0；菌群线 45600.0；课程线 6619.0</t>
+          <t>咨询线 205178.0；菌群线 45600.0；课程线 6619.0；医疗线 200.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>87201.2</v>
+        <v>105001.2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>89.8</v>
+        <v>85.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 78264.0；课程线 6619.0；医疗线 2318.2</t>
+          <t>咨询线 89464.0；课程线 13219.0；医疗线 2318.2；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166831.25</v>
+        <v>174531.25</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>77.3</v>
+        <v>78.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 128980.0；考证 30000.0；医疗线 7842.25；课程线 9.0</t>
+          <t>咨询线 136480.0；考证 30000.0；医疗线 8042.25；课程线 9.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51228.9</v>
+        <v>62024.9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>87.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 44788.0；医疗线 6021.4；其他 333.5；课程线 86.0</t>
+          <t>咨询线 55584.0；医疗线 6021.4；其他 333.5；课程线 86.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16952</v>
+        <v>18651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>89.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 15196.0；课程线 1756.0；其他 0.0</t>
+          <t>咨询线 15196.0；课程线 3455.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>150397</v>
+        <v>220245</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>82.3</v>
+        <v>58.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 123778.0；其他 20000.0；课程线 6619.0</t>
+          <t>咨询线 128778.0；其他 60000.0；菌群线 24800.0；课程线 6667.0</t>
         </is>
       </c>
     </row>
@@ -1128,11 +1128,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34860</v>
+        <v>42140</v>
       </c>
     </row>
     <row r="3">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32780</v>
+        <v>37760</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32180</v>
+        <v>34860</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24900</v>
+        <v>31160</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21200</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>231208</v>
+        <v>220808</v>
       </c>
     </row>
     <row r="8">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62388</v>
+        <v>69796</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59398</v>
+        <v>62388</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>朱碧丹</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>52398</v>
+        <v>53194</v>
       </c>
     </row>
     <row r="12">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>仇晓艳</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>60977.64</v>
+        <v>128100.6</v>
       </c>
     </row>
     <row r="13">
@@ -1326,11 +1326,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>仇</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>39679</v>
+        <v>112331.61</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>39316</v>
+        <v>75946</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>32384</v>
+        <v>64606</v>
       </c>
     </row>
     <row r="16">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>小程序</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31691.11</v>
+        <v>63726.2</v>
       </c>
     </row>
     <row r="17">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="22">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>40000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="27">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1596,11 +1596,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="29">
@@ -1614,11 +1614,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>333.5</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="30">
@@ -1632,11 +1632,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>汪贝妮</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>180</v>
+        <v>20000</v>
       </c>
     </row>
   </sheetData>
@@ -1702,26 +1702,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>488348.57</v>
+        <v>670171.5699999999</v>
       </c>
       <c r="C2" t="n">
-        <v>74561.03999999999</v>
+        <v>101119.04</v>
       </c>
       <c r="D2" t="n">
-        <v>6666</v>
+        <v>8248</v>
       </c>
       <c r="E2" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="F2" t="n">
-        <v>67895.03999999999</v>
+        <v>92871.03999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划领航营 17542.7；青少年同行者计划护航营（6月） 11685.0；青少年同行者计划-护航营 9826.0</t>
+          <t>青少年同行者计划领航营 42442.7；青少年同行者计划护航营（6月） 11685.0；青少年同行者计划-护航营 9826.0</t>
         </is>
       </c>
     </row>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1503890</v>
+        <v>1582374</v>
       </c>
       <c r="C3" t="n">
-        <v>228103.33</v>
+        <v>247521.33</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1744,14 +1744,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>228103.33</v>
+        <v>247521.33</v>
       </c>
       <c r="G3" t="n">
-        <v>15.17</v>
+        <v>15.64</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 127383.33；家庭守护计划2.0（二阶） 26820.0；电商咨询 26000.0</t>
+          <t>儿童青少年 131383.33；家庭守护计划2.0（二阶） 26820.0；电商咨询 26000.0</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>675688.11</v>
+        <v>684305.78</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>144800</v>
+        <v>170600</v>
       </c>
       <c r="C5" t="n">
         <v>92200</v>
@@ -1803,7 +1803,7 @@
         <v>92200</v>
       </c>
       <c r="G5" t="n">
-        <v>63.67</v>
+        <v>54.04</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>30000</v>
       </c>
       <c r="C6" t="n">
-        <v>27354</v>
+        <v>57080</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1830,14 +1830,14 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>27354</v>
+        <v>57080</v>
       </c>
       <c r="G6" t="n">
-        <v>91.18000000000001</v>
+        <v>190.27</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 27354.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 57080.0</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>97180</v>
+        <v>150780</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1860,14 +1860,14 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>97180</v>
+        <v>150780</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>青少年成长基地3月营（金盏基地） 46800.0；青少年【未来之翼】身心节律复能7日营 33600.0；蛋壳跳动身心复能营21天（一阶） 14800.0</t>
+          <t>青少年成长基地3月营（金盏基地） 83600.0；青少年【未来之翼】身心节律复能7日营 33600.0；海南心理能量唤醒营 16800.0</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
         <v>9900</v>
       </c>
       <c r="C8" t="n">
-        <v>1980</v>
+        <v>5940</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1980</v>
+        <v>5940</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>【廖文婷】萨提亚家庭系统工作坊 1980.0</t>
+          <t>【廖文婷】萨提亚家庭系统工作坊 5940.0</t>
         </is>
       </c>
     </row>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110467.86</v>
+        <v>190467.86</v>
       </c>
       <c r="C9" t="n">
-        <v>4696</v>
+        <v>5611.75</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1920,14 +1920,14 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4696</v>
+        <v>5611.75</v>
       </c>
       <c r="G9" t="n">
-        <v>4.25</v>
+        <v>2.95</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8周系统性心身综合干预+深度服务包（全国统一价） 3900.0；门店《一日一生》 796.0</t>
+          <t>8周系统性心身综合干预+深度服务包（全国统一价） 3900.0；[自我成长/疗愈] 完形心理认知课，增加智慧。 915.75；门店《一日一生》 796.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -469,10 +469,10 @@
         <v>2264</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>580961.5699999999</v>
       </c>
       <c r="F2" t="n">
-        <v>670171.5699999999</v>
+        <v>89210</v>
       </c>
     </row>
     <row r="3">
@@ -493,10 +493,10 @@
         <v>113</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>509131</v>
       </c>
       <c r="F3" t="n">
-        <v>595051</v>
+        <v>85920</v>
       </c>
     </row>
     <row r="4">
@@ -517,10 +517,10 @@
         <v>2151</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>71830.57000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>75120.57000000001</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="5">
@@ -541,10 +541,10 @@
         <v>307</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>304784</v>
       </c>
       <c r="F5" t="n">
-        <v>1582374</v>
+        <v>1277590</v>
       </c>
     </row>
     <row r="6">
@@ -565,10 +565,10 @@
         <v>170</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="F6" t="n">
-        <v>1019916</v>
+        <v>997916</v>
       </c>
     </row>
     <row r="7">
@@ -589,10 +589,10 @@
         <v>134</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>282784</v>
       </c>
       <c r="F7" t="n">
-        <v>532060</v>
+        <v>249276</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>684305.78</v>
+        <v>685434.5</v>
       </c>
       <c r="D8" t="n">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>31572.13</v>
       </c>
       <c r="F8" t="n">
-        <v>684305.78</v>
+        <v>653862.37</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>433234.54</v>
+        <v>434073.26</v>
       </c>
       <c r="D9" t="n">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1107.89</v>
       </c>
       <c r="F9" t="n">
-        <v>433234.54</v>
+        <v>432965.37</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>251071.24</v>
+        <v>251361.24</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>30464.24</v>
       </c>
       <c r="F10" t="n">
-        <v>251071.24</v>
+        <v>220897</v>
       </c>
     </row>
     <row r="11">
@@ -685,10 +685,10 @@
         <v>22</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>99200</v>
       </c>
       <c r="F11" t="n">
-        <v>170600</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="12">
@@ -781,10 +781,10 @@
         <v>70</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>47776.36</v>
       </c>
       <c r="F15" t="n">
-        <v>190467.86</v>
+        <v>142691.5</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>575901.63</v>
+        <v>596299.63</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>96.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 555124.63；咨询线 20398.0；其他 360.0；课程线 19.0</t>
+          <t>医疗线 555124.63；咨询线 40796.0；其他 360.0；课程线 19.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69069</v>
+        <v>48671</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>89.3</v>
+        <v>84.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 61674.0；课程线 7395.0</t>
+          <t>咨询线 41276.0；课程线 7395.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>203952.18</v>
+        <v>205080.9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>92.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 188882.0；医疗线 7414.18；课程线 6657.0；其他 999.0；菌群线 0.0</t>
+          <t>咨询线 188882.0；医疗线 8542.9；课程线 6657.0；其他 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>684305.78</v>
+        <v>685434.5</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>670171.5699999999</v>
+        <v>782913.5699999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2264</v>
+        <v>2558</v>
       </c>
       <c r="E2" t="n">
-        <v>580961.5699999999</v>
+        <v>660550.5699999999</v>
       </c>
       <c r="F2" t="n">
-        <v>89210</v>
+        <v>122363</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>595051</v>
+        <v>697991</v>
       </c>
       <c r="D3" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E3" t="n">
-        <v>509131</v>
+        <v>579071</v>
       </c>
       <c r="F3" t="n">
-        <v>85920</v>
+        <v>118920</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75120.57000000001</v>
+        <v>84922.57000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>2151</v>
+        <v>2431</v>
       </c>
       <c r="E4" t="n">
-        <v>71830.57000000001</v>
+        <v>81479.57000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>3290</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1582374</v>
+        <v>1750946</v>
       </c>
       <c r="D5" t="n">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="E5" t="n">
-        <v>304784</v>
+        <v>316376</v>
       </c>
       <c r="F5" t="n">
-        <v>1277590</v>
+        <v>1434570</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1019916</v>
+        <v>1116106</v>
       </c>
       <c r="D6" t="n">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="E6" t="n">
-        <v>22000</v>
+        <v>32000</v>
       </c>
       <c r="F6" t="n">
-        <v>997916</v>
+        <v>1084106</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>532060</v>
+        <v>596442</v>
       </c>
       <c r="D7" t="n">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="E7" t="n">
-        <v>282784</v>
+        <v>284376</v>
       </c>
       <c r="F7" t="n">
-        <v>249276</v>
+        <v>312066</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>685434.5</v>
+        <v>710791.84</v>
       </c>
       <c r="D8" t="n">
-        <v>807</v>
+        <v>896</v>
       </c>
       <c r="E8" t="n">
-        <v>31572.13</v>
+        <v>32427.1</v>
       </c>
       <c r="F8" t="n">
-        <v>653862.37</v>
+        <v>678364.74</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>434073.26</v>
+        <v>439387.6</v>
       </c>
       <c r="D9" t="n">
-        <v>449</v>
+        <v>493</v>
       </c>
       <c r="E9" t="n">
-        <v>1107.89</v>
+        <v>1962.86</v>
       </c>
       <c r="F9" t="n">
-        <v>432965.37</v>
+        <v>437424.74</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>251361.24</v>
+        <v>271404.24</v>
       </c>
       <c r="D10" t="n">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="E10" t="n">
         <v>30464.24</v>
       </c>
       <c r="F10" t="n">
-        <v>220897</v>
+        <v>240940</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>170600</v>
+        <v>178600</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
         <v>99200</v>
       </c>
       <c r="F11" t="n">
-        <v>71400</v>
+        <v>79400</v>
       </c>
     </row>
     <row r="12">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30000</v>
+        <v>30800</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>30000</v>
+        <v>30800</v>
       </c>
     </row>
     <row r="13">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>190467.86</v>
+        <v>192442.86</v>
       </c>
       <c r="D15" t="n">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="E15" t="n">
-        <v>47776.36</v>
+        <v>48775.36</v>
       </c>
       <c r="F15" t="n">
-        <v>142691.5</v>
+        <v>143667.5</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>596299.63</v>
+        <v>623807.92</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>93.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 555124.63；咨询线 40796.0；其他 360.0；课程线 19.0</t>
+          <t>医疗线 575852.92；咨询线 40796.0；课程线 6619.0；其他 540.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48671</v>
+        <v>81488</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>84.8</v>
+        <v>89.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 41276.0；课程线 7395.0</t>
+          <t>咨询线 72674.0；课程线 7414.0；考证 800.0；医疗线 600.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57135</v>
+        <v>58154</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>67.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 38780.0；医疗线 17000.0；其他 999.0；课程线 356.0</t>
+          <t>咨询线 39780.0；医疗线 17000.0；其他 999.0；课程线 375.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>529416.99</v>
+        <v>625443.51</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 337176.0；其他 80000.0；医疗线 56612.99；课程线 44728.0；工作坊 9900.0；菌群线 1000.0</t>
+          <t>咨询线 397772.0；其他 80000.0；课程线 71176.0；医疗线 57595.51；工作坊 9900.0；菌群线 9000.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>205080.9</v>
+        <v>227628.9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 188882.0；医疗线 8542.9；课程线 6657.0；其他 999.0；菌群线 0.0</t>
+          <t>咨询线 209680.0；医疗线 10292.9；课程线 6657.0；其他 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>257597</v>
+        <v>268393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79.7</v>
+        <v>80.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 205178.0；菌群线 45600.0；课程线 6619.0；医疗线 200.0</t>
+          <t>咨询线 215576.0；菌群线 45600.0；课程线 6619.0；其他 398.0；医疗线 200.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>105001.2</v>
+        <v>105466.36</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 89464.0；课程线 13219.0；医疗线 2318.2；菌群线 0.0</t>
+          <t>咨询线 89862.0；课程线 13219.0；医疗线 2385.36；其他 0.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>174531.25</v>
+        <v>196472.65</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78.2</v>
+        <v>80.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 136480.0；考证 30000.0；医疗线 8042.25；课程线 9.0；菌群线 0.0</t>
+          <t>咨询线 157678.0；考证 30000.0；医疗线 8387.65；其他 398.0；课程线 9.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62024.9</v>
+        <v>62082.9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>89.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 55584.0；医疗线 6021.4；其他 333.5；课程线 86.0</t>
+          <t>咨询线 55584.0；医疗线 6050.4；其他 333.5；课程线 115.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18651</v>
+        <v>19068</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>81.5</v>
+        <v>81.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 15196.0；课程线 3455.0；其他 0.0</t>
+          <t>咨询线 15594.0；课程线 3474.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>220245</v>
+        <v>231060</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>58.5</v>
+        <v>60.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 128778.0；其他 60000.0；菌群线 24800.0；课程线 6667.0</t>
+          <t>咨询线 139574.0；其他 60000.0；菌群线 24800.0；课程线 6686.0</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,11 +1128,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>42140</v>
+        <v>44820</v>
       </c>
     </row>
     <row r="3">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>37760</v>
+        <v>42140</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34860</v>
+        <v>37760</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31160</v>
+        <v>34280</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26400</v>
+        <v>31380</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>220808</v>
+        <v>231604</v>
       </c>
     </row>
     <row r="8">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>70796</v>
+        <v>82188</v>
       </c>
     </row>
     <row r="9">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>69796</v>
+        <v>80194</v>
       </c>
     </row>
     <row r="10">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>62388</v>
+        <v>70796</v>
       </c>
     </row>
     <row r="11">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>53194</v>
+        <v>54190</v>
       </c>
     </row>
     <row r="12">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>112331.61</v>
+        <v>115986.61</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>75946</v>
+        <v>84726.2</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>64606</v>
+        <v>77660.28999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>63726.2</v>
+        <v>53951</v>
       </c>
     </row>
     <row r="17">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1516,19 +1516,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>考证</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="25">
@@ -1538,33 +1538,33 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1980</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60000</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="27">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="28">
@@ -1592,11 +1592,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1610,15 +1610,15 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="30">
@@ -1628,14 +1628,32 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>岳伟伟</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>5</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>岳伟伟</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>赵越</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -1702,26 +1720,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>670171.5699999999</v>
+        <v>782913.5699999999</v>
       </c>
       <c r="C2" t="n">
-        <v>101119.04</v>
+        <v>132973.04</v>
       </c>
       <c r="D2" t="n">
-        <v>8248</v>
+        <v>8800</v>
       </c>
       <c r="E2" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="F2" t="n">
-        <v>92871.03999999999</v>
+        <v>124173.04</v>
       </c>
       <c r="G2" t="n">
-        <v>13.86</v>
+        <v>15.86</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划领航营 42442.7；青少年同行者计划护航营（6月） 11685.0；青少年同行者计划-护航营 9826.0</t>
+          <t>青少年同行者计划领航营 45759.7；少年说陪伴计划 19800.0；青少年同行者计划 13856.67</t>
         </is>
       </c>
     </row>
@@ -1732,10 +1750,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1582374</v>
+        <v>1750946</v>
       </c>
       <c r="C3" t="n">
-        <v>247521.33</v>
+        <v>279017.33</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1744,14 +1762,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>247521.33</v>
+        <v>279017.33</v>
       </c>
       <c r="G3" t="n">
-        <v>15.64</v>
+        <v>15.94</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 131383.33；家庭守护计划2.0（二阶） 26820.0；电商咨询 26000.0</t>
+          <t>儿童青少年 155781.33；电商咨询 31500.0；家庭守护计划2.0（二阶） 26820.0</t>
         </is>
       </c>
     </row>
@@ -1762,10 +1780,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>685434.5</v>
+        <v>710791.84</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1774,12 +1792,16 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>20分钟问诊（专家医师） -线上 500.0；AI测评V9.0-多维父母教养行为测评 49.0；AI测评V5.0-原型家庭模式评估 29.0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1788,10 +1810,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>170600</v>
+        <v>178600</v>
       </c>
       <c r="C5" t="n">
-        <v>92200</v>
+        <v>117000</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1800,14 +1822,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>92200</v>
+        <v>117000</v>
       </c>
       <c r="G5" t="n">
-        <v>54.04</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群检测（医生专用） 1000.0</t>
+          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群移植 24800.0；肠道菌群检测（医生专用） 1000.0</t>
         </is>
       </c>
     </row>
@@ -1818,10 +1840,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30000</v>
+        <v>30800</v>
       </c>
       <c r="C6" t="n">
-        <v>57080</v>
+        <v>76054.88</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1830,14 +1852,14 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>57080</v>
+        <v>76054.88</v>
       </c>
       <c r="G6" t="n">
-        <v>190.27</v>
+        <v>246.93</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 57080.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 75254.88；[心灯计划]咨询师执业能力培养 (订金，含心理学入门基础实体书) 800.0</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>150780</v>
+        <v>152280</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1860,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>150780</v>
+        <v>152280</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1908,10 +1930,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>190467.86</v>
+        <v>192442.86</v>
       </c>
       <c r="C9" t="n">
-        <v>5611.75</v>
+        <v>6009.75</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1920,14 +1942,14 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5611.75</v>
+        <v>6009.75</v>
       </c>
       <c r="G9" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8周系统性心身综合干预+深度服务包（全国统一价） 3900.0；[自我成长/疗愈] 完形心理认知课，增加智慧。 915.75；门店《一日一生》 796.0</t>
+          <t>8周系统性心身综合干预+深度服务包（全国统一价） 3900.0；门店《一日一生》 1194.0；[自我成长/疗愈] 完形心理认知课，增加智慧。 915.75</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>782913.5699999999</v>
+        <v>922904.5699999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2558</v>
+        <v>2964</v>
       </c>
       <c r="E2" t="n">
-        <v>660550.5699999999</v>
+        <v>766447.5699999999</v>
       </c>
       <c r="F2" t="n">
-        <v>122363</v>
+        <v>156457</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>697991</v>
+        <v>825942</v>
       </c>
       <c r="D3" t="n">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="E3" t="n">
-        <v>579071</v>
+        <v>673032</v>
       </c>
       <c r="F3" t="n">
-        <v>118920</v>
+        <v>152910</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>84922.57000000001</v>
+        <v>96962.57000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>2431</v>
+        <v>2817</v>
       </c>
       <c r="E4" t="n">
-        <v>81479.57000000001</v>
+        <v>93415.57000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>3443</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1750946</v>
+        <v>1912854</v>
       </c>
       <c r="D5" t="n">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="E5" t="n">
-        <v>316376</v>
+        <v>385594</v>
       </c>
       <c r="F5" t="n">
-        <v>1434570</v>
+        <v>1527260</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1116106</v>
+        <v>1177602</v>
       </c>
       <c r="D6" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E6" t="n">
-        <v>32000</v>
+        <v>22000</v>
       </c>
       <c r="F6" t="n">
-        <v>1084106</v>
+        <v>1155602</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>596442</v>
+        <v>686854</v>
       </c>
       <c r="D7" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="E7" t="n">
-        <v>284376</v>
+        <v>363594</v>
       </c>
       <c r="F7" t="n">
-        <v>312066</v>
+        <v>323260</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>710791.84</v>
+        <v>835657.71</v>
       </c>
       <c r="D8" t="n">
-        <v>896</v>
+        <v>1032</v>
       </c>
       <c r="E8" t="n">
-        <v>32427.1</v>
+        <v>34268.31</v>
       </c>
       <c r="F8" t="n">
-        <v>678364.74</v>
+        <v>801389.4</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>439387.6</v>
+        <v>517802.98</v>
       </c>
       <c r="D9" t="n">
-        <v>493</v>
+        <v>558</v>
       </c>
       <c r="E9" t="n">
-        <v>1962.86</v>
+        <v>2625.58</v>
       </c>
       <c r="F9" t="n">
-        <v>437424.74</v>
+        <v>515177.4</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>271404.24</v>
+        <v>317854.73</v>
       </c>
       <c r="D10" t="n">
-        <v>403</v>
+        <v>474</v>
       </c>
       <c r="E10" t="n">
-        <v>30464.24</v>
+        <v>31642.73</v>
       </c>
       <c r="F10" t="n">
-        <v>240940</v>
+        <v>286212</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>178600</v>
+        <v>224200</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
         <v>99200</v>
       </c>
       <c r="F11" t="n">
-        <v>79400</v>
+        <v>125000</v>
       </c>
     </row>
     <row r="12">
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30800</v>
+        <v>34600</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="F12" t="n">
         <v>30800</v>
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>5940</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="14">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>192442.86</v>
+        <v>209234.86</v>
       </c>
       <c r="D15" t="n">
-        <v>133</v>
+        <v>225</v>
       </c>
       <c r="E15" t="n">
-        <v>48775.36</v>
+        <v>63975.36</v>
       </c>
       <c r="F15" t="n">
-        <v>143667.5</v>
+        <v>145259.5</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>623807.92</v>
+        <v>742474.92</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>92.3</v>
+        <v>93.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 575852.92；咨询线 40796.0；课程线 6619.0；其他 540.0</t>
+          <t>医疗线 694500.92；咨询线 40796.0；课程线 6638.0；其他 540.0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81488</v>
+        <v>83487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>89.2</v>
+        <v>87</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 72674.0；课程线 7414.0；考证 800.0；医疗线 600.0</t>
+          <t>咨询线 72674.0；课程线 7433.0；营地 1980.0；考证 800.0；医疗线 600.0</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58154</v>
+        <v>79027.84</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -889,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>68.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 39780.0；医疗线 17000.0；其他 999.0；课程线 375.0</t>
+          <t>咨询线 60178.0；医疗线 17456.84；其他 999.0；课程线 394.0</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>625443.51</v>
+        <v>715177.51</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63.6</v>
+        <v>57</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 397772.0；其他 80000.0；课程线 71176.0；医疗线 57595.51；工作坊 9900.0；菌群线 9000.0</t>
+          <t>咨询线 407772.0；课程线 104214.0；其他 80796.0；医疗线 57895.51；菌群线 54600.0；工作坊 9900.0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>227628.9</v>
+        <v>231626.72</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>92.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 209680.0；医疗线 10292.9；课程线 6657.0；其他 999.0；菌群线 0.0</t>
+          <t>咨询线 210078.0；医疗线 13873.72；课程线 6676.0；其他 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>268393</v>
+        <v>278412</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80.3</v>
+        <v>81</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 215576.0；菌群线 45600.0；课程线 6619.0；其他 398.0；医疗线 200.0</t>
+          <t>咨询线 225576.0；菌群线 45600.0；课程线 6638.0；其他 398.0；医疗线 200.0</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>105466.36</v>
+        <v>129014.36</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>85.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 89862.0；课程线 13219.0；医疗线 2385.36；其他 0.0；菌群线 0.0</t>
+          <t>咨询线 108460.0；课程线 14209.0；营地 3960.0；医疗线 2385.36；其他 0.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>196472.65</v>
+        <v>214768.65</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>80.3</v>
+        <v>81.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 157678.0；考证 30000.0；医疗线 8387.65；其他 398.0；课程线 9.0；菌群线 0.0</t>
+          <t>咨询线 175576.0；考证 30000.0；医疗线 8387.65；其他 796.0；课程线 9.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62082.9</v>
+        <v>62519.9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>89.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 55584.0；医疗线 6050.4；其他 333.5；课程线 115.0</t>
+          <t>咨询线 55584.0；医疗线 6089.4；其他 731.5；课程线 115.0</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19068</v>
+        <v>34466</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>81.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 15594.0；课程线 3474.0；其他 0.0</t>
+          <t>咨询线 30992.0；课程线 3474.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>231060</v>
+        <v>231031</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 139574.0；其他 60000.0；菌群线 24800.0；课程线 6686.0</t>
+          <t>咨询线 139574.0；其他 60000.0；菌群线 24800.0；课程线 6657.0</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,11 +1128,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>44820</v>
+        <v>67280</v>
       </c>
     </row>
     <row r="3">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>42140</v>
+        <v>49560</v>
       </c>
     </row>
     <row r="4">
@@ -1164,11 +1164,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37760</v>
+        <v>47120</v>
       </c>
     </row>
     <row r="5">
@@ -1182,11 +1182,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34280</v>
+        <v>44820</v>
       </c>
     </row>
     <row r="6">
@@ -1200,11 +1200,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31380</v>
+        <v>39600</v>
       </c>
     </row>
     <row r="7">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82188</v>
+        <v>92188</v>
       </c>
     </row>
     <row r="9">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>54190</v>
+        <v>63592</v>
       </c>
     </row>
     <row r="12">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>128100.6</v>
+        <v>167786.61</v>
       </c>
     </row>
     <row r="13">
@@ -1326,11 +1326,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>115986.61</v>
+        <v>153676.6</v>
       </c>
     </row>
     <row r="14">
@@ -1344,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>84726.2</v>
+        <v>98086.28999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77660.28999999999</v>
+        <v>93816.2</v>
       </c>
     </row>
     <row r="16">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>53951</v>
+        <v>60763</v>
       </c>
     </row>
     <row r="17">
@@ -1398,11 +1398,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49600</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="18">
@@ -1416,11 +1416,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>李颜君</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>45600</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="19">
@@ -1434,11 +1434,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>李颜君</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>24800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="20">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1524,101 +1524,101 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>800</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>考证</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>冯兰兰</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>刘馨</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>60000</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>40000</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>40000</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="30">
@@ -1628,15 +1628,15 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>20000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="31">
@@ -1646,14 +1646,68 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>陈翔宇</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>高曌</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>岳伟伟</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>20796</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>5</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>赵越</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D34" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -1720,26 +1774,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>782913.5699999999</v>
+        <v>922904.5699999999</v>
       </c>
       <c r="C2" t="n">
-        <v>132973.04</v>
+        <v>156150.74</v>
       </c>
       <c r="D2" t="n">
-        <v>8800</v>
+        <v>9511</v>
       </c>
       <c r="E2" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="F2" t="n">
-        <v>124173.04</v>
+        <v>146639.74</v>
       </c>
       <c r="G2" t="n">
-        <v>15.86</v>
+        <v>15.89</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划领航营 45759.7；少年说陪伴计划 19800.0；青少年同行者计划 13856.67</t>
+          <t>青少年同行者计划领航营 50739.7；少年说陪伴计划 26400.0；青少年同行者计划向阳营 14593.37</t>
         </is>
       </c>
     </row>
@@ -1750,10 +1804,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1750946</v>
+        <v>1912854</v>
       </c>
       <c r="C3" t="n">
-        <v>279017.33</v>
+        <v>315517.33</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1762,14 +1816,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>279017.33</v>
+        <v>315517.33</v>
       </c>
       <c r="G3" t="n">
-        <v>15.94</v>
+        <v>16.49</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 155781.33；电商咨询 31500.0；家庭守护计划2.0（二阶） 26820.0</t>
+          <t>儿童青少年 181781.33；精神心理 31696.0；电商咨询 31500.0</t>
         </is>
       </c>
     </row>
@@ -1780,26 +1834,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>710791.84</v>
+        <v>835657.71</v>
       </c>
       <c r="C4" t="n">
-        <v>578</v>
+        <v>3178</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>578</v>
+        <v>2578</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08</v>
+        <v>0.31</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20分钟问诊（专家医师） -线上 500.0；AI测评V9.0-多维父母教养行为测评 49.0；AI测评V5.0-原型家庭模式评估 29.0</t>
+          <t>线上/线下门诊 1800.0；20分钟问诊（医师） -线上 800.0；20分钟问诊（专家医师） -线上 500.0</t>
         </is>
       </c>
     </row>
@@ -1810,10 +1864,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>178600</v>
+        <v>224200</v>
       </c>
       <c r="C5" t="n">
-        <v>117000</v>
+        <v>138800</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1822,14 +1876,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>117000</v>
+        <v>138800</v>
       </c>
       <c r="G5" t="n">
-        <v>65.51000000000001</v>
+        <v>61.91</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群移植 24800.0；肠道菌群检测（医生专用） 1000.0</t>
+          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群移植 24800.0；肠道菌群移植（双疗程优惠） 20800.0</t>
         </is>
       </c>
     </row>
@@ -1840,10 +1894,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30800</v>
+        <v>34600</v>
       </c>
       <c r="C6" t="n">
-        <v>76054.88</v>
+        <v>77633.17999999999</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1852,14 +1906,14 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>76054.88</v>
+        <v>77633.17999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>246.93</v>
+        <v>224.37</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 75254.88；[心灯计划]咨询师执业能力培养 (订金，含心理学入门基础实体书) 800.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 75254.88；心理咨询取证班+实操案例直播课+群内答疑+讲义=3188 1578.3；[心灯计划]咨询师执业能力培养 (订金，含心理学入门基础实体书) 800.0</t>
         </is>
       </c>
     </row>
@@ -1870,10 +1924,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>5940</v>
       </c>
       <c r="C7" t="n">
-        <v>152280</v>
+        <v>172080</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1882,14 +1936,14 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>152280</v>
+        <v>172080</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2896.97</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>青少年成长基地3月营（金盏基地） 83600.0；青少年【未来之翼】身心节律复能7日营 33600.0；海南心理能量唤醒营 16800.0</t>
+          <t>青少年成长基地3月营（金盏基地） 83600.0；蛋壳跳动身心复能营21天（一阶） 34600.0；青少年【未来之翼】身心节律复能7日营 33600.0</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1984,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>192442.86</v>
+        <v>209234.86</v>
       </c>
       <c r="C9" t="n">
         <v>6009.75</v>
@@ -1945,7 +1999,7 @@
         <v>6009.75</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -2436,23 +2436,23 @@
         <v>11815</v>
       </c>
       <c r="D2" t="n">
-        <v>1385</v>
+        <v>14207</v>
       </c>
       <c r="E2" t="n">
-        <v>1385</v>
+        <v>11596</v>
       </c>
       <c r="F2" t="n">
-        <v>11.72</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2611</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 299.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 266.0；1号课：睡前静心基础营-心理学网课+陪伴能量提升 203.0</t>
+          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 2392.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 1280.0；青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题 1083.0</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>131041.74</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2480,12 +2480,16 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>131041.74</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>青少年同行者计划领航营 69328.7；青少年同行者计划-护航营 16598.0；青少年同行者计划向阳营 14593.37</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2502,7 +2506,7 @@
         <v>48398</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>293577.33</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2511,12 +2515,16 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>293577.33</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>606.59</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>儿童青少年 195981.33；精神心理 37196.0；电商咨询 31500.0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2533,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>85530</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2542,12 +2550,16 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>85530</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>家庭守护计划2.0（二阶） 26820.0；少年说陪伴计划 26400.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2564,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>163600</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2573,12 +2585,16 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>163600</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群移植 49600.0；肠道菌群移植（双疗程优惠） 20800.0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2595,23 +2611,23 @@
         <v>787371.21</v>
       </c>
       <c r="D7" t="n">
-        <v>1341.59</v>
+        <v>4519.59</v>
       </c>
       <c r="E7" t="n">
-        <v>1341.59</v>
+        <v>1941.59</v>
       </c>
       <c r="F7" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2578</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59</t>
+          <t>线上/线下门诊 1800.0；【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59；20分钟问诊（医师） -线上 800.0</t>
         </is>
       </c>
     </row>
@@ -2630,23 +2646,23 @@
         <v>32332.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1056</v>
+        <v>268896.93</v>
       </c>
       <c r="E8" t="n">
-        <v>1056</v>
+        <v>1160</v>
       </c>
       <c r="F8" t="n">
-        <v>3.27</v>
+        <v>3.59</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>267736.93</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>828.0700000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[自我成长/疗愈] 完形心理认知课，增加智慧。 999.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 38.0；（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题 19.0</t>
+          <t>青少年成长基地3月营（金盏基地） 83600.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 75254.88；蛋壳跳动身心复能营21天（一阶） 34600.0</t>
         </is>
       </c>
     </row>
@@ -2665,23 +2681,23 @@
         <v>11815</v>
       </c>
       <c r="D9" t="n">
-        <v>1385</v>
+        <v>14207</v>
       </c>
       <c r="E9" t="n">
-        <v>1385</v>
+        <v>11596</v>
       </c>
       <c r="F9" t="n">
-        <v>11.72</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2611</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 299.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 266.0；1号课：睡前静心基础营-心理学网课+陪伴能量提升 203.0</t>
+          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 2392.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 1280.0；青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题 1083.0</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>131041.74</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2709,12 +2725,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>131041.74</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>青少年同行者计划领航营 69328.7；青少年同行者计划-护航营 16598.0；青少年同行者计划向阳营 14593.37</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2731,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>73298</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -2740,12 +2760,16 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>73298</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>儿童青少年 50900.0；精神心理 22398.0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2762,7 +2786,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>82170</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -2771,12 +2795,16 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>82170</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>家庭守护计划2.0（二阶） 26820.0；少年说陪伴计划 26400.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2793,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>96200</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -2802,12 +2830,16 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>96200</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>肠道菌群移植 49600.0；肠道菌群移植（双疗程） 45600.0；肠道菌群检测 1000.0</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2824,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>778</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -2833,12 +2865,16 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>778</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20分钟问诊（专家医师） -线上 500.0；20分钟问诊（医师） -线上 200.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2855,7 +2891,7 @@
         <v>999</v>
       </c>
       <c r="D15" t="n">
-        <v>999</v>
+        <v>188106.93</v>
       </c>
       <c r="E15" t="n">
         <v>999</v>
@@ -2864,14 +2900,14 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>187107.93</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>18729.52</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[自我成长/疗愈] 完形心理认知课，增加智慧。 999.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 75254.88；青少年成长基地3月营（金盏基地） 46800.0；蛋壳跳动身心复能营21天（一阶） 34600.0</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2926,7 @@
         <v>48398</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>220279.33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -2899,12 +2935,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>220279.33</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>455.14</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>儿童青少年 145081.33；电商咨询 31500.0；精神心理 14798.0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2921,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3360</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -2930,12 +2970,16 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3360</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>少年说倾听计划 3360.0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2952,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>67400</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -2961,12 +3005,16 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>67400</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>肠道菌群移植（双疗程） 45600.0；肠道菌群移植（双疗程优惠） 20800.0；肠道菌群检测（医生专用） 1000.0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2983,23 +3031,23 @@
         <v>787371.21</v>
       </c>
       <c r="D19" t="n">
-        <v>1341.59</v>
+        <v>3741.59</v>
       </c>
       <c r="E19" t="n">
-        <v>1341.59</v>
+        <v>1941.59</v>
       </c>
       <c r="F19" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59</t>
+          <t>线上/线下门诊 1800.0；【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59；20分钟问诊（医师） -线上 600.0</t>
         </is>
       </c>
     </row>
@@ -3018,23 +3066,23 @@
         <v>31333.5</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>80790</v>
       </c>
       <c r="E20" t="n">
-        <v>57</v>
+        <v>161</v>
       </c>
       <c r="F20" t="n">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>80629</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>257.33</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 38.0；（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题 19.0</t>
+          <t>青少年成长基地3月营（金盏基地） 36800.0；青少年【未来之翼】身心节律复能7日营 33600.0；完形心理成长计划 4999.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>147790.57</v>
+        <v>147733.57</v>
       </c>
       <c r="E2" t="n">
-        <v>4654</v>
+        <v>4650</v>
       </c>
       <c r="F2" t="n">
-        <v>147790.57</v>
+        <v>147733.57</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>799963</v>
+        <v>814903</v>
       </c>
       <c r="E3" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F3" t="n">
-        <v>799963</v>
+        <v>814903</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2242334.01</v>
+        <v>2231338.01</v>
       </c>
       <c r="E4" t="n">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F4" t="n">
         <v>285946</v>
       </c>
       <c r="G4" t="n">
-        <v>1956388.01</v>
+        <v>1945392.01</v>
       </c>
     </row>
     <row r="5">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1582912.01</v>
+        <v>1573110.01</v>
       </c>
       <c r="E5" t="n">
         <v>311</v>
@@ -571,7 +571,7 @@
         <v>10000</v>
       </c>
       <c r="G5" t="n">
-        <v>1572912.01</v>
+        <v>1563110.01</v>
       </c>
     </row>
     <row r="6">
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>659422</v>
+        <v>658228</v>
       </c>
       <c r="E6" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F6" t="n">
         <v>275946</v>
       </c>
       <c r="G6" t="n">
-        <v>383476</v>
+        <v>382282</v>
       </c>
     </row>
     <row r="7">
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1714636</v>
+        <v>1677244</v>
       </c>
       <c r="E7" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F7" t="n">
-        <v>1248036</v>
+        <v>1218924</v>
       </c>
       <c r="G7" t="n">
-        <v>466600</v>
+        <v>458320</v>
       </c>
     </row>
     <row r="8">
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1259492</v>
+        <v>1261900</v>
       </c>
       <c r="E8" t="n">
         <v>116</v>
       </c>
       <c r="F8" t="n">
-        <v>950732</v>
+        <v>961420</v>
       </c>
       <c r="G8" t="n">
-        <v>308760</v>
+        <v>300480</v>
       </c>
     </row>
     <row r="9">
@@ -678,13 +678,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>455144</v>
+        <v>415344</v>
       </c>
       <c r="E9" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F9" t="n">
-        <v>297304</v>
+        <v>257504</v>
       </c>
       <c r="G9" t="n">
         <v>157840</v>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1102958.9</v>
+        <v>1130205.1</v>
       </c>
       <c r="E11" t="n">
-        <v>1212</v>
+        <v>1346</v>
       </c>
       <c r="F11" t="n">
         <v>41814.73</v>
       </c>
       <c r="G11" t="n">
-        <v>1061144.17</v>
+        <v>1088390.37</v>
       </c>
     </row>
     <row r="12">
@@ -765,16 +765,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>694148.39</v>
+        <v>707202.59</v>
       </c>
       <c r="E12" t="n">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="F12" t="n">
         <v>7308</v>
       </c>
       <c r="G12" t="n">
-        <v>686840.39</v>
+        <v>699894.59</v>
       </c>
     </row>
     <row r="13">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>408810.51</v>
+        <v>423002.51</v>
       </c>
       <c r="E13" t="n">
-        <v>582</v>
+        <v>705</v>
       </c>
       <c r="F13" t="n">
         <v>34506.73</v>
       </c>
       <c r="G13" t="n">
-        <v>374303.78</v>
+        <v>388495.78</v>
       </c>
     </row>
     <row r="14">
@@ -823,16 +823,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>598375.5600000001</v>
+        <v>674858.34</v>
       </c>
       <c r="E14" t="n">
-        <v>1371</v>
+        <v>1231</v>
       </c>
       <c r="F14" t="n">
         <v>125210.36</v>
       </c>
       <c r="G14" t="n">
-        <v>473165.2</v>
+        <v>549647.98</v>
       </c>
     </row>
     <row r="15">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>147790.57</v>
+        <v>147733.57</v>
       </c>
       <c r="E15" t="n">
-        <v>4654</v>
+        <v>4650</v>
       </c>
       <c r="F15" t="n">
-        <v>147790.57</v>
+        <v>147733.57</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>799963</v>
+        <v>814903</v>
       </c>
       <c r="E16" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F16" t="n">
-        <v>799963</v>
+        <v>814903</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1248036</v>
+        <v>1218924</v>
       </c>
       <c r="E20" t="n">
         <v>214</v>
       </c>
       <c r="F20" t="n">
-        <v>1248036</v>
+        <v>1218924</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>950732</v>
+        <v>961420</v>
       </c>
       <c r="E21" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" t="n">
-        <v>950732</v>
+        <v>961420</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>297304</v>
+        <v>257504</v>
       </c>
       <c r="E22" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F22" t="n">
-        <v>297304</v>
+        <v>257504</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1229,16 +1229,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1956388.01</v>
+        <v>1945392.01</v>
       </c>
       <c r="E28" t="n">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1956388.01</v>
+        <v>1945392.01</v>
       </c>
     </row>
     <row r="29">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1572912.01</v>
+        <v>1563110.01</v>
       </c>
       <c r="E29" t="n">
         <v>310</v>
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1572912.01</v>
+        <v>1563110.01</v>
       </c>
     </row>
     <row r="30">
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>383476</v>
+        <v>382282</v>
       </c>
       <c r="E30" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>383476</v>
+        <v>382282</v>
       </c>
     </row>
     <row r="31">
@@ -1316,16 +1316,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>466600</v>
+        <v>458320</v>
       </c>
       <c r="E31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>466600</v>
+        <v>458320</v>
       </c>
     </row>
     <row r="32">
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>308760</v>
+        <v>300480</v>
       </c>
       <c r="E32" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>308760</v>
+        <v>300480</v>
       </c>
     </row>
     <row r="33">
@@ -1432,16 +1432,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1061144.17</v>
+        <v>1088390.37</v>
       </c>
       <c r="E35" t="n">
-        <v>1142</v>
+        <v>1276</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1061144.17</v>
+        <v>1088390.37</v>
       </c>
     </row>
     <row r="36">
@@ -1461,16 +1461,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>686840.39</v>
+        <v>699894.59</v>
       </c>
       <c r="E36" t="n">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>686840.39</v>
+        <v>699894.59</v>
       </c>
     </row>
     <row r="37">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>374303.78</v>
+        <v>388495.78</v>
       </c>
       <c r="E37" t="n">
-        <v>526</v>
+        <v>649</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>374303.78</v>
+        <v>388495.78</v>
       </c>
     </row>
     <row r="38">
@@ -1519,16 +1519,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>473165.2</v>
+        <v>549647.98</v>
       </c>
       <c r="E38" t="n">
-        <v>1135</v>
+        <v>995</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>473165.2</v>
+        <v>549647.98</v>
       </c>
     </row>
   </sheetData>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1013467.92</v>
+        <v>1041378.92</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1597,11 +1597,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>93.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>医疗 944981.92；咨询 61194.0；家守/千金方/少年说 6600.0；其他 692.0</t>
+          <t>医疗 972352.92；咨询 61194.0；家守/千金方/少年说 6600.0；其他 1232.0</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>93303.84</v>
+        <v>91623.84</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1653,11 +1653,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>77.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>咨询 71970.0；医疗 17856.84；其他 1797.0；家守/千金方/少年说 1680.0</t>
+          <t>咨询 71970.0；医疗 17856.84；其他 1797.0；家守/千金方/少年说 0.0</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>369595.9</v>
+        <v>370371.98</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1709,11 +1709,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>咨询 314760.0；家守/千金方/少年说 26400.0；其他 24814.43；医疗 3621.47；菌群 0.0</t>
+          <t>咨询 314760.0；家守/千金方/少年说 26400.0；其他 25590.51；医疗 3621.47；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -1757,19 +1757,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>210874.8</v>
+        <v>258457.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49.5</v>
+        <v>54.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>咨询 104444.0；其他 93230.8；家守/千金方/少年说 13200.0；菌群 0.0</t>
+          <t>其他 140813.4；咨询 104444.0；家守/千金方/少年说 13200.0；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>372511.87</v>
+        <v>373364.21</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1793,11 +1793,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>76.7</v>
+        <v>76.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>咨询 285772.0；其他 52819.87；家守/千金方/少年说 33420.0；医疗 500.0；菌群 0.0</t>
+          <t>咨询 285772.0；其他 53672.21；家守/千金方/少年说 33420.0；医疗 500.0；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>242704.11</v>
+        <v>206497.87</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1821,11 +1821,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>51.9</v>
+        <v>55.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>咨询 125964.01；其他 90272.1；家守/千金方/少年说 26400.0；医疗 68.0</t>
+          <t>咨询 114968.01；其他 71661.86；家守/千金方/少年说 19800.0；医疗 68.0</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>63761.8</v>
+        <v>63608</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,11 +1849,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>咨询 51778.0；家守/千金方/少年说 11640.0；其他 219.0；医疗 124.8</t>
+          <t>咨询 51778.0；家守/千金方/少年说 11640.0；其他 190.0</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29086</v>
+        <v>74457</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,11 +1905,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>94.2</v>
+        <v>97.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>其他 27406.0；家守/千金方/少年说 1680.0</t>
+          <t>其他 72777.0；家守/千金方/少年说 1680.0</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1013467.92</v>
+        <v>1041378.92</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1933,11 +1933,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>93.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>医疗 944981.92；咨询 61194.0；家守/千金方/少年说 6600.0；其他 692.0</t>
+          <t>医疗 972352.92；咨询 61194.0；家守/千金方/少年说 6600.0；其他 1232.0</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>93303.84</v>
+        <v>91623.84</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1989,11 +1989,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>77.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>咨询 71970.0；医疗 17856.84；其他 1797.0；家守/千金方/少年说 1680.0</t>
+          <t>咨询 71970.0；医疗 17856.84；其他 1797.0；家守/千金方/少年说 0.0</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>369595.9</v>
+        <v>370371.98</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2045,11 +2045,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>咨询 314760.0；家守/千金方/少年说 26400.0；其他 24814.43；医疗 3621.47；菌群 0.0</t>
+          <t>咨询 314760.0；家守/千金方/少年说 26400.0；其他 25590.51；医疗 3621.47；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -2093,19 +2093,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>210874.8</v>
+        <v>258457.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>49.5</v>
+        <v>54.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>咨询 104444.0；其他 93230.8；家守/千金方/少年说 13200.0；菌群 0.0</t>
+          <t>其他 140813.4；咨询 104444.0；家守/千金方/少年说 13200.0；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>372511.87</v>
+        <v>373364.21</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2129,11 +2129,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>76.7</v>
+        <v>76.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>咨询 285772.0；其他 52819.87；家守/千金方/少年说 33420.0；医疗 500.0；菌群 0.0</t>
+          <t>咨询 285772.0；其他 53672.21；家守/千金方/少年说 33420.0；医疗 500.0；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>242704.11</v>
+        <v>206497.87</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>51.9</v>
+        <v>55.7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>咨询 125964.01；其他 90272.1；家守/千金方/少年说 26400.0；医疗 68.0</t>
+          <t>咨询 114968.01；其他 71661.86；家守/千金方/少年说 19800.0；医疗 68.0</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63761.8</v>
+        <v>63608</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2185,11 +2185,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>咨询 51778.0；家守/千金方/少年说 11640.0；其他 219.0；医疗 124.8</t>
+          <t>咨询 51778.0；家守/千金方/少年说 11640.0；其他 190.0</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29086</v>
+        <v>74457</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2241,11 +2241,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>94.2</v>
+        <v>97.7</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>其他 27406.0；家守/千金方/少年说 1680.0</t>
+          <t>其他 72777.0；家守/千金方/少年说 1680.0</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54481</v>
+        <v>59461</v>
       </c>
     </row>
     <row r="9">
@@ -2467,11 +2467,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47240</v>
+        <v>47310</v>
       </c>
     </row>
     <row r="10">
@@ -2490,11 +2490,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>44820</v>
+        <v>47240</v>
       </c>
     </row>
     <row r="11">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>严闽龙虚拟</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2697,11 +2697,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>109020</v>
+        <v>112200</v>
       </c>
     </row>
     <row r="20">
@@ -2720,11 +2720,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>98212</v>
+        <v>109020</v>
       </c>
     </row>
     <row r="21">
@@ -2743,11 +2743,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>姜人荷</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>96640</v>
+        <v>86220</v>
       </c>
     </row>
     <row r="22">
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>184289.6</v>
+        <v>185725.6</v>
       </c>
     </row>
     <row r="29">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>158882.29</v>
+        <v>169125.29</v>
       </c>
     </row>
     <row r="30">
@@ -3019,11 +3019,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>胡炫明</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>50610</v>
+        <v>53760</v>
       </c>
     </row>
     <row r="34">
@@ -3042,11 +3042,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>郭海明</t>
+          <t>章浩进</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>49920</v>
+        <v>51960</v>
       </c>
     </row>
     <row r="35">
@@ -3065,11 +3065,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>胡炫明</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>40300</v>
+        <v>50160</v>
       </c>
     </row>
     <row r="36">
@@ -3088,11 +3088,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>郭海明</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>40000</v>
+        <v>49920</v>
       </c>
     </row>
     <row r="37">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>54481</v>
+        <v>59461</v>
       </c>
     </row>
     <row r="44">
@@ -3272,11 +3272,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>47240</v>
+        <v>47310</v>
       </c>
     </row>
     <row r="45">
@@ -3295,11 +3295,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>44820</v>
+        <v>47240</v>
       </c>
     </row>
     <row r="46">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>严闽龙虚拟</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -3479,11 +3479,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>109020</v>
+        <v>112200</v>
       </c>
     </row>
     <row r="54">
@@ -3502,11 +3502,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>98212</v>
+        <v>109020</v>
       </c>
     </row>
     <row r="55">
@@ -3525,11 +3525,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>姜人荷</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>96640</v>
+        <v>86220</v>
       </c>
     </row>
     <row r="56">
@@ -3548,11 +3548,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>姜人荷</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>86220</v>
+        <v>83400</v>
       </c>
     </row>
     <row r="57">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -3824,11 +3824,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="69">
@@ -3847,11 +3847,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3800</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="70">
@@ -3870,11 +3870,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1440</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="71">
@@ -3893,11 +3893,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="72">
@@ -4100,11 +4100,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>黄慧作</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>26400</v>
+        <v>21480</v>
       </c>
     </row>
     <row r="81">
@@ -4123,11 +4123,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>21480</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="82">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>184289.6</v>
+        <v>185725.6</v>
       </c>
     </row>
     <row r="89">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>158882.29</v>
+        <v>169125.29</v>
       </c>
     </row>
     <row r="90">
@@ -4399,11 +4399,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>胡炫明</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>50610</v>
+        <v>53760</v>
       </c>
     </row>
     <row r="94">
@@ -4422,11 +4422,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>郭海明</t>
+          <t>章浩进</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>49920</v>
+        <v>51960</v>
       </c>
     </row>
     <row r="95">
@@ -4445,11 +4445,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>胡炫明</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>40300</v>
+        <v>50160</v>
       </c>
     </row>
     <row r="96">
@@ -4468,11 +4468,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>郭海明</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>30493.04</v>
+        <v>49920</v>
       </c>
     </row>
   </sheetData>
@@ -4548,26 +4548,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>147790.57</v>
+        <v>147733.57</v>
       </c>
       <c r="D2" t="n">
-        <v>17725</v>
+        <v>18411</v>
       </c>
       <c r="E2" t="n">
-        <v>14754</v>
+        <v>15383</v>
       </c>
       <c r="F2" t="n">
-        <v>9.98</v>
+        <v>10.41</v>
       </c>
       <c r="G2" t="n">
-        <v>2971</v>
+        <v>3028</v>
       </c>
       <c r="H2" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 2691.0；青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题 1368.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 1280.0</t>
+          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 2691.0；青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题 1444.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 1441.0</t>
         </is>
       </c>
     </row>
@@ -4583,26 +4583,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>799963</v>
+        <v>814903</v>
       </c>
       <c r="D3" t="n">
-        <v>142420.44</v>
+        <v>167320.44</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="G3" t="n">
-        <v>142420.44</v>
+        <v>162340.44</v>
       </c>
       <c r="H3" t="n">
-        <v>17.8</v>
+        <v>19.92</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>青少年同行者计划领航营 76625.4；青少年同行者计划-护航营 16598.0；青少年同行者计划向阳营 14593.37</t>
+          <t>青少年同行者计划领航营 96545.4；青少年同行者计划-护航营 16598.0；青少年同行者计划向阳营 14593.37</t>
         </is>
       </c>
     </row>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2242334.01</v>
+        <v>2231338.01</v>
       </c>
       <c r="D4" t="n">
-        <v>363677.33</v>
+        <v>385475.33</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -4630,14 +4630,14 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>363677.33</v>
+        <v>385475.33</v>
       </c>
       <c r="H4" t="n">
-        <v>16.22</v>
+        <v>17.28</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>儿童青少年 207981.33；精神心理 83896.0；电商咨询 37500.0</t>
+          <t>儿童青少年 229779.33；精神心理 83896.0；电商咨询 37500.0</t>
         </is>
       </c>
     </row>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1714636</v>
+        <v>1677244</v>
       </c>
       <c r="D5" t="n">
-        <v>150690</v>
+        <v>195690</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -4665,14 +4665,14 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>150690</v>
+        <v>195690</v>
       </c>
       <c r="H5" t="n">
-        <v>8.789999999999999</v>
+        <v>11.67</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 39600.0；家庭守护计划2.0（一阶） 31380.0；家庭守护计划2.0（二阶） 26820.0</t>
+          <t>家庭守护计划2.0（二阶） 58620.0；少年说陪伴计划 52800.0；家庭守护计划2.0（一阶） 31380.0</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
         <v>249000</v>
       </c>
       <c r="D6" t="n">
-        <v>163600</v>
+        <v>186400</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -4700,14 +4700,14 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>163600</v>
+        <v>186400</v>
       </c>
       <c r="H6" t="n">
-        <v>65.7</v>
+        <v>74.86</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群移植 49600.0；肠道菌群移植（双疗程优惠） 20800.0</t>
+          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群移植 72400.0；肠道菌群移植（双疗程优惠） 20800.0</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1102958.9</v>
+        <v>1130205.1</v>
       </c>
       <c r="D7" t="n">
         <v>6319.59</v>
@@ -4732,13 +4732,13 @@
         <v>1941.59</v>
       </c>
       <c r="F7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G7" t="n">
         <v>4378</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4758,26 +4758,26 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>598375.5600000001</v>
+        <v>674858.34</v>
       </c>
       <c r="D8" t="n">
-        <v>547141.59</v>
+        <v>599718.59</v>
       </c>
       <c r="E8" t="n">
-        <v>26795</v>
+        <v>26871</v>
       </c>
       <c r="F8" t="n">
-        <v>4.48</v>
+        <v>3.98</v>
       </c>
       <c r="G8" t="n">
-        <v>520346.59</v>
+        <v>572847.59</v>
       </c>
       <c r="H8" t="n">
-        <v>86.95999999999999</v>
+        <v>84.88</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>青少年成长基地3月营（金盏基地） 83600.0；青少年营地家族赋能方案 80000.0；青少年身心复能成长方案 80000.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；青少年营地动力唤醒方案 85000.0；青少年成长基地3月营（金盏基地） 83600.0</t>
         </is>
       </c>
     </row>
@@ -4793,26 +4793,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>147790.57</v>
+        <v>147733.57</v>
       </c>
       <c r="D9" t="n">
-        <v>17725</v>
+        <v>18411</v>
       </c>
       <c r="E9" t="n">
-        <v>14754</v>
+        <v>15383</v>
       </c>
       <c r="F9" t="n">
-        <v>9.98</v>
+        <v>10.41</v>
       </c>
       <c r="G9" t="n">
-        <v>2971</v>
+        <v>3028</v>
       </c>
       <c r="H9" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 2691.0；青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题 1368.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 1280.0</t>
+          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 2691.0；青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题 1444.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 1441.0</t>
         </is>
       </c>
     </row>
@@ -4828,26 +4828,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>799963</v>
+        <v>814903</v>
       </c>
       <c r="D10" t="n">
-        <v>142420.44</v>
+        <v>167320.44</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="G10" t="n">
-        <v>142420.44</v>
+        <v>162340.44</v>
       </c>
       <c r="H10" t="n">
-        <v>17.8</v>
+        <v>19.92</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>青少年同行者计划领航营 76625.4；青少年同行者计划-护航营 16598.0；青少年同行者计划向阳营 14593.37</t>
+          <t>青少年同行者计划领航营 96545.4；青少年同行者计划-护航营 16598.0；青少年同行者计划向阳营 14593.37</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
         <v>285946</v>
       </c>
       <c r="D11" t="n">
-        <v>101998</v>
+        <v>108396</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4875,14 +4875,14 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>101998</v>
+        <v>108396</v>
       </c>
       <c r="H11" t="n">
-        <v>35.67</v>
+        <v>37.91</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>精神心理 51098.0；儿童青少年 50900.0</t>
+          <t>儿童青少年 57298.0；精神心理 51098.0</t>
         </is>
       </c>
     </row>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1248036</v>
+        <v>1218924</v>
       </c>
       <c r="D12" t="n">
-        <v>88770</v>
+        <v>127170</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -4910,14 +4910,14 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>88770</v>
+        <v>127170</v>
       </c>
       <c r="H12" t="n">
-        <v>7.11</v>
+        <v>10.43</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 33000.0；家庭守护计划2.0（二阶） 26820.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
+          <t>家庭守护计划2.0（二阶） 58620.0；少年说陪伴计划 39600.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
         <v>125210.36</v>
       </c>
       <c r="D15" t="n">
-        <v>189369.59</v>
+        <v>215930.59</v>
       </c>
       <c r="E15" t="n">
         <v>999</v>
@@ -5015,14 +5015,14 @@
         <v>0.8</v>
       </c>
       <c r="G15" t="n">
-        <v>188370.59</v>
+        <v>214931.59</v>
       </c>
       <c r="H15" t="n">
-        <v>150.44</v>
+        <v>171.66</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 75254.88；青少年成长基地3月营（金盏基地） 46800.0；蛋壳跳动身心复能营21天（一阶） 34600.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；青少年成长基地3月营（金盏基地） 46800.0；蛋壳跳动身心复能营21天（一阶） 34600.0</t>
         </is>
       </c>
     </row>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1956388.01</v>
+        <v>1945392.01</v>
       </c>
       <c r="D16" t="n">
-        <v>261679.33</v>
+        <v>277079.33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -5050,14 +5050,14 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>261679.33</v>
+        <v>277079.33</v>
       </c>
       <c r="H16" t="n">
-        <v>13.38</v>
+        <v>14.24</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>儿童青少年 157081.33；电商咨询 37500.0；精神心理 32798.0</t>
+          <t>儿童青少年 172481.33；电商咨询 37500.0；精神心理 32798.0</t>
         </is>
       </c>
     </row>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>466600</v>
+        <v>458320</v>
       </c>
       <c r="D17" t="n">
-        <v>61920</v>
+        <v>68520</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -5085,14 +5085,14 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>61920</v>
+        <v>68520</v>
       </c>
       <c r="H17" t="n">
-        <v>13.27</v>
+        <v>14.95</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（三阶） 26310.0；家庭守护计划2.0（一阶） 23970.0；少年说陪伴计划 6600.0</t>
+          <t>家庭守护计划2.0（三阶） 26310.0；家庭守护计划2.0（一阶） 23970.0；少年说陪伴计划 13200.0</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
         <v>149800</v>
       </c>
       <c r="D18" t="n">
-        <v>67400</v>
+        <v>90200</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -5120,14 +5120,14 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>67400</v>
+        <v>90200</v>
       </c>
       <c r="H18" t="n">
-        <v>44.99</v>
+        <v>60.21</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程） 45600.0；肠道菌群移植（双疗程优惠） 20800.0；肠道菌群检测（医生专用） 1000.0</t>
+          <t>肠道菌群移植（双疗程） 45600.0；肠道菌群移植 22800.0；肠道菌群移植（双疗程优惠） 20800.0</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1061144.17</v>
+        <v>1088390.37</v>
       </c>
       <c r="D19" t="n">
         <v>5541.59</v>
@@ -5158,7 +5158,7 @@
         <v>3600</v>
       </c>
       <c r="H19" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5178,26 +5178,26 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>473165.2</v>
+        <v>549647.98</v>
       </c>
       <c r="D20" t="n">
-        <v>357772</v>
+        <v>383788</v>
       </c>
       <c r="E20" t="n">
-        <v>25796</v>
+        <v>25872</v>
       </c>
       <c r="F20" t="n">
-        <v>5.45</v>
+        <v>4.71</v>
       </c>
       <c r="G20" t="n">
-        <v>331976</v>
+        <v>357916</v>
       </c>
       <c r="H20" t="n">
-        <v>70.16</v>
+        <v>65.12</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>青少年营地家族赋能方案 80000.0；青少年身心复能成长方案 80000.0；青少年营地动力唤醒方案 65000.0</t>
+          <t>青少年营地动力唤醒方案 85000.0；青少年营地家族赋能方案 80000.0；青少年身心复能成长方案 80000.0</t>
         </is>
       </c>
     </row>
@@ -5264,13 +5264,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56979.57</v>
+        <v>56941.57</v>
       </c>
       <c r="E2" t="n">
-        <v>559077.01</v>
+        <v>564019.01</v>
       </c>
       <c r="F2" t="n">
-        <v>10.1917</v>
+        <v>10.0957</v>
       </c>
     </row>
     <row r="3">
@@ -5290,13 +5290,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>272022</v>
+        <v>277002</v>
       </c>
       <c r="E3" t="n">
-        <v>559077.01</v>
+        <v>564019.01</v>
       </c>
       <c r="F3" t="n">
-        <v>48.6556</v>
+        <v>49.1122</v>
       </c>
     </row>
     <row r="4">
@@ -5319,10 +5319,10 @@
         <v>47178</v>
       </c>
       <c r="E4" t="n">
-        <v>559077.01</v>
+        <v>564019.01</v>
       </c>
       <c r="F4" t="n">
-        <v>8.438599999999999</v>
+        <v>8.364599999999999</v>
       </c>
     </row>
     <row r="5">
@@ -5345,10 +5345,10 @@
         <v>99483</v>
       </c>
       <c r="E5" t="n">
-        <v>559077.01</v>
+        <v>564019.01</v>
       </c>
       <c r="F5" t="n">
-        <v>17.7941</v>
+        <v>17.6382</v>
       </c>
     </row>
     <row r="6">
@@ -5371,7 +5371,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>559077.01</v>
+        <v>564019.01</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -5397,10 +5397,10 @@
         <v>12420.44</v>
       </c>
       <c r="E7" t="n">
-        <v>559077.01</v>
+        <v>564019.01</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2216</v>
+        <v>2.2021</v>
       </c>
     </row>
     <row r="8">
@@ -5423,10 +5423,10 @@
         <v>70994</v>
       </c>
       <c r="E8" t="n">
-        <v>559077.01</v>
+        <v>564019.01</v>
       </c>
       <c r="F8" t="n">
-        <v>12.6984</v>
+        <v>12.5872</v>
       </c>
     </row>
     <row r="9">
@@ -5628,13 +5628,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>54585</v>
+        <v>54566</v>
       </c>
       <c r="E16" t="n">
-        <v>657617.88</v>
+        <v>667558.88</v>
       </c>
       <c r="F16" t="n">
-        <v>8.3004</v>
+        <v>8.173999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>358691</v>
+        <v>368651</v>
       </c>
       <c r="E17" t="n">
-        <v>657617.88</v>
+        <v>667558.88</v>
       </c>
       <c r="F17" t="n">
-        <v>54.544</v>
+        <v>55.2237</v>
       </c>
     </row>
     <row r="18">
@@ -5683,10 +5683,10 @@
         <v>83184</v>
       </c>
       <c r="E18" t="n">
-        <v>657617.88</v>
+        <v>667558.88</v>
       </c>
       <c r="F18" t="n">
-        <v>12.6493</v>
+        <v>12.4609</v>
       </c>
     </row>
     <row r="19">
@@ -5709,10 +5709,10 @@
         <v>150300</v>
       </c>
       <c r="E19" t="n">
-        <v>657617.88</v>
+        <v>667558.88</v>
       </c>
       <c r="F19" t="n">
-        <v>22.8552</v>
+        <v>22.5149</v>
       </c>
     </row>
     <row r="20">
@@ -5735,7 +5735,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>657617.88</v>
+        <v>667558.88</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -5761,10 +5761,10 @@
         <v>1058.88</v>
       </c>
       <c r="E21" t="n">
-        <v>657617.88</v>
+        <v>667558.88</v>
       </c>
       <c r="F21" t="n">
-        <v>0.161</v>
+        <v>0.1586</v>
       </c>
     </row>
     <row r="22">
@@ -5787,10 +5787,10 @@
         <v>9799</v>
       </c>
       <c r="E22" t="n">
-        <v>657617.88</v>
+        <v>667558.88</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4901</v>
+        <v>1.4679</v>
       </c>
     </row>
     <row r="23">
@@ -5813,10 +5813,10 @@
         <v>6141</v>
       </c>
       <c r="E23" t="n">
-        <v>1291095.36</v>
+        <v>1261983.36</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4756</v>
+        <v>0.4866</v>
       </c>
     </row>
     <row r="24">
@@ -5839,10 +5839,10 @@
         <v>17430</v>
       </c>
       <c r="E24" t="n">
-        <v>1291095.36</v>
+        <v>1261983.36</v>
       </c>
       <c r="F24" t="n">
-        <v>1.35</v>
+        <v>1.3812</v>
       </c>
     </row>
     <row r="25">
@@ -5865,10 +5865,10 @@
         <v>154190</v>
       </c>
       <c r="E25" t="n">
-        <v>1291095.36</v>
+        <v>1261983.36</v>
       </c>
       <c r="F25" t="n">
-        <v>11.9426</v>
+        <v>12.2181</v>
       </c>
     </row>
     <row r="26">
@@ -5888,13 +5888,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>950372</v>
+        <v>921260</v>
       </c>
       <c r="E26" t="n">
-        <v>1291095.36</v>
+        <v>1261983.36</v>
       </c>
       <c r="F26" t="n">
-        <v>73.6097</v>
+        <v>73.001</v>
       </c>
     </row>
     <row r="27">
@@ -5917,10 +5917,10 @@
         <v>99200</v>
       </c>
       <c r="E27" t="n">
-        <v>1291095.36</v>
+        <v>1261983.36</v>
       </c>
       <c r="F27" t="n">
-        <v>7.6834</v>
+        <v>7.8606</v>
       </c>
     </row>
     <row r="28">
@@ -5943,10 +5943,10 @@
         <v>19545</v>
       </c>
       <c r="E28" t="n">
-        <v>1291095.36</v>
+        <v>1261983.36</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5138</v>
+        <v>1.5488</v>
       </c>
     </row>
     <row r="29">
@@ -5969,10 +5969,10 @@
         <v>44217.36</v>
       </c>
       <c r="E29" t="n">
-        <v>1291095.36</v>
+        <v>1261983.36</v>
       </c>
       <c r="F29" t="n">
-        <v>3.4248</v>
+        <v>3.5038</v>
       </c>
     </row>
     <row r="30">
@@ -5992,13 +5992,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>147790.57</v>
+        <v>147733.57</v>
       </c>
       <c r="E30" t="n">
-        <v>2747960.66</v>
+        <v>2733731.66</v>
       </c>
       <c r="F30" t="n">
-        <v>5.3782</v>
+        <v>5.4041</v>
       </c>
     </row>
     <row r="31">
@@ -6018,13 +6018,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>799963</v>
+        <v>814903</v>
       </c>
       <c r="E31" t="n">
-        <v>2747960.66</v>
+        <v>2733731.66</v>
       </c>
       <c r="F31" t="n">
-        <v>29.1112</v>
+        <v>29.8092</v>
       </c>
     </row>
     <row r="32">
@@ -6047,10 +6047,10 @@
         <v>285946</v>
       </c>
       <c r="E32" t="n">
-        <v>2747960.66</v>
+        <v>2733731.66</v>
       </c>
       <c r="F32" t="n">
-        <v>10.4058</v>
+        <v>10.4599</v>
       </c>
     </row>
     <row r="33">
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1248036</v>
+        <v>1218924</v>
       </c>
       <c r="E33" t="n">
-        <v>2747960.66</v>
+        <v>2733731.66</v>
       </c>
       <c r="F33" t="n">
-        <v>45.4168</v>
+        <v>44.5883</v>
       </c>
     </row>
     <row r="34">
@@ -6099,10 +6099,10 @@
         <v>99200</v>
       </c>
       <c r="E34" t="n">
-        <v>2747960.66</v>
+        <v>2733731.66</v>
       </c>
       <c r="F34" t="n">
-        <v>3.6099</v>
+        <v>3.6287</v>
       </c>
     </row>
     <row r="35">
@@ -6125,10 +6125,10 @@
         <v>41814.73</v>
       </c>
       <c r="E35" t="n">
-        <v>2747960.66</v>
+        <v>2733731.66</v>
       </c>
       <c r="F35" t="n">
-        <v>1.5217</v>
+        <v>1.5296</v>
       </c>
     </row>
     <row r="36">
@@ -6151,10 +6151,10 @@
         <v>125210.36</v>
       </c>
       <c r="E36" t="n">
-        <v>2747960.66</v>
+        <v>2733731.66</v>
       </c>
       <c r="F36" t="n">
-        <v>4.5565</v>
+        <v>4.5802</v>
       </c>
     </row>
     <row r="37">
@@ -6177,10 +6177,10 @@
         <v>61194</v>
       </c>
       <c r="E37" t="n">
-        <v>1013467.92</v>
+        <v>1041378.92</v>
       </c>
       <c r="F37" t="n">
-        <v>6.0381</v>
+        <v>5.8762</v>
       </c>
     </row>
     <row r="38">
@@ -6203,10 +6203,10 @@
         <v>6600</v>
       </c>
       <c r="E38" t="n">
-        <v>1013467.92</v>
+        <v>1041378.92</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6512</v>
+        <v>0.6338</v>
       </c>
     </row>
     <row r="39">
@@ -6229,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1013467.92</v>
+        <v>1041378.92</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>944981.92</v>
+        <v>972352.92</v>
       </c>
       <c r="E40" t="n">
-        <v>1013467.92</v>
+        <v>1041378.92</v>
       </c>
       <c r="F40" t="n">
-        <v>93.2424</v>
+        <v>93.3717</v>
       </c>
     </row>
     <row r="41">
@@ -6278,13 +6278,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>692</v>
+        <v>1232</v>
       </c>
       <c r="E41" t="n">
-        <v>1013467.92</v>
+        <v>1041378.92</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0683</v>
+        <v>0.1183</v>
       </c>
     </row>
     <row r="42">
@@ -6437,10 +6437,10 @@
         <v>71970</v>
       </c>
       <c r="E47" t="n">
-        <v>93303.84</v>
+        <v>91623.84</v>
       </c>
       <c r="F47" t="n">
-        <v>77.13509999999999</v>
+        <v>78.54940000000001</v>
       </c>
     </row>
     <row r="48">
@@ -6460,13 +6460,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>93303.84</v>
+        <v>91623.84</v>
       </c>
       <c r="F48" t="n">
-        <v>1.8006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6489,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>93303.84</v>
+        <v>91623.84</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -6515,10 +6515,10 @@
         <v>17856.84</v>
       </c>
       <c r="E50" t="n">
-        <v>93303.84</v>
+        <v>91623.84</v>
       </c>
       <c r="F50" t="n">
-        <v>19.1384</v>
+        <v>19.4893</v>
       </c>
     </row>
     <row r="51">
@@ -6541,10 +6541,10 @@
         <v>1797</v>
       </c>
       <c r="E51" t="n">
-        <v>93303.84</v>
+        <v>91623.84</v>
       </c>
       <c r="F51" t="n">
-        <v>1.926</v>
+        <v>1.9613</v>
       </c>
     </row>
     <row r="52">
@@ -6697,10 +6697,10 @@
         <v>314760</v>
       </c>
       <c r="E57" t="n">
-        <v>369595.9</v>
+        <v>370371.98</v>
       </c>
       <c r="F57" t="n">
-        <v>85.16330000000001</v>
+        <v>84.98480000000001</v>
       </c>
     </row>
     <row r="58">
@@ -6723,10 +6723,10 @@
         <v>26400</v>
       </c>
       <c r="E58" t="n">
-        <v>369595.9</v>
+        <v>370371.98</v>
       </c>
       <c r="F58" t="n">
-        <v>7.1429</v>
+        <v>7.128</v>
       </c>
     </row>
     <row r="59">
@@ -6749,7 +6749,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>369595.9</v>
+        <v>370371.98</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -6775,10 +6775,10 @@
         <v>3621.47</v>
       </c>
       <c r="E60" t="n">
-        <v>369595.9</v>
+        <v>370371.98</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9798</v>
+        <v>0.9778</v>
       </c>
     </row>
     <row r="61">
@@ -6798,13 +6798,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>24814.43</v>
+        <v>25590.51</v>
       </c>
       <c r="E61" t="n">
-        <v>369595.9</v>
+        <v>370371.98</v>
       </c>
       <c r="F61" t="n">
-        <v>6.7139</v>
+        <v>6.9094</v>
       </c>
     </row>
     <row r="62">
@@ -6957,10 +6957,10 @@
         <v>104444</v>
       </c>
       <c r="E67" t="n">
-        <v>210874.8</v>
+        <v>258457.4</v>
       </c>
       <c r="F67" t="n">
-        <v>49.5289</v>
+        <v>40.4105</v>
       </c>
     </row>
     <row r="68">
@@ -6983,10 +6983,10 @@
         <v>13200</v>
       </c>
       <c r="E68" t="n">
-        <v>210874.8</v>
+        <v>258457.4</v>
       </c>
       <c r="F68" t="n">
-        <v>6.2596</v>
+        <v>5.1072</v>
       </c>
     </row>
     <row r="69">
@@ -7009,7 +7009,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>210874.8</v>
+        <v>258457.4</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -7035,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>210874.8</v>
+        <v>258457.4</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>93230.8</v>
+        <v>140813.4</v>
       </c>
       <c r="E71" t="n">
-        <v>210874.8</v>
+        <v>258457.4</v>
       </c>
       <c r="F71" t="n">
-        <v>44.2114</v>
+        <v>54.4822</v>
       </c>
     </row>
     <row r="72">
@@ -7087,10 +7087,10 @@
         <v>285772</v>
       </c>
       <c r="E72" t="n">
-        <v>372511.87</v>
+        <v>373364.21</v>
       </c>
       <c r="F72" t="n">
-        <v>76.7149</v>
+        <v>76.5397</v>
       </c>
     </row>
     <row r="73">
@@ -7113,10 +7113,10 @@
         <v>33420</v>
       </c>
       <c r="E73" t="n">
-        <v>372511.87</v>
+        <v>373364.21</v>
       </c>
       <c r="F73" t="n">
-        <v>8.971500000000001</v>
+        <v>8.951000000000001</v>
       </c>
     </row>
     <row r="74">
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>372511.87</v>
+        <v>373364.21</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -7165,10 +7165,10 @@
         <v>500</v>
       </c>
       <c r="E75" t="n">
-        <v>372511.87</v>
+        <v>373364.21</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1342</v>
+        <v>0.1339</v>
       </c>
     </row>
     <row r="76">
@@ -7188,13 +7188,13 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>52819.87</v>
+        <v>53672.21</v>
       </c>
       <c r="E76" t="n">
-        <v>372511.87</v>
+        <v>373364.21</v>
       </c>
       <c r="F76" t="n">
-        <v>14.1794</v>
+        <v>14.3753</v>
       </c>
     </row>
     <row r="77">
@@ -7214,13 +7214,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>125964.01</v>
+        <v>114968.01</v>
       </c>
       <c r="E77" t="n">
-        <v>242704.11</v>
+        <v>206497.87</v>
       </c>
       <c r="F77" t="n">
-        <v>51.9002</v>
+        <v>55.6752</v>
       </c>
     </row>
     <row r="78">
@@ -7240,13 +7240,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>26400</v>
+        <v>19800</v>
       </c>
       <c r="E78" t="n">
-        <v>242704.11</v>
+        <v>206497.87</v>
       </c>
       <c r="F78" t="n">
-        <v>10.8774</v>
+        <v>9.5885</v>
       </c>
     </row>
     <row r="79">
@@ -7269,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>242704.11</v>
+        <v>206497.87</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -7295,10 +7295,10 @@
         <v>68</v>
       </c>
       <c r="E80" t="n">
-        <v>242704.11</v>
+        <v>206497.87</v>
       </c>
       <c r="F80" t="n">
-        <v>0.028</v>
+        <v>0.0329</v>
       </c>
     </row>
     <row r="81">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>90272.10000000001</v>
+        <v>71661.86</v>
       </c>
       <c r="E81" t="n">
-        <v>242704.11</v>
+        <v>206497.87</v>
       </c>
       <c r="F81" t="n">
-        <v>37.1943</v>
+        <v>34.7034</v>
       </c>
     </row>
     <row r="82">
@@ -7347,10 +7347,10 @@
         <v>51778</v>
       </c>
       <c r="E82" t="n">
-        <v>63761.8</v>
+        <v>63608</v>
       </c>
       <c r="F82" t="n">
-        <v>81.2054</v>
+        <v>81.40170000000001</v>
       </c>
     </row>
     <row r="83">
@@ -7373,10 +7373,10 @@
         <v>11640</v>
       </c>
       <c r="E83" t="n">
-        <v>63761.8</v>
+        <v>63608</v>
       </c>
       <c r="F83" t="n">
-        <v>18.2554</v>
+        <v>18.2996</v>
       </c>
     </row>
     <row r="84">
@@ -7399,7 +7399,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>63761.8</v>
+        <v>63608</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -7422,13 +7422,13 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>124.8</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>63761.8</v>
+        <v>63608</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -7448,13 +7448,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="E86" t="n">
-        <v>63761.8</v>
+        <v>63608</v>
       </c>
       <c r="F86" t="n">
-        <v>0.3435</v>
+        <v>0.2987</v>
       </c>
     </row>
     <row r="87">
@@ -7607,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>29086</v>
+        <v>74457</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -7633,10 +7633,10 @@
         <v>1680</v>
       </c>
       <c r="E93" t="n">
-        <v>29086</v>
+        <v>74457</v>
       </c>
       <c r="F93" t="n">
-        <v>5.776</v>
+        <v>2.2563</v>
       </c>
     </row>
     <row r="94">
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>29086</v>
+        <v>74457</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>29086</v>
+        <v>74457</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -7708,13 +7708,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>27406</v>
+        <v>72777</v>
       </c>
       <c r="E96" t="n">
-        <v>29086</v>
+        <v>74457</v>
       </c>
       <c r="F96" t="n">
-        <v>94.224</v>
+        <v>97.7437</v>
       </c>
     </row>
     <row r="97">
@@ -7734,13 +7734,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1956388.01</v>
+        <v>1945392.01</v>
       </c>
       <c r="E97" t="n">
-        <v>4107097.38</v>
+        <v>4191550.36</v>
       </c>
       <c r="F97" t="n">
-        <v>47.6343</v>
+        <v>46.4122</v>
       </c>
     </row>
     <row r="98">
@@ -7760,13 +7760,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>466600</v>
+        <v>458320</v>
       </c>
       <c r="E98" t="n">
-        <v>4107097.38</v>
+        <v>4191550.36</v>
       </c>
       <c r="F98" t="n">
-        <v>11.3608</v>
+        <v>10.9344</v>
       </c>
     </row>
     <row r="99">
@@ -7789,10 +7789,10 @@
         <v>149800</v>
       </c>
       <c r="E99" t="n">
-        <v>4107097.38</v>
+        <v>4191550.36</v>
       </c>
       <c r="F99" t="n">
-        <v>3.6473</v>
+        <v>3.5739</v>
       </c>
     </row>
     <row r="100">
@@ -7812,13 +7812,13 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1061144.17</v>
+        <v>1088390.37</v>
       </c>
       <c r="E100" t="n">
-        <v>4107097.38</v>
+        <v>4191550.36</v>
       </c>
       <c r="F100" t="n">
-        <v>25.8368</v>
+        <v>25.9663</v>
       </c>
     </row>
     <row r="101">
@@ -7838,13 +7838,13 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>473165.2</v>
+        <v>549647.98</v>
       </c>
       <c r="E101" t="n">
-        <v>4107097.38</v>
+        <v>4191550.36</v>
       </c>
       <c r="F101" t="n">
-        <v>11.5207</v>
+        <v>13.1132</v>
       </c>
     </row>
   </sheetData>
@@ -7858,7 +7858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E757"/>
+  <dimension ref="A1:E751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3569</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="6">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2390.57</v>
+        <v>2371.57</v>
       </c>
     </row>
     <row r="14">
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>238442</v>
+        <v>243422</v>
       </c>
     </row>
     <row r="61">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4440</v>
+        <v>4459</v>
       </c>
     </row>
     <row r="178">
@@ -12360,7 +12360,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3512</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="181">
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2432</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="185">
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>966</v>
+        <v>947</v>
       </c>
     </row>
     <row r="189">
@@ -12906,11 +12906,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
+          <t>lhr（网课、家长学）青少年家庭同行者计划一周短训营</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>171</v>
+        <v>152</v>
       </c>
     </row>
     <row r="203">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>lhr（网课、家长学）青少年家庭同行者计划一周短训营</t>
+          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -13785,7 +13785,7 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>322121</v>
+        <v>332081</v>
       </c>
     </row>
     <row r="238">
@@ -15210,7 +15210,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>520612</v>
+        <v>524700</v>
       </c>
     </row>
     <row r="295">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>191400</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="296">
@@ -15281,11 +15281,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（二阶）</t>
+          <t>少年说-认知引导</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>58620</v>
+        <v>53800</v>
       </c>
     </row>
     <row r="298">
@@ -15306,11 +15306,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>少年说-认知引导</t>
+          <t>家庭守护计划2.0（二阶）</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>53800</v>
+        <v>33640</v>
       </c>
     </row>
     <row r="299">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>29640</v>
+        <v>14820</v>
       </c>
     </row>
     <row r="300">
@@ -15910,7 +15910,7 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>535998</v>
+        <v>529998</v>
       </c>
     </row>
     <row r="323">
@@ -16010,7 +16010,7 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>18000</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="327">
@@ -16056,11 +16056,11 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>诊费X1（800）</t>
+          <t>草酸艾司西酞普兰片</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>15200</v>
+        <v>15664</v>
       </c>
     </row>
     <row r="329">
@@ -16081,11 +16081,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>草酸艾司西酞普兰片</t>
+          <t>诊费X1（800）</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>15136</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="330">
@@ -16106,11 +16106,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>治疗（个体398）</t>
+          <t>诊费I（1000）</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>12338</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="331">
@@ -16131,11 +16131,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>诊费I（1000）</t>
+          <t>治疗（个体398）</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>11000</v>
+        <v>12338</v>
       </c>
     </row>
     <row r="332">
@@ -16156,11 +16156,11 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>基因检测(迈基诺）（抗抑郁类药物）</t>
+          <t>大韦氏智力测验(6-16岁)</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>10989</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="333">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>基因检测(迈基诺）（抗精神分裂类药物）</t>
+          <t>基因检测(迈基诺）（抗癫痫类药物/心境稳定剂）</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>基因检测(迈基诺）（抗癫痫类药物/心境稳定剂）</t>
+          <t>基因检测(迈基诺）（抗抑郁类药物）</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -16231,11 +16231,11 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>大韦氏智力测验(6-16岁)</t>
+          <t>基因检测(迈基诺）（抗精神分裂类药物）</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>8400</v>
+        <v>10989</v>
       </c>
     </row>
     <row r="336">
@@ -16260,7 +16260,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>8082</v>
+        <v>8298</v>
       </c>
     </row>
     <row r="337">
@@ -16281,7 +16281,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>诊费X2（400）</t>
+          <t>韦氏四代（完整版）</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -16306,11 +16306,11 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>盐酸鲁拉西酮片</t>
+          <t>诊费X2（400）</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>4235</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="339">
@@ -16331,11 +16331,11 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>盐酸文拉法辛缓释胶囊</t>
+          <t>盐酸鲁拉西酮片</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>3850</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="340">
@@ -16356,11 +16356,11 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>盐酸舍曲林片</t>
+          <t>父母养育方式</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>3818</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="341">
@@ -16381,11 +16381,11 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>韦氏四代（完整版）</t>
+          <t>盐酸文拉法辛缓释胶囊</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>3600</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="342">
@@ -16406,11 +16406,11 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>韦氏成人测验（16岁以上）</t>
+          <t>盐酸舍曲林片</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>3600</v>
+        <v>3818</v>
       </c>
     </row>
     <row r="343">
@@ -16431,11 +16431,11 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>莱博雷生片</t>
+          <t>韦氏成人测验（16岁以上）</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>3432</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="344">
@@ -16456,11 +16456,11 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>父母养育方式</t>
+          <t>莱博雷生片</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>3220</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="345">
@@ -16481,11 +16481,11 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>马来酸氟伏沙明片</t>
+          <t>简易门诊</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>2844</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="346">
@@ -16506,11 +16506,11 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>明尼苏达多项人格测验</t>
+          <t>马来酸氟伏沙明片</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2760</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="347">
@@ -16531,11 +16531,11 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>简易门诊</t>
+          <t>明尼苏达多项人格测验</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>2700</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="348">
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>2587</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="349">
@@ -16581,11 +16581,11 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>盐酸度洛西汀肠溶胶囊</t>
+          <t>艾森克个性测验少年版（EPQC）</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>2458</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="350">
@@ -16606,11 +16606,11 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>盐酸哌罗匹隆片</t>
+          <t>家庭功能评定（FAD）父母评</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>2436</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="351">
@@ -16631,11 +16631,11 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>治疗II（个体1200）</t>
+          <t>盐酸哌罗匹隆片</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>2400</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="352">
@@ -16656,11 +16656,11 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>盐酸安非他酮缓释片</t>
+          <t>盐酸度洛西汀肠溶胶囊</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>2050</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="353">
@@ -16681,11 +16681,11 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>盐酸曲唑酮片</t>
+          <t>治疗II（个体1200）</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>1942.5</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="354">
@@ -16706,11 +16706,11 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>奥氮平片</t>
+          <t>盐酸安非他酮缓释片</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>1870.71</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="355">
@@ -16731,11 +16731,11 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>家庭功能评定（FAD）父母评</t>
+          <t>盐酸曲唑酮片</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>1800</v>
+        <v>1942.5</v>
       </c>
     </row>
     <row r="356">
@@ -16756,11 +16756,11 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>艾森克个性测验少年版（EPQC）</t>
+          <t>奥氮平片</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>1800</v>
+        <v>1870.71</v>
       </c>
     </row>
     <row r="357">
@@ -16781,11 +16781,11 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>帕利哌酮缓释片</t>
+          <t>儿童焦虑性情绪障碍筛查表（SCARED)</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>1690</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="358">
@@ -16806,11 +16806,11 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>阿戈美拉汀片</t>
+          <t>帕利哌酮缓释片</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>1488</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="359">
@@ -16831,11 +16831,11 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>儿童焦虑性情绪障碍筛查表（SCARED)</t>
+          <t>中国中学生心理健康量表</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>1320</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="360">
@@ -16856,11 +16856,11 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>认知情绪调节量表</t>
+          <t>阿戈美拉汀片</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>1200</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="361">
@@ -16881,11 +16881,11 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>（儿童）孤独症行为评定量表（ABC）</t>
+          <t>认知情绪调节量表</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>1160</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="362">
@@ -16906,11 +16906,11 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>盐酸氟西汀口服溶液</t>
+          <t>抑郁自评量表（SDS）</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>1152</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="363">
@@ -16931,11 +16931,11 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>抑郁自评量表（SDS）</t>
+          <t>匹兹堡睡眠质量指数（PSQI）</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>1080</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="364">
@@ -16956,11 +16956,11 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>中国中学生心理健康量表</t>
+          <t>焦虑自评量表（SAS）</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>1080</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="365">
@@ -16981,11 +16981,11 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>中学生人际关系测量</t>
+          <t>考试焦虑测验</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>1080</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="366">
@@ -17006,11 +17006,11 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>匹兹堡睡眠质量指数（PSQI）</t>
+          <t>（儿童）孤独症行为评定量表（ABC）</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>1020</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="367">
@@ -17031,11 +17031,11 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>焦虑自评量表（SAS）</t>
+          <t>盐酸氟西汀口服溶液</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>1020</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="368">
@@ -17060,7 +17060,7 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>960</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="369">
@@ -17081,11 +17081,11 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>中学生心理素质量表</t>
+          <t>中学生人际关系测量</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>840</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="370">
@@ -17106,11 +17106,11 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>氢溴酸伏硫西汀片</t>
+          <t>中学生心理素质量表</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>800</v>
+        <v>960</v>
       </c>
     </row>
     <row r="371">
@@ -17135,7 +17135,7 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>765</v>
+        <v>855</v>
       </c>
     </row>
     <row r="372">
@@ -17156,11 +17156,11 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>考试焦虑测验</t>
+          <t>自我效能测评</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="373">
@@ -17181,11 +17181,11 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>儿童行为量表(CBCL)(12-16,女)</t>
+          <t>氢溴酸伏硫西汀片</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>690</v>
+        <v>800</v>
       </c>
     </row>
     <row r="374">
@@ -17206,11 +17206,11 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>盐酸米那普伦片</t>
+          <t>儿童躯体化量表</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>605</v>
+        <v>720</v>
       </c>
     </row>
     <row r="375">
@@ -17231,11 +17231,11 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>自我效能测评</t>
+          <t>儿童行为量表(CBCL)(12-16,女)</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>600</v>
+        <v>690</v>
       </c>
     </row>
     <row r="376">
@@ -17256,11 +17256,11 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>儿童躯体化量表</t>
+          <t>儿童行为量表(CBCL)(12-16,男)</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>540</v>
+        <v>690</v>
       </c>
     </row>
     <row r="377">
@@ -17281,11 +17281,11 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>艾森克个性测验成人版（EPQA）</t>
+          <t>圣约翰草提取物片</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>540</v>
+        <v>611</v>
       </c>
     </row>
     <row r="378">
@@ -17306,11 +17306,11 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>状态-特质焦虑问卷（STAI）</t>
+          <t>盐酸米那普伦片</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>480</v>
+        <v>605</v>
       </c>
     </row>
     <row r="379">
@@ -17331,11 +17331,11 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>90项症状清单（scl90）</t>
+          <t>注意力情况测评表</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="380">
@@ -17356,11 +17356,11 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Marks恐怖强迫量表</t>
+          <t>青少年生活事件量表（ASLEC）</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="381">
@@ -17381,11 +17381,11 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>儿童行为量表(CBCL)(12-16,男)</t>
+          <t>注意缺陷多动障碍 SNAP-IV 26</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>460</v>
+        <v>575</v>
       </c>
     </row>
     <row r="382">
@@ -17406,11 +17406,11 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>阿立哌唑口服溶液</t>
+          <t>状态-特质焦虑问卷（STAI）</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>455</v>
+        <v>540</v>
       </c>
     </row>
     <row r="383">
@@ -17431,11 +17431,11 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>地达西尼胶囊</t>
+          <t>艾森克个性测验成人版（EPQA）</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>444</v>
+        <v>540</v>
       </c>
     </row>
     <row r="384">
@@ -17456,11 +17456,11 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>盐酸安非他酮片</t>
+          <t>Marks恐怖强迫量表</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>440</v>
+        <v>540</v>
       </c>
     </row>
     <row r="385">
@@ -17481,11 +17481,11 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>圣约翰草提取物片</t>
+          <t>90项症状清单（scl90）</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>423</v>
+        <v>480</v>
       </c>
     </row>
     <row r="386">
@@ -17506,11 +17506,11 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>青少年生活事件量表（ASLEC）</t>
+          <t>阿立哌唑口服溶液</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>420</v>
+        <v>455</v>
       </c>
     </row>
     <row r="387">
@@ -17531,11 +17531,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>自杀风险因素评估量表</t>
+          <t>地达西尼胶囊</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>400</v>
+        <v>444</v>
       </c>
     </row>
     <row r="388">
@@ -17556,11 +17556,11 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>盐酸帕罗西汀片</t>
+          <t>盐酸安非他酮片</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>392</v>
+        <v>440</v>
       </c>
     </row>
     <row r="389">
@@ -17581,11 +17581,11 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>注意力情况测评表</t>
+          <t>自杀风险因素评估量表</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
     </row>
     <row r="390">
@@ -17606,11 +17606,11 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>一般性焦虑问卷</t>
+          <t>盐酸帕罗西汀片</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>360</v>
+        <v>392</v>
       </c>
     </row>
     <row r="391">
@@ -17656,11 +17656,11 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>注意缺陷多动障碍 SNAP-IV 26</t>
+          <t>一般性焦虑问卷</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>345</v>
+        <v>360</v>
       </c>
     </row>
     <row r="393">
@@ -17681,11 +17681,11 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>生活事件量表</t>
+          <t>焦虑自评量表（SAS）母亲版</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
     </row>
     <row r="394">
@@ -17706,11 +17706,11 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>儿童抑郁量表</t>
+          <t>抑郁自评量表（SDS）母亲版</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>280</v>
+        <v>360</v>
       </c>
     </row>
     <row r="395">
@@ -17731,11 +17731,11 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>心境障碍问卷（MDQ）</t>
+          <t>自杀自伤风险评估表</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>280</v>
+        <v>360</v>
       </c>
     </row>
     <row r="396">
@@ -17756,11 +17756,11 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>社交焦虑量表</t>
+          <t>Conners儿童行为问卷（父母用量表）</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>240</v>
+        <v>350</v>
       </c>
     </row>
     <row r="397">
@@ -17781,11 +17781,11 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>阿斯伯格综合征儿童筛查量表</t>
+          <t>学习方法测验</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
     </row>
     <row r="398">
@@ -17806,11 +17806,11 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>自杀自伤风险评估表</t>
+          <t>生活事件量表</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
     </row>
     <row r="399">
@@ -17831,11 +17831,11 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>YALE-BROWN强迫量表</t>
+          <t>阿斯伯格综合征儿童筛查量表</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
     </row>
     <row r="400">
@@ -17856,11 +17856,11 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>学习方法测验</t>
+          <t>简明精神病量表（BPRS）</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
     </row>
     <row r="401">
@@ -17881,11 +17881,11 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>简明精神病量表（BPRS）</t>
+          <t>心境障碍问卷（MDQ）</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
     </row>
     <row r="402">
@@ -17906,11 +17906,11 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>自信心测验</t>
+          <t>儿童抑郁量表</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>200</v>
+        <v>280</v>
       </c>
     </row>
     <row r="403">
@@ -17931,11 +17931,11 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>焦虑自评量表（SAS）母亲版</t>
+          <t>自信心测验</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>180</v>
+        <v>280</v>
       </c>
     </row>
     <row r="404">
@@ -17956,11 +17956,11 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>抑郁自评量表（SDS）母亲版</t>
+          <t>焦虑自评量表（SAS）父亲版</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
     </row>
     <row r="405">
@@ -17981,11 +17981,11 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>耶鲁综合抽动严重程度量表（TGTSS）</t>
+          <t>社交焦虑量表</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
     </row>
     <row r="406">
@@ -18006,11 +18006,11 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Conners儿童行为问卷（父母用量表）</t>
+          <t>YALE-BROWN强迫量表</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>175</v>
+        <v>240</v>
       </c>
     </row>
     <row r="407">
@@ -18031,11 +18031,11 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>人际关系综合诊断量表</t>
+          <t>抑郁自评量表（SDS）父亲版</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>160</v>
+        <v>240</v>
       </c>
     </row>
     <row r="408">
@@ -18056,11 +18056,11 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>米氮平片</t>
+          <t>压力测试问卷</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>144</v>
+        <v>240</v>
       </c>
     </row>
     <row r="409">
@@ -18081,11 +18081,11 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>盐酸氟西汀胶囊</t>
+          <t>人际关系综合诊断量表</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>126</v>
+        <v>200</v>
       </c>
     </row>
     <row r="410">
@@ -18106,11 +18106,11 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>小学生心理健康综合测量量表</t>
+          <t>创造力测试</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="411">
@@ -18131,11 +18131,11 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>抑郁自评量表（SDS）父亲版</t>
+          <t>观察力测试</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="412">
@@ -18156,11 +18156,11 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>压力测试问卷</t>
+          <t>耶鲁综合抽动严重程度量表（TGTSS）</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="413">
@@ -18181,11 +18181,11 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>长处和困难问卷（SDQ）家长版</t>
+          <t>儿童感觉统合能力失调检核表</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="414">
@@ -18206,11 +18206,11 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>焦虑自评量表（SAS）父亲版</t>
+          <t>学习时间管理</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="415">
@@ -18231,11 +18231,11 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>社交回避及苦恼量表（SAD）</t>
+          <t>米氮平片</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
     </row>
     <row r="416">
@@ -18256,11 +18256,11 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>抑郁状态问卷（DSI）</t>
+          <t>盐酸氟西汀胶囊</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="417">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>学习时间管理</t>
+          <t>小学生心理健康综合测量量表</t>
         </is>
       </c>
       <c r="E417" t="n">
@@ -18306,11 +18306,11 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>盐酸托莫西汀口服液</t>
+          <t>抑郁状态问卷（DSI）</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
     </row>
     <row r="419">
@@ -18331,11 +18331,11 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>睡眠觉醒模式自评问卷</t>
+          <t>社交回避及苦恼量表（SAD）</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="420">
@@ -18356,11 +18356,11 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>观察力测试</t>
+          <t>人际关系测试量表</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="421">
@@ -18381,11 +18381,11 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>关系评估量表（RSQ）</t>
+          <t>长处和困难问卷（SDQ）家长版</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="422">
@@ -18406,11 +18406,11 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>创造力测试</t>
+          <t>盐酸托莫西汀口服液</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="423">
@@ -18431,11 +18431,11 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>碳酸锂缓释片</t>
+          <t>睡眠觉醒模式自评问卷</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
     </row>
     <row r="424">
@@ -18456,11 +18456,11 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>儿童社交焦虑量表</t>
+          <t>攻击行为问卷（AQ）</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="425">
@@ -18481,11 +18481,11 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>心理适应性评定量表</t>
+          <t>关系评估量表（RSQ）</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="426">
@@ -18506,11 +18506,11 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>丙戊酸镁缓释片</t>
+          <t>碳酸锂缓释片</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
     </row>
     <row r="427">
@@ -18531,11 +18531,11 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>自我认知量表</t>
+          <t>儿童社交焦虑量表</t>
         </is>
       </c>
       <c r="E427" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="428">
@@ -18556,11 +18556,11 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>自杀意念自评量表</t>
+          <t>冲动性量表第11版中文版</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="429">
@@ -18581,11 +18581,11 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>人际关系测试量表</t>
+          <t>心理适应性评定量表</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="430">
@@ -18606,11 +18606,11 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>创新思维能力测试</t>
+          <t>盐酸苯海索片</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="431">
@@ -18631,11 +18631,11 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>创伤后应激障碍自评量表</t>
+          <t>丙戊酸镁缓释片</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="432">
@@ -18656,7 +18656,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>成人依恋量表修订版（RAAS)</t>
+          <t>社会适应能力诊断量表</t>
         </is>
       </c>
       <c r="E432" t="n">
@@ -18681,7 +18681,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>攻击行为问卷（AQ）</t>
+          <t>创新思维能力测试</t>
         </is>
       </c>
       <c r="E433" t="n">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>社会适应能力诊断量表</t>
+          <t>创伤后应激障碍自评量表</t>
         </is>
       </c>
       <c r="E434" t="n">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>自卑心理诊断量表</t>
+          <t>自我认知量表</t>
         </is>
       </c>
       <c r="E435" t="n">
@@ -18781,11 +18781,11 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>AI测评V2.0-家庭教养类型评估</t>
+          <t>自杀意念自评量表</t>
         </is>
       </c>
       <c r="E437" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="438">
@@ -18806,11 +18806,11 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>氨磺必利片</t>
+          <t>自卑心理诊断量表</t>
         </is>
       </c>
       <c r="E438" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="439">
@@ -18831,11 +18831,11 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>劳拉西泮片</t>
+          <t>成人依恋量表修订版（RAAS)</t>
         </is>
       </c>
       <c r="E439" t="n">
-        <v>31.85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="440">
@@ -18856,11 +18856,11 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>患者健康问卷躯体症状分量表（PHQ-15）</t>
+          <t>AI测评V2.0-家庭教养类型评估</t>
         </is>
       </c>
       <c r="E440" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="441">
@@ -18881,11 +18881,11 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>阿普唑仑片</t>
+          <t>氨磺必利片</t>
         </is>
       </c>
       <c r="E441" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="442">
@@ -18906,11 +18906,11 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>盐酸苯海索片</t>
+          <t>劳拉西泮片</t>
         </is>
       </c>
       <c r="E442" t="n">
-        <v>24</v>
+        <v>31.85</v>
       </c>
     </row>
     <row r="443">
@@ -18931,11 +18931,11 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>MBTI测试</t>
+          <t>患者健康问卷躯体症状分量表（PHQ-15）</t>
         </is>
       </c>
       <c r="E443" t="n">
-        <v>19.9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="444">
@@ -18956,11 +18956,11 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>右佐匹克隆片</t>
+          <t>阿普唑仑片</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="445">
@@ -18981,11 +18981,11 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>中学生心理健康状况测试</t>
+          <t>MBTI测试</t>
         </is>
       </c>
       <c r="E445" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="446">
@@ -19006,11 +19006,11 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>日常生活能力评定量表（ADL）</t>
+          <t>右佐匹克隆片</t>
         </is>
       </c>
       <c r="E446" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="447">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>基因检测(昂朴)（抗抑郁类药物）</t>
+          <t>中学生心理健康状况测试</t>
         </is>
       </c>
       <c r="E447" t="n">
@@ -19056,7 +19056,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>基因检测(昂朴)（抗癫痫药物/心境稳定剂）</t>
+          <t>基因检测(昂朴)（抗抑郁类药物）</t>
         </is>
       </c>
       <c r="E448" t="n">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>基因检测(昂朴)（抗精神分裂类药物）</t>
+          <t>情商量表</t>
         </is>
       </c>
       <c r="E449" t="n">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>社会功能缺陷筛选量表（SDSS）</t>
+          <t>日常生活能力评定量表（ADL）</t>
         </is>
       </c>
       <c r="E450" t="n">
@@ -19131,11 +19131,11 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>儿童康复（个人800）</t>
+          <t>基因检测(昂朴)（抗癫痫药物/心境稳定剂）</t>
         </is>
       </c>
       <c r="E451" t="n">
-        <v>-800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452">
@@ -19156,11 +19156,11 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>经颅磁仪</t>
+          <t>基因检测(昂朴)（抗精神分裂类药物）</t>
         </is>
       </c>
       <c r="E452" t="n">
-        <v>-1200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -19181,11 +19181,11 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>多动精灵产品套餐</t>
+          <t>社会功能缺陷筛选量表（SDSS）</t>
         </is>
       </c>
       <c r="E453" t="n">
-        <v>-5800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -19206,11 +19206,11 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>儿童康复IV（团体1500）</t>
+          <t>儿童康复（个人800）</t>
         </is>
       </c>
       <c r="E454" t="n">
-        <v>-6000</v>
+        <v>-800</v>
       </c>
     </row>
     <row r="455">
@@ -19231,11 +19231,11 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>日间中心 Ⅱ</t>
+          <t>经颅磁仪</t>
         </is>
       </c>
       <c r="E455" t="n">
-        <v>-55668.33</v>
+        <v>-1200</v>
       </c>
     </row>
     <row r="456">
@@ -19251,16 +19251,16 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>S-M婴儿-初中学生社会生活能力评定(0.5-14岁)</t>
+          <t>多动精灵产品套餐</t>
         </is>
       </c>
       <c r="E456" t="n">
-        <v>540</v>
+        <v>-5800</v>
       </c>
     </row>
     <row r="457">
@@ -19276,16 +19276,16 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>儿童康复IV（团体1500）</t>
         </is>
       </c>
       <c r="E457" t="n">
-        <v>38</v>
+        <v>-6000</v>
       </c>
     </row>
     <row r="458">
@@ -19301,16 +19301,16 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>青少年同行者计划周训营（网课）tcly</t>
+          <t>日间中心 Ⅱ</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>38</v>
+        <v>-55668.33</v>
       </c>
     </row>
     <row r="459">
@@ -19331,11 +19331,11 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>qy（网课、家长学）青少年家庭同行者计划一周短训营</t>
+          <t>S-M婴儿-初中学生社会生活能力评定(0.5-14岁)</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>19</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="460">
@@ -19356,11 +19356,11 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>19元青少年-LH</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E460" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="461">
@@ -19381,11 +19381,11 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>青少年同行者计划：试听课</t>
+          <t>青少年同行者计划周训营（网课）tcly</t>
         </is>
       </c>
       <c r="E461" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="462">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
+          <t>qy（网课、家长学）青少年家庭同行者计划一周短训营</t>
         </is>
       </c>
       <c r="E462" t="n">
@@ -19421,21 +19421,21 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>儿童青少年</t>
+          <t>19元青少年-LH</t>
         </is>
       </c>
       <c r="E463" t="n">
-        <v>78786</v>
+        <v>19</v>
       </c>
     </row>
     <row r="464">
@@ -19446,21 +19446,21 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>青少年-资深咨询</t>
+          <t>青少年同行者计划：试听课</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>20000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="465">
@@ -19471,21 +19471,21 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>精神心理</t>
+          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>3980</v>
+        <v>19</v>
       </c>
     </row>
     <row r="466">
@@ -19506,11 +19506,11 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>青少年-甄选咨询1次</t>
+          <t>儿童青少年</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>1500</v>
+        <v>78786</v>
       </c>
     </row>
     <row r="467">
@@ -19531,11 +19531,11 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>首单优惠咨询</t>
+          <t>青少年-资深咨询</t>
         </is>
       </c>
       <c r="E467" t="n">
-        <v>796</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="468">
@@ -19556,11 +19556,11 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>首次优惠咨询【甄选/专家】</t>
+          <t>精神心理</t>
         </is>
       </c>
       <c r="E468" t="n">
-        <v>598</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="469">
@@ -19581,11 +19581,11 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>电商咨询</t>
+          <t>青少年-甄选咨询1次</t>
         </is>
       </c>
       <c r="E469" t="n">
-        <v>398</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="470">
@@ -19601,16 +19601,16 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>首单优惠咨询</t>
         </is>
       </c>
       <c r="E470" t="n">
-        <v>19800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="471">
@@ -19626,16 +19626,16 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>儿童多动精灵专注站 PEERS 专项（16 节课）</t>
+          <t>首次优惠咨询【甄选/专家】</t>
         </is>
       </c>
       <c r="E471" t="n">
-        <v>16800</v>
+        <v>598</v>
       </c>
     </row>
     <row r="472">
@@ -19651,16 +19651,16 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>20分钟问诊（医师） -线上</t>
+          <t>电商咨询</t>
         </is>
       </c>
       <c r="E472" t="n">
-        <v>600</v>
+        <v>398</v>
       </c>
     </row>
     <row r="473">
@@ -19676,16 +19676,16 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>AI测评V4.0-手机成瘾程度评估</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>69</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="474">
@@ -19701,16 +19701,16 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>儿童多动精灵专注站 PEERS 专项（16 节课）</t>
         </is>
       </c>
       <c r="E474" t="n">
-        <v>1980</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="475">
@@ -19726,16 +19726,16 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>心灯计划实战派心理咨询师执业培训项目（定金）</t>
+          <t>20分钟问诊（医师） -线上</t>
         </is>
       </c>
       <c r="E475" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="476">
@@ -19751,16 +19751,16 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>安全感核心课：激活孩子内驱力第一步</t>
+          <t>AI测评V4.0-手机成瘾程度评估</t>
         </is>
       </c>
       <c r="E476" t="n">
-        <v>598</v>
+        <v>69</v>
       </c>
     </row>
     <row r="477">
@@ -19781,11 +19781,11 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买）</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E477" t="n">
-        <v>299</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="478">
@@ -19806,11 +19806,11 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
+          <t>心灯计划实战派心理咨询师执业培训项目（定金）</t>
         </is>
       </c>
       <c r="E478" t="n">
-        <v>263</v>
+        <v>800</v>
       </c>
     </row>
     <row r="479">
@@ -19831,11 +19831,11 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>安全感核心课：激活孩子内驱力第一步</t>
         </is>
       </c>
       <c r="E479" t="n">
-        <v>57</v>
+        <v>598</v>
       </c>
     </row>
     <row r="480">
@@ -19856,11 +19856,11 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>（网课、家长学）青少年家庭同行者计划一周LH</t>
+          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买）</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="481">
@@ -19881,11 +19881,11 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>青少年同行者计划周训营网课，家长学习应对孩子青春期问题</t>
+          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
         </is>
       </c>
       <c r="E481" t="n">
-        <v>38</v>
+        <v>263</v>
       </c>
     </row>
     <row r="482">
@@ -19906,11 +19906,11 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E482" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="483">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>qy（网课、家长学）青少年家庭同行者计划一周短训营</t>
+          <t>（网课、家长学）青少年家庭同行者计划一周LH</t>
         </is>
       </c>
       <c r="E483" t="n">
@@ -19956,7 +19956,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>（网课、家长学）青少年家庭同行者计划一周短训营LH</t>
+          <t>青少年同行者计划周训营网课，家长学习应对孩子青春期问题</t>
         </is>
       </c>
       <c r="E484" t="n">
@@ -19981,11 +19981,11 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>（不是书)1号课：睡前静心基础营-心理学网课+陪伴能量提升</t>
+          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
         </is>
       </c>
       <c r="E485" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="486">
@@ -20006,11 +20006,11 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>1号课：睡前静心基础营-心理学网课+陪伴能量提升</t>
+          <t>qy（网课、家长学）青少年家庭同行者计划一周短训营</t>
         </is>
       </c>
       <c r="E486" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="487">
@@ -20031,11 +20031,11 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>（没有书）青少年同行者计划一周短训营YL</t>
+          <t>（网课、家长学）青少年家庭同行者计划一周短训营LH</t>
         </is>
       </c>
       <c r="E487" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="488">
@@ -20056,11 +20056,11 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>青少年同行者计划：试听课</t>
+          <t>（不是书)1号课：睡前静心基础营-心理学网课+陪伴能量提升</t>
         </is>
       </c>
       <c r="E488" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="489">
@@ -20081,11 +20081,11 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
+          <t>1号课：睡前静心基础营-心理学网课+陪伴能量提升</t>
         </is>
       </c>
       <c r="E489" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="490">
@@ -20106,11 +20106,11 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>zh（网课、家长学）青少年家庭同行者计划一周短训营</t>
+          <t>（没有书）青少年同行者计划一周短训营YL</t>
         </is>
       </c>
       <c r="E490" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="491">
@@ -20131,7 +20131,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>青少年19元腾讯广告</t>
+          <t>青少年同行者计划：试听课</t>
         </is>
       </c>
       <c r="E491" t="n">
@@ -20156,11 +20156,11 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>（没有书）青少年同行者计划一周短训营-直播</t>
+          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
         </is>
       </c>
       <c r="E492" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="493">
@@ -20181,11 +20181,11 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>（没有书）青少年同行者计划一周短训营XY</t>
+          <t>zh（网课、家长学）青少年家庭同行者计划一周短训营</t>
         </is>
       </c>
       <c r="E493" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="494">
@@ -20206,11 +20206,11 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>青少年19元腾讯广告</t>
         </is>
       </c>
       <c r="E494" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="495">
@@ -20221,21 +20221,21 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>精神心理</t>
+          <t>（没有书）青少年同行者计划一周短训营-直播</t>
         </is>
       </c>
       <c r="E495" t="n">
-        <v>56390</v>
+        <v>9</v>
       </c>
     </row>
     <row r="496">
@@ -20246,21 +20246,21 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>青少年-资深咨询</t>
+          <t>（没有书）青少年同行者计划一周短训营XY</t>
         </is>
       </c>
       <c r="E496" t="n">
-        <v>10000</v>
+        <v>9</v>
       </c>
     </row>
     <row r="497">
@@ -20271,21 +20271,21 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>儿童青少年</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>2588</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498">
@@ -20306,11 +20306,11 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>首次优惠咨询【甄选/专家】</t>
+          <t>精神心理</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>1196</v>
+        <v>56390</v>
       </c>
     </row>
     <row r="499">
@@ -20331,11 +20331,11 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>电商咨询</t>
+          <t>青少年-资深咨询</t>
         </is>
       </c>
       <c r="E499" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="500">
@@ -20356,11 +20356,11 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>首单优惠咨询</t>
+          <t>儿童青少年</t>
         </is>
       </c>
       <c r="E500" t="n">
-        <v>796</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="501">
@@ -20376,16 +20376,16 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>首次优惠咨询【甄选/专家】</t>
         </is>
       </c>
       <c r="E501" t="n">
-        <v>1680</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="502">
@@ -20401,16 +20401,16 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>儿童多动精灵专注站 PEERS 专项（16 节课）</t>
+          <t>电商咨询</t>
         </is>
       </c>
       <c r="E502" t="n">
-        <v>16800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="503">
@@ -20426,16 +20426,16 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>20分钟问诊（医师） -线上</t>
+          <t>首单优惠咨询</t>
         </is>
       </c>
       <c r="E503" t="n">
-        <v>600</v>
+        <v>796</v>
       </c>
     </row>
     <row r="504">
@@ -20451,16 +20451,16 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>处方</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="E504" t="n">
-        <v>388.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="505">
@@ -20481,11 +20481,11 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>AI测评V2.0-家庭教养类型评估</t>
+          <t>儿童多动精灵专注站 PEERS 专项（16 节课）</t>
         </is>
       </c>
       <c r="E505" t="n">
-        <v>39</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="506">
@@ -20506,11 +20506,11 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>AI测评V5.0-原型家庭模式评估</t>
+          <t>20分钟问诊（医师） -线上</t>
         </is>
       </c>
       <c r="E506" t="n">
-        <v>29</v>
+        <v>600</v>
       </c>
     </row>
     <row r="507">
@@ -20526,16 +20526,16 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>[自我成长/疗愈] 完形心理认知课，增加智慧。</t>
+          <t>处方</t>
         </is>
       </c>
       <c r="E507" t="n">
-        <v>999</v>
+        <v>388.84</v>
       </c>
     </row>
     <row r="508">
@@ -20551,16 +20551,16 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>安全感核心课：激活孩子内驱力第一步</t>
+          <t>AI测评V2.0-家庭教养类型评估</t>
         </is>
       </c>
       <c r="E508" t="n">
-        <v>299</v>
+        <v>39</v>
       </c>
     </row>
     <row r="509">
@@ -20576,16 +20576,16 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>AI测评V5.0-原型家庭模式评估</t>
         </is>
       </c>
       <c r="E509" t="n">
-        <v>200</v>
+        <v>29</v>
       </c>
     </row>
     <row r="510">
@@ -20606,11 +20606,11 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
+          <t>[自我成长/疗愈] 完形心理认知课，增加智慧。</t>
         </is>
       </c>
       <c r="E510" t="n">
-        <v>133</v>
+        <v>999</v>
       </c>
     </row>
     <row r="511">
@@ -20631,11 +20631,11 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>青少年同行者计划：试听课</t>
+          <t>安全感核心课：激活孩子内驱力第一步</t>
         </is>
       </c>
       <c r="E511" t="n">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="512">
@@ -20656,11 +20656,11 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>青少年同行者计划周训营（网课）tcly</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E512" t="n">
-        <v>38</v>
+        <v>200</v>
       </c>
     </row>
     <row r="513">
@@ -20681,11 +20681,11 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>（不是书)1号课：睡前静心基础营-心理学网课+陪伴能量提升</t>
+          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
         </is>
       </c>
       <c r="E513" t="n">
-        <v>29</v>
+        <v>133</v>
       </c>
     </row>
     <row r="514">
@@ -20706,11 +20706,11 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>（不是书，不是药）睡前正念练习训练营</t>
+          <t>青少年同行者计划：试听课</t>
         </is>
       </c>
       <c r="E514" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="515">
@@ -20731,11 +20731,11 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
+          <t>青少年同行者计划周训营（网课）tcly</t>
         </is>
       </c>
       <c r="E515" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="516">
@@ -20756,11 +20756,11 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>yl5（网课、家长学）青少年家庭同行者计划一周短训营</t>
+          <t>（不是书)1号课：睡前静心基础营-心理学网课+陪伴能量提升</t>
         </is>
       </c>
       <c r="E516" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="517">
@@ -20781,11 +20781,11 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>义诊-线上</t>
+          <t>（不是书，不是药）睡前正念练习训练营</t>
         </is>
       </c>
       <c r="E517" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="518">
@@ -20796,21 +20796,21 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>精神心理</t>
+          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
         </is>
       </c>
       <c r="E518" t="n">
-        <v>194378</v>
+        <v>19</v>
       </c>
     </row>
     <row r="519">
@@ -20821,21 +20821,21 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>儿童青少年</t>
+          <t>yl5（网课、家长学）青少年家庭同行者计划一周短训营</t>
         </is>
       </c>
       <c r="E519" t="n">
-        <v>133978</v>
+        <v>19</v>
       </c>
     </row>
     <row r="520">
@@ -20846,21 +20846,21 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>青少年-资深咨询</t>
+          <t>义诊-线上</t>
         </is>
       </c>
       <c r="E520" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="521">
@@ -20881,11 +20881,11 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>电商咨询</t>
+          <t>精神心理</t>
         </is>
       </c>
       <c r="E521" t="n">
-        <v>11990</v>
+        <v>194378</v>
       </c>
     </row>
     <row r="522">
@@ -20906,11 +20906,11 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>首单优惠咨询</t>
+          <t>儿童青少年</t>
         </is>
       </c>
       <c r="E522" t="n">
-        <v>3184</v>
+        <v>133978</v>
       </c>
     </row>
     <row r="523">
@@ -20931,11 +20931,11 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>青少年-资深咨询1次</t>
+          <t>青少年-资深咨询</t>
         </is>
       </c>
       <c r="E523" t="n">
-        <v>1200</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="524">
@@ -20956,11 +20956,11 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>首单 优惠咨询</t>
+          <t>电商咨询</t>
         </is>
       </c>
       <c r="E524" t="n">
-        <v>796</v>
+        <v>11990</v>
       </c>
     </row>
     <row r="525">
@@ -20981,11 +20981,11 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>（赠）1v1咨询 1次</t>
+          <t>首单优惠咨询</t>
         </is>
       </c>
       <c r="E525" t="n">
-        <v>0</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="526">
@@ -21001,16 +21001,16 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>动力唤醒-少年说</t>
+          <t>青少年-资深咨询1次</t>
         </is>
       </c>
       <c r="E526" t="n">
-        <v>118800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="527">
@@ -21026,16 +21026,16 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>首单 优惠咨询</t>
         </is>
       </c>
       <c r="E527" t="n">
-        <v>72600</v>
+        <v>796</v>
       </c>
     </row>
     <row r="528">
@@ -21051,16 +21051,16 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（三阶）</t>
+          <t>（赠）1v1咨询 1次</t>
         </is>
       </c>
       <c r="E528" t="n">
-        <v>38820</v>
+        <v>0</v>
       </c>
     </row>
     <row r="529">
@@ -21081,11 +21081,11 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（一阶）</t>
+          <t>动力唤醒-少年说</t>
         </is>
       </c>
       <c r="E529" t="n">
-        <v>19800</v>
+        <v>118800</v>
       </c>
     </row>
     <row r="530">
@@ -21106,11 +21106,11 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>少年说-认知引导</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="E530" t="n">
-        <v>13200</v>
+        <v>72600</v>
       </c>
     </row>
     <row r="531">
@@ -21131,11 +21131,11 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>家庭守护计划2.0（三阶）</t>
         </is>
       </c>
       <c r="E531" t="n">
-        <v>3360</v>
+        <v>38820</v>
       </c>
     </row>
     <row r="532">
@@ -21151,16 +21151,16 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程）</t>
+          <t>家庭守护计划2.0（一阶）</t>
         </is>
       </c>
       <c r="E532" t="n">
-        <v>45600</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="533">
@@ -21176,16 +21176,16 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>少年说-认知引导</t>
         </is>
       </c>
       <c r="E533" t="n">
-        <v>8000</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="534">
@@ -21201,16 +21201,16 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>肠道菌群检测</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="E534" t="n">
-        <v>1000</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="535">
@@ -21226,16 +21226,16 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>儿童多动精灵专注站 PEERS 专项（16 节课）</t>
+          <t>肠道菌群移植（双疗程）</t>
         </is>
       </c>
       <c r="E535" t="n">
-        <v>67200</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="536">
@@ -21251,16 +21251,16 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>20分钟问诊（高级医师）-线上</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="E536" t="n">
-        <v>3600</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="537">
@@ -21276,16 +21276,16 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱---</t>
+          <t>肠道菌群检测</t>
         </is>
       </c>
       <c r="E537" t="n">
-        <v>2005.59</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="538">
@@ -21306,11 +21306,11 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>处方</t>
+          <t>儿童多动精灵专注站 PEERS 专项（16 节课）</t>
         </is>
       </c>
       <c r="E538" t="n">
-        <v>1956.56</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="539">
@@ -21331,11 +21331,11 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>50分钟问诊（高级医师）-线下</t>
+          <t>20分钟问诊（高级医师）-线上</t>
         </is>
       </c>
       <c r="E539" t="n">
-        <v>1200</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="540">
@@ -21356,11 +21356,11 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>20分钟问诊（高级医师）-线下</t>
+          <t>【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱---</t>
         </is>
       </c>
       <c r="E540" t="n">
-        <v>300</v>
+        <v>2005.59</v>
       </c>
     </row>
     <row r="541">
@@ -21381,11 +21381,11 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>AI测评V3.0-青少年心理与家庭综合评估</t>
+          <t>处方</t>
         </is>
       </c>
       <c r="E541" t="n">
-        <v>59</v>
+        <v>1956.56</v>
       </c>
     </row>
     <row r="542">
@@ -21406,11 +21406,11 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>全方位心理健康检查｜洞察内心</t>
+          <t>50分钟问诊（高级医师）-线下</t>
         </is>
       </c>
       <c r="E542" t="n">
-        <v>0.99</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="543">
@@ -21426,16 +21426,16 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>韩冰老师一百天疗愈计划</t>
+          <t>20分钟问诊（高级医师）-线下</t>
         </is>
       </c>
       <c r="E543" t="n">
-        <v>80000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="544">
@@ -21451,16 +21451,16 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>AI测评V3.0-青少年心理与家庭综合评估</t>
         </is>
       </c>
       <c r="E544" t="n">
-        <v>21500</v>
+        <v>59</v>
       </c>
     </row>
     <row r="545">
@@ -21476,16 +21476,16 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>压力创伤释放工作坊</t>
+          <t>全方位心理健康检查｜洞察内心</t>
         </is>
       </c>
       <c r="E545" t="n">
-        <v>9900</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="546">
@@ -21506,11 +21506,11 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>门店《一日一生》</t>
+          <t>韩冰老师一百天疗愈计划</t>
         </is>
       </c>
       <c r="E546" t="n">
-        <v>2388</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="547">
@@ -21531,11 +21531,11 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>青少年同行者智慧父母启航营</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E547" t="n">
-        <v>1280</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="548">
@@ -21556,11 +21556,11 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题</t>
+          <t>压力创伤释放工作坊</t>
         </is>
       </c>
       <c r="E548" t="n">
-        <v>1280</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="549">
@@ -21581,11 +21581,11 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练网课-直播专享zx</t>
+          <t>门店《一日一生》</t>
         </is>
       </c>
       <c r="E549" t="n">
-        <v>299</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="550">
@@ -21606,11 +21606,11 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>青少年同行者计划：试听课</t>
+          <t>青少年同行者智慧父母启航营</t>
         </is>
       </c>
       <c r="E550" t="n">
-        <v>76</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="551">
@@ -21631,11 +21631,11 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
+          <t>（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题</t>
         </is>
       </c>
       <c r="E551" t="n">
-        <v>57</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="552">
@@ -21656,11 +21656,11 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>qy（网课、家长学）青少年家庭同行者计划一周短训营</t>
+          <t>青春期家庭困扰21天陪跑指导训练网课-直播专享zx</t>
         </is>
       </c>
       <c r="E552" t="n">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="553">
@@ -21681,11 +21681,11 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>青少年19元腾讯广告</t>
+          <t>青少年同行者计划：试听课</t>
         </is>
       </c>
       <c r="E553" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="554">
@@ -21706,11 +21706,11 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>青少年19元巨量</t>
+          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
         </is>
       </c>
       <c r="E554" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="555">
@@ -21731,7 +21731,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>19元青少年-LH</t>
+          <t>qy（网课、家长学）青少年家庭同行者计划一周短训营</t>
         </is>
       </c>
       <c r="E555" t="n">
@@ -21756,11 +21756,11 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>1号课：睡前静心基础营-心理学网课+陪伴能量提升</t>
+          <t>青少年19元腾讯广告</t>
         </is>
       </c>
       <c r="E556" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="557">
@@ -21781,11 +21781,11 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>青少年同行者计划周训营（网课）tcly</t>
+          <t>青少年19元巨量</t>
         </is>
       </c>
       <c r="E557" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="558">
@@ -21806,11 +21806,11 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>19元青少年-LH</t>
         </is>
       </c>
       <c r="E558" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="559">
@@ -21831,11 +21831,11 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>（网课、家长学）青少年家庭同行者计划一周LH</t>
+          <t>1号课：睡前静心基础营-心理学网课+陪伴能量提升</t>
         </is>
       </c>
       <c r="E559" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="560">
@@ -21856,11 +21856,11 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>（没有书）青少年同行者计划一周短训营XY</t>
+          <t>青少年同行者计划周训营（网课）tcly</t>
         </is>
       </c>
       <c r="E560" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="561">
@@ -21881,11 +21881,11 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>（没有书）青少年同行者计划一周短训营YL</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E561" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="562">
@@ -21906,11 +21906,11 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>（网课、家长学）青少年家庭同行者计划一周LH</t>
         </is>
       </c>
       <c r="E562" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="563">
@@ -21931,11 +21931,11 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>义诊-线上</t>
+          <t>（没有书）青少年同行者计划一周短训营XY</t>
         </is>
       </c>
       <c r="E563" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="564">
@@ -21956,11 +21956,11 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>21天蛋壳跳动休学复能营</t>
+          <t>（没有书）青少年同行者计划一周短训营YL</t>
         </is>
       </c>
       <c r="E564" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="565">
@@ -21981,7 +21981,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E565" t="n">
@@ -22006,7 +22006,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>义诊-线上</t>
         </is>
       </c>
       <c r="E566" t="n">
@@ -22021,21 +22021,21 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>儿童青少年</t>
+          <t>21天蛋壳跳动休学复能营</t>
         </is>
       </c>
       <c r="E567" t="n">
-        <v>244392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="568">
@@ -22046,21 +22046,21 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>京东渠道10次咨询套餐</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E568" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569">
@@ -22071,21 +22071,21 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>京东渠道4次咨询套餐</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E569" t="n">
-        <v>12400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="570">
@@ -22106,11 +22106,11 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>精神心理</t>
+          <t>儿童青少年</t>
         </is>
       </c>
       <c r="E570" t="n">
-        <v>8586</v>
+        <v>244392</v>
       </c>
     </row>
     <row r="571">
@@ -22131,11 +22131,11 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>电商咨询</t>
+          <t>京东渠道10次咨询套餐</t>
         </is>
       </c>
       <c r="E571" t="n">
-        <v>3582</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="572">
@@ -22156,11 +22156,11 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>京东渠道1次咨询套餐</t>
+          <t>京东渠道4次咨询套餐</t>
         </is>
       </c>
       <c r="E572" t="n">
-        <v>800</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="573">
@@ -22176,16 +22176,16 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>家庭守护计划【专业版】</t>
+          <t>精神心理</t>
         </is>
       </c>
       <c r="E573" t="n">
-        <v>12000</v>
+        <v>8586</v>
       </c>
     </row>
     <row r="574">
@@ -22201,16 +22201,16 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（一阶）</t>
+          <t>电商咨询</t>
         </is>
       </c>
       <c r="E574" t="n">
-        <v>7800</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="575">
@@ -22226,16 +22226,16 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>京东渠道1次咨询套餐</t>
         </is>
       </c>
       <c r="E575" t="n">
-        <v>6600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="576">
@@ -22251,16 +22251,16 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>肠道菌群检测</t>
+          <t>家庭守护计划【专业版】</t>
         </is>
       </c>
       <c r="E576" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="577">
@@ -22276,16 +22276,16 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>20分钟问诊（医师） -线上</t>
+          <t>家庭守护计划2.0（一阶）</t>
         </is>
       </c>
       <c r="E577" t="n">
-        <v>2200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="578">
@@ -22301,16 +22301,16 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>处方</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="E578" t="n">
-        <v>1419.49</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="579">
@@ -22326,16 +22326,16 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>全方位心理健康检查｜洞察内心</t>
+          <t>肠道菌群检测</t>
         </is>
       </c>
       <c r="E579" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="580">
@@ -22351,16 +22351,16 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20分钟问诊（医师） -线上</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>23412.43</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="581">
@@ -22376,16 +22376,16 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>[自我成长/疗愈] 完形心理认知课，增加智慧。</t>
+          <t>处方</t>
         </is>
       </c>
       <c r="E581" t="n">
-        <v>999</v>
+        <v>1419.49</v>
       </c>
     </row>
     <row r="582">
@@ -22401,16 +22401,16 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>安全感核心课：激活孩子内驱力第一步</t>
+          <t>全方位心理健康检查｜洞察内心</t>
         </is>
       </c>
       <c r="E582" t="n">
-        <v>299</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="583">
@@ -22431,11 +22431,11 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E583" t="n">
-        <v>38</v>
+        <v>24188.51</v>
       </c>
     </row>
     <row r="584">
@@ -22456,11 +22456,11 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>青少年19元巨量</t>
+          <t>[自我成长/疗愈] 完形心理认知课，增加智慧。</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>19</v>
+        <v>999</v>
       </c>
     </row>
     <row r="585">
@@ -22481,11 +22481,11 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>青少年19元腾讯广告</t>
+          <t>安全感核心课：激活孩子内驱力第一步</t>
         </is>
       </c>
       <c r="E585" t="n">
-        <v>19</v>
+        <v>299</v>
       </c>
     </row>
     <row r="586">
@@ -22506,11 +22506,11 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题yh</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E586" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="587">
@@ -22531,11 +22531,11 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>（没有书）青少年同行者计划一周短训营WY</t>
+          <t>青少年19元巨量</t>
         </is>
       </c>
       <c r="E587" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="588">
@@ -22556,11 +22556,11 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>青少年19元腾讯广告</t>
         </is>
       </c>
       <c r="E588" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="589">
@@ -22581,11 +22581,11 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>义诊-线上</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题yh</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="590">
@@ -22606,11 +22606,11 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>（没有书）青少年同行者计划一周短训营WY</t>
         </is>
       </c>
       <c r="E590" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="591">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E591" t="n">
@@ -22656,7 +22656,7 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>义诊-线上</t>
         </is>
       </c>
       <c r="E592" t="n">
@@ -22671,21 +22671,21 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>精神心理</t>
+          <t>观心少年2天1夜心理赋能营-ys-北京</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>151194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="594">
@@ -22696,21 +22696,21 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>儿童青少年</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>82388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="595">
@@ -22721,21 +22721,21 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>青少年10次咨询-资深</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="596">
@@ -22756,11 +22756,11 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>青少年-资深咨询</t>
+          <t>精神心理</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>10000</v>
+        <v>151194</v>
       </c>
     </row>
     <row r="597">
@@ -22781,11 +22781,11 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>首单优惠咨询</t>
+          <t>儿童青少年</t>
         </is>
       </c>
       <c r="E597" t="n">
-        <v>2388</v>
+        <v>82388</v>
       </c>
     </row>
     <row r="598">
@@ -22806,11 +22806,11 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>首单 优惠咨询</t>
+          <t>青少年10次咨询-资深</t>
         </is>
       </c>
       <c r="E598" t="n">
-        <v>1990</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="599">
@@ -22826,16 +22826,16 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（一阶）</t>
+          <t>青少年-资深咨询</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>19800</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="600">
@@ -22851,16 +22851,16 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>少年说-认知引导</t>
+          <t>首单优惠咨询</t>
         </is>
       </c>
       <c r="E600" t="n">
-        <v>13200</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="601">
@@ -22876,16 +22876,16 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0续航升级</t>
+          <t>首单 优惠咨询</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>13000</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="602">
@@ -22906,11 +22906,11 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>家庭守护计划2.0（一阶）</t>
         </is>
       </c>
       <c r="E602" t="n">
-        <v>6600</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="603">
@@ -22926,16 +22926,16 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>肠道菌群移植（双疗程）</t>
+          <t>少年说-认知引导</t>
         </is>
       </c>
       <c r="E603" t="n">
-        <v>45600</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="604">
@@ -22951,16 +22951,16 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>家庭守护计划2.0续航升级</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>24800</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="605">
@@ -22976,16 +22976,16 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>20分钟问诊（医师） -线上</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="E605" t="n">
-        <v>200</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="606">
@@ -23001,16 +23001,16 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>门店《一日一生》</t>
+          <t>肠道菌群移植（双疗程）</t>
         </is>
       </c>
       <c r="E606" t="n">
-        <v>398</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="607">
@@ -23026,16 +23026,16 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>青少年19元巨量</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="E607" t="n">
-        <v>19</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="608">
@@ -23051,16 +23051,16 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题yh</t>
+          <t>20分钟问诊（医师） -线上</t>
         </is>
       </c>
       <c r="E608" t="n">
-        <v>19</v>
+        <v>200</v>
       </c>
     </row>
     <row r="609">
@@ -23081,11 +23081,11 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>门店《一日一生》</t>
         </is>
       </c>
       <c r="E609" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="610">
@@ -23106,11 +23106,11 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>青少年19元巨量</t>
         </is>
       </c>
       <c r="E610" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="611">
@@ -23131,11 +23131,11 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题yh</t>
         </is>
       </c>
       <c r="E611" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="612">
@@ -23156,7 +23156,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>青少年同行者智慧父母启航营</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E612" t="n">
@@ -23171,21 +23171,21 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>儿童青少年</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E613" t="n">
-        <v>55176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="614">
@@ -23196,21 +23196,21 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>青少年-资深咨询</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E614" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="615">
@@ -23221,21 +23221,21 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>精神心理</t>
+          <t>青少年同行者智慧父母启航营</t>
         </is>
       </c>
       <c r="E615" t="n">
-        <v>10796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="616">
@@ -23256,11 +23256,11 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>电商咨询</t>
+          <t>儿童青少年</t>
         </is>
       </c>
       <c r="E616" t="n">
-        <v>5186</v>
+        <v>55176</v>
       </c>
     </row>
     <row r="617">
@@ -23281,11 +23281,11 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>青少年-资深咨询1次</t>
+          <t>青少年-资深咨询</t>
         </is>
       </c>
       <c r="E617" t="n">
-        <v>4800</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="618">
@@ -23306,11 +23306,11 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>青少年-甄选咨询1次</t>
+          <t>精神心理</t>
         </is>
       </c>
       <c r="E618" t="n">
-        <v>4500</v>
+        <v>10796</v>
       </c>
     </row>
     <row r="619">
@@ -23331,11 +23331,11 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>首次优惠咨询【甄选/专家】</t>
+          <t>电商咨询</t>
         </is>
       </c>
       <c r="E619" t="n">
-        <v>3588</v>
+        <v>5186</v>
       </c>
     </row>
     <row r="620">
@@ -23356,11 +23356,11 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>首单优惠咨询</t>
+          <t>青少年-资深咨询1次</t>
         </is>
       </c>
       <c r="E620" t="n">
-        <v>398</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="621">
@@ -23376,16 +23376,16 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>青少年-甄选咨询1次</t>
         </is>
       </c>
       <c r="E621" t="n">
-        <v>13200</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="622">
@@ -23401,16 +23401,16 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>1元家庭守护计划ys</t>
+          <t>首次优惠咨询【甄选/专家】</t>
         </is>
       </c>
       <c r="E622" t="n">
-        <v>0</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="623">
@@ -23426,16 +23426,16 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>肠道菌群检测</t>
+          <t>首单优惠咨询</t>
         </is>
       </c>
       <c r="E623" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="624">
@@ -23451,16 +23451,16 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>青少年营地动力唤醒方案</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="E624" t="n">
-        <v>49800</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="625">
@@ -23476,16 +23476,16 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1元家庭守护计划ys</t>
         </is>
       </c>
       <c r="E625" t="n">
-        <v>30918.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="626">
@@ -23501,16 +23501,16 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>肠道菌群检测</t>
         </is>
       </c>
       <c r="E626" t="n">
-        <v>7920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="627">
@@ -23531,11 +23531,11 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营补差链接</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E627" t="n">
-        <v>4380</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="628">
@@ -23556,11 +23556,11 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
+          <t>青少年营地动力唤醒方案</t>
         </is>
       </c>
       <c r="E628" t="n">
-        <v>76</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="629">
@@ -23581,11 +23581,11 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>（网课、家长学）青少年家庭同行者计划一周短训营LH</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E629" t="n">
-        <v>57</v>
+        <v>31169.4</v>
       </c>
     </row>
     <row r="630">
@@ -23606,11 +23606,11 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E630" t="n">
-        <v>19</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="631">
@@ -23631,11 +23631,11 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
+          <t>【青春进化论】亲子成长2日营补差链接</t>
         </is>
       </c>
       <c r="E631" t="n">
-        <v>19</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="632">
@@ -23656,11 +23656,11 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>青少年同行者计划：试听课</t>
+          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
         </is>
       </c>
       <c r="E632" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="633">
@@ -23681,11 +23681,11 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>青少年同行者计划周训营（网课）WY</t>
+          <t>（网课、家长学）青少年家庭同行者计划一周短训营LH</t>
         </is>
       </c>
       <c r="E633" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="634">
@@ -23706,11 +23706,11 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>（没有书）青少年同行者计划一周短训营YL</t>
+          <t>青少年同行者计划：试听课</t>
         </is>
       </c>
       <c r="E634" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="635">
@@ -23731,11 +23731,11 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
         </is>
       </c>
       <c r="E635" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="636">
@@ -23756,11 +23756,11 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>21天蛋壳跳动休学复能营</t>
+          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
         </is>
       </c>
       <c r="E636" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="637">
@@ -23781,11 +23781,11 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>青少年同行者计划周训营（网课）WY</t>
         </is>
       </c>
       <c r="E637" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="638">
@@ -23806,11 +23806,11 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>（没有书）青少年同行者计划一周短训营YL</t>
         </is>
       </c>
       <c r="E638" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="639">
@@ -23831,7 +23831,7 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>杭州一日一间体验课</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E639" t="n">
@@ -23856,7 +23856,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>杭州一日一生体验课</t>
+          <t>21天蛋壳跳动休学复能营</t>
         </is>
       </c>
       <c r="E640" t="n">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E642" t="n">
@@ -23931,7 +23931,7 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>青少年同行者智慧父母启航营</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E643" t="n">
@@ -23946,21 +23946,21 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>京东渠道10次咨询套餐</t>
+          <t>杭州一日一间体验课</t>
         </is>
       </c>
       <c r="E644" t="n">
-        <v>105000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="645">
@@ -23971,21 +23971,21 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>儿童青少年</t>
+          <t>青少年同行者智慧父母启航营</t>
         </is>
       </c>
       <c r="E645" t="n">
-        <v>86796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="646">
@@ -24006,11 +24006,11 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>精神心理</t>
+          <t>京东渠道10次咨询套餐</t>
         </is>
       </c>
       <c r="E646" t="n">
-        <v>33192</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="647">
@@ -24031,11 +24031,11 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>青少年-资深咨询</t>
+          <t>儿童青少年</t>
         </is>
       </c>
       <c r="E647" t="n">
-        <v>30000</v>
+        <v>86796</v>
       </c>
     </row>
     <row r="648">
@@ -24056,11 +24056,11 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>京东渠道1次咨询套餐</t>
+          <t>精神心理</t>
         </is>
       </c>
       <c r="E648" t="n">
-        <v>14400</v>
+        <v>33192</v>
       </c>
     </row>
     <row r="649">
@@ -24081,11 +24081,11 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>京东渠道4次咨询套餐</t>
+          <t>青少年-资深咨询</t>
         </is>
       </c>
       <c r="E649" t="n">
-        <v>6200</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="650">
@@ -24106,11 +24106,11 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>5次咨询（成人）</t>
+          <t>京东渠道1次咨询套餐</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>5000</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="651">
@@ -24131,11 +24131,11 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>电商咨询</t>
+          <t>京东渠道4次咨询套餐</t>
         </is>
       </c>
       <c r="E651" t="n">
-        <v>2388</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="652">
@@ -24156,11 +24156,11 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>青少年-青英咨询1次</t>
+          <t>5次咨询（成人）</t>
         </is>
       </c>
       <c r="E652" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="653">
@@ -24181,11 +24181,11 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>首单优惠咨询</t>
+          <t>电商咨询</t>
         </is>
       </c>
       <c r="E653" t="n">
-        <v>796</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="654">
@@ -24201,16 +24201,16 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0二阶（4980补差价产品）</t>
+          <t>青少年-青英咨询1次</t>
         </is>
       </c>
       <c r="E654" t="n">
-        <v>26820</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="655">
@@ -24226,16 +24226,16 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>首单优惠咨询</t>
         </is>
       </c>
       <c r="E655" t="n">
-        <v>6600</v>
+        <v>796</v>
       </c>
     </row>
     <row r="656">
@@ -24251,16 +24251,16 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>肠道菌群检测</t>
+          <t>家庭守护计划2.0二阶（4980补差价产品）</t>
         </is>
       </c>
       <c r="E656" t="n">
-        <v>0</v>
+        <v>26820</v>
       </c>
     </row>
     <row r="657">
@@ -24276,16 +24276,16 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>20分钟问诊（专家医师） -线下</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="E657" t="n">
-        <v>500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="658">
@@ -24301,16 +24301,16 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>肠道菌群检测</t>
         </is>
       </c>
       <c r="E658" t="n">
-        <v>50346.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="659">
@@ -24326,16 +24326,16 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>门店《一日一生》</t>
+          <t>20分钟问诊（专家医师） -线下</t>
         </is>
       </c>
       <c r="E659" t="n">
-        <v>2388</v>
+        <v>500</v>
       </c>
     </row>
     <row r="660">
@@ -24356,11 +24356,11 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>57</v>
+        <v>51199.21</v>
       </c>
     </row>
     <row r="661">
@@ -24381,11 +24381,11 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>门店《一日一生》</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>19</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="662">
@@ -24406,11 +24406,11 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>（没有书）青少年同行者计划一周短训营YL</t>
+          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="663">
@@ -24431,11 +24431,11 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E663" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="664">
@@ -24456,11 +24456,11 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>（没有书）青少年同行者计划一周短训营YL</t>
         </is>
       </c>
       <c r="E664" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="665">
@@ -24481,7 +24481,7 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E665" t="n">
@@ -24506,7 +24506,7 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>观心少年2天1夜心理赋能营-ys-北京</t>
         </is>
       </c>
       <c r="E666" t="n">
@@ -24531,7 +24531,7 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>青少年同行者智慧父母启航营</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E667" t="n">
@@ -24546,21 +24546,21 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>青少年-资深咨询</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E668" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="669">
@@ -24571,21 +24571,21 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>儿童青少年</t>
+          <t>青少年同行者智慧父母启航营</t>
         </is>
       </c>
       <c r="E669" t="n">
-        <v>32996.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="670">
@@ -24606,11 +24606,11 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>精神心理</t>
+          <t>青少年-资深咨询</t>
         </is>
       </c>
       <c r="E670" t="n">
-        <v>28380</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="671">
@@ -24631,11 +24631,11 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>首次优惠咨询【甄选/专家】</t>
+          <t>精神心理</t>
         </is>
       </c>
       <c r="E671" t="n">
-        <v>2990</v>
+        <v>27982</v>
       </c>
     </row>
     <row r="672">
@@ -24656,11 +24656,11 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>青少年-资深咨询1次</t>
+          <t>儿童青少年</t>
         </is>
       </c>
       <c r="E672" t="n">
-        <v>1200</v>
+        <v>22996.01</v>
       </c>
     </row>
     <row r="673">
@@ -24681,11 +24681,11 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>电商咨询</t>
+          <t>首次优惠咨询【甄选/专家】</t>
         </is>
       </c>
       <c r="E673" t="n">
-        <v>398</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="674">
@@ -24701,16 +24701,16 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（一阶）</t>
+          <t>青少年-资深咨询1次</t>
         </is>
       </c>
       <c r="E674" t="n">
-        <v>19800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="675">
@@ -24726,16 +24726,16 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>电商咨询</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>6600</v>
+        <v>398</v>
       </c>
     </row>
     <row r="676">
@@ -24756,11 +24756,11 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>1元家庭守护计划ys</t>
+          <t>家庭守护计划2.0（一阶）</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>0</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="677">
@@ -24776,16 +24776,16 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>AI测评V2.0-家庭教养类型评估</t>
+          <t>1元家庭守护计划ys</t>
         </is>
       </c>
       <c r="E677" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="678">
@@ -24806,11 +24806,11 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>AI测评V5.0-原型家庭模式评估</t>
+          <t>AI测评V2.0-家庭教养类型评估</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="679">
@@ -24826,16 +24826,16 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>青少年营地动力唤醒方案</t>
+          <t>AI测评V5.0-原型家庭模式评估</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>49800</v>
+        <v>29</v>
       </c>
     </row>
     <row r="680">
@@ -24856,11 +24856,11 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>未来之翼7日心理能量唤醒营</t>
+          <t>青少年营地动力唤醒方案</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>19800</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="681">
@@ -24885,7 +24885,7 @@
         </is>
       </c>
       <c r="E681" t="n">
-        <v>12547.1</v>
+        <v>13765.86</v>
       </c>
     </row>
     <row r="682">
@@ -25010,7 +25010,7 @@
         </is>
       </c>
       <c r="E686" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="687">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>21天蛋壳跳动休学复能营</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E693" t="n">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>21天蛋壳跳动休学复能营</t>
         </is>
       </c>
       <c r="E694" t="n">
@@ -25231,7 +25231,7 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>杭州一日一间体验课</t>
         </is>
       </c>
       <c r="E695" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>杭州一日一间体验课</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E696" t="n">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>杭州一日一生体验课</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E697" t="n">
@@ -25306,7 +25306,7 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>杭州一日一生体验课</t>
         </is>
       </c>
       <c r="E698" t="n">
@@ -25331,7 +25331,7 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>青少年同行者计划</t>
         </is>
       </c>
       <c r="E699" t="n">
@@ -25346,21 +25346,21 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>青少年同行者计划</t>
+          <t>青少年-专家咨询</t>
         </is>
       </c>
       <c r="E700" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="701">
@@ -25381,11 +25381,11 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>青少年-专家咨询</t>
+          <t>精神心理</t>
         </is>
       </c>
       <c r="E701" t="n">
-        <v>15000</v>
+        <v>11592</v>
       </c>
     </row>
     <row r="702">
@@ -25406,11 +25406,11 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>精神心理</t>
+          <t>儿童青少年</t>
         </is>
       </c>
       <c r="E702" t="n">
-        <v>11592</v>
+        <v>9792</v>
       </c>
     </row>
     <row r="703">
@@ -25431,11 +25431,11 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>儿童青少年</t>
+          <t>青少年-青英咨询</t>
         </is>
       </c>
       <c r="E703" t="n">
-        <v>9792</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="704">
@@ -25456,11 +25456,11 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>青少年-青英咨询</t>
+          <t>5次咨询（成人）</t>
         </is>
       </c>
       <c r="E704" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="705">
@@ -25481,11 +25481,11 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>5次咨询（成人）</t>
+          <t>青少年-资深咨询1次</t>
         </is>
       </c>
       <c r="E705" t="n">
-        <v>5000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="706">
@@ -25506,11 +25506,11 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>青少年-资深咨询1次</t>
+          <t>首单优惠咨询</t>
         </is>
       </c>
       <c r="E706" t="n">
-        <v>1200</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="707">
@@ -25526,16 +25526,16 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>首单优惠咨询</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="E707" t="n">
-        <v>1194</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="708">
@@ -25556,11 +25556,11 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>6600</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="709">
@@ -25576,16 +25576,16 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
         </is>
       </c>
       <c r="E709" t="n">
-        <v>5040</v>
+        <v>76</v>
       </c>
     </row>
     <row r="710">
@@ -25601,16 +25601,16 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>处方</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E710" t="n">
-        <v>124.8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="711">
@@ -25631,11 +25631,11 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
+          <t>yl（网课、家长学）青少年家庭同行者计划一周短训营</t>
         </is>
       </c>
       <c r="E711" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
     </row>
     <row r="712">
@@ -25656,11 +25656,11 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>yl（网课、家长学）青少年家庭同行者计划一周短训营</t>
+          <t>（网课、家长学）青少年家庭同行者计划一周短训营LH</t>
         </is>
       </c>
       <c r="E712" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="713">
@@ -25681,11 +25681,11 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>青少年同行者计划：试听课</t>
         </is>
       </c>
       <c r="E713" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="714">
@@ -25706,11 +25706,11 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>1号课：睡前静心基础营-心理学网课+陪伴能量提升</t>
+          <t>惠民保专属心理权益-cxjk</t>
         </is>
       </c>
       <c r="E714" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="715">
@@ -25731,11 +25731,11 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>（网课、家长学）青少年家庭同行者计划一周短训营LH</t>
+          <t>惠民保-熠保科技-总部</t>
         </is>
       </c>
       <c r="E715" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="716">
@@ -25756,11 +25756,11 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>青少年同行者计划：试听课</t>
+          <t>青少年同行者智慧父母启航营</t>
         </is>
       </c>
       <c r="E716" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="717">
@@ -25781,7 +25781,7 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>惠民保专属心理权益-cxjk</t>
+          <t>观心少年2天1夜心理赋能营-ys-北京</t>
         </is>
       </c>
       <c r="E717" t="n">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>惠民保-熠保科技-总部</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E718" t="n">
@@ -25831,7 +25831,7 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>青少年同行者智慧父母启航营</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E719" t="n">
@@ -25846,21 +25846,21 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>儿童青少年</t>
         </is>
       </c>
       <c r="E720" t="n">
-        <v>0</v>
+        <v>131768</v>
       </c>
     </row>
     <row r="721">
@@ -25871,21 +25871,21 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>青少年-甄选咨询</t>
         </is>
       </c>
       <c r="E721" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="722">
@@ -25896,21 +25896,21 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>青少年-青英咨询</t>
         </is>
       </c>
       <c r="E722" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="723">
@@ -25931,11 +25931,11 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>儿童青少年</t>
+          <t>精神心理</t>
         </is>
       </c>
       <c r="E723" t="n">
-        <v>131768</v>
+        <v>5796</v>
       </c>
     </row>
     <row r="724">
@@ -25956,11 +25956,11 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>青少年-甄选咨询</t>
+          <t>电商咨询</t>
         </is>
       </c>
       <c r="E724" t="n">
-        <v>24000</v>
+        <v>398</v>
       </c>
     </row>
     <row r="725">
@@ -25981,11 +25981,11 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>青少年-青英咨询</t>
+          <t>（赠）1v1咨询 1次</t>
         </is>
       </c>
       <c r="E725" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="726">
@@ -26001,16 +26001,16 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>精神心理</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="E726" t="n">
-        <v>5796</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="727">
@@ -26026,16 +26026,16 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>电商咨询</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="E727" t="n">
-        <v>398</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="728">
@@ -26051,12 +26051,12 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>（赠）1v1咨询 1次</t>
+          <t>肠道菌群检测</t>
         </is>
       </c>
       <c r="E728" t="n">
@@ -26076,16 +26076,16 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>韩冰老师一百天疗愈计划</t>
         </is>
       </c>
       <c r="E729" t="n">
-        <v>6600</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="730">
@@ -26101,16 +26101,16 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
         </is>
       </c>
       <c r="E730" t="n">
-        <v>24800</v>
+        <v>38</v>
       </c>
     </row>
     <row r="731">
@@ -26126,16 +26126,16 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>肠道菌群检测</t>
+          <t>qy（网课、家长学）青少年家庭同行者计划一周短训营</t>
         </is>
       </c>
       <c r="E731" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="732">
@@ -26156,11 +26156,11 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>韩冰老师一百天疗愈计划</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E732" t="n">
-        <v>60000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="733">
@@ -26181,11 +26181,11 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E733" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="734">
@@ -26206,11 +26206,11 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>qy（网课、家长学）青少年家庭同行者计划一周短训营</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E734" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="735">
@@ -26231,11 +26231,11 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E735" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="736">
@@ -26256,7 +26256,7 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>义诊-线上</t>
         </is>
       </c>
       <c r="E736" t="n">
@@ -26281,7 +26281,7 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>观心少年2天1夜心理赋能营-ys-北京</t>
         </is>
       </c>
       <c r="E737" t="n">
@@ -26296,21 +26296,21 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="E738" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="739">
@@ -26321,17 +26321,17 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>义诊-线上</t>
+          <t>1元家庭守护计划ys</t>
         </is>
       </c>
       <c r="E739" t="n">
@@ -26346,7 +26346,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -26356,11 +26356,11 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E740" t="n">
-        <v>0</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="741">
@@ -26376,16 +26376,16 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E741" t="n">
-        <v>1680</v>
+        <v>13860</v>
       </c>
     </row>
     <row r="742">
@@ -26401,16 +26401,16 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>1元家庭守护计划ys</t>
+          <t>青少年同行者计划之领航营亲子教育网课</t>
         </is>
       </c>
       <c r="E742" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="743">
@@ -26431,11 +26431,11 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>心理咨询师职业能力水平评价考试培训</t>
         </is>
       </c>
       <c r="E743" t="n">
-        <v>17820</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="744">
@@ -26456,11 +26456,11 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>青少年同行者计划之领航营亲子教育网课</t>
+          <t>【青春进化论】亲子成长2日营补差链接</t>
         </is>
       </c>
       <c r="E744" t="n">
-        <v>4980</v>
+        <v>280</v>
       </c>
     </row>
     <row r="745">
@@ -26481,11 +26481,11 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>心理咨询师职业能力水平评价考试培训</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E745" t="n">
-        <v>3800</v>
+        <v>19</v>
       </c>
     </row>
     <row r="746">
@@ -26506,11 +26506,11 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营补差链接</t>
+          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
         </is>
       </c>
       <c r="E746" t="n">
-        <v>730</v>
+        <v>19</v>
       </c>
     </row>
     <row r="747">
@@ -26531,7 +26531,7 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>青少年同行者计划周训营（网课）WY</t>
         </is>
       </c>
       <c r="E747" t="n">
@@ -26556,11 +26556,11 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
+          <t>青少年【未来之翼】身心节律复能7日营</t>
         </is>
       </c>
       <c r="E748" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="749">
@@ -26581,11 +26581,11 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>青少年同行者计划周训营（网课）WY</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E749" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="750">
@@ -26606,11 +26606,11 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>（网课、家长学）青少年家庭同行者计划一周短训营LH</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E750" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="751">
@@ -26631,160 +26631,10 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>杭州一日一生体验课</t>
+          <t>未来之翼7日身心复能营</t>
         </is>
       </c>
       <c r="E751" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
-        <is>
-          <t>线下</t>
-        </is>
-      </c>
-      <c r="B752" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="C752" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D752" t="inlineStr">
-        <is>
-          <t>未来之翼7日身心复能营</t>
-        </is>
-      </c>
-      <c r="E752" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
-        <is>
-          <t>线下</t>
-        </is>
-      </c>
-      <c r="B753" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="C753" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D753" t="inlineStr">
-        <is>
-          <t>0元青少年--LH</t>
-        </is>
-      </c>
-      <c r="E753" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
-          <t>线下</t>
-        </is>
-      </c>
-      <c r="B754" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="C754" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D754" t="inlineStr">
-        <is>
-          <t>观心少年-腾讯-lmt</t>
-        </is>
-      </c>
-      <c r="E754" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>线下</t>
-        </is>
-      </c>
-      <c r="B755" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="C755" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D755" t="inlineStr">
-        <is>
-          <t>青少年【未来之翼】身心节律复能7日营</t>
-        </is>
-      </c>
-      <c r="E755" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
-        <is>
-          <t>线下</t>
-        </is>
-      </c>
-      <c r="B756" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="C756" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D756" t="inlineStr">
-        <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
-        </is>
-      </c>
-      <c r="E756" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
-        <is>
-          <t>线下</t>
-        </is>
-      </c>
-      <c r="B757" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="C757" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D757" t="inlineStr">
-        <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
-        </is>
-      </c>
-      <c r="E757" t="n">
         <v>0</v>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -2421,11 +2421,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>司法虚拟</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>84660</v>
+        <v>134460</v>
       </c>
     </row>
     <row r="8">
@@ -2444,11 +2444,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>62180</v>
+        <v>93340</v>
       </c>
     </row>
     <row r="9">
@@ -2467,11 +2467,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>59461</v>
+        <v>84062</v>
       </c>
     </row>
     <row r="10">
@@ -2490,11 +2490,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>严闽龙虚拟</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>54780</v>
+        <v>75910</v>
       </c>
     </row>
     <row r="11">
@@ -2513,11 +2513,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>刘俊彤虚拟</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>54481</v>
+        <v>62180</v>
       </c>
     </row>
     <row r="12">
@@ -3226,11 +3226,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>司法虚拟</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>84660</v>
+        <v>134460</v>
       </c>
     </row>
     <row r="43">
@@ -3249,11 +3249,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>62180</v>
+        <v>93340</v>
       </c>
     </row>
     <row r="44">
@@ -3272,11 +3272,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>59461</v>
+        <v>84062</v>
       </c>
     </row>
     <row r="45">
@@ -3295,11 +3295,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>严闽龙虚拟</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>54780</v>
+        <v>75910</v>
       </c>
     </row>
     <row r="46">
@@ -3318,11 +3318,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>刘俊彤虚拟</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>54481</v>
+        <v>62180</v>
       </c>
     </row>
     <row r="47">

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,7 +814,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -823,27 +823,27 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2563515.54</v>
+        <v>195865</v>
       </c>
       <c r="E14" t="n">
-        <v>3313</v>
+        <v>135</v>
       </c>
       <c r="F14" t="n">
-        <v>643574.36</v>
+        <v>90390</v>
       </c>
       <c r="G14" t="n">
-        <v>1919941.18</v>
+        <v>105475</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -852,16 +852,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>181525.57</v>
+        <v>2367650.54</v>
       </c>
       <c r="E15" t="n">
-        <v>5893</v>
+        <v>3178</v>
       </c>
       <c r="F15" t="n">
-        <v>181525.57</v>
+        <v>553184.36</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1814466.18</v>
       </c>
     </row>
     <row r="16">
@@ -872,7 +872,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1142004</v>
+        <v>181525.57</v>
       </c>
       <c r="E16" t="n">
-        <v>234</v>
+        <v>5893</v>
       </c>
       <c r="F16" t="n">
-        <v>1142004</v>
+        <v>181525.57</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -901,7 +901,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>355326</v>
+        <v>1142004</v>
       </c>
       <c r="E17" t="n">
-        <v>88</v>
+        <v>234</v>
       </c>
       <c r="F17" t="n">
-        <v>355326</v>
+        <v>1142004</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -935,17 +935,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>新客</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>345326</v>
+        <v>355326</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F18" t="n">
-        <v>345326</v>
+        <v>355326</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -964,17 +964,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>老客</t>
+          <t>新客</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10000</v>
+        <v>345326</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="F19" t="n">
-        <v>10000</v>
+        <v>345326</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -988,22 +988,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>老客</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1497534</v>
+        <v>10000</v>
       </c>
       <c r="E20" t="n">
-        <v>270</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>1497534</v>
+        <v>10000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>少年说</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1116610</v>
+        <v>1497534</v>
       </c>
       <c r="E21" t="n">
-        <v>97</v>
+        <v>270</v>
       </c>
       <c r="F21" t="n">
-        <v>1116610</v>
+        <v>1497534</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>家守</t>
+          <t>少年说</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>380924</v>
+        <v>1116610</v>
       </c>
       <c r="E22" t="n">
-        <v>173</v>
+        <v>97</v>
       </c>
       <c r="F22" t="n">
-        <v>380924</v>
+        <v>1116610</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1075,22 +1075,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>家守</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>99200</v>
+        <v>380924</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="F23" t="n">
-        <v>99200</v>
+        <v>380924</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1113,13 +1113,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>49696.78</v>
+        <v>99200</v>
       </c>
       <c r="E24" t="n">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>49696.78</v>
+        <v>99200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1138,17 +1138,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>初诊</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>37785.67</v>
+        <v>49696.78</v>
       </c>
       <c r="E25" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F25" t="n">
-        <v>37785.67</v>
+        <v>49696.78</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>复诊</t>
+          <t>初诊</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11911.11</v>
+        <v>37785.67</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="F26" t="n">
-        <v>11911.11</v>
+        <v>37785.67</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1191,22 +1191,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>复诊</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>643574.36</v>
+        <v>11911.11</v>
       </c>
       <c r="E27" t="n">
-        <v>373</v>
+        <v>21</v>
       </c>
       <c r="F27" t="n">
-        <v>643574.36</v>
+        <v>11911.11</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1215,12 +1215,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1229,45 +1229,45 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2386608.01</v>
+        <v>90390</v>
       </c>
       <c r="E28" t="n">
-        <v>582</v>
+        <v>58</v>
       </c>
       <c r="F28" t="n">
+        <v>90390</v>
+      </c>
+      <c r="G28" t="n">
         <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2386608.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>老客</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1910462.01</v>
+        <v>553184.36</v>
       </c>
       <c r="E29" t="n">
-        <v>392</v>
+        <v>315</v>
       </c>
       <c r="F29" t="n">
+        <v>553184.36</v>
+      </c>
+      <c r="G29" t="n">
         <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1910462.01</v>
       </c>
     </row>
     <row r="30">
@@ -1283,20 +1283,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>新客</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>418748</v>
+        <v>2386608.01</v>
       </c>
       <c r="E30" t="n">
-        <v>183</v>
+        <v>582</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>418748</v>
+        <v>2386608.01</v>
       </c>
     </row>
     <row r="31">
@@ -1307,25 +1307,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>老客</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>571481</v>
+        <v>1910462.01</v>
       </c>
       <c r="E31" t="n">
-        <v>74</v>
+        <v>392</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>571481</v>
+        <v>1910462.01</v>
       </c>
     </row>
     <row r="32">
@@ -1336,25 +1336,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>少年说</t>
+          <t>新客</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>330240</v>
+        <v>418748</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>330240</v>
+        <v>418748</v>
       </c>
     </row>
     <row r="33">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>家守</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>241241</v>
+        <v>571481</v>
       </c>
       <c r="E33" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>241241</v>
+        <v>571481</v>
       </c>
     </row>
     <row r="34">
@@ -1394,25 +1394,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>少年说</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>150800</v>
+        <v>330240</v>
       </c>
       <c r="E34" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>150800</v>
+        <v>330240</v>
       </c>
     </row>
     <row r="35">
@@ -1423,25 +1423,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>家守</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1279518.2</v>
+        <v>241241</v>
       </c>
       <c r="E35" t="n">
-        <v>2105</v>
+        <v>32</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1279518.2</v>
+        <v>241241</v>
       </c>
     </row>
     <row r="36">
@@ -1452,25 +1452,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>复诊</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>824010.16</v>
+        <v>150800</v>
       </c>
       <c r="E36" t="n">
-        <v>916</v>
+        <v>21</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>824010.16</v>
+        <v>150800</v>
       </c>
     </row>
     <row r="37">
@@ -1486,20 +1486,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>初诊</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>455508.04</v>
+        <v>1279518.2</v>
       </c>
       <c r="E37" t="n">
-        <v>1189</v>
+        <v>2105</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>455508.04</v>
+        <v>1279518.2</v>
       </c>
     </row>
     <row r="38">
@@ -1510,25 +1510,112 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>复诊</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1919941.18</v>
+        <v>824010.16</v>
       </c>
       <c r="E38" t="n">
-        <v>2940</v>
+        <v>916</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1919941.18</v>
+        <v>824010.16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>初诊</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>455508.04</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1189</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>455508.04</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>105475</v>
+      </c>
+      <c r="E40" t="n">
+        <v>77</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>105475</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1814466.18</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2863</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1814466.18</v>
       </c>
     </row>
   </sheetData>
@@ -1629,7 +1716,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>咨询 139650.0；家守/千金方/少年说 21480.0；医疗 17469.0；其他 4674.0</t>
+          <t>咨询 139650.0；家守/千金方/少年说 21480.0；医疗 17469.0；其他 2694.0；进化论 1980.0</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1772,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>咨询 483720.0；家守/千金方/少年说 246780.0；其他 103694.0；医疗 78122.14；菌群 54600.0</t>
+          <t>咨询 483720.0；家守/千金方/少年说 246780.0；其他 99734.0；医疗 78122.14；菌群 54600.0；进化论 3960.0</t>
         </is>
       </c>
     </row>
@@ -1765,11 +1852,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>87.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>其他 1282342.0；咨询 146542.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
+          <t>其他 1210627.0；咨询 146542.0；进化论 71715.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -1821,11 +1908,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>61.2</v>
+        <v>57.1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>其他 418892.5；咨询 141738.01；家守/千金方/少年说 109800.0；医疗 14327.36</t>
+          <t>其他 391072.5；咨询 141738.01；家守/千金方/少年说 109800.0；进化论 27820.0；医疗 14327.36</t>
         </is>
       </c>
     </row>
@@ -1965,7 +2052,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>咨询 139650.0；家守/千金方/少年说 21480.0；医疗 17469.0；其他 4674.0</t>
+          <t>咨询 139650.0；家守/千金方/少年说 21480.0；医疗 17469.0；其他 2694.0；进化论 1980.0</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2108,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>咨询 483720.0；家守/千金方/少年说 246780.0；其他 103694.0；医疗 78122.14；菌群 54600.0</t>
+          <t>咨询 483720.0；家守/千金方/少年说 246780.0；其他 99734.0；医疗 78122.14；菌群 54600.0；进化论 3960.0</t>
         </is>
       </c>
     </row>
@@ -2101,11 +2188,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>87.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>其他 1282342.0；咨询 146542.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
+          <t>其他 1210627.0；咨询 146542.0；进化论 71715.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -2157,11 +2244,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>61.2</v>
+        <v>57.1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>其他 418892.5；咨询 141738.01；家守/千金方/少年说 109800.0；医疗 14327.36</t>
+          <t>其他 391072.5；咨询 141738.01；家守/千金方/少年说 109800.0；进化论 27820.0；医疗 14327.36</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2988,7 +3075,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2996,11 +3083,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>胡炫明</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>398820</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="33">
@@ -3011,7 +3098,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3019,11 +3106,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>陈鑫</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>292350</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="34">
@@ -3034,7 +3121,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3042,11 +3129,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>徐艳霞</t>
+          <t>高丹</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>277500</v>
+        <v>16520</v>
       </c>
     </row>
     <row r="35">
@@ -3057,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3065,11 +3152,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>梁志前</t>
+          <t>余文静</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220060</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="36">
@@ -3080,7 +3167,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3088,22 +3175,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>陈磊</t>
+          <t>徐艳霞</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>171510</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3111,22 +3198,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>胡炫明</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1280</v>
+        <v>391000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3134,22 +3221,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>徐艳霞</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1280</v>
+        <v>267600</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3157,22 +3244,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1280</v>
+        <v>267600</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3180,22 +3267,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>梁志前</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1280</v>
+        <v>217900</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3203,11 +3290,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>陈磊</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1280</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="42">
@@ -3218,7 +3305,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3226,11 +3313,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>169320</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="43">
@@ -3241,7 +3328,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3249,11 +3336,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103300</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="44">
@@ -3264,7 +3351,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3272,11 +3359,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>89042</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="45">
@@ -3287,7 +3374,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3295,11 +3382,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>79381</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="46">
@@ -3310,7 +3397,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3318,11 +3405,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>75910</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="47">
@@ -3333,7 +3420,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3341,11 +3428,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53194</v>
+        <v>169320</v>
       </c>
     </row>
     <row r="48">
@@ -3356,7 +3443,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3364,11 +3451,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>刘士明</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>30796</v>
+        <v>103300</v>
       </c>
     </row>
     <row r="49">
@@ -3379,7 +3466,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3387,11 +3474,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>30398</v>
+        <v>89042</v>
       </c>
     </row>
     <row r="50">
@@ -3402,7 +3489,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3410,11 +3497,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>24598</v>
+        <v>79381</v>
       </c>
     </row>
     <row r="51">
@@ -3425,7 +3512,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3433,11 +3520,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>20000</v>
+        <v>75910</v>
       </c>
     </row>
     <row r="52">
@@ -3448,7 +3535,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3456,11 +3543,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>165000</v>
+        <v>53194</v>
       </c>
     </row>
     <row r="53">
@@ -3471,7 +3558,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3479,11 +3566,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>132000</v>
+        <v>30796</v>
       </c>
     </row>
     <row r="54">
@@ -3494,7 +3581,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3502,11 +3589,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>109640</v>
+        <v>30398</v>
       </c>
     </row>
     <row r="55">
@@ -3517,7 +3604,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3525,11 +3612,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>109020</v>
+        <v>24598</v>
       </c>
     </row>
     <row r="56">
@@ -3540,7 +3627,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3548,11 +3635,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>张天昂</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103200</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="57">
@@ -3563,7 +3650,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3571,11 +3658,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>49600</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="58">
@@ -3586,7 +3673,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3594,11 +3681,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>24800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="59">
@@ -3609,7 +3696,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3617,11 +3704,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>24800</v>
+        <v>109640</v>
       </c>
     </row>
     <row r="60">
@@ -3632,7 +3719,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -3640,11 +3727,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>109020</v>
       </c>
     </row>
     <row r="61">
@@ -3655,7 +3742,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3663,11 +3750,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>103200</v>
       </c>
     </row>
     <row r="62">
@@ -3678,7 +3765,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3690,7 +3777,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>16800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="63">
@@ -3701,7 +3788,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -3709,11 +3796,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1200</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="64">
@@ -3724,7 +3811,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3736,7 +3823,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>500</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="65">
@@ -3747,7 +3834,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3755,11 +3842,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3770,7 +3857,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -3778,11 +3865,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3793,7 +3880,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -3801,11 +3888,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>陈鑫</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>292350</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="68">
@@ -3816,7 +3903,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -3824,11 +3911,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>吴云龙</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>57280</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="69">
@@ -3839,7 +3926,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -3847,11 +3934,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>姚闯</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>55740</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70">
@@ -3862,7 +3949,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -3870,11 +3957,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>杨旺忠</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>54040</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71">
@@ -3885,7 +3972,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -3893,22 +3980,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>40000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -3916,22 +4003,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>233168</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -3939,22 +4026,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>158786</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -3962,22 +4049,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>余文静</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>91194</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -3985,22 +4072,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>吴云龙</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>85698</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -4008,22 +4095,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>魏恺志</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>81982</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -4031,22 +4118,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>164220</v>
+        <v>267600</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -4054,22 +4141,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>黄慧作</t>
+          <t>姚闯</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>90000</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4077,22 +4164,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>杨旺忠</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>46200</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -4100,22 +4187,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>林非凡</t>
+          <t>吴云龙</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>26820</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -4123,11 +4210,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>26200</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="82">
@@ -4138,7 +4225,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -4150,7 +4237,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>54600</v>
+        <v>233168</v>
       </c>
     </row>
     <row r="83">
@@ -4161,7 +4248,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -4169,11 +4256,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>李颜君</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>45600</v>
+        <v>158786</v>
       </c>
     </row>
     <row r="84">
@@ -4184,7 +4271,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -4192,11 +4279,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>24800</v>
+        <v>91194</v>
       </c>
     </row>
     <row r="85">
@@ -4207,7 +4294,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -4215,11 +4302,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>24800</v>
+        <v>85698</v>
       </c>
     </row>
     <row r="86">
@@ -4230,7 +4317,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -4238,11 +4325,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>王秀丽</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1000</v>
+        <v>81982</v>
       </c>
     </row>
     <row r="87">
@@ -4253,7 +4340,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -4261,11 +4348,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>245315.88</v>
+        <v>164220</v>
       </c>
     </row>
     <row r="88">
@@ -4276,7 +4363,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -4284,11 +4371,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>黄慧作</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>196025.61</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="89">
@@ -4299,7 +4386,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -4307,11 +4394,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>190639.29</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="90">
@@ -4322,7 +4409,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -4330,11 +4417,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>157856.3</v>
+        <v>26820</v>
       </c>
     </row>
     <row r="91">
@@ -4345,7 +4432,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -4353,11 +4440,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>105286</v>
+        <v>26200</v>
       </c>
     </row>
     <row r="92">
@@ -4368,7 +4455,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -4376,11 +4463,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>胡炫明</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>398820</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="93">
@@ -4391,7 +4478,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -4399,11 +4486,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>徐艳霞</t>
+          <t>李颜君</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>277500</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="94">
@@ -4414,7 +4501,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -4422,11 +4509,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>梁志前</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220060</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="95">
@@ -4437,7 +4524,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -4445,11 +4532,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>陈磊</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>171510</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="96">
@@ -4460,7 +4547,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -4468,11 +4555,356 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>王秀丽</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>王倩雅</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>245315.88</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>李怡慧</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>196025.61</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>李菲菲</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>190639.29</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>李浩然</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>157856.3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>5</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>韦微</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>105286</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>高丹</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>16520</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>徐艳霞</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>郭海明</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>8560</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>4</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>章浩进</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>韦新妮</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>7920</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>胡炫明</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>391000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>徐艳霞</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>267600</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>梁志前</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>217900</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>4</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>陈磊</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>168000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>5</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
           <t>胡威特</t>
         </is>
       </c>
-      <c r="E96" t="n">
-        <v>105540</v>
+      <c r="E111" t="n">
+        <v>99600</v>
       </c>
     </row>
   </sheetData>
@@ -4486,7 +4918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4754,65 +5186,65 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2563515.54</v>
+        <v>195865</v>
       </c>
       <c r="D8" t="n">
-        <v>670158.59</v>
+        <v>57250</v>
       </c>
       <c r="E8" t="n">
-        <v>31112</v>
+        <v>4060</v>
       </c>
       <c r="F8" t="n">
-        <v>1.21</v>
+        <v>2.07</v>
       </c>
       <c r="G8" t="n">
-        <v>639046.59</v>
+        <v>53190</v>
       </c>
       <c r="H8" t="n">
-        <v>24.93</v>
+        <v>27.16</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；青少年营地动力唤醒方案 85000.0；青少年成长基地3月营（金盏基地） 83600.0</t>
+          <t>【青春进化论】亲子成长2日营 53010.0；青春进化论（两日制亲子营） 3960.0；【青春进化论】亲子成长2日营补差链接 280.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>181525.57</v>
+        <v>2367650.54</v>
       </c>
       <c r="D9" t="n">
-        <v>22555</v>
+        <v>612908.59</v>
       </c>
       <c r="E9" t="n">
-        <v>18920</v>
+        <v>27052</v>
       </c>
       <c r="F9" t="n">
-        <v>10.42</v>
+        <v>1.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3635</v>
+        <v>585856.59</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>24.74</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 3588.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 2560.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 1688.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；青少年营地动力唤醒方案 85000.0；青少年成长基地3月营（金盏基地） 83600.0</t>
         </is>
       </c>
     </row>
@@ -4824,30 +5256,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1142004</v>
+        <v>181525.57</v>
       </c>
       <c r="D10" t="n">
-        <v>193920.44</v>
+        <v>22555</v>
       </c>
       <c r="E10" t="n">
-        <v>4980</v>
+        <v>18920</v>
       </c>
       <c r="F10" t="n">
-        <v>0.44</v>
+        <v>10.42</v>
       </c>
       <c r="G10" t="n">
-        <v>188940.44</v>
+        <v>3635</v>
       </c>
       <c r="H10" t="n">
-        <v>16.54</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>青少年同行者计划领航营 118165.4；青少年同行者计划-护航营 21578.0；青少年同行者计划向阳营 14593.37</t>
+          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 3588.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 2560.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 1688.0</t>
         </is>
       </c>
     </row>
@@ -4859,30 +5291,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>355326</v>
+        <v>1142004</v>
       </c>
       <c r="D11" t="n">
-        <v>143025.9</v>
+        <v>193920.44</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="G11" t="n">
-        <v>143025.9</v>
+        <v>188940.44</v>
       </c>
       <c r="H11" t="n">
-        <v>40.25</v>
+        <v>16.54</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>儿童青少年 63298.0；精神心理 61198.0；青少年-资深咨询 18500.0</t>
+          <t>青少年同行者计划领航营 118165.4；青少年同行者计划-护航营 21578.0；青少年同行者计划向阳营 14593.37</t>
         </is>
       </c>
     </row>
@@ -4894,30 +5326,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1497534</v>
+        <v>355326</v>
       </c>
       <c r="D12" t="n">
-        <v>145410</v>
+        <v>143025.9</v>
       </c>
       <c r="E12" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>143730</v>
+        <v>143025.9</v>
       </c>
       <c r="H12" t="n">
-        <v>9.6</v>
+        <v>40.25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（二阶） 58620.0；少年说陪伴计划 52800.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
+          <t>儿童青少年 63298.0；精神心理 61198.0；青少年-资深咨询 18500.0</t>
         </is>
       </c>
     </row>
@@ -4929,30 +5361,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>99200</v>
+        <v>1497534</v>
       </c>
       <c r="D13" t="n">
-        <v>121000</v>
+        <v>145410</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G13" t="n">
-        <v>121000</v>
+        <v>143730</v>
       </c>
       <c r="H13" t="n">
-        <v>121.98</v>
+        <v>9.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>肠道菌群移植 74400.0；肠道菌群移植（双疗程） 45600.0；肠道菌群检测 1000.0</t>
+          <t>家庭守护计划2.0（二阶） 58620.0；少年说陪伴计划 52800.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
         </is>
       </c>
     </row>
@@ -4964,14 +5396,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>49696.78</v>
+        <v>99200</v>
       </c>
       <c r="D14" t="n">
-        <v>778</v>
+        <v>121000</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -4980,14 +5412,14 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>778</v>
+        <v>121000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.57</v>
+        <v>121.98</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20分钟问诊（专家医师） -线上 500.0；20分钟问诊（医师） -线上 200.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
+          <t>肠道菌群移植 74400.0；肠道菌群移植（双疗程） 45600.0；肠道菌群检测 1000.0</t>
         </is>
       </c>
     </row>
@@ -4999,100 +5431,100 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>643574.36</v>
+        <v>49696.78</v>
       </c>
       <c r="D15" t="n">
-        <v>290090.59</v>
+        <v>778</v>
       </c>
       <c r="E15" t="n">
-        <v>3079</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>287011.59</v>
+        <v>778</v>
       </c>
       <c r="H15" t="n">
-        <v>44.6</v>
+        <v>1.57</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；蛋壳跳动身心复能营21天（一阶） 74200.0；青少年成长基地3月营（金盏基地） 46800.0</t>
+          <t>20分钟问诊（专家医师） -线上 500.0；20分钟问诊（医师） -线上 200.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2386608.01</v>
+        <v>90390</v>
       </c>
       <c r="D16" t="n">
-        <v>409927.33</v>
+        <v>15940</v>
       </c>
       <c r="E16" t="n">
-        <v>10398</v>
+        <v>2080</v>
       </c>
       <c r="F16" t="n">
-        <v>0.44</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>399529.33</v>
+        <v>13860</v>
       </c>
       <c r="H16" t="n">
-        <v>16.74</v>
+        <v>15.33</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>儿童青少年 286931.33；电商咨询 37500.0；精神心理 32798.0</t>
+          <t>【青春进化论】亲子成长2日营 13860.0；青春进化论（两日制亲子营） 1980.0；【青春进化论】亲子成长2日营补差链接 100.0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>571481</v>
+        <v>553184.36</v>
       </c>
       <c r="D17" t="n">
-        <v>68520</v>
+        <v>274150.59</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="G17" t="n">
-        <v>68520</v>
+        <v>273151.59</v>
       </c>
       <c r="H17" t="n">
-        <v>11.99</v>
+        <v>49.38</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（三阶） 26310.0；家庭守护计划2.0（一阶） 23970.0；少年说陪伴计划 13200.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；蛋壳跳动身心复能营21天（一阶） 74200.0；青少年成长基地3月营（金盏基地） 46800.0</t>
         </is>
       </c>
     </row>
@@ -5104,30 +5536,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>150800</v>
+        <v>2386608.01</v>
       </c>
       <c r="D18" t="n">
-        <v>115000</v>
+        <v>409927.33</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="G18" t="n">
-        <v>115000</v>
+        <v>399529.33</v>
       </c>
       <c r="H18" t="n">
-        <v>76.26000000000001</v>
+        <v>16.74</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>肠道菌群移植 47600.0；肠道菌群移植（双疗程） 45600.0；肠道菌群移植（双疗程优惠） 20800.0</t>
+          <t>儿童青少年 286931.33；电商咨询 37500.0；精神心理 32798.0</t>
         </is>
       </c>
     </row>
@@ -5139,30 +5571,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1279518.2</v>
+        <v>571481</v>
       </c>
       <c r="D19" t="n">
-        <v>5541.59</v>
+        <v>68520</v>
       </c>
       <c r="E19" t="n">
-        <v>1941.59</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3600</v>
+        <v>68520</v>
       </c>
       <c r="H19" t="n">
-        <v>0.28</v>
+        <v>11.99</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>线上/线下门诊 3200.0；【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59；20分钟问诊（医师） -线上 600.0</t>
+          <t>家庭守护计划2.0（三阶） 26310.0；家庭守护计划2.0（一阶） 23970.0；少年说陪伴计划 13200.0</t>
         </is>
       </c>
     </row>
@@ -5174,28 +5606,133 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>150800</v>
+      </c>
+      <c r="D20" t="n">
+        <v>115000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>肠道菌群移植 47600.0；肠道菌群移植（双疗程） 45600.0；肠道菌群移植（双疗程优惠） 20800.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1279518.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5541.59</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1941.59</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3600</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>线上/线下门诊 3200.0；【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59；20分钟问诊（医师） -线上 600.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>105475</v>
+      </c>
+      <c r="D22" t="n">
+        <v>41310</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G22" t="n">
+        <v>39330</v>
+      </c>
+      <c r="H22" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>【青春进化论】亲子成长2日营 39150.0；青春进化论（两日制亲子营） 1980.0；【青春进化论】亲子成长2日营补差链接 180.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>1919941.18</v>
-      </c>
-      <c r="D20" t="n">
-        <v>380068</v>
-      </c>
-      <c r="E20" t="n">
-        <v>28033</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="G20" t="n">
-        <v>352035</v>
-      </c>
-      <c r="H20" t="n">
-        <v>18.34</v>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="C23" t="n">
+        <v>1814466.18</v>
+      </c>
+      <c r="D23" t="n">
+        <v>338758</v>
+      </c>
+      <c r="E23" t="n">
+        <v>26053</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G23" t="n">
+        <v>312705</v>
+      </c>
+      <c r="H23" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>青少年营地动力唤醒方案 85000.0；青少年营地家族赋能方案 80000.0；青少年身心复能成长方案 80000.0</t>
         </is>
@@ -5212,7 +5749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5416,17 +5953,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78189</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>783326.16</v>
       </c>
       <c r="F8" t="n">
-        <v>9.9817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5437,22 +5974,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>37895</v>
+        <v>78189</v>
       </c>
       <c r="E9" t="n">
-        <v>325870.41</v>
+        <v>783326.16</v>
       </c>
       <c r="F9" t="n">
-        <v>11.6289</v>
+        <v>9.9817</v>
       </c>
     </row>
     <row r="10">
@@ -5468,17 +6005,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>216560</v>
+        <v>37895</v>
       </c>
       <c r="E10" t="n">
         <v>325870.41</v>
       </c>
       <c r="F10" t="n">
-        <v>66.4559</v>
+        <v>11.6289</v>
       </c>
     </row>
     <row r="11">
@@ -5494,17 +6031,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11394</v>
+        <v>216560</v>
       </c>
       <c r="E11" t="n">
         <v>325870.41</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4965</v>
+        <v>66.4559</v>
       </c>
     </row>
     <row r="12">
@@ -5520,17 +6057,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49531</v>
+        <v>11394</v>
       </c>
       <c r="E12" t="n">
         <v>325870.41</v>
       </c>
       <c r="F12" t="n">
-        <v>15.1996</v>
+        <v>3.4965</v>
       </c>
     </row>
     <row r="13">
@@ -5546,17 +6083,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>49531</v>
       </c>
       <c r="E13" t="n">
         <v>325870.41</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>15.1996</v>
       </c>
     </row>
     <row r="14">
@@ -5572,17 +6109,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10290.41</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>325870.41</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5598,17 +6135,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>200</v>
+        <v>10290.41</v>
       </c>
       <c r="E15" t="n">
         <v>325870.41</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0614</v>
+        <v>3.1578</v>
       </c>
     </row>
     <row r="16">
@@ -5619,22 +6156,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>67050</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>824725.78</v>
+        <v>325870.41</v>
       </c>
       <c r="F16" t="n">
-        <v>8.130000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5645,22 +6182,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>466672</v>
+        <v>200</v>
       </c>
       <c r="E17" t="n">
-        <v>824725.78</v>
+        <v>325870.41</v>
       </c>
       <c r="F17" t="n">
-        <v>56.5851</v>
+        <v>0.0614</v>
       </c>
     </row>
     <row r="18">
@@ -5676,17 +6213,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>116578</v>
+        <v>67050</v>
       </c>
       <c r="E18" t="n">
         <v>824725.78</v>
       </c>
       <c r="F18" t="n">
-        <v>14.1354</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -5702,17 +6239,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>163500</v>
+        <v>466672</v>
       </c>
       <c r="E19" t="n">
         <v>824725.78</v>
       </c>
       <c r="F19" t="n">
-        <v>19.8248</v>
+        <v>56.5851</v>
       </c>
     </row>
     <row r="20">
@@ -5728,17 +6265,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>116578</v>
       </c>
       <c r="E20" t="n">
         <v>824725.78</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>14.1354</v>
       </c>
     </row>
     <row r="21">
@@ -5754,17 +6291,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1107.78</v>
+        <v>163500</v>
       </c>
       <c r="E21" t="n">
         <v>824725.78</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1343</v>
+        <v>19.8248</v>
       </c>
     </row>
     <row r="22">
@@ -5780,17 +6317,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9818</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>824725.78</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -5801,22 +6338,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6574</v>
+        <v>1107.78</v>
       </c>
       <c r="E23" t="n">
-        <v>1446274.36</v>
+        <v>824725.78</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4545</v>
+        <v>0.1343</v>
       </c>
     </row>
     <row r="24">
@@ -5827,22 +6364,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22410</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1446274.36</v>
+        <v>824725.78</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -5853,22 +6390,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>152588</v>
+        <v>9818</v>
       </c>
       <c r="E25" t="n">
-        <v>1446274.36</v>
+        <v>824725.78</v>
       </c>
       <c r="F25" t="n">
-        <v>10.5504</v>
+        <v>1.1905</v>
       </c>
     </row>
     <row r="26">
@@ -5884,17 +6421,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1077980</v>
+        <v>6574</v>
       </c>
       <c r="E26" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F26" t="n">
-        <v>74.535</v>
+        <v>0.4545</v>
       </c>
     </row>
     <row r="27">
@@ -5910,17 +6447,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>99200</v>
+        <v>22410</v>
       </c>
       <c r="E27" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F27" t="n">
-        <v>6.859</v>
+        <v>1.5495</v>
       </c>
     </row>
     <row r="28">
@@ -5936,17 +6473,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>19545</v>
+        <v>152588</v>
       </c>
       <c r="E28" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3514</v>
+        <v>10.5504</v>
       </c>
     </row>
     <row r="29">
@@ -5962,17 +6499,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>67977.36</v>
+        <v>1077980</v>
       </c>
       <c r="E29" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F29" t="n">
-        <v>4.7002</v>
+        <v>74.535</v>
       </c>
     </row>
     <row r="30">
@@ -5983,22 +6520,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>99200</v>
       </c>
       <c r="E30" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>6.859</v>
       </c>
     </row>
     <row r="31">
@@ -6009,22 +6546,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>19545</v>
       </c>
       <c r="E31" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.3514</v>
       </c>
     </row>
     <row r="32">
@@ -6035,22 +6572,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16194</v>
+        <v>25200</v>
       </c>
       <c r="E32" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F32" t="n">
-        <v>2.751</v>
+        <v>1.7424</v>
       </c>
     </row>
     <row r="33">
@@ -6061,22 +6598,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>85080</v>
+        <v>42777.36</v>
       </c>
       <c r="E33" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F33" t="n">
-        <v>14.4531</v>
+        <v>2.9578</v>
       </c>
     </row>
     <row r="34">
@@ -6092,7 +6629,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -6118,7 +6655,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -6144,17 +6681,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>487390</v>
+        <v>16194</v>
       </c>
       <c r="E36" t="n">
         <v>588664</v>
       </c>
       <c r="F36" t="n">
-        <v>82.79600000000001</v>
+        <v>2.751</v>
       </c>
     </row>
     <row r="37">
@@ -6165,22 +6702,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>181525.57</v>
+        <v>85080</v>
       </c>
       <c r="E37" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F37" t="n">
-        <v>4.5737</v>
+        <v>14.4531</v>
       </c>
     </row>
     <row r="38">
@@ -6191,22 +6728,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1142004</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F38" t="n">
-        <v>28.7741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -6217,22 +6754,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>355326</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F39" t="n">
-        <v>8.9528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -6243,22 +6780,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1497534</v>
+        <v>65190</v>
       </c>
       <c r="E40" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F40" t="n">
-        <v>37.7321</v>
+        <v>11.0742</v>
       </c>
     </row>
     <row r="41">
@@ -6269,22 +6806,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>99200</v>
+        <v>422200</v>
       </c>
       <c r="E41" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F41" t="n">
-        <v>2.4995</v>
+        <v>71.7217</v>
       </c>
     </row>
     <row r="42">
@@ -6300,17 +6837,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>49696.78</v>
+        <v>181525.57</v>
       </c>
       <c r="E42" t="n">
         <v>3968860.71</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2522</v>
+        <v>4.5737</v>
       </c>
     </row>
     <row r="43">
@@ -6326,28 +6863,28 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>643574.36</v>
+        <v>1142004</v>
       </c>
       <c r="E43" t="n">
         <v>3968860.71</v>
       </c>
       <c r="F43" t="n">
-        <v>16.2156</v>
+        <v>28.7741</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6356,24 +6893,24 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>61592</v>
+        <v>355326</v>
       </c>
       <c r="E44" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F44" t="n">
-        <v>5.1982</v>
+        <v>8.9528</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6382,24 +6919,24 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>8280</v>
+        <v>1497534</v>
       </c>
       <c r="E45" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6988</v>
+        <v>37.7321</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6408,24 +6945,24 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>99200</v>
       </c>
       <c r="E46" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>2.4995</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6434,65 +6971,65 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1112992</v>
+        <v>49696.78</v>
       </c>
       <c r="E47" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F47" t="n">
-        <v>93.9336</v>
+        <v>1.2522</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2007</v>
+        <v>90390</v>
       </c>
       <c r="E48" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1694</v>
+        <v>2.2775</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>139650</v>
+        <v>553184.36</v>
       </c>
       <c r="E49" t="n">
-        <v>183273</v>
+        <v>3968860.71</v>
       </c>
       <c r="F49" t="n">
-        <v>76.1978</v>
+        <v>13.9381</v>
       </c>
     </row>
     <row r="50">
@@ -6503,22 +7040,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>21480</v>
+        <v>61592</v>
       </c>
       <c r="E50" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F50" t="n">
-        <v>11.7202</v>
+        <v>5.1982</v>
       </c>
     </row>
     <row r="51">
@@ -6529,22 +7066,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>8280</v>
       </c>
       <c r="E51" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>0.6988</v>
       </c>
     </row>
     <row r="52">
@@ -6555,22 +7092,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>17469</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F52" t="n">
-        <v>9.531700000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -6581,22 +7118,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4674</v>
+        <v>1112992</v>
       </c>
       <c r="E53" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F53" t="n">
-        <v>2.5503</v>
+        <v>93.9336</v>
       </c>
     </row>
     <row r="54">
@@ -6607,22 +7144,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>119960</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>153032.84</v>
+        <v>1184871</v>
       </c>
       <c r="F54" t="n">
-        <v>78.3884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -6633,22 +7170,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13200</v>
+        <v>2007</v>
       </c>
       <c r="E55" t="n">
-        <v>153032.84</v>
+        <v>1184871</v>
       </c>
       <c r="F55" t="n">
-        <v>8.6256</v>
+        <v>0.1694</v>
       </c>
     </row>
     <row r="56">
@@ -6659,22 +7196,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>139650</v>
       </c>
       <c r="E56" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>76.1978</v>
       </c>
     </row>
     <row r="57">
@@ -6685,22 +7222,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>18256.84</v>
+        <v>21480</v>
       </c>
       <c r="E57" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F57" t="n">
-        <v>11.93</v>
+        <v>11.7202</v>
       </c>
     </row>
     <row r="58">
@@ -6711,22 +7248,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1616</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F58" t="n">
-        <v>1.056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -6737,22 +7274,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>483720</v>
+        <v>17469</v>
       </c>
       <c r="E59" t="n">
-        <v>966916.14</v>
+        <v>183273</v>
       </c>
       <c r="F59" t="n">
-        <v>50.0271</v>
+        <v>9.531700000000001</v>
       </c>
     </row>
     <row r="60">
@@ -6763,22 +7300,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>246780</v>
+        <v>1980</v>
       </c>
       <c r="E60" t="n">
-        <v>966916.14</v>
+        <v>183273</v>
       </c>
       <c r="F60" t="n">
-        <v>25.5224</v>
+        <v>1.0804</v>
       </c>
     </row>
     <row r="61">
@@ -6789,22 +7326,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>54600</v>
+        <v>2694</v>
       </c>
       <c r="E61" t="n">
-        <v>966916.14</v>
+        <v>183273</v>
       </c>
       <c r="F61" t="n">
-        <v>5.6468</v>
+        <v>1.4699</v>
       </c>
     </row>
     <row r="62">
@@ -6815,22 +7352,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>78122.14</v>
+        <v>119960</v>
       </c>
       <c r="E62" t="n">
-        <v>966916.14</v>
+        <v>153032.84</v>
       </c>
       <c r="F62" t="n">
-        <v>8.079499999999999</v>
+        <v>78.3884</v>
       </c>
     </row>
     <row r="63">
@@ -6841,22 +7378,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>103694</v>
+        <v>13200</v>
       </c>
       <c r="E63" t="n">
-        <v>966916.14</v>
+        <v>153032.84</v>
       </c>
       <c r="F63" t="n">
-        <v>10.7242</v>
+        <v>8.6256</v>
       </c>
     </row>
     <row r="64">
@@ -6867,22 +7404,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>421948</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F64" t="n">
-        <v>89.5044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -6893,22 +7430,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>26400</v>
+        <v>18256.84</v>
       </c>
       <c r="E65" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F65" t="n">
-        <v>5.6</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="66">
@@ -6919,19 +7456,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -6945,22 +7482,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>21080.65</v>
+        <v>1616</v>
       </c>
       <c r="E67" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F67" t="n">
-        <v>4.4717</v>
+        <v>1.056</v>
       </c>
     </row>
     <row r="68">
@@ -6971,22 +7508,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1998.68</v>
+        <v>483720</v>
       </c>
       <c r="E68" t="n">
-        <v>471427.33</v>
+        <v>966916.14</v>
       </c>
       <c r="F68" t="n">
-        <v>0.424</v>
+        <v>50.0271</v>
       </c>
     </row>
     <row r="69">
@@ -6997,22 +7534,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>280956</v>
+        <v>246780</v>
       </c>
       <c r="E69" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F69" t="n">
-        <v>68.01130000000001</v>
+        <v>25.5224</v>
       </c>
     </row>
     <row r="70">
@@ -7023,22 +7560,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>59200</v>
+        <v>54600</v>
       </c>
       <c r="E70" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F70" t="n">
-        <v>14.3306</v>
+        <v>5.6468</v>
       </c>
     </row>
     <row r="71">
@@ -7049,22 +7586,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>70400</v>
+        <v>78122.14</v>
       </c>
       <c r="E71" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F71" t="n">
-        <v>17.0418</v>
+        <v>8.079499999999999</v>
       </c>
     </row>
     <row r="72">
@@ -7075,22 +7612,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>200</v>
+        <v>3960</v>
       </c>
       <c r="E72" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0484</v>
+        <v>0.4095</v>
       </c>
     </row>
     <row r="73">
@@ -7101,7 +7638,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7110,13 +7647,13 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2346</v>
+        <v>99734</v>
       </c>
       <c r="E73" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F73" t="n">
-        <v>0.5679</v>
+        <v>10.3146</v>
       </c>
     </row>
     <row r="74">
@@ -7127,7 +7664,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7136,13 +7673,13 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>146542</v>
+        <v>421948</v>
       </c>
       <c r="E74" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F74" t="n">
-        <v>9.9986</v>
+        <v>89.5044</v>
       </c>
     </row>
     <row r="75">
@@ -7153,7 +7690,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7162,13 +7699,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>33000</v>
+        <v>26400</v>
       </c>
       <c r="E75" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F75" t="n">
-        <v>2.2516</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="76">
@@ -7179,7 +7716,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7191,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -7205,7 +7742,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7214,13 +7751,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3736.4</v>
+        <v>21080.65</v>
       </c>
       <c r="E77" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2549</v>
+        <v>4.4717</v>
       </c>
     </row>
     <row r="78">
@@ -7231,22 +7768,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1282342</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F78" t="n">
-        <v>87.4948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -7257,22 +7794,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>330466</v>
+        <v>1998.68</v>
       </c>
       <c r="E79" t="n">
-        <v>408765.21</v>
+        <v>471427.33</v>
       </c>
       <c r="F79" t="n">
-        <v>80.8449</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="80">
@@ -7283,22 +7820,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>33420</v>
+        <v>280956</v>
       </c>
       <c r="E80" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F80" t="n">
-        <v>8.175800000000001</v>
+        <v>68.01130000000001</v>
       </c>
     </row>
     <row r="81">
@@ -7309,22 +7846,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>59200</v>
       </c>
       <c r="E81" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>14.3306</v>
       </c>
     </row>
     <row r="82">
@@ -7335,22 +7872,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12301.21</v>
+        <v>70400</v>
       </c>
       <c r="E82" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F82" t="n">
-        <v>3.0094</v>
+        <v>17.0418</v>
       </c>
     </row>
     <row r="83">
@@ -7361,22 +7898,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>32578</v>
+        <v>200</v>
       </c>
       <c r="E83" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F83" t="n">
-        <v>7.9699</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="84">
@@ -7387,22 +7924,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>141738.01</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>684757.87</v>
+        <v>413102</v>
       </c>
       <c r="F84" t="n">
-        <v>20.699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -7413,22 +7950,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>109800</v>
+        <v>2346</v>
       </c>
       <c r="E85" t="n">
-        <v>684757.87</v>
+        <v>413102</v>
       </c>
       <c r="F85" t="n">
-        <v>16.0349</v>
+        <v>0.5679</v>
       </c>
     </row>
     <row r="86">
@@ -7439,22 +7976,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>146542</v>
       </c>
       <c r="E86" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>9.9986</v>
       </c>
     </row>
     <row r="87">
@@ -7465,22 +8002,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>14327.36</v>
+        <v>33000</v>
       </c>
       <c r="E87" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F87" t="n">
-        <v>2.0923</v>
+        <v>2.2516</v>
       </c>
     </row>
     <row r="88">
@@ -7491,22 +8028,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>418892.5</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F88" t="n">
-        <v>61.1738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -7517,22 +8054,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>68574</v>
+        <v>3736.4</v>
       </c>
       <c r="E89" t="n">
-        <v>80605.8</v>
+        <v>1465620.4</v>
       </c>
       <c r="F89" t="n">
-        <v>85.0733</v>
+        <v>0.2549</v>
       </c>
     </row>
     <row r="90">
@@ -7543,22 +8080,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11640</v>
+        <v>71715</v>
       </c>
       <c r="E90" t="n">
-        <v>80605.8</v>
+        <v>1465620.4</v>
       </c>
       <c r="F90" t="n">
-        <v>14.4406</v>
+        <v>4.8931</v>
       </c>
     </row>
     <row r="91">
@@ -7569,22 +8106,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1210627</v>
       </c>
       <c r="E91" t="n">
-        <v>80605.8</v>
+        <v>1465620.4</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>82.60169999999999</v>
       </c>
     </row>
     <row r="92">
@@ -7595,22 +8132,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>124.8</v>
+        <v>330466</v>
       </c>
       <c r="E92" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1548</v>
+        <v>80.8449</v>
       </c>
     </row>
     <row r="93">
@@ -7621,22 +8158,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>267</v>
+        <v>33420</v>
       </c>
       <c r="E93" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F93" t="n">
-        <v>0.3312</v>
+        <v>8.175800000000001</v>
       </c>
     </row>
     <row r="94">
@@ -7647,22 +8184,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>171462</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>262957</v>
+        <v>408765.21</v>
       </c>
       <c r="F94" t="n">
-        <v>65.20529999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -7673,22 +8210,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6600</v>
+        <v>12301.21</v>
       </c>
       <c r="E95" t="n">
-        <v>262957</v>
+        <v>408765.21</v>
       </c>
       <c r="F95" t="n">
-        <v>2.5099</v>
+        <v>3.0094</v>
       </c>
     </row>
     <row r="96">
@@ -7699,22 +8236,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>262957</v>
+        <v>408765.21</v>
       </c>
       <c r="F96" t="n">
-        <v>9.4312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -7725,22 +8262,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>32578</v>
       </c>
       <c r="E97" t="n">
-        <v>262957</v>
+        <v>408765.21</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>7.9699</v>
       </c>
     </row>
     <row r="98">
@@ -7751,22 +8288,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>60095</v>
+        <v>141738.01</v>
       </c>
       <c r="E98" t="n">
-        <v>262957</v>
+        <v>684757.87</v>
       </c>
       <c r="F98" t="n">
-        <v>22.8535</v>
+        <v>20.699</v>
       </c>
     </row>
     <row r="99">
@@ -7777,22 +8314,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>20000</v>
+        <v>109800</v>
       </c>
       <c r="E99" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F99" t="n">
-        <v>60.5697</v>
+        <v>16.0349</v>
       </c>
     </row>
     <row r="100">
@@ -7803,22 +8340,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1681</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F100" t="n">
-        <v>5.0909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -7829,22 +8366,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1000</v>
+        <v>14327.36</v>
       </c>
       <c r="E101" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F101" t="n">
-        <v>3.0285</v>
+        <v>2.0923</v>
       </c>
     </row>
     <row r="102">
@@ -7855,22 +8392,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>907.8</v>
+        <v>27820</v>
       </c>
       <c r="E102" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F102" t="n">
-        <v>2.7493</v>
+        <v>4.0627</v>
       </c>
     </row>
     <row r="103">
@@ -7881,7 +8418,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7890,13 +8427,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>9431</v>
+        <v>391072.5</v>
       </c>
       <c r="E103" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F103" t="n">
-        <v>28.5617</v>
+        <v>57.1111</v>
       </c>
     </row>
     <row r="104">
@@ -7907,7 +8444,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7916,13 +8453,13 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2386608.01</v>
+        <v>68574</v>
       </c>
       <c r="E104" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F104" t="n">
-        <v>37.8325</v>
+        <v>85.0733</v>
       </c>
     </row>
     <row r="105">
@@ -7933,7 +8470,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7942,13 +8479,13 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>571481</v>
+        <v>11640</v>
       </c>
       <c r="E105" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F105" t="n">
-        <v>9.059100000000001</v>
+        <v>14.4406</v>
       </c>
     </row>
     <row r="106">
@@ -7959,7 +8496,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7968,13 +8505,13 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>150800</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F106" t="n">
-        <v>2.3905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -7985,7 +8522,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7994,13 +8531,13 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1279518.2</v>
+        <v>124.8</v>
       </c>
       <c r="E107" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F107" t="n">
-        <v>20.2829</v>
+        <v>0.1548</v>
       </c>
     </row>
     <row r="108">
@@ -8011,22 +8548,516 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>80605.8</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>267</v>
+      </c>
+      <c r="E109" t="n">
+        <v>80605.8</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.3312</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>171462</v>
+      </c>
+      <c r="E110" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F110" t="n">
+        <v>65.20529999999999</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>家守/千金方/少年说</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E111" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2.5099</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>24800</v>
+      </c>
+      <c r="E112" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9.4312</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>60095</v>
+      </c>
+      <c r="E115" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F115" t="n">
+        <v>22.8535</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E116" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F116" t="n">
+        <v>60.5697</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>家守/千金方/少年说</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1681</v>
+      </c>
+      <c r="E117" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F117" t="n">
+        <v>5.0909</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E118" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F118" t="n">
+        <v>3.0285</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>907.8</v>
+      </c>
+      <c r="E119" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2.7493</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>9431</v>
+      </c>
+      <c r="E121" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F121" t="n">
+        <v>28.5617</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>2386608.01</v>
+      </c>
+      <c r="E122" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F122" t="n">
+        <v>37.8325</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>家守/千金方/少年说</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>571481</v>
+      </c>
+      <c r="E123" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F123" t="n">
+        <v>9.059100000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>150800</v>
+      </c>
+      <c r="E124" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2.3905</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1279518.2</v>
+      </c>
+      <c r="E125" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F125" t="n">
+        <v>20.2829</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>105475</v>
+      </c>
+      <c r="E126" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.672</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>1919941.18</v>
-      </c>
-      <c r="E108" t="n">
+      <c r="D127" t="n">
+        <v>1814466.18</v>
+      </c>
+      <c r="E127" t="n">
         <v>6308348.39</v>
       </c>
-      <c r="F108" t="n">
-        <v>30.4349</v>
+      <c r="F127" t="n">
+        <v>28.7629</v>
       </c>
     </row>
   </sheetData>
@@ -16208,16 +17239,16 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>韩冰老师一百天疗愈计划</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>40000</v>
+        <v>23760</v>
       </c>
     </row>
     <row r="328">
@@ -16233,16 +17264,16 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>【青春进化论】亲子成长2日营补差链接</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>23760</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="329">
@@ -16263,11 +17294,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>源生衡十五株益生菌 （买五赠一）</t>
+          <t>韩冰老师一百天疗愈计划</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>1490</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="330">
@@ -16288,11 +17319,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营补差链接</t>
+          <t>源生衡十五株益生菌 （买五赠一）</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>1440</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="331">
@@ -16558,16 +17589,16 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>青少年营地动力唤醒方案</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>199200</v>
+        <v>57420</v>
       </c>
     </row>
     <row r="342">
@@ -16583,16 +17614,16 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>青少年营地家族赋能方案</t>
+          <t>【青春进化论】亲子成长2日营补差链接</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>168000</v>
+        <v>7770</v>
       </c>
     </row>
     <row r="343">
@@ -16613,11 +17644,11 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>青少年营地动力唤醒方案</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>57420</v>
+        <v>199200</v>
       </c>
     </row>
     <row r="344">
@@ -16638,11 +17669,11 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>动力唤醒方案</t>
+          <t>青少年营地家族赋能方案</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>49800</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="345">
@@ -16663,11 +17694,11 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营补差链接</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>7770</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="346">
@@ -21158,7 +22189,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -23158,16 +24189,16 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>韩冰老师一百天疗愈计划</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E605" t="n">
-        <v>80000</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="606">
@@ -23188,11 +24219,11 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>压力创伤释放工作坊</t>
+          <t>韩冰老师一百天疗愈计划</t>
         </is>
       </c>
       <c r="E606" t="n">
-        <v>13860</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="607">
@@ -23213,11 +24244,11 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>压力创伤释放工作坊</t>
         </is>
       </c>
       <c r="E607" t="n">
-        <v>3960</v>
+        <v>13860</v>
       </c>
     </row>
     <row r="608">
@@ -27158,16 +28189,16 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>青少年营地家族赋能方案</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E765" t="n">
-        <v>672000</v>
+        <v>62685</v>
       </c>
     </row>
     <row r="766">
@@ -27183,16 +28214,16 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>青少年营地动力唤醒方案</t>
+          <t>【青春进化论】亲子成长2日营补差链接</t>
         </is>
       </c>
       <c r="E766" t="n">
-        <v>448200</v>
+        <v>9030</v>
       </c>
     </row>
     <row r="767">
@@ -27213,11 +28244,11 @@
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>青少年营地家族赋能方案</t>
         </is>
       </c>
       <c r="E767" t="n">
-        <v>62685</v>
+        <v>672000</v>
       </c>
     </row>
     <row r="768">
@@ -27238,11 +28269,11 @@
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>动力唤醒方案</t>
+          <t>青少年营地动力唤醒方案</t>
         </is>
       </c>
       <c r="E768" t="n">
-        <v>49800</v>
+        <v>448200</v>
       </c>
     </row>
     <row r="769">
@@ -27263,11 +28294,11 @@
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>未来之翼7日身心复能营</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E769" t="n">
-        <v>19800</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="770">
@@ -27288,11 +28319,11 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营补差链接</t>
+          <t>未来之翼7日身心复能营</t>
         </is>
       </c>
       <c r="E770" t="n">
-        <v>9030</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="771">
@@ -27588,7 +28619,7 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>青少年19元巨量</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E782" t="n">
@@ -27613,7 +28644,7 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>青少年19元巨量</t>
         </is>
       </c>
       <c r="E783" t="n">
@@ -27688,7 +28719,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>青少年同行者计划：试听课</t>
+          <t>青少年同行者一周家长短训营亲子教育网课</t>
         </is>
       </c>
       <c r="E786" t="n">
@@ -27713,7 +28744,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>青少年adq新链接XY</t>
+          <t>青少年同行者计划：试听课</t>
         </is>
       </c>
       <c r="E787" t="n">
@@ -27788,7 +28819,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>青少年同行者一周家长短训营亲子教育网课</t>
+          <t>青少年adq新链接XY</t>
         </is>
       </c>
       <c r="E790" t="n">
@@ -27888,7 +28919,7 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>21天蛋壳跳动休学复能营</t>
+          <t>0元青少年-LH</t>
         </is>
       </c>
       <c r="E794" t="n">
@@ -27913,7 +28944,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>0元青少年-LH</t>
+          <t>观心少年2天1夜心理赋能营-ys-北京</t>
         </is>
       </c>
       <c r="E795" t="n">
@@ -27988,7 +29019,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>义诊-线上</t>
+          <t>21天蛋壳跳动休学复能营</t>
         </is>
       </c>
       <c r="E798" t="n">
@@ -28013,7 +29044,7 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>义诊-线上</t>
         </is>
       </c>
       <c r="E799" t="n">
@@ -30383,16 +31414,16 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>青少年营地家族赋能方案</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E894" t="n">
-        <v>168000</v>
+        <v>23760</v>
       </c>
     </row>
     <row r="895">
@@ -30408,16 +31439,16 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>青少年营地动力唤醒方案</t>
+          <t>【青春进化论】亲子成长2日营补差链接</t>
         </is>
       </c>
       <c r="E895" t="n">
-        <v>149400</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="896">
@@ -30438,11 +31469,11 @@
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>动力唤醒方案</t>
+          <t>青少年营地家族赋能方案</t>
         </is>
       </c>
       <c r="E896" t="n">
-        <v>49800</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="897">
@@ -30463,11 +31494,11 @@
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>青少年营地动力唤醒方案</t>
         </is>
       </c>
       <c r="E897" t="n">
-        <v>23760</v>
+        <v>149400</v>
       </c>
     </row>
     <row r="898">
@@ -30488,11 +31519,11 @@
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>未来之翼7日心理能量唤醒营</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E898" t="n">
-        <v>19800</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="899">
@@ -30513,11 +31544,11 @@
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营补差链接</t>
+          <t>未来之翼7日心理能量唤醒营</t>
         </is>
       </c>
       <c r="E899" t="n">
-        <v>4060</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="900">
@@ -31063,7 +32094,7 @@
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>21天蛋壳跳动休学复能营</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E921" t="n">
@@ -31088,7 +32119,7 @@
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>21天蛋壳跳动休学复能营</t>
         </is>
       </c>
       <c r="E922" t="n">

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,7 +843,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -852,27 +852,27 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2367650.54</v>
+        <v>1854900</v>
       </c>
       <c r="E15" t="n">
-        <v>3178</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>553184.36</v>
+        <v>372400</v>
       </c>
       <c r="G15" t="n">
-        <v>1814466.18</v>
+        <v>1482500</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -881,16 +881,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>181525.57</v>
+        <v>512750.54</v>
       </c>
       <c r="E16" t="n">
-        <v>5893</v>
+        <v>3149</v>
       </c>
       <c r="F16" t="n">
-        <v>181525.57</v>
+        <v>180784.36</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>331966.18</v>
       </c>
     </row>
     <row r="17">
@@ -901,7 +901,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1142004</v>
+        <v>181525.57</v>
       </c>
       <c r="E17" t="n">
-        <v>234</v>
+        <v>5893</v>
       </c>
       <c r="F17" t="n">
-        <v>1142004</v>
+        <v>181525.57</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -930,7 +930,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>355326</v>
+        <v>1142004</v>
       </c>
       <c r="E18" t="n">
-        <v>88</v>
+        <v>234</v>
       </c>
       <c r="F18" t="n">
-        <v>355326</v>
+        <v>1142004</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -964,17 +964,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>新客</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>345326</v>
+        <v>355326</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F19" t="n">
-        <v>345326</v>
+        <v>355326</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -993,17 +993,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>老客</t>
+          <t>新客</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10000</v>
+        <v>345326</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="F20" t="n">
-        <v>10000</v>
+        <v>345326</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1017,22 +1017,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>老客</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1497534</v>
+        <v>10000</v>
       </c>
       <c r="E21" t="n">
-        <v>270</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>1497534</v>
+        <v>10000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>少年说</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1116610</v>
+        <v>1497534</v>
       </c>
       <c r="E22" t="n">
-        <v>97</v>
+        <v>270</v>
       </c>
       <c r="F22" t="n">
-        <v>1116610</v>
+        <v>1497534</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>家守</t>
+          <t>少年说</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>380924</v>
+        <v>1116610</v>
       </c>
       <c r="E23" t="n">
-        <v>173</v>
+        <v>97</v>
       </c>
       <c r="F23" t="n">
-        <v>380924</v>
+        <v>1116610</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1104,22 +1104,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>家守</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>99200</v>
+        <v>380924</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="F24" t="n">
-        <v>99200</v>
+        <v>380924</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>49696.78</v>
+        <v>99200</v>
       </c>
       <c r="E25" t="n">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>49696.78</v>
+        <v>99200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>初诊</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>37785.67</v>
+        <v>49696.78</v>
       </c>
       <c r="E26" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F26" t="n">
-        <v>37785.67</v>
+        <v>49696.78</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>复诊</t>
+          <t>初诊</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11911.11</v>
+        <v>37785.67</v>
       </c>
       <c r="E27" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="F27" t="n">
-        <v>11911.11</v>
+        <v>37785.67</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1220,22 +1220,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>复诊</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>90390</v>
+        <v>11911.11</v>
       </c>
       <c r="E28" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="F28" t="n">
-        <v>90390</v>
+        <v>11911.11</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>553184.36</v>
+        <v>90390</v>
       </c>
       <c r="E29" t="n">
-        <v>315</v>
+        <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>553184.36</v>
+        <v>90390</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1273,12 +1273,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1287,45 +1287,45 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2386608.01</v>
+        <v>372400</v>
       </c>
       <c r="E30" t="n">
-        <v>582</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
+        <v>372400</v>
+      </c>
+      <c r="G30" t="n">
         <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2386608.01</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>老客</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1910462.01</v>
+        <v>180784.36</v>
       </c>
       <c r="E31" t="n">
-        <v>392</v>
+        <v>309</v>
       </c>
       <c r="F31" t="n">
+        <v>180784.36</v>
+      </c>
+      <c r="G31" t="n">
         <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1910462.01</v>
       </c>
     </row>
     <row r="32">
@@ -1341,20 +1341,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>新客</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>418748</v>
+        <v>2386608.01</v>
       </c>
       <c r="E32" t="n">
-        <v>183</v>
+        <v>582</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>418748</v>
+        <v>2386608.01</v>
       </c>
     </row>
     <row r="33">
@@ -1365,25 +1365,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>老客</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>571481</v>
+        <v>1910462.01</v>
       </c>
       <c r="E33" t="n">
-        <v>74</v>
+        <v>392</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>571481</v>
+        <v>1910462.01</v>
       </c>
     </row>
     <row r="34">
@@ -1394,25 +1394,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>少年说</t>
+          <t>新客</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>330240</v>
+        <v>418748</v>
       </c>
       <c r="E34" t="n">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>330240</v>
+        <v>418748</v>
       </c>
     </row>
     <row r="35">
@@ -1428,20 +1428,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>家守</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>241241</v>
+        <v>571481</v>
       </c>
       <c r="E35" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>241241</v>
+        <v>571481</v>
       </c>
     </row>
     <row r="36">
@@ -1452,25 +1452,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>少年说</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>150800</v>
+        <v>330240</v>
       </c>
       <c r="E36" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>150800</v>
+        <v>330240</v>
       </c>
     </row>
     <row r="37">
@@ -1481,25 +1481,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>家守</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1279518.2</v>
+        <v>241241</v>
       </c>
       <c r="E37" t="n">
-        <v>2105</v>
+        <v>32</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1279518.2</v>
+        <v>241241</v>
       </c>
     </row>
     <row r="38">
@@ -1510,25 +1510,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>复诊</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>824010.16</v>
+        <v>150800</v>
       </c>
       <c r="E38" t="n">
-        <v>916</v>
+        <v>21</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>824010.16</v>
+        <v>150800</v>
       </c>
     </row>
     <row r="39">
@@ -1544,20 +1544,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>初诊</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>455508.04</v>
+        <v>1279518.2</v>
       </c>
       <c r="E39" t="n">
-        <v>1189</v>
+        <v>2105</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>455508.04</v>
+        <v>1279518.2</v>
       </c>
     </row>
     <row r="40">
@@ -1568,25 +1568,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>复诊</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>105475</v>
+        <v>824010.16</v>
       </c>
       <c r="E40" t="n">
-        <v>77</v>
+        <v>916</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>105475</v>
+        <v>824010.16</v>
       </c>
     </row>
     <row r="41">
@@ -1597,25 +1597,112 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>初诊</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1814466.18</v>
+        <v>455508.04</v>
       </c>
       <c r="E41" t="n">
-        <v>2863</v>
+        <v>1189</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1814466.18</v>
+        <v>455508.04</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>105475</v>
+      </c>
+      <c r="E42" t="n">
+        <v>77</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>105475</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1482500</v>
+      </c>
+      <c r="E43" t="n">
+        <v>23</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1482500</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>331966.18</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2840</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>331966.18</v>
       </c>
     </row>
   </sheetData>
@@ -1848,15 +1935,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>82.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>其他 1210627.0；咨询 146542.0；进化论 71715.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
+          <t>营地 1145200.0；咨询 146542.0；进化论 71715.0；其他 65427.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -1904,15 +1991,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>57.1</v>
+        <v>49.3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>其他 391072.5；咨询 141738.01；家守/千金方/少年说 109800.0；进化论 27820.0；医疗 14327.36</t>
+          <t>营地 337300.0；咨询 141738.01；家守/千金方/少年说 109800.0；其他 53772.5；进化论 27820.0；医疗 14327.36</t>
         </is>
       </c>
     </row>
@@ -1996,7 +2083,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>咨询 20000.0；其他 9431.0；家守/千金方/少年说 1681.0；菌群 1000.0；医疗 907.8</t>
+          <t>咨询 20000.0；其他 9431.0；家守/千金方/少年说 1681.0；菌群 1000.0；医疗 907.8；营地 0.0</t>
         </is>
       </c>
     </row>
@@ -2184,15 +2271,15 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>82.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>其他 1210627.0；咨询 146542.0；进化论 71715.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
+          <t>营地 1145200.0；咨询 146542.0；进化论 71715.0；其他 65427.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -2240,15 +2327,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>57.1</v>
+        <v>49.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>其他 391072.5；咨询 141738.01；家守/千金方/少年说 109800.0；进化论 27820.0；医疗 14327.36</t>
+          <t>营地 337300.0；咨询 141738.01；家守/千金方/少年说 109800.0；其他 53772.5；进化论 27820.0；医疗 14327.36</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2419,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>咨询 20000.0；其他 9431.0；家守/千金方/少年说 1681.0；菌群 1000.0；医疗 907.8</t>
+          <t>咨询 20000.0；其他 9431.0；家守/千金方/少年说 1681.0；菌群 1000.0；医疗 907.8；营地 0.0</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3190,7 +3277,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3213,7 +3300,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3236,7 +3323,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3248,7 +3335,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>267600</v>
+        <v>217800</v>
       </c>
     </row>
     <row r="40">
@@ -3259,7 +3346,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3271,7 +3358,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>217900</v>
+        <v>168100</v>
       </c>
     </row>
     <row r="41">
@@ -3282,7 +3369,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3300,12 +3387,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3313,22 +3400,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1280</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3336,22 +3423,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1280</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3359,22 +3446,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>章浩进</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1280</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3382,22 +3469,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>梁志前</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1280</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3405,11 +3492,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1280</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="47">
@@ -3420,7 +3507,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3428,11 +3515,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>169320</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="48">
@@ -3443,7 +3530,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3451,11 +3538,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103300</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="49">
@@ -3466,7 +3553,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3474,11 +3561,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>89042</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="50">
@@ -3489,7 +3576,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3497,11 +3584,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>79381</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="51">
@@ -3512,7 +3599,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3520,11 +3607,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>75910</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="52">
@@ -3535,7 +3622,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3543,11 +3630,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53194</v>
+        <v>169320</v>
       </c>
     </row>
     <row r="53">
@@ -3558,7 +3645,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3566,11 +3653,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>刘士明</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>30796</v>
+        <v>103300</v>
       </c>
     </row>
     <row r="54">
@@ -3581,7 +3668,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3589,11 +3676,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>30398</v>
+        <v>89042</v>
       </c>
     </row>
     <row r="55">
@@ -3604,7 +3691,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3612,11 +3699,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>24598</v>
+        <v>79381</v>
       </c>
     </row>
     <row r="56">
@@ -3627,7 +3714,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3635,11 +3722,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>20000</v>
+        <v>75910</v>
       </c>
     </row>
     <row r="57">
@@ -3650,7 +3737,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3658,11 +3745,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>165000</v>
+        <v>53194</v>
       </c>
     </row>
     <row r="58">
@@ -3673,7 +3760,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3681,11 +3768,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>132000</v>
+        <v>30796</v>
       </c>
     </row>
     <row r="59">
@@ -3696,7 +3783,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3704,11 +3791,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>109640</v>
+        <v>30398</v>
       </c>
     </row>
     <row r="60">
@@ -3719,7 +3806,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -3727,11 +3814,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>109020</v>
+        <v>24598</v>
       </c>
     </row>
     <row r="61">
@@ -3742,7 +3829,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3750,11 +3837,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>张天昂</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103200</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="62">
@@ -3765,7 +3852,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3773,11 +3860,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>49600</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="63">
@@ -3788,7 +3875,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -3796,11 +3883,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>24800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="64">
@@ -3811,7 +3898,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3819,11 +3906,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>24800</v>
+        <v>109640</v>
       </c>
     </row>
     <row r="65">
@@ -3834,7 +3921,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3842,11 +3929,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>109020</v>
       </c>
     </row>
     <row r="66">
@@ -3857,7 +3944,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -3865,11 +3952,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>103200</v>
       </c>
     </row>
     <row r="67">
@@ -3880,7 +3967,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -3892,7 +3979,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>16800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="68">
@@ -3903,7 +3990,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -3911,11 +3998,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1200</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="69">
@@ -3926,7 +4013,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -3938,7 +4025,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>500</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="70">
@@ -3949,7 +4036,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -3957,11 +4044,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3972,7 +4059,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -3980,11 +4067,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3995,7 +4082,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -4003,11 +4090,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>陈鑫</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>24750</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="73">
@@ -4018,7 +4105,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -4026,11 +4113,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>21780</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="74">
@@ -4041,7 +4128,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4049,11 +4136,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>余文静</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>14400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="75">
@@ -4064,7 +4151,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4072,11 +4159,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>吴云龙</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>7480</v>
+        <v>300</v>
       </c>
     </row>
     <row r="76">
@@ -4087,7 +4174,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -4095,11 +4182,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>魏恺志</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77">
@@ -4110,7 +4197,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -4122,7 +4209,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>267600</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="78">
@@ -4133,7 +4220,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -4141,11 +4228,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>姚闯</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>49800</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="79">
@@ -4156,7 +4243,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4164,11 +4251,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>杨旺忠</t>
+          <t>余文静</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>49800</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="80">
@@ -4179,7 +4266,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -4191,7 +4278,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>49800</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="81">
@@ -4202,7 +4289,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -4210,22 +4297,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>魏恺志</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>40000</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -4233,22 +4320,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>233168</v>
+        <v>217800</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -4256,22 +4343,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>姚闯</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>158786</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -4279,22 +4366,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>吴云龙</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>91194</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -4302,22 +4389,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>杨旺忠</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>85698</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -4325,22 +4412,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>余文静</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>81982</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -4348,22 +4435,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>164220</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -4371,22 +4458,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄慧作</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>90000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -4394,22 +4481,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>46200</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -4417,22 +4504,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>林非凡</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>26820</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -4440,11 +4527,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>26200</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="92">
@@ -4455,7 +4542,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -4467,7 +4554,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>54600</v>
+        <v>233168</v>
       </c>
     </row>
     <row r="93">
@@ -4478,7 +4565,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -4486,11 +4573,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>李颜君</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>45600</v>
+        <v>158786</v>
       </c>
     </row>
     <row r="94">
@@ -4501,7 +4588,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -4509,11 +4596,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>24800</v>
+        <v>91194</v>
       </c>
     </row>
     <row r="95">
@@ -4524,7 +4611,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -4532,11 +4619,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>24800</v>
+        <v>85698</v>
       </c>
     </row>
     <row r="96">
@@ -4547,7 +4634,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -4555,11 +4642,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>王秀丽</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1000</v>
+        <v>81982</v>
       </c>
     </row>
     <row r="97">
@@ -4570,7 +4657,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -4578,11 +4665,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>245315.88</v>
+        <v>164220</v>
       </c>
     </row>
     <row r="98">
@@ -4593,7 +4680,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -4601,11 +4688,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>黄慧作</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>196025.61</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="99">
@@ -4616,7 +4703,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -4624,11 +4711,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>190639.29</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="100">
@@ -4639,7 +4726,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -4647,11 +4734,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>157856.3</v>
+        <v>26820</v>
       </c>
     </row>
     <row r="101">
@@ -4662,7 +4749,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -4670,11 +4757,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>105286</v>
+        <v>26200</v>
       </c>
     </row>
     <row r="102">
@@ -4685,7 +4772,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -4693,11 +4780,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>高丹</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>16520</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="103">
@@ -4708,7 +4795,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -4716,11 +4803,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>徐艳霞</t>
+          <t>李颜君</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>9900</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="104">
@@ -4731,7 +4818,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -4739,11 +4826,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>郭海明</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>8560</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="105">
@@ -4754,7 +4841,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -4762,11 +4849,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>章浩进</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>8100</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="106">
@@ -4777,7 +4864,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -4785,11 +4872,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>韦新妮</t>
+          <t>王秀丽</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>7920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="107">
@@ -4800,7 +4887,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -4808,11 +4895,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>胡炫明</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>391000</v>
+        <v>245315.88</v>
       </c>
     </row>
     <row r="108">
@@ -4823,7 +4910,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -4831,11 +4918,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>徐艳霞</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>267600</v>
+        <v>196025.61</v>
       </c>
     </row>
     <row r="109">
@@ -4846,7 +4933,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -4854,11 +4941,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>梁志前</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>217900</v>
+        <v>190639.29</v>
       </c>
     </row>
     <row r="110">
@@ -4869,7 +4956,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -4877,11 +4964,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>陈磊</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>168000</v>
+        <v>157856.3</v>
       </c>
     </row>
     <row r="111">
@@ -4892,7 +4979,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -4900,11 +4987,356 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>胡威特</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="E111" t="n">
+        <v>105286</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>高丹</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>16520</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>徐艳霞</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>郭海明</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>8560</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>章浩进</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>5</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>韦新妮</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>7920</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>胡炫明</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>391000</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>徐艳霞</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>267600</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>梁志前</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>168100</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>陈磊</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>168000</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>5</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>张佳慧</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
         <v>99600</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>张虹</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>梁志前</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>49800</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>3</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>章浩进</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>49800</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>4</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>陈翔宇</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>5</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>岳伟伟</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>33956</v>
       </c>
     </row>
   </sheetData>
@@ -4918,7 +5350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5221,65 +5653,65 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2367650.54</v>
+        <v>1854900</v>
       </c>
       <c r="D9" t="n">
-        <v>612908.59</v>
+        <v>391600</v>
       </c>
       <c r="E9" t="n">
-        <v>27052</v>
+        <v>20100</v>
       </c>
       <c r="F9" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="G9" t="n">
-        <v>585856.59</v>
+        <v>371500</v>
       </c>
       <c r="H9" t="n">
-        <v>24.74</v>
+        <v>20.03</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；青少年营地动力唤醒方案 85000.0；青少年成长基地3月营（金盏基地） 83600.0</t>
+          <t>青少年营地动力唤醒方案 85000.0；青少年成长基地3月营（金盏基地） 83600.0；青少年营地家族赋能方案 80000.0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>181525.57</v>
+        <v>512750.54</v>
       </c>
       <c r="D10" t="n">
-        <v>22555</v>
+        <v>221308.59</v>
       </c>
       <c r="E10" t="n">
-        <v>18920</v>
+        <v>6952</v>
       </c>
       <c r="F10" t="n">
-        <v>10.42</v>
+        <v>1.36</v>
       </c>
       <c r="G10" t="n">
-        <v>3635</v>
+        <v>214356.59</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>41.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 3588.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 2560.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 1688.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；青少年身心复能成长方案 80000.0；【廖文婷】萨提亚家庭系统工作坊 5940.0</t>
         </is>
       </c>
     </row>
@@ -5291,30 +5723,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1142004</v>
+        <v>181525.57</v>
       </c>
       <c r="D11" t="n">
-        <v>193920.44</v>
+        <v>22555</v>
       </c>
       <c r="E11" t="n">
-        <v>4980</v>
+        <v>18920</v>
       </c>
       <c r="F11" t="n">
-        <v>0.44</v>
+        <v>10.42</v>
       </c>
       <c r="G11" t="n">
-        <v>188940.44</v>
+        <v>3635</v>
       </c>
       <c r="H11" t="n">
-        <v>16.54</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>青少年同行者计划领航营 118165.4；青少年同行者计划-护航营 21578.0；青少年同行者计划向阳营 14593.37</t>
+          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 3588.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 2560.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 1688.0</t>
         </is>
       </c>
     </row>
@@ -5326,30 +5758,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>355326</v>
+        <v>1142004</v>
       </c>
       <c r="D12" t="n">
-        <v>143025.9</v>
+        <v>193920.44</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="G12" t="n">
-        <v>143025.9</v>
+        <v>188940.44</v>
       </c>
       <c r="H12" t="n">
-        <v>40.25</v>
+        <v>16.54</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>儿童青少年 63298.0；精神心理 61198.0；青少年-资深咨询 18500.0</t>
+          <t>青少年同行者计划领航营 118165.4；青少年同行者计划-护航营 21578.0；青少年同行者计划向阳营 14593.37</t>
         </is>
       </c>
     </row>
@@ -5361,30 +5793,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1497534</v>
+        <v>355326</v>
       </c>
       <c r="D13" t="n">
-        <v>145410</v>
+        <v>143025.9</v>
       </c>
       <c r="E13" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>143730</v>
+        <v>143025.9</v>
       </c>
       <c r="H13" t="n">
-        <v>9.6</v>
+        <v>40.25</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（二阶） 58620.0；少年说陪伴计划 52800.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
+          <t>儿童青少年 63298.0；精神心理 61198.0；青少年-资深咨询 18500.0</t>
         </is>
       </c>
     </row>
@@ -5396,30 +5828,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>99200</v>
+        <v>1497534</v>
       </c>
       <c r="D14" t="n">
-        <v>121000</v>
+        <v>145410</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G14" t="n">
-        <v>121000</v>
+        <v>143730</v>
       </c>
       <c r="H14" t="n">
-        <v>121.98</v>
+        <v>9.6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>肠道菌群移植 74400.0；肠道菌群移植（双疗程） 45600.0；肠道菌群检测 1000.0</t>
+          <t>家庭守护计划2.0（二阶） 58620.0；少年说陪伴计划 52800.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
         </is>
       </c>
     </row>
@@ -5431,14 +5863,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>49696.78</v>
+        <v>99200</v>
       </c>
       <c r="D15" t="n">
-        <v>778</v>
+        <v>121000</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -5447,14 +5879,14 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>778</v>
+        <v>121000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.57</v>
+        <v>121.98</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20分钟问诊（专家医师） -线上 500.0；20分钟问诊（医师） -线上 200.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
+          <t>肠道菌群移植 74400.0；肠道菌群移植（双疗程） 45600.0；肠道菌群检测 1000.0</t>
         </is>
       </c>
     </row>
@@ -5466,30 +5898,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>90390</v>
+        <v>49696.78</v>
       </c>
       <c r="D16" t="n">
-        <v>15940</v>
+        <v>778</v>
       </c>
       <c r="E16" t="n">
-        <v>2080</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>13860</v>
+        <v>778</v>
       </c>
       <c r="H16" t="n">
-        <v>15.33</v>
+        <v>1.57</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营 13860.0；青春进化论（两日制亲子营） 1980.0；【青春进化论】亲子成长2日营补差链接 100.0</t>
+          <t>20分钟问诊（专家医师） -线上 500.0；20分钟问诊（医师） -线上 200.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
         </is>
       </c>
     </row>
@@ -5501,100 +5933,100 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>553184.36</v>
+        <v>90390</v>
       </c>
       <c r="D17" t="n">
-        <v>274150.59</v>
+        <v>15940</v>
       </c>
       <c r="E17" t="n">
-        <v>999</v>
+        <v>2080</v>
       </c>
       <c r="F17" t="n">
-        <v>0.18</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>273151.59</v>
+        <v>13860</v>
       </c>
       <c r="H17" t="n">
-        <v>49.38</v>
+        <v>15.33</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；蛋壳跳动身心复能营21天（一阶） 74200.0；青少年成长基地3月营（金盏基地） 46800.0</t>
+          <t>【青春进化论】亲子成长2日营 13860.0；青春进化论（两日制亲子营） 1980.0；【青春进化论】亲子成长2日营补差链接 100.0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2386608.01</v>
+        <v>372400</v>
       </c>
       <c r="D18" t="n">
-        <v>409927.33</v>
+        <v>156100</v>
       </c>
       <c r="E18" t="n">
-        <v>10398</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>399529.33</v>
+        <v>156100</v>
       </c>
       <c r="H18" t="n">
-        <v>16.74</v>
+        <v>41.92</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>儿童青少年 286931.33；电商咨询 37500.0；精神心理 32798.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 74200.0；青少年成长基地3月营（金盏基地） 46800.0；未来王者（AI探索&amp;学习力营） 16800.0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>571481</v>
+        <v>180784.36</v>
       </c>
       <c r="D19" t="n">
-        <v>68520</v>
+        <v>118050.59</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="G19" t="n">
-        <v>68520</v>
+        <v>117051.59</v>
       </c>
       <c r="H19" t="n">
-        <v>11.99</v>
+        <v>64.75</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（三阶） 26310.0；家庭守护计划2.0（一阶） 23970.0；少年说陪伴计划 13200.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；8周系统性心身综合干预+深度服务包（全国统一价） 3900.0；心理咨询师职业能力水平评价考试培训 3800.0</t>
         </is>
       </c>
     </row>
@@ -5606,30 +6038,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>150800</v>
+        <v>2386608.01</v>
       </c>
       <c r="D20" t="n">
-        <v>115000</v>
+        <v>409927.33</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="G20" t="n">
-        <v>115000</v>
+        <v>399529.33</v>
       </c>
       <c r="H20" t="n">
-        <v>76.26000000000001</v>
+        <v>16.74</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>肠道菌群移植 47600.0；肠道菌群移植（双疗程） 45600.0；肠道菌群移植（双疗程优惠） 20800.0</t>
+          <t>儿童青少年 286931.33；电商咨询 37500.0；精神心理 32798.0</t>
         </is>
       </c>
     </row>
@@ -5641,30 +6073,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1279518.2</v>
+        <v>571481</v>
       </c>
       <c r="D21" t="n">
-        <v>5541.59</v>
+        <v>68520</v>
       </c>
       <c r="E21" t="n">
-        <v>1941.59</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>3600</v>
+        <v>68520</v>
       </c>
       <c r="H21" t="n">
-        <v>0.28</v>
+        <v>11.99</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>线上/线下门诊 3200.0；【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59；20分钟问诊（医师） -线上 600.0</t>
+          <t>家庭守护计划2.0（三阶） 26310.0；家庭守护计划2.0（一阶） 23970.0；少年说陪伴计划 13200.0</t>
         </is>
       </c>
     </row>
@@ -5676,30 +6108,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>105475</v>
+        <v>150800</v>
       </c>
       <c r="D22" t="n">
-        <v>41310</v>
+        <v>115000</v>
       </c>
       <c r="E22" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>39330</v>
+        <v>115000</v>
       </c>
       <c r="H22" t="n">
-        <v>37.29</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营 39150.0；青春进化论（两日制亲子营） 1980.0；【青春进化论】亲子成长2日营补差链接 180.0</t>
+          <t>肠道菌群移植 47600.0；肠道菌群移植（双疗程） 45600.0；肠道菌群移植（双疗程优惠） 20800.0</t>
         </is>
       </c>
     </row>
@@ -5711,30 +6143,135 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1279518.2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5541.59</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1941.59</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3600</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>线上/线下门诊 3200.0；【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59；20分钟问诊（医师） -线上 600.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>105475</v>
+      </c>
+      <c r="D24" t="n">
+        <v>41310</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G24" t="n">
+        <v>39330</v>
+      </c>
+      <c r="H24" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>【青春进化论】亲子成长2日营 39150.0；青春进化论（两日制亲子营） 1980.0；【青春进化论】亲子成长2日营补差链接 180.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1482500</v>
+      </c>
+      <c r="D25" t="n">
+        <v>235500</v>
+      </c>
+      <c r="E25" t="n">
+        <v>20100</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G25" t="n">
+        <v>215400</v>
+      </c>
+      <c r="H25" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>青少年营地动力唤醒方案 85000.0；青少年营地家族赋能方案 80000.0；青少年成长基地3月营（金盏基地） 36800.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1814466.18</v>
-      </c>
-      <c r="D23" t="n">
-        <v>338758</v>
-      </c>
-      <c r="E23" t="n">
-        <v>26053</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G23" t="n">
-        <v>312705</v>
-      </c>
-      <c r="H23" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>青少年营地动力唤醒方案 85000.0；青少年营地家族赋能方案 80000.0；青少年身心复能成长方案 80000.0</t>
+      <c r="C26" t="n">
+        <v>331966.18</v>
+      </c>
+      <c r="D26" t="n">
+        <v>103258</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5953</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G26" t="n">
+        <v>97305</v>
+      </c>
+      <c r="H26" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>青少年身心复能成长方案 80000.0；完形心理成长计划 4999.0；青少年同行者计划之领航营亲子教育网课 4980.0</t>
         </is>
       </c>
     </row>
@@ -5749,7 +6286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5979,17 +6516,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78189</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>783326.16</v>
       </c>
       <c r="F9" t="n">
-        <v>9.9817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6000,22 +6537,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>37895</v>
+        <v>78189</v>
       </c>
       <c r="E10" t="n">
-        <v>325870.41</v>
+        <v>783326.16</v>
       </c>
       <c r="F10" t="n">
-        <v>11.6289</v>
+        <v>9.9817</v>
       </c>
     </row>
     <row r="11">
@@ -6031,17 +6568,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>216560</v>
+        <v>37895</v>
       </c>
       <c r="E11" t="n">
         <v>325870.41</v>
       </c>
       <c r="F11" t="n">
-        <v>66.4559</v>
+        <v>11.6289</v>
       </c>
     </row>
     <row r="12">
@@ -6057,17 +6594,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11394</v>
+        <v>216560</v>
       </c>
       <c r="E12" t="n">
         <v>325870.41</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4965</v>
+        <v>66.4559</v>
       </c>
     </row>
     <row r="13">
@@ -6083,17 +6620,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>49531</v>
+        <v>11394</v>
       </c>
       <c r="E13" t="n">
         <v>325870.41</v>
       </c>
       <c r="F13" t="n">
-        <v>15.1996</v>
+        <v>3.4965</v>
       </c>
     </row>
     <row r="14">
@@ -6109,17 +6646,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>49531</v>
       </c>
       <c r="E14" t="n">
         <v>325870.41</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>15.1996</v>
       </c>
     </row>
     <row r="15">
@@ -6135,17 +6672,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10290.41</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>325870.41</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -6161,17 +6698,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>10290.41</v>
       </c>
       <c r="E16" t="n">
         <v>325870.41</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>3.1578</v>
       </c>
     </row>
     <row r="17">
@@ -6187,17 +6724,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>325870.41</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -6208,22 +6745,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>67050</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>824725.78</v>
+        <v>325870.41</v>
       </c>
       <c r="F18" t="n">
-        <v>8.130000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -6234,22 +6771,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>466672</v>
+        <v>200</v>
       </c>
       <c r="E19" t="n">
-        <v>824725.78</v>
+        <v>325870.41</v>
       </c>
       <c r="F19" t="n">
-        <v>56.5851</v>
+        <v>0.0614</v>
       </c>
     </row>
     <row r="20">
@@ -6265,17 +6802,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>116578</v>
+        <v>67050</v>
       </c>
       <c r="E20" t="n">
         <v>824725.78</v>
       </c>
       <c r="F20" t="n">
-        <v>14.1354</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -6291,17 +6828,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>163500</v>
+        <v>466672</v>
       </c>
       <c r="E21" t="n">
         <v>824725.78</v>
       </c>
       <c r="F21" t="n">
-        <v>19.8248</v>
+        <v>56.5851</v>
       </c>
     </row>
     <row r="22">
@@ -6317,17 +6854,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>116578</v>
       </c>
       <c r="E22" t="n">
         <v>824725.78</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>14.1354</v>
       </c>
     </row>
     <row r="23">
@@ -6343,17 +6880,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1107.78</v>
+        <v>163500</v>
       </c>
       <c r="E23" t="n">
         <v>824725.78</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1343</v>
+        <v>19.8248</v>
       </c>
     </row>
     <row r="24">
@@ -6369,7 +6906,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -6395,17 +6932,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9818</v>
+        <v>1107.78</v>
       </c>
       <c r="E25" t="n">
         <v>824725.78</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1905</v>
+        <v>0.1343</v>
       </c>
     </row>
     <row r="26">
@@ -6416,22 +6953,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6574</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1446274.36</v>
+        <v>824725.78</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -6442,22 +6979,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>22410</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1446274.36</v>
+        <v>824725.78</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -6468,22 +7005,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>152588</v>
+        <v>9818</v>
       </c>
       <c r="E28" t="n">
-        <v>1446274.36</v>
+        <v>824725.78</v>
       </c>
       <c r="F28" t="n">
-        <v>10.5504</v>
+        <v>1.1905</v>
       </c>
     </row>
     <row r="29">
@@ -6499,17 +7036,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1077980</v>
+        <v>6574</v>
       </c>
       <c r="E29" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F29" t="n">
-        <v>74.535</v>
+        <v>0.4545</v>
       </c>
     </row>
     <row r="30">
@@ -6525,17 +7062,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>99200</v>
+        <v>22410</v>
       </c>
       <c r="E30" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F30" t="n">
-        <v>6.859</v>
+        <v>1.5495</v>
       </c>
     </row>
     <row r="31">
@@ -6551,17 +7088,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19545</v>
+        <v>152588</v>
       </c>
       <c r="E31" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3514</v>
+        <v>10.5504</v>
       </c>
     </row>
     <row r="32">
@@ -6577,17 +7114,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>25200</v>
+        <v>1077980</v>
       </c>
       <c r="E32" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7424</v>
+        <v>74.535</v>
       </c>
     </row>
     <row r="33">
@@ -6603,17 +7140,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>42777.36</v>
+        <v>99200</v>
       </c>
       <c r="E33" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F33" t="n">
-        <v>2.9578</v>
+        <v>6.859</v>
       </c>
     </row>
     <row r="34">
@@ -6624,22 +7161,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>19545</v>
       </c>
       <c r="E34" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.3514</v>
       </c>
     </row>
     <row r="35">
@@ -6650,22 +7187,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>25200</v>
       </c>
       <c r="E35" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.7424</v>
       </c>
     </row>
     <row r="36">
@@ -6676,22 +7213,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16194</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F36" t="n">
-        <v>2.751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -6702,22 +7239,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>85080</v>
+        <v>42777.36</v>
       </c>
       <c r="E37" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F37" t="n">
-        <v>14.4531</v>
+        <v>2.9578</v>
       </c>
     </row>
     <row r="38">
@@ -6733,7 +7270,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -6759,7 +7296,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -6785,17 +7322,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>65190</v>
+        <v>16194</v>
       </c>
       <c r="E40" t="n">
         <v>588664</v>
       </c>
       <c r="F40" t="n">
-        <v>11.0742</v>
+        <v>2.751</v>
       </c>
     </row>
     <row r="41">
@@ -6811,17 +7348,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>422200</v>
+        <v>85080</v>
       </c>
       <c r="E41" t="n">
         <v>588664</v>
       </c>
       <c r="F41" t="n">
-        <v>71.7217</v>
+        <v>14.4531</v>
       </c>
     </row>
     <row r="42">
@@ -6832,22 +7369,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>181525.57</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F42" t="n">
-        <v>4.5737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -6858,22 +7395,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1142004</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F43" t="n">
-        <v>28.7741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -6884,22 +7421,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>355326</v>
+        <v>65190</v>
       </c>
       <c r="E44" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F44" t="n">
-        <v>8.9528</v>
+        <v>11.0742</v>
       </c>
     </row>
     <row r="45">
@@ -6910,22 +7447,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1497534</v>
+        <v>372400</v>
       </c>
       <c r="E45" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F45" t="n">
-        <v>37.7321</v>
+        <v>63.2619</v>
       </c>
     </row>
     <row r="46">
@@ -6936,22 +7473,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>99200</v>
+        <v>49800</v>
       </c>
       <c r="E46" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F46" t="n">
-        <v>2.4995</v>
+        <v>8.4598</v>
       </c>
     </row>
     <row r="47">
@@ -6967,17 +7504,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>49696.78</v>
+        <v>181525.57</v>
       </c>
       <c r="E47" t="n">
         <v>3968860.71</v>
       </c>
       <c r="F47" t="n">
-        <v>1.2522</v>
+        <v>4.5737</v>
       </c>
     </row>
     <row r="48">
@@ -6993,17 +7530,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>90390</v>
+        <v>1142004</v>
       </c>
       <c r="E48" t="n">
         <v>3968860.71</v>
       </c>
       <c r="F48" t="n">
-        <v>2.2775</v>
+        <v>28.7741</v>
       </c>
     </row>
     <row r="49">
@@ -7019,158 +7556,158 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>553184.36</v>
+        <v>355326</v>
       </c>
       <c r="E49" t="n">
         <v>3968860.71</v>
       </c>
       <c r="F49" t="n">
-        <v>13.9381</v>
+        <v>8.9528</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>61592</v>
+        <v>1497534</v>
       </c>
       <c r="E50" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F50" t="n">
-        <v>5.1982</v>
+        <v>37.7321</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8280</v>
+        <v>99200</v>
       </c>
       <c r="E51" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6988</v>
+        <v>2.4995</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>49696.78</v>
       </c>
       <c r="E52" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1.2522</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1112992</v>
+        <v>90390</v>
       </c>
       <c r="E53" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F53" t="n">
-        <v>93.9336</v>
+        <v>2.2775</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>372400</v>
       </c>
       <c r="E54" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>9.382999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7179,13 +7716,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2007</v>
+        <v>180784.36</v>
       </c>
       <c r="E55" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1694</v>
+        <v>4.5551</v>
       </c>
     </row>
     <row r="56">
@@ -7196,7 +7733,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7205,13 +7742,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>139650</v>
+        <v>61592</v>
       </c>
       <c r="E56" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F56" t="n">
-        <v>76.1978</v>
+        <v>5.1982</v>
       </c>
     </row>
     <row r="57">
@@ -7222,7 +7759,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7231,13 +7768,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>21480</v>
+        <v>8280</v>
       </c>
       <c r="E57" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F57" t="n">
-        <v>11.7202</v>
+        <v>0.6988</v>
       </c>
     </row>
     <row r="58">
@@ -7248,7 +7785,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7260,7 +7797,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -7274,7 +7811,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -7283,13 +7820,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>17469</v>
+        <v>1112992</v>
       </c>
       <c r="E59" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F59" t="n">
-        <v>9.531700000000001</v>
+        <v>93.9336</v>
       </c>
     </row>
     <row r="60">
@@ -7300,7 +7837,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7309,13 +7846,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F60" t="n">
-        <v>1.0804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -7326,22 +7863,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2694</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F61" t="n">
-        <v>1.4699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -7352,22 +7889,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>119960</v>
+        <v>2007</v>
       </c>
       <c r="E62" t="n">
-        <v>153032.84</v>
+        <v>1184871</v>
       </c>
       <c r="F62" t="n">
-        <v>78.3884</v>
+        <v>0.1694</v>
       </c>
     </row>
     <row r="63">
@@ -7378,22 +7915,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13200</v>
+        <v>139650</v>
       </c>
       <c r="E63" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F63" t="n">
-        <v>8.6256</v>
+        <v>76.1978</v>
       </c>
     </row>
     <row r="64">
@@ -7404,22 +7941,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>21480</v>
       </c>
       <c r="E64" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>11.7202</v>
       </c>
     </row>
     <row r="65">
@@ -7430,22 +7967,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>18256.84</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F65" t="n">
-        <v>11.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -7456,22 +7993,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>17469</v>
       </c>
       <c r="E66" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>9.531700000000001</v>
       </c>
     </row>
     <row r="67">
@@ -7482,22 +8019,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1616</v>
+        <v>1980</v>
       </c>
       <c r="E67" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F67" t="n">
-        <v>1.056</v>
+        <v>1.0804</v>
       </c>
     </row>
     <row r="68">
@@ -7508,22 +8045,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>483720</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>966916.14</v>
+        <v>183273</v>
       </c>
       <c r="F68" t="n">
-        <v>50.0271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -7534,22 +8071,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>246780</v>
+        <v>2694</v>
       </c>
       <c r="E69" t="n">
-        <v>966916.14</v>
+        <v>183273</v>
       </c>
       <c r="F69" t="n">
-        <v>25.5224</v>
+        <v>1.4699</v>
       </c>
     </row>
     <row r="70">
@@ -7560,22 +8097,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>54600</v>
+        <v>119960</v>
       </c>
       <c r="E70" t="n">
-        <v>966916.14</v>
+        <v>153032.84</v>
       </c>
       <c r="F70" t="n">
-        <v>5.6468</v>
+        <v>78.3884</v>
       </c>
     </row>
     <row r="71">
@@ -7586,22 +8123,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>78122.14</v>
+        <v>13200</v>
       </c>
       <c r="E71" t="n">
-        <v>966916.14</v>
+        <v>153032.84</v>
       </c>
       <c r="F71" t="n">
-        <v>8.079499999999999</v>
+        <v>8.6256</v>
       </c>
     </row>
     <row r="72">
@@ -7612,22 +8149,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3960</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>966916.14</v>
+        <v>153032.84</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -7638,22 +8175,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>99734</v>
+        <v>18256.84</v>
       </c>
       <c r="E73" t="n">
-        <v>966916.14</v>
+        <v>153032.84</v>
       </c>
       <c r="F73" t="n">
-        <v>10.3146</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="74">
@@ -7664,22 +8201,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>421948</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F74" t="n">
-        <v>89.5044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -7690,22 +8227,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>26400</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F75" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -7716,22 +8253,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="E76" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1.056</v>
       </c>
     </row>
     <row r="77">
@@ -7742,22 +8279,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>21080.65</v>
+        <v>483720</v>
       </c>
       <c r="E77" t="n">
-        <v>471427.33</v>
+        <v>966916.14</v>
       </c>
       <c r="F77" t="n">
-        <v>4.4717</v>
+        <v>50.0271</v>
       </c>
     </row>
     <row r="78">
@@ -7768,22 +8305,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>246780</v>
       </c>
       <c r="E78" t="n">
-        <v>471427.33</v>
+        <v>966916.14</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>25.5224</v>
       </c>
     </row>
     <row r="79">
@@ -7794,22 +8331,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1998.68</v>
+        <v>54600</v>
       </c>
       <c r="E79" t="n">
-        <v>471427.33</v>
+        <v>966916.14</v>
       </c>
       <c r="F79" t="n">
-        <v>0.424</v>
+        <v>5.6468</v>
       </c>
     </row>
     <row r="80">
@@ -7820,22 +8357,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>280956</v>
+        <v>78122.14</v>
       </c>
       <c r="E80" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F80" t="n">
-        <v>68.01130000000001</v>
+        <v>8.079499999999999</v>
       </c>
     </row>
     <row r="81">
@@ -7846,22 +8383,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>59200</v>
+        <v>3960</v>
       </c>
       <c r="E81" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F81" t="n">
-        <v>14.3306</v>
+        <v>0.4095</v>
       </c>
     </row>
     <row r="82">
@@ -7872,22 +8409,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>70400</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F82" t="n">
-        <v>17.0418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -7898,22 +8435,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>200</v>
+        <v>99734</v>
       </c>
       <c r="E83" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0484</v>
+        <v>10.3146</v>
       </c>
     </row>
     <row r="84">
@@ -7924,22 +8461,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>421948</v>
       </c>
       <c r="E84" t="n">
-        <v>413102</v>
+        <v>471427.33</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>89.5044</v>
       </c>
     </row>
     <row r="85">
@@ -7950,22 +8487,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2346</v>
+        <v>26400</v>
       </c>
       <c r="E85" t="n">
-        <v>413102</v>
+        <v>471427.33</v>
       </c>
       <c r="F85" t="n">
-        <v>0.5679</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="86">
@@ -7976,22 +8513,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>146542</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F86" t="n">
-        <v>9.9986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -8002,22 +8539,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>33000</v>
+        <v>21080.65</v>
       </c>
       <c r="E87" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F87" t="n">
-        <v>2.2516</v>
+        <v>4.4717</v>
       </c>
     </row>
     <row r="88">
@@ -8028,19 +8565,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -8054,22 +8591,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3736.4</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F89" t="n">
-        <v>0.2549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -8080,22 +8617,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>71715</v>
+        <v>1998.68</v>
       </c>
       <c r="E90" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F90" t="n">
-        <v>4.8931</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="91">
@@ -8106,22 +8643,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1210627</v>
+        <v>280956</v>
       </c>
       <c r="E91" t="n">
-        <v>1465620.4</v>
+        <v>413102</v>
       </c>
       <c r="F91" t="n">
-        <v>82.60169999999999</v>
+        <v>68.01130000000001</v>
       </c>
     </row>
     <row r="92">
@@ -8132,22 +8669,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>330466</v>
+        <v>59200</v>
       </c>
       <c r="E92" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F92" t="n">
-        <v>80.8449</v>
+        <v>14.3306</v>
       </c>
     </row>
     <row r="93">
@@ -8158,22 +8695,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>33420</v>
+        <v>70400</v>
       </c>
       <c r="E93" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F93" t="n">
-        <v>8.175800000000001</v>
+        <v>17.0418</v>
       </c>
     </row>
     <row r="94">
@@ -8184,22 +8721,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E94" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="95">
@@ -8210,22 +8747,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12301.21</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F95" t="n">
-        <v>3.0094</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -8236,19 +8773,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D96" t="n">
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -8262,7 +8799,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8271,13 +8808,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>32578</v>
+        <v>2346</v>
       </c>
       <c r="E97" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F97" t="n">
-        <v>7.9699</v>
+        <v>0.5679</v>
       </c>
     </row>
     <row r="98">
@@ -8288,7 +8825,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8297,13 +8834,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>141738.01</v>
+        <v>146542</v>
       </c>
       <c r="E98" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F98" t="n">
-        <v>20.699</v>
+        <v>9.9986</v>
       </c>
     </row>
     <row r="99">
@@ -8314,7 +8851,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8323,13 +8860,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>109800</v>
+        <v>33000</v>
       </c>
       <c r="E99" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F99" t="n">
-        <v>16.0349</v>
+        <v>2.2516</v>
       </c>
     </row>
     <row r="100">
@@ -8340,7 +8877,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -8352,7 +8889,7 @@
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -8366,7 +8903,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8375,13 +8912,13 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>14327.36</v>
+        <v>3736.4</v>
       </c>
       <c r="E101" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F101" t="n">
-        <v>2.0923</v>
+        <v>0.2549</v>
       </c>
     </row>
     <row r="102">
@@ -8392,7 +8929,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -8401,13 +8938,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>27820</v>
+        <v>71715</v>
       </c>
       <c r="E102" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F102" t="n">
-        <v>4.0627</v>
+        <v>4.8931</v>
       </c>
     </row>
     <row r="103">
@@ -8418,22 +8955,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>391072.5</v>
+        <v>1145200</v>
       </c>
       <c r="E103" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F103" t="n">
-        <v>57.1111</v>
+        <v>78.13760000000001</v>
       </c>
     </row>
     <row r="104">
@@ -8444,22 +8981,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>68574</v>
+        <v>65427</v>
       </c>
       <c r="E104" t="n">
-        <v>80605.8</v>
+        <v>1465620.4</v>
       </c>
       <c r="F104" t="n">
-        <v>85.0733</v>
+        <v>4.4641</v>
       </c>
     </row>
     <row r="105">
@@ -8470,22 +9007,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11640</v>
+        <v>330466</v>
       </c>
       <c r="E105" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F105" t="n">
-        <v>14.4406</v>
+        <v>80.8449</v>
       </c>
     </row>
     <row r="106">
@@ -8496,22 +9033,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>33420</v>
       </c>
       <c r="E106" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>8.175800000000001</v>
       </c>
     </row>
     <row r="107">
@@ -8522,22 +9059,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>124.8</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F107" t="n">
-        <v>0.1548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -8548,22 +9085,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>12301.21</v>
       </c>
       <c r="E108" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>3.0094</v>
       </c>
     </row>
     <row r="109">
@@ -8574,22 +9111,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F109" t="n">
-        <v>0.3312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -8600,22 +9137,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>171462</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>262957</v>
+        <v>408765.21</v>
       </c>
       <c r="F110" t="n">
-        <v>65.20529999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -8626,22 +9163,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>6600</v>
+        <v>32578</v>
       </c>
       <c r="E111" t="n">
-        <v>262957</v>
+        <v>408765.21</v>
       </c>
       <c r="F111" t="n">
-        <v>2.5099</v>
+        <v>7.9699</v>
       </c>
     </row>
     <row r="112">
@@ -8652,22 +9189,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>24800</v>
+        <v>141738.01</v>
       </c>
       <c r="E112" t="n">
-        <v>262957</v>
+        <v>684757.87</v>
       </c>
       <c r="F112" t="n">
-        <v>9.4312</v>
+        <v>20.699</v>
       </c>
     </row>
     <row r="113">
@@ -8678,22 +9215,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>109800</v>
       </c>
       <c r="E113" t="n">
-        <v>262957</v>
+        <v>684757.87</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>16.0349</v>
       </c>
     </row>
     <row r="114">
@@ -8704,19 +9241,19 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>262957</v>
+        <v>684757.87</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -8730,22 +9267,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>60095</v>
+        <v>14327.36</v>
       </c>
       <c r="E115" t="n">
-        <v>262957</v>
+        <v>684757.87</v>
       </c>
       <c r="F115" t="n">
-        <v>22.8535</v>
+        <v>2.0923</v>
       </c>
     </row>
     <row r="116">
@@ -8756,22 +9293,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>20000</v>
+        <v>27820</v>
       </c>
       <c r="E116" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F116" t="n">
-        <v>60.5697</v>
+        <v>4.0627</v>
       </c>
     </row>
     <row r="117">
@@ -8782,22 +9319,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1681</v>
+        <v>337300</v>
       </c>
       <c r="E117" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F117" t="n">
-        <v>5.0909</v>
+        <v>49.2583</v>
       </c>
     </row>
     <row r="118">
@@ -8808,22 +9345,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1000</v>
+        <v>53772.5</v>
       </c>
       <c r="E118" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F118" t="n">
-        <v>3.0285</v>
+        <v>7.8528</v>
       </c>
     </row>
     <row r="119">
@@ -8834,22 +9371,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>907.8</v>
+        <v>68574</v>
       </c>
       <c r="E119" t="n">
-        <v>33019.8</v>
+        <v>80605.8</v>
       </c>
       <c r="F119" t="n">
-        <v>2.7493</v>
+        <v>85.0733</v>
       </c>
     </row>
     <row r="120">
@@ -8860,22 +9397,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>11640</v>
       </c>
       <c r="E120" t="n">
-        <v>33019.8</v>
+        <v>80605.8</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>14.4406</v>
       </c>
     </row>
     <row r="121">
@@ -8886,22 +9423,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>9431</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>33019.8</v>
+        <v>80605.8</v>
       </c>
       <c r="F121" t="n">
-        <v>28.5617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -8912,22 +9449,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2386608.01</v>
+        <v>124.8</v>
       </c>
       <c r="E122" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F122" t="n">
-        <v>37.8325</v>
+        <v>0.1548</v>
       </c>
     </row>
     <row r="123">
@@ -8938,22 +9475,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>571481</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F123" t="n">
-        <v>9.059100000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -8964,22 +9501,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>150800</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F124" t="n">
-        <v>2.3905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -8990,22 +9527,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1279518.2</v>
+        <v>267</v>
       </c>
       <c r="E125" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F125" t="n">
-        <v>20.2829</v>
+        <v>0.3312</v>
       </c>
     </row>
     <row r="126">
@@ -9016,22 +9553,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>105475</v>
+        <v>171462</v>
       </c>
       <c r="E126" t="n">
-        <v>6308348.39</v>
+        <v>262957</v>
       </c>
       <c r="F126" t="n">
-        <v>1.672</v>
+        <v>65.20529999999999</v>
       </c>
     </row>
     <row r="127">
@@ -9042,22 +9579,516 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>家守/千金方/少年说</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E127" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2.5099</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>24800</v>
+      </c>
+      <c r="E128" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F128" t="n">
+        <v>9.4312</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>60095</v>
+      </c>
+      <c r="E132" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F132" t="n">
+        <v>22.8535</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E133" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F133" t="n">
+        <v>60.5697</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>家守/千金方/少年说</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1681</v>
+      </c>
+      <c r="E134" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F134" t="n">
+        <v>5.0909</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E135" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F135" t="n">
+        <v>3.0285</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>907.8</v>
+      </c>
+      <c r="E136" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2.7493</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>9431</v>
+      </c>
+      <c r="E139" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F139" t="n">
+        <v>28.5617</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>2386608.01</v>
+      </c>
+      <c r="E140" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F140" t="n">
+        <v>37.8325</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>家守/千金方/少年说</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>571481</v>
+      </c>
+      <c r="E141" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F141" t="n">
+        <v>9.059100000000001</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>150800</v>
+      </c>
+      <c r="E142" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2.3905</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1279518.2</v>
+      </c>
+      <c r="E143" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F143" t="n">
+        <v>20.2829</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>105475</v>
+      </c>
+      <c r="E144" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.672</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1482500</v>
+      </c>
+      <c r="E145" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F145" t="n">
+        <v>23.5006</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D127" t="n">
-        <v>1814466.18</v>
-      </c>
-      <c r="E127" t="n">
+      <c r="D146" t="n">
+        <v>331966.18</v>
+      </c>
+      <c r="E146" t="n">
         <v>6308348.39</v>
       </c>
-      <c r="F127" t="n">
-        <v>28.7629</v>
+      <c r="F146" t="n">
+        <v>5.2623</v>
       </c>
     </row>
   </sheetData>
@@ -17639,7 +18670,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -17664,7 +18695,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -17689,16 +18720,16 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>动力唤醒方案</t>
+          <t>青少年营地食宿费补差价</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>49800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="346">
@@ -17719,11 +18750,11 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>青少年营地食宿费补差价</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>5200</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="347">
@@ -28239,7 +29270,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -28264,7 +29295,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
@@ -28289,16 +29320,16 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>动力唤醒方案</t>
+          <t>未来之翼7日身心复能营</t>
         </is>
       </c>
       <c r="E769" t="n">
-        <v>49800</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="770">
@@ -28314,16 +29345,16 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>未来之翼7日身心复能营</t>
+          <t>青少年营地食宿费补差价</t>
         </is>
       </c>
       <c r="E770" t="n">
-        <v>19800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="771">
@@ -28344,11 +29375,11 @@
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>心理咨询 - 青英咨询 - 10次</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E771" t="n">
-        <v>8000</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="772">
@@ -28369,11 +29400,11 @@
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>青少年营地食宿费补差价</t>
+          <t>心理咨询 - 青英咨询 - 10次</t>
         </is>
       </c>
       <c r="E772" t="n">
-        <v>5200</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="773">
@@ -28569,7 +29600,7 @@
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>yl5（网课、家长学）青少年家庭同行者计划一周短训营</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E780" t="n">
@@ -28594,7 +29625,7 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>qy（网课、家长学）青少年家庭同行者计划一周短训营</t>
+          <t>青少年19元巨量</t>
         </is>
       </c>
       <c r="E781" t="n">
@@ -28619,7 +29650,7 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>yl5（网课、家长学）青少年家庭同行者计划一周短训营</t>
         </is>
       </c>
       <c r="E782" t="n">
@@ -28644,7 +29675,7 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>青少年19元巨量</t>
+          <t>qy（网课、家长学）青少年家庭同行者计划一周短训营</t>
         </is>
       </c>
       <c r="E783" t="n">
@@ -28719,7 +29750,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>青少年同行者一周家长短训营亲子教育网课</t>
+          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
         </is>
       </c>
       <c r="E786" t="n">
@@ -28744,7 +29775,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>青少年同行者计划：试听课</t>
+          <t>青少年adq新链接XY</t>
         </is>
       </c>
       <c r="E787" t="n">
@@ -28769,7 +29800,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
+          <t>青少年同行者一周家长短训营亲子教育网课</t>
         </is>
       </c>
       <c r="E788" t="n">
@@ -28819,7 +29850,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>青少年adq新链接XY</t>
+          <t>青少年同行者计划：试听课</t>
         </is>
       </c>
       <c r="E790" t="n">
@@ -28894,7 +29925,7 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>21天蛋壳跳动休学复能营</t>
         </is>
       </c>
       <c r="E793" t="n">
@@ -28919,7 +29950,7 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>0元青少年-LH</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E794" t="n">
@@ -28944,7 +29975,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E795" t="n">
@@ -28969,7 +30000,7 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>杭州一日一生体验课</t>
         </is>
       </c>
       <c r="E796" t="n">
@@ -28994,7 +30025,7 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>义诊-线上</t>
         </is>
       </c>
       <c r="E797" t="n">
@@ -29019,7 +30050,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>21天蛋壳跳动休学复能营</t>
+          <t>0元青少年-LH</t>
         </is>
       </c>
       <c r="E798" t="n">
@@ -29044,7 +30075,7 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>义诊-线上</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E799" t="n">
@@ -29069,7 +30100,7 @@
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>杭州一日一生体验课</t>
+          <t>青少年同行者智慧父母启航营</t>
         </is>
       </c>
       <c r="E800" t="n">
@@ -29094,7 +30125,7 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>青少年同行者智慧父母启航营</t>
+          <t>观心少年2天1夜心理赋能营-ys-北京</t>
         </is>
       </c>
       <c r="E801" t="n">
@@ -31464,7 +32495,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -31489,7 +32520,7 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -31514,16 +32545,16 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>动力唤醒方案</t>
+          <t>未来之翼7日心理能量唤醒营</t>
         </is>
       </c>
       <c r="E898" t="n">
-        <v>49800</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="899">
@@ -31539,16 +32570,16 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>未来之翼7日心理能量唤醒营</t>
+          <t>青少年营地食宿费补差价</t>
         </is>
       </c>
       <c r="E899" t="n">
-        <v>19800</v>
+        <v>100</v>
       </c>
     </row>
     <row r="900">
@@ -31569,11 +32600,11 @@
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>门店《一日一生》</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E900" t="n">
-        <v>1592</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="901">
@@ -31594,11 +32625,11 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>ACT个案概念化工作坊</t>
+          <t>门店《一日一生》</t>
         </is>
       </c>
       <c r="E901" t="n">
-        <v>1500</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="902">
@@ -31619,11 +32650,11 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>解郁丸[4g*9袋]</t>
+          <t>ACT个案概念化工作坊</t>
         </is>
       </c>
       <c r="E902" t="n">
-        <v>333.5</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="903">
@@ -31644,11 +32675,11 @@
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
+          <t>解郁丸[4g*9袋]</t>
         </is>
       </c>
       <c r="E903" t="n">
-        <v>114</v>
+        <v>333.5</v>
       </c>
     </row>
     <row r="904">
@@ -31669,11 +32700,11 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>青少年营地食宿费补差价</t>
+          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
         </is>
       </c>
       <c r="E904" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="905">
@@ -31844,7 +32875,7 @@
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>青少年同行者计划周训营（网课）WY</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E911" t="n">
@@ -31869,7 +32900,7 @@
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>青少年同行者计划周训营（网课）WY</t>
         </is>
       </c>
       <c r="E912" t="n">
@@ -31894,7 +32925,7 @@
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题yh</t>
+          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
         </is>
       </c>
       <c r="E913" t="n">
@@ -31919,7 +32950,7 @@
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>青少年同行者计划：试听课</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题yh</t>
         </is>
       </c>
       <c r="E914" t="n">
@@ -31944,7 +32975,7 @@
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
+          <t>青少年同行者计划：试听课</t>
         </is>
       </c>
       <c r="E915" t="n">
@@ -32019,7 +33050,7 @@
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>杭州一日一生体验课</t>
         </is>
       </c>
       <c r="E918" t="n">
@@ -32044,7 +33075,7 @@
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>21天蛋壳跳动休学复能营</t>
         </is>
       </c>
       <c r="E919" t="n">
@@ -32069,7 +33100,7 @@
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>杭州一日一生体验课</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E920" t="n">
@@ -32094,7 +33125,7 @@
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E921" t="n">
@@ -32119,7 +33150,7 @@
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>21天蛋壳跳动休学复能营</t>
+          <t>青少年同行者计划</t>
         </is>
       </c>
       <c r="E922" t="n">
@@ -32144,7 +33175,7 @@
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>观心少年2天1夜心理赋能营-ys-北京</t>
         </is>
       </c>
       <c r="E923" t="n">
@@ -32169,7 +33200,7 @@
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>青少年同行者计划</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E924" t="n">
@@ -33489,16 +34520,16 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>青少年同行者计划之领航营亲子教育网课</t>
+          <t>未来之翼7日身心复能营</t>
         </is>
       </c>
       <c r="E977" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
     </row>
     <row r="978">
@@ -33514,16 +34545,16 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>心理咨询师职业能力水平评价考试培训</t>
+          <t>青少年【未来之翼】身心节律复能7日营</t>
         </is>
       </c>
       <c r="E978" t="n">
-        <v>3800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="979">
@@ -33544,11 +34575,11 @@
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>考务服务费（心理咨询专业技能培训）</t>
+          <t>青少年同行者计划之领航营亲子教育网课</t>
         </is>
       </c>
       <c r="E979" t="n">
-        <v>540</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="980">
@@ -33569,11 +34600,11 @@
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>（网课、家长学）青少年家庭同行者计划一周短训营LH</t>
+          <t>心理咨询师职业能力水平评价考试培训</t>
         </is>
       </c>
       <c r="E980" t="n">
-        <v>35</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="981">
@@ -33594,11 +34625,11 @@
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>青少年同行者计划周训营（网课）WY</t>
+          <t>考务服务费（心理咨询专业技能培训）</t>
         </is>
       </c>
       <c r="E981" t="n">
-        <v>19</v>
+        <v>540</v>
       </c>
     </row>
     <row r="982">
@@ -33619,11 +34650,11 @@
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
+          <t>（网课、家长学）青少年家庭同行者计划一周短训营LH</t>
         </is>
       </c>
       <c r="E982" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="983">
@@ -33669,7 +34700,7 @@
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
         </is>
       </c>
       <c r="E984" t="n">
@@ -33694,11 +34725,11 @@
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E985" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="986">
@@ -33719,11 +34750,11 @@
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>杭州一日一生体验课</t>
+          <t>青少年同行者计划周训营（网课）WY</t>
         </is>
       </c>
       <c r="E986" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="987">
@@ -33744,7 +34775,7 @@
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>未来之翼7日身心复能营</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E987" t="n">
@@ -33794,7 +34825,7 @@
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>杭州一日一生体验课</t>
         </is>
       </c>
       <c r="E989" t="n">
@@ -33819,7 +34850,7 @@
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>青少年【未来之翼】身心节律复能7日营</t>
+          <t>观心少年2天1夜心理赋能营-ys-北京</t>
         </is>
       </c>
       <c r="E990" t="n">
@@ -33844,7 +34875,7 @@
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E991" t="n">
@@ -33869,7 +34900,7 @@
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E992" t="n">
